--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
@@ -1517,7 +1517,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3579,7 +3579,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6011,7 +6011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6171,22 +6171,484 @@
       <c r="AF2" s="10" t="n"/>
       <c r="AG2" s="11" t="n"/>
     </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>2026/05/27</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="11" t="n"/>
+      <c r="R3" s="19" t="inlineStr">
+        <is>
+          <t>画面設計書 v1.1 反映：読者情報変更適用日（joho_henko_tekiyo_date）を入力項目として追加。項目仕様の整合修正</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="11" t="n"/>
+      <c r="AB3" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>画面設計書 v1.1 追加反映：①郵送区分（yubin_kubun）を販売店連動の自動表示から `m_code.code_category='YUBIN_KUBUN'` プルダウン入力項目へ変更（commit e4a3721）、②引落口座支店をテキスト1項目から `bank_shiten_id`（`m_shiten.shiten_id` を `kinyu_shiten_flg=TRUE` で絞り込み）+ 自動表示ラベル（`jastem_toriatsukai_tenpo_code` / `jastem_tenpo_name`）の3項目構成へ分割（commit cdc7ae6）、③機能定義の API パスを `/api/subscribers` から `/api/dokusya` へ統一（commit b2bbe9f）、④画面設計書のマークダウン表構造正規化への追従（commit a3b3204）。</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="11" t="n"/>
+      <c r="AB4" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="11" t="n"/>
+    </row>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n"/>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="11" t="n"/>
+      <c r="R5" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-06 反映：更新時の履歴 zenkai_* 退避ルールを変更。`haitatsu_same_flg=TRUE` のときは住所が変更されていなくても購読者住所（todofuken_code / shikuchoson / chome_banchi / tatemono_mei + yubin_no）を常に zenkai_* に格納する。増減報告フラグ（zougen_hokoku_flg）は zenkai_* 退避有無とは独立に、実際の変更（購読部数 / 販売店 / 住所）でのみ判定するよう明確化。</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="10" t="n"/>
+      <c r="V5" s="11" t="n"/>
+      <c r="W5" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X5" s="10" t="n"/>
+      <c r="Y5" s="10" t="n"/>
+      <c r="Z5" s="10" t="n"/>
+      <c r="AA5" s="11" t="n"/>
+      <c r="AB5" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC5" s="10" t="n"/>
+      <c r="AD5" s="10" t="n"/>
+      <c r="AE5" s="10" t="n"/>
+      <c r="AF5" s="10" t="n"/>
+      <c r="AG5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="11" t="n"/>
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07：更新(API-011-003)に情報変更モード `change_mode`（'today'当日変更 / 'reserved'予約変更）を追加。当日変更は適用日を本日固定＋紙版の帳票影響項目変更を VALIDATION_ERROR で拒否（電子版は制限なし）。予約変更は適用日必須・未来日のみ・全項目可。</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="n"/>
+      <c r="V6" s="11" t="n"/>
+      <c r="W6" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X6" s="10" t="n"/>
+      <c r="Y6" s="10" t="n"/>
+      <c r="Z6" s="10" t="n"/>
+      <c r="AA6" s="11" t="n"/>
+      <c r="AB6" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC6" s="10" t="n"/>
+      <c r="AD6" s="10" t="n"/>
+      <c r="AE6" s="10" t="n"/>
+      <c r="AF6" s="10" t="n"/>
+      <c r="AG6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="11" t="n"/>
+      <c r="R7" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07 改訂：購読停止（解約予約）を更新(API-011-003)から分離し、専用エンドポイント `POST /api/v1/dokusya/{dokusya_id}/stop`（ACSMS-API-014-004・購読停止）へ移設。更新APIは `dokusya_chushi_date` を受け付けず、body に含まれると `VALIDATION_ERROR`（@IsEmpty）で 400。当日変更モードの帳票影響項目一覧から `dokusya_chushi_date` を除外。更新画面では購読中止日は読取専用。</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="11" t="n"/>
+      <c r="W7" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="11" t="n"/>
+      <c r="AB7" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC7" s="10" t="n"/>
+      <c r="AD7" s="10" t="n"/>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="10" t="n"/>
+      <c r="AG7" s="11" t="n"/>
+    </row>
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="11" t="n"/>
+      <c r="R8" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件：併読（dokusya_shubetsu=3・紙版＋電子版）は新規登録(API-011-002)不可を明記＋BEガード追加。併読データは電子版読者管理システムがバッチ連携で管理するため、作成は `VALIDATION_ERROR`、編集/停止/削除は `DOKUSYA_READ_ONLY`(403)、Excel取込は取込不可で統一。</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="11" t="n"/>
+      <c r="W8" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X8" s="10" t="n"/>
+      <c r="Y8" s="10" t="n"/>
+      <c r="Z8" s="10" t="n"/>
+      <c r="AA8" s="11" t="n"/>
+      <c r="AB8" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC8" s="10" t="n"/>
+      <c r="AD8" s="10" t="n"/>
+      <c r="AE8" s="10" t="n"/>
+      <c r="AF8" s="10" t="n"/>
+      <c r="AG8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="11" t="n"/>
+      <c r="R9" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07 改訂：更新(API-011-003)で **電子版（dokusya_shubetsu=2）は当日変更のみ**とし、`change_mode='reserved'`（予約変更）を `VALIDATION_ERROR`(field=`change_mode`)で拒否（再購読は例外）。紙版のみ当日変更／予約変更の2モードを保持。FEは電子版で編集画面のモードバーを非表示にし当日変更固定で開く。</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="11" t="n"/>
+      <c r="W9" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="10" t="n"/>
+      <c r="Z9" s="10" t="n"/>
+      <c r="AA9" s="11" t="n"/>
+      <c r="AB9" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC9" s="10" t="n"/>
+      <c r="AD9" s="10" t="n"/>
+      <c r="AE9" s="10" t="n"/>
+      <c r="AF9" s="10" t="n"/>
+      <c r="AG9" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="H1:J1"/>
+  <mergeCells count="63">
     <mergeCell ref="R1:V1"/>
-    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="W1:AA1"/>
-    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="AB9:AG9"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="W5:AA5"/>
+    <mergeCell ref="R4:V4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="R7:V7"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="W4:AA4"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="W3:AA3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="AB8:AG8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="AB7:AG7"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="AB6:AG6"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="W9:AA9"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="AB5:AG5"/>
+    <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K8:Q8"/>
+    <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="R9:V9"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6359,7 +6821,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6669,7 +7131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6830,7 +7292,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7470,8 +7932,61 @@
       <c r="AJ15" s="10" t="n"/>
       <c r="AK15" s="11" t="n"/>
     </row>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>画面固有</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>SHUBETSU_PERMISSION_DENIED</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n"/>
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="10" t="n"/>
+      <c r="O16" s="10" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n"/>
+      <c r="R16" s="10" t="n"/>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="n"/>
+      <c r="U16" s="11" t="n"/>
+      <c r="V16" s="19" t="inlineStr">
+        <is>
+          <t>紙版購読者の登録・編集を行う権限がありません。／電子版購読者の登録・編集・承認を行う権限がありません。</t>
+        </is>
+      </c>
+      <c r="W16" s="10" t="n"/>
+      <c r="X16" s="10" t="n"/>
+      <c r="Y16" s="10" t="n"/>
+      <c r="Z16" s="10" t="n"/>
+      <c r="AA16" s="10" t="n"/>
+      <c r="AB16" s="10" t="n"/>
+      <c r="AC16" s="10" t="n"/>
+      <c r="AD16" s="10" t="n"/>
+      <c r="AE16" s="10" t="n"/>
+      <c r="AF16" s="10" t="n"/>
+      <c r="AG16" s="10" t="n"/>
+      <c r="AH16" s="10" t="n"/>
+      <c r="AI16" s="10" t="n"/>
+      <c r="AJ16" s="10" t="n"/>
+      <c r="AK16" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="62">
     <mergeCell ref="V11:AK11"/>
     <mergeCell ref="J15:U15"/>
     <mergeCell ref="A15:B15"/>
@@ -7481,12 +7996,15 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="V16:AK16"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="V7:AK7"/>
     <mergeCell ref="J11:U11"/>
     <mergeCell ref="C13:I13"/>
     <mergeCell ref="J7:U7"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="J16:U16"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="V12:AK12"/>
@@ -7507,6 +8025,7 @@
     <mergeCell ref="V13:AK13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C16:I16"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="J8:U8"/>
     <mergeCell ref="A8:B8"/>
@@ -7702,7 +8221,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8228,7 +8747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK135"/>
+  <dimension ref="A1:AK139"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -8389,7 +8908,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -11590,7 +12109,7 @@
       <c r="AJ68" s="10" t="n"/>
       <c r="AK68" s="11" t="n"/>
     </row>
-    <row r="69" ht="36" customHeight="1">
+    <row r="69" ht="54" customHeight="1">
       <c r="B69" s="31" t="n">
         <v>42</v>
       </c>
@@ -11641,7 +12160,7 @@
       <c r="AE69" s="11" t="n"/>
       <c r="AF69" s="19" t="inlineStr">
         <is>
-          <t>郵送区分 ※m_code.code_category='YUBIN_KUBUN'を参照（0:空, 1:郵送）</t>
+          <t>郵送区分 ※m_code.code_category='YUBIN_KUBUN'を参照（0:空, 1:郵送）。デフォルト: '0'</t>
         </is>
       </c>
       <c r="AG69" s="10" t="n"/>
@@ -11770,14 +12289,14 @@
       <c r="AJ71" s="10" t="n"/>
       <c r="AK71" s="11" t="n"/>
     </row>
-    <row r="72" ht="18" customHeight="1">
+    <row r="72" ht="72" customHeight="1">
       <c r="B72" s="31" t="n">
         <v>45</v>
       </c>
       <c r="C72" s="38" t="n"/>
       <c r="D72" s="19" t="inlineStr">
         <is>
-          <t>bank_branch_code</t>
+          <t>bank_shiten_id</t>
         </is>
       </c>
       <c r="E72" s="10" t="n"/>
@@ -11790,7 +12309,7 @@
       <c r="L72" s="11" t="n"/>
       <c r="M72" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N72" s="10" t="n"/>
@@ -11810,7 +12329,7 @@
       <c r="X72" s="11" t="n"/>
       <c r="Y72" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z72" s="10" t="n"/>
@@ -11821,7 +12340,7 @@
       <c r="AE72" s="11" t="n"/>
       <c r="AF72" s="19" t="inlineStr">
         <is>
-          <t>引落口座支店コード</t>
+          <t>引落口座支店ID（m_shiten.shiten_id を `kinyu_shiten_flg=TRUE` で絞り込んだ値。プルダウン再ハイドレーション用）。口座引落以外の場合は null</t>
         </is>
       </c>
       <c r="AG72" s="10" t="n"/>
@@ -11830,14 +12349,14 @@
       <c r="AJ72" s="10" t="n"/>
       <c r="AK72" s="11" t="n"/>
     </row>
-    <row r="73" ht="18" customHeight="1">
+    <row r="73" ht="36" customHeight="1">
       <c r="B73" s="31" t="n">
         <v>46</v>
       </c>
       <c r="C73" s="38" t="n"/>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t>bank_branch_name</t>
+          <t>jastem_toriatsukai_tenpo_code</t>
         </is>
       </c>
       <c r="E73" s="10" t="n"/>
@@ -11868,11 +12387,7 @@
       <c r="V73" s="10" t="n"/>
       <c r="W73" s="10" t="n"/>
       <c r="X73" s="11" t="n"/>
-      <c r="Y73" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y73" s="17" t="inlineStr"/>
       <c r="Z73" s="10" t="n"/>
       <c r="AA73" s="10" t="n"/>
       <c r="AB73" s="10" t="n"/>
@@ -11881,7 +12396,7 @@
       <c r="AE73" s="11" t="n"/>
       <c r="AF73" s="19" t="inlineStr">
         <is>
-          <t>引落口座支店名</t>
+          <t>引落元口座店舗コード（m_shiten結合取得、bank_shiten_id 選択後の自動表示用ラベル、空文字許容）</t>
         </is>
       </c>
       <c r="AG73" s="10" t="n"/>
@@ -11890,14 +12405,14 @@
       <c r="AJ73" s="10" t="n"/>
       <c r="AK73" s="11" t="n"/>
     </row>
-    <row r="74" ht="54" customHeight="1">
+    <row r="74" ht="36" customHeight="1">
       <c r="B74" s="31" t="n">
         <v>47</v>
       </c>
       <c r="C74" s="38" t="n"/>
       <c r="D74" s="19" t="inlineStr">
         <is>
-          <t>hikiotoshi_yokin_shubetsu</t>
+          <t>jastem_tenpo_name</t>
         </is>
       </c>
       <c r="E74" s="10" t="n"/>
@@ -11910,7 +12425,7 @@
       <c r="L74" s="11" t="n"/>
       <c r="M74" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N74" s="10" t="n"/>
@@ -11928,11 +12443,7 @@
       <c r="V74" s="10" t="n"/>
       <c r="W74" s="10" t="n"/>
       <c r="X74" s="11" t="n"/>
-      <c r="Y74" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="Y74" s="17" t="inlineStr"/>
       <c r="Z74" s="10" t="n"/>
       <c r="AA74" s="10" t="n"/>
       <c r="AB74" s="10" t="n"/>
@@ -11941,7 +12452,7 @@
       <c r="AE74" s="11" t="n"/>
       <c r="AF74" s="19" t="inlineStr">
         <is>
-          <t>引落口座貯金種目 ※m_code.code_category='YOKIN_SHUBETSU'を参照（1:普通, 2:当座）</t>
+          <t>引落元口座店舗名（m_shiten結合取得、bank_shiten_id 選択後の自動表示用ラベル、空文字許容）</t>
         </is>
       </c>
       <c r="AG74" s="10" t="n"/>
@@ -11950,14 +12461,14 @@
       <c r="AJ74" s="10" t="n"/>
       <c r="AK74" s="11" t="n"/>
     </row>
-    <row r="75" ht="18" customHeight="1">
+    <row r="75" ht="72" customHeight="1">
       <c r="B75" s="31" t="n">
         <v>48</v>
       </c>
       <c r="C75" s="38" t="n"/>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t>hikiotoshi_koza_no</t>
+          <t>bank_branch_code</t>
         </is>
       </c>
       <c r="E75" s="10" t="n"/>
@@ -11988,7 +12499,11 @@
       <c r="V75" s="10" t="n"/>
       <c r="W75" s="10" t="n"/>
       <c r="X75" s="11" t="n"/>
-      <c r="Y75" s="17" t="inlineStr"/>
+      <c r="Y75" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z75" s="10" t="n"/>
       <c r="AA75" s="10" t="n"/>
       <c r="AB75" s="10" t="n"/>
@@ -11997,7 +12512,7 @@
       <c r="AE75" s="11" t="n"/>
       <c r="AF75" s="19" t="inlineStr">
         <is>
-          <t>引落口座番号（空文字許容）</t>
+          <t>引落口座支店コード（t_dokusya 永続列。bank_shiten_id 選択時に m_shiten.jastem_toriatsukai_tenpo_code から非正規化保存）</t>
         </is>
       </c>
       <c r="AG75" s="10" t="n"/>
@@ -12006,14 +12521,14 @@
       <c r="AJ75" s="10" t="n"/>
       <c r="AK75" s="11" t="n"/>
     </row>
-    <row r="76" ht="18" customHeight="1">
+    <row r="76" ht="54" customHeight="1">
       <c r="B76" s="31" t="n">
         <v>49</v>
       </c>
       <c r="C76" s="38" t="n"/>
       <c r="D76" s="19" t="inlineStr">
         <is>
-          <t>hikiotoshi_koza_meigi</t>
+          <t>bank_branch_name</t>
         </is>
       </c>
       <c r="E76" s="10" t="n"/>
@@ -12044,7 +12559,11 @@
       <c r="V76" s="10" t="n"/>
       <c r="W76" s="10" t="n"/>
       <c r="X76" s="11" t="n"/>
-      <c r="Y76" s="17" t="inlineStr"/>
+      <c r="Y76" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z76" s="10" t="n"/>
       <c r="AA76" s="10" t="n"/>
       <c r="AB76" s="10" t="n"/>
@@ -12053,7 +12572,7 @@
       <c r="AE76" s="11" t="n"/>
       <c r="AF76" s="19" t="inlineStr">
         <is>
-          <t>引落口座名義（空文字許容）</t>
+          <t>引落口座支店名（t_dokusya 永続列。bank_shiten_id 選択時に m_shiten.jastem_tenpo_name から非正規化保存）</t>
         </is>
       </c>
       <c r="AG76" s="10" t="n"/>
@@ -12062,14 +12581,14 @@
       <c r="AJ76" s="10" t="n"/>
       <c r="AK76" s="11" t="n"/>
     </row>
-    <row r="77" ht="18" customHeight="1">
+    <row r="77" ht="54" customHeight="1">
       <c r="B77" s="31" t="n">
         <v>50</v>
       </c>
       <c r="C77" s="38" t="n"/>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t>dokusyaso_bunrui</t>
+          <t>hikiotoshi_yokin_shubetsu</t>
         </is>
       </c>
       <c r="E77" s="10" t="n"/>
@@ -12082,7 +12601,7 @@
       <c r="L77" s="11" t="n"/>
       <c r="M77" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N77" s="10" t="n"/>
@@ -12100,7 +12619,11 @@
       <c r="V77" s="10" t="n"/>
       <c r="W77" s="10" t="n"/>
       <c r="X77" s="11" t="n"/>
-      <c r="Y77" s="17" t="inlineStr"/>
+      <c r="Y77" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="Z77" s="10" t="n"/>
       <c r="AA77" s="10" t="n"/>
       <c r="AB77" s="10" t="n"/>
@@ -12109,7 +12632,7 @@
       <c r="AE77" s="11" t="n"/>
       <c r="AF77" s="19" t="inlineStr">
         <is>
-          <t>購読者層分類（カンマ区切り、空文字許容）</t>
+          <t>引落口座貯金種目 ※m_code.code_category='YOKIN_SHUBETSU'を参照（1:普通, 2:当座）</t>
         </is>
       </c>
       <c r="AG77" s="10" t="n"/>
@@ -12125,7 +12648,7 @@
       <c r="C78" s="38" t="n"/>
       <c r="D78" s="19" t="inlineStr">
         <is>
-          <t>nogyosya_bunrui</t>
+          <t>hikiotoshi_koza_no</t>
         </is>
       </c>
       <c r="E78" s="10" t="n"/>
@@ -12165,7 +12688,7 @@
       <c r="AE78" s="11" t="n"/>
       <c r="AF78" s="19" t="inlineStr">
         <is>
-          <t>農業者分類（カンマ区切り、空文字許容）</t>
+          <t>引落口座番号（空文字許容）</t>
         </is>
       </c>
       <c r="AG78" s="10" t="n"/>
@@ -12181,7 +12704,7 @@
       <c r="C79" s="38" t="n"/>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t>shoki_dokusya_kaishi_date</t>
+          <t>hikiotoshi_koza_meigi</t>
         </is>
       </c>
       <c r="E79" s="10" t="n"/>
@@ -12207,20 +12730,12 @@
       </c>
       <c r="R79" s="10" t="n"/>
       <c r="S79" s="11" t="n"/>
-      <c r="T79" s="17" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+      <c r="T79" s="17" t="inlineStr"/>
       <c r="U79" s="10" t="n"/>
       <c r="V79" s="10" t="n"/>
       <c r="W79" s="10" t="n"/>
       <c r="X79" s="11" t="n"/>
-      <c r="Y79" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y79" s="17" t="inlineStr"/>
       <c r="Z79" s="10" t="n"/>
       <c r="AA79" s="10" t="n"/>
       <c r="AB79" s="10" t="n"/>
@@ -12229,7 +12744,7 @@
       <c r="AE79" s="11" t="n"/>
       <c r="AF79" s="19" t="inlineStr">
         <is>
-          <t>初回購読開始日</t>
+          <t>引落口座名義（空文字許容）</t>
         </is>
       </c>
       <c r="AG79" s="10" t="n"/>
@@ -12245,7 +12760,7 @@
       <c r="C80" s="38" t="n"/>
       <c r="D80" s="19" t="inlineStr">
         <is>
-          <t>dokusya_kaishi_date</t>
+          <t>dokusyaso_bunrui</t>
         </is>
       </c>
       <c r="E80" s="10" t="n"/>
@@ -12271,20 +12786,12 @@
       </c>
       <c r="R80" s="10" t="n"/>
       <c r="S80" s="11" t="n"/>
-      <c r="T80" s="17" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+      <c r="T80" s="17" t="inlineStr"/>
       <c r="U80" s="10" t="n"/>
       <c r="V80" s="10" t="n"/>
       <c r="W80" s="10" t="n"/>
       <c r="X80" s="11" t="n"/>
-      <c r="Y80" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y80" s="17" t="inlineStr"/>
       <c r="Z80" s="10" t="n"/>
       <c r="AA80" s="10" t="n"/>
       <c r="AB80" s="10" t="n"/>
@@ -12293,7 +12800,7 @@
       <c r="AE80" s="11" t="n"/>
       <c r="AF80" s="19" t="inlineStr">
         <is>
-          <t>購読開始日</t>
+          <t>購読者層分類（カンマ区切り、空文字許容）</t>
         </is>
       </c>
       <c r="AG80" s="10" t="n"/>
@@ -12309,7 +12816,7 @@
       <c r="C81" s="38" t="n"/>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date</t>
+          <t>nogyosya_bunrui</t>
         </is>
       </c>
       <c r="E81" s="10" t="n"/>
@@ -12335,20 +12842,12 @@
       </c>
       <c r="R81" s="10" t="n"/>
       <c r="S81" s="11" t="n"/>
-      <c r="T81" s="17" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+      <c r="T81" s="17" t="inlineStr"/>
       <c r="U81" s="10" t="n"/>
       <c r="V81" s="10" t="n"/>
       <c r="W81" s="10" t="n"/>
       <c r="X81" s="11" t="n"/>
-      <c r="Y81" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="Y81" s="17" t="inlineStr"/>
       <c r="Z81" s="10" t="n"/>
       <c r="AA81" s="10" t="n"/>
       <c r="AB81" s="10" t="n"/>
@@ -12357,7 +12856,7 @@
       <c r="AE81" s="11" t="n"/>
       <c r="AF81" s="19" t="inlineStr">
         <is>
-          <t>購読中止日</t>
+          <t>農業者分類（カンマ区切り、空文字許容）</t>
         </is>
       </c>
       <c r="AG81" s="10" t="n"/>
@@ -12373,7 +12872,7 @@
       <c r="C82" s="38" t="n"/>
       <c r="D82" s="19" t="inlineStr">
         <is>
-          <t>joho_henko_tekiyo_date</t>
+          <t>shoki_dokusya_kaishi_date</t>
         </is>
       </c>
       <c r="E82" s="10" t="n"/>
@@ -12410,7 +12909,7 @@
       <c r="X82" s="11" t="n"/>
       <c r="Y82" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z82" s="10" t="n"/>
@@ -12421,7 +12920,7 @@
       <c r="AE82" s="11" t="n"/>
       <c r="AF82" s="19" t="inlineStr">
         <is>
-          <t>読者情報変更適用日</t>
+          <t>初回購読開始日</t>
         </is>
       </c>
       <c r="AG82" s="10" t="n"/>
@@ -12437,7 +12936,7 @@
       <c r="C83" s="38" t="n"/>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t>seikyu_kaishi_month</t>
+          <t>dokusya_kaishi_date</t>
         </is>
       </c>
       <c r="E83" s="10" t="n"/>
@@ -12465,14 +12964,18 @@
       <c r="S83" s="11" t="n"/>
       <c r="T83" s="17" t="inlineStr">
         <is>
-          <t>YYYYMM</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="U83" s="10" t="n"/>
       <c r="V83" s="10" t="n"/>
       <c r="W83" s="10" t="n"/>
       <c r="X83" s="11" t="n"/>
-      <c r="Y83" s="17" t="inlineStr"/>
+      <c r="Y83" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z83" s="10" t="n"/>
       <c r="AA83" s="10" t="n"/>
       <c r="AB83" s="10" t="n"/>
@@ -12481,7 +12984,7 @@
       <c r="AE83" s="11" t="n"/>
       <c r="AF83" s="19" t="inlineStr">
         <is>
-          <t>請求開始月（空文字許容）</t>
+          <t>購読開始日</t>
         </is>
       </c>
       <c r="AG83" s="10" t="n"/>
@@ -12497,7 +13000,7 @@
       <c r="C84" s="38" t="n"/>
       <c r="D84" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>dokusya_chushi_date</t>
         </is>
       </c>
       <c r="E84" s="10" t="n"/>
@@ -12523,12 +13026,20 @@
       </c>
       <c r="R84" s="10" t="n"/>
       <c r="S84" s="11" t="n"/>
-      <c r="T84" s="17" t="inlineStr"/>
+      <c r="T84" s="17" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="U84" s="10" t="n"/>
       <c r="V84" s="10" t="n"/>
       <c r="W84" s="10" t="n"/>
       <c r="X84" s="11" t="n"/>
-      <c r="Y84" s="17" t="inlineStr"/>
+      <c r="Y84" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="Z84" s="10" t="n"/>
       <c r="AA84" s="10" t="n"/>
       <c r="AB84" s="10" t="n"/>
@@ -12537,7 +13048,7 @@
       <c r="AE84" s="11" t="n"/>
       <c r="AF84" s="19" t="inlineStr">
         <is>
-          <t>備考（空文字許容）</t>
+          <t>購読中止日</t>
         </is>
       </c>
       <c r="AG84" s="10" t="n"/>
@@ -12553,7 +13064,7 @@
       <c r="C85" s="38" t="n"/>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t>rireki_no</t>
+          <t>joho_henko_tekiyo_date</t>
         </is>
       </c>
       <c r="E85" s="10" t="n"/>
@@ -12566,7 +13077,7 @@
       <c r="L85" s="11" t="n"/>
       <c r="M85" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N85" s="10" t="n"/>
@@ -12579,14 +13090,18 @@
       </c>
       <c r="R85" s="10" t="n"/>
       <c r="S85" s="11" t="n"/>
-      <c r="T85" s="17" t="inlineStr"/>
+      <c r="T85" s="17" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="U85" s="10" t="n"/>
       <c r="V85" s="10" t="n"/>
       <c r="W85" s="10" t="n"/>
       <c r="X85" s="11" t="n"/>
       <c r="Y85" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z85" s="10" t="n"/>
@@ -12597,7 +13112,7 @@
       <c r="AE85" s="11" t="n"/>
       <c r="AF85" s="19" t="inlineStr">
         <is>
-          <t>履歴No（最新の履歴番号）</t>
+          <t>読者情報変更適用日</t>
         </is>
       </c>
       <c r="AG85" s="10" t="n"/>
@@ -12606,14 +13121,14 @@
       <c r="AJ85" s="10" t="n"/>
       <c r="AK85" s="11" t="n"/>
     </row>
-    <row r="86" ht="36" customHeight="1">
+    <row r="86" ht="18" customHeight="1">
       <c r="B86" s="31" t="n">
         <v>59</v>
       </c>
       <c r="C86" s="38" t="n"/>
       <c r="D86" s="19" t="inlineStr">
         <is>
-          <t>denshi_shonin_status</t>
+          <t>seikyu_kaishi_month</t>
         </is>
       </c>
       <c r="E86" s="10" t="n"/>
@@ -12626,7 +13141,7 @@
       <c r="L86" s="11" t="n"/>
       <c r="M86" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N86" s="10" t="n"/>
@@ -12639,16 +13154,16 @@
       </c>
       <c r="R86" s="10" t="n"/>
       <c r="S86" s="11" t="n"/>
-      <c r="T86" s="17" t="inlineStr"/>
+      <c r="T86" s="17" t="inlineStr">
+        <is>
+          <t>YYYYMM</t>
+        </is>
+      </c>
       <c r="U86" s="10" t="n"/>
       <c r="V86" s="10" t="n"/>
       <c r="W86" s="10" t="n"/>
       <c r="X86" s="11" t="n"/>
-      <c r="Y86" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="Y86" s="17" t="inlineStr"/>
       <c r="Z86" s="10" t="n"/>
       <c r="AA86" s="10" t="n"/>
       <c r="AB86" s="10" t="n"/>
@@ -12657,7 +13172,7 @@
       <c r="AE86" s="11" t="n"/>
       <c r="AF86" s="19" t="inlineStr">
         <is>
-          <t>電子申込承認ステータス（0:承認待ち, 1:承認済み, 2:否認）</t>
+          <t>請求開始月（空文字許容）</t>
         </is>
       </c>
       <c r="AG86" s="10" t="n"/>
@@ -12673,7 +13188,7 @@
       <c r="C87" s="38" t="n"/>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="E87" s="10" t="n"/>
@@ -12699,20 +13214,12 @@
       </c>
       <c r="R87" s="10" t="n"/>
       <c r="S87" s="11" t="n"/>
-      <c r="T87" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T87" s="17" t="inlineStr"/>
       <c r="U87" s="10" t="n"/>
       <c r="V87" s="10" t="n"/>
       <c r="W87" s="10" t="n"/>
       <c r="X87" s="11" t="n"/>
-      <c r="Y87" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y87" s="17" t="inlineStr"/>
       <c r="Z87" s="10" t="n"/>
       <c r="AA87" s="10" t="n"/>
       <c r="AB87" s="10" t="n"/>
@@ -12721,7 +13228,7 @@
       <c r="AE87" s="11" t="n"/>
       <c r="AF87" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>備考（空文字許容）</t>
         </is>
       </c>
       <c r="AG87" s="10" t="n"/>
@@ -12734,10 +13241,10 @@
       <c r="B88" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="C88" s="39" t="n"/>
+      <c r="C88" s="38" t="n"/>
       <c r="D88" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>rireki_no</t>
         </is>
       </c>
       <c r="E88" s="10" t="n"/>
@@ -12750,7 +13257,7 @@
       <c r="L88" s="11" t="n"/>
       <c r="M88" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N88" s="10" t="n"/>
@@ -12763,11 +13270,7 @@
       </c>
       <c r="R88" s="10" t="n"/>
       <c r="S88" s="11" t="n"/>
-      <c r="T88" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T88" s="17" t="inlineStr"/>
       <c r="U88" s="10" t="n"/>
       <c r="V88" s="10" t="n"/>
       <c r="W88" s="10" t="n"/>
@@ -12785,7 +13288,7 @@
       <c r="AE88" s="11" t="n"/>
       <c r="AF88" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>履歴No（最新の履歴番号）</t>
         </is>
       </c>
       <c r="AG88" s="10" t="n"/>
@@ -12794,21 +13297,140 @@
       <c r="AJ88" s="10" t="n"/>
       <c r="AK88" s="11" t="n"/>
     </row>
-    <row r="89" ht="19.5" customHeight="1"/>
-    <row r="90" ht="19.5" customHeight="1">
-      <c r="B90" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="89" ht="36" customHeight="1">
+      <c r="B89" s="31" t="n">
+        <v>62</v>
+      </c>
+      <c r="C89" s="38" t="n"/>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
+          <t>denshi_shonin_status</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="n"/>
+      <c r="F89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
+      <c r="H89" s="10" t="n"/>
+      <c r="I89" s="10" t="n"/>
+      <c r="J89" s="10" t="n"/>
+      <c r="K89" s="10" t="n"/>
+      <c r="L89" s="11" t="n"/>
+      <c r="M89" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N89" s="10" t="n"/>
+      <c r="O89" s="10" t="n"/>
+      <c r="P89" s="11" t="n"/>
+      <c r="Q89" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R89" s="10" t="n"/>
+      <c r="S89" s="11" t="n"/>
+      <c r="T89" s="17" t="inlineStr"/>
+      <c r="U89" s="10" t="n"/>
+      <c r="V89" s="10" t="n"/>
+      <c r="W89" s="10" t="n"/>
+      <c r="X89" s="11" t="n"/>
+      <c r="Y89" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z89" s="10" t="n"/>
+      <c r="AA89" s="10" t="n"/>
+      <c r="AB89" s="10" t="n"/>
+      <c r="AC89" s="10" t="n"/>
+      <c r="AD89" s="10" t="n"/>
+      <c r="AE89" s="11" t="n"/>
+      <c r="AF89" s="19" t="inlineStr">
+        <is>
+          <t>電子申込承認ステータス（0:承認待ち, 1:承認済み, 2:否認）</t>
+        </is>
+      </c>
+      <c r="AG89" s="10" t="n"/>
+      <c r="AH89" s="10" t="n"/>
+      <c r="AI89" s="10" t="n"/>
+      <c r="AJ89" s="10" t="n"/>
+      <c r="AK89" s="11" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="B90" s="31" t="n">
+        <v>63</v>
+      </c>
+      <c r="C90" s="38" t="n"/>
+      <c r="D90" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="11" t="n"/>
+      <c r="M90" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="11" t="n"/>
+      <c r="Q90" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="11" t="n"/>
+      <c r="T90" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="11" t="n"/>
+      <c r="Y90" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="11" t="n"/>
+      <c r="AF90" s="19" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="C91" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/dokusya/1</t>
-        </is>
-      </c>
-      <c r="D91" s="10" t="n"/>
+      <c r="B91" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="C91" s="39" t="n"/>
+      <c r="D91" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
       <c r="E91" s="10" t="n"/>
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
@@ -12816,42 +13438,111 @@
       <c r="I91" s="10" t="n"/>
       <c r="J91" s="10" t="n"/>
       <c r="K91" s="10" t="n"/>
-      <c r="L91" s="10" t="n"/>
-      <c r="M91" s="10" t="n"/>
+      <c r="L91" s="11" t="n"/>
+      <c r="M91" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
       <c r="N91" s="10" t="n"/>
       <c r="O91" s="10" t="n"/>
-      <c r="P91" s="10" t="n"/>
-      <c r="Q91" s="10" t="n"/>
+      <c r="P91" s="11" t="n"/>
+      <c r="Q91" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R91" s="10" t="n"/>
-      <c r="S91" s="10" t="n"/>
-      <c r="T91" s="10" t="n"/>
+      <c r="S91" s="11" t="n"/>
+      <c r="T91" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U91" s="10" t="n"/>
       <c r="V91" s="10" t="n"/>
       <c r="W91" s="10" t="n"/>
-      <c r="X91" s="10" t="n"/>
-      <c r="Y91" s="10" t="n"/>
+      <c r="X91" s="11" t="n"/>
+      <c r="Y91" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z91" s="10" t="n"/>
       <c r="AA91" s="10" t="n"/>
       <c r="AB91" s="10" t="n"/>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
-      <c r="AE91" s="10" t="n"/>
-      <c r="AF91" s="10" t="n"/>
+      <c r="AE91" s="11" t="n"/>
+      <c r="AF91" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
       <c r="AG91" s="10" t="n"/>
       <c r="AH91" s="10" t="n"/>
       <c r="AI91" s="10" t="n"/>
       <c r="AJ91" s="10" t="n"/>
       <c r="AK91" s="11" t="n"/>
     </row>
+    <row r="92" ht="19.5" customHeight="1"/>
     <row r="93" ht="19.5" customHeight="1">
       <c r="B93" s="40" t="inlineStr">
         <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="C94" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/dokusya/1</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="10" t="n"/>
+      <c r="J94" s="10" t="n"/>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="10" t="n"/>
+      <c r="M94" s="10" t="n"/>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="10" t="n"/>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="10" t="n"/>
+      <c r="X94" s="10" t="n"/>
+      <c r="Y94" s="10" t="n"/>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="10" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="10" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="10" t="n"/>
+      <c r="AK94" s="11" t="n"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="B96" s="40" t="inlineStr">
+        <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="409" customHeight="1">
-      <c r="C94" s="19" t="inlineStr">
+    <row r="97" ht="409" customHeight="1">
+      <c r="C97" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -12898,6 +13589,9 @@
     "yubin_kubun": "0",
     "shiharai_hoho": 1,
     "dokusyaryo_shiharai_cycle": 1,
+    "bank_shiten_id": 50,
+    "jastem_toriatsukai_tenpo_code": "001",
+    "jastem_tenpo_name": "本店",
     "bank_branch_code": "001",
     "bank_branch_name": "本店",
     "hikiotoshi_yokin_shubetsu": 1,
@@ -12916,57 +13610,6 @@
     "created_at": "2026-04-01T10:00:00+09:00",
     "updated_at": "2026-04-01T10:00:00+09:00"
   }
-}</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
-      <c r="J94" s="10" t="n"/>
-      <c r="K94" s="10" t="n"/>
-      <c r="L94" s="10" t="n"/>
-      <c r="M94" s="10" t="n"/>
-      <c r="N94" s="10" t="n"/>
-      <c r="O94" s="10" t="n"/>
-      <c r="P94" s="10" t="n"/>
-      <c r="Q94" s="10" t="n"/>
-      <c r="R94" s="10" t="n"/>
-      <c r="S94" s="10" t="n"/>
-      <c r="T94" s="10" t="n"/>
-      <c r="U94" s="10" t="n"/>
-      <c r="V94" s="10" t="n"/>
-      <c r="W94" s="10" t="n"/>
-      <c r="X94" s="10" t="n"/>
-      <c r="Y94" s="10" t="n"/>
-      <c r="Z94" s="10" t="n"/>
-      <c r="AA94" s="10" t="n"/>
-      <c r="AB94" s="10" t="n"/>
-      <c r="AC94" s="10" t="n"/>
-      <c r="AD94" s="10" t="n"/>
-      <c r="AE94" s="10" t="n"/>
-      <c r="AF94" s="10" t="n"/>
-      <c r="AG94" s="10" t="n"/>
-      <c r="AH94" s="10" t="n"/>
-      <c r="AI94" s="10" t="n"/>
-      <c r="AJ94" s="10" t="n"/>
-      <c r="AK94" s="11" t="n"/>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="B96" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 401 Unauthorized）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="72" customHeight="1">
-      <c r="C97" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください。"
 }</t>
         </is>
       </c>
@@ -13008,7 +13651,7 @@
     <row r="99" ht="19.5" customHeight="1">
       <c r="B99" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
+          <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
@@ -13016,8 +13659,8 @@
       <c r="C100" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません。"
+  "error_code": "UNAUTHORIZED",
+  "message": "セッションが切れました。再度ログインしてください。"
 }</t>
         </is>
       </c>
@@ -13059,7 +13702,7 @@
     <row r="102" ht="19.5" customHeight="1">
       <c r="B102" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 404 Not Found）</t>
+          <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
@@ -13067,8 +13710,8 @@
       <c r="C103" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "NOT_FOUND",
-  "message": "指定された購読者が見つかりません。"
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません。"
 }</t>
         </is>
       </c>
@@ -13110,7 +13753,7 @@
     <row r="105" ht="19.5" customHeight="1">
       <c r="B105" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
+          <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
@@ -13118,8 +13761,8 @@
       <c r="C106" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください。"
+  "error_code": "NOT_FOUND",
+  "message": "指定された購読者が見つかりません。"
 }</t>
         </is>
       </c>
@@ -13158,240 +13801,305 @@
       <c r="AJ106" s="10" t="n"/>
       <c r="AK106" s="11" t="n"/>
     </row>
-    <row r="108" ht="19.5" customHeight="1"/>
-    <row r="109" ht="19.5" customHeight="1">
-      <c r="A109" s="27" t="inlineStr">
+    <row r="108" ht="19.5" customHeight="1">
+      <c r="B108" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="72" customHeight="1">
+      <c r="C109" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください。"
+}</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="10" t="n"/>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="10" t="n"/>
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="10" t="n"/>
+      <c r="J109" s="10" t="n"/>
+      <c r="K109" s="10" t="n"/>
+      <c r="L109" s="10" t="n"/>
+      <c r="M109" s="10" t="n"/>
+      <c r="N109" s="10" t="n"/>
+      <c r="O109" s="10" t="n"/>
+      <c r="P109" s="10" t="n"/>
+      <c r="Q109" s="10" t="n"/>
+      <c r="R109" s="10" t="n"/>
+      <c r="S109" s="10" t="n"/>
+      <c r="T109" s="10" t="n"/>
+      <c r="U109" s="10" t="n"/>
+      <c r="V109" s="10" t="n"/>
+      <c r="W109" s="10" t="n"/>
+      <c r="X109" s="10" t="n"/>
+      <c r="Y109" s="10" t="n"/>
+      <c r="Z109" s="10" t="n"/>
+      <c r="AA109" s="10" t="n"/>
+      <c r="AB109" s="10" t="n"/>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="10" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="10" t="n"/>
+      <c r="AK109" s="11" t="n"/>
+    </row>
+    <row r="111" ht="19.5" customHeight="1"/>
+    <row r="112" ht="19.5" customHeight="1">
+      <c r="A112" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="B110" s="27" t="inlineStr">
+    <row r="113" ht="18" customHeight="1">
+      <c r="B113" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="C111" s="41" t="inlineStr">
+    <row r="114" ht="18" customHeight="1">
+      <c r="C114" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="D112" s="41" t="inlineStr">
+    <row r="115" ht="18" customHeight="1">
+      <c r="D115" s="41" t="inlineStr">
         <is>
           <t>dokusya_id：数値型チェック、必須チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="C113" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="D114" s="41" t="inlineStr">
-        <is>
-          <t>HTTP 400 (`BAD_REQUEST`) を返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="B115" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="C116" s="41" t="inlineStr">
         <is>
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="D117" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 400 (`BAD_REQUEST`) を返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="B118" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="C119" s="41" t="inlineStr">
+        <is>
           <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="C117" s="41" t="inlineStr">
-        <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="C118" s="41" t="inlineStr">
-        <is>
-          <t>必要権限: `dokusya.view`</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="36" customHeight="1">
-      <c r="C119" s="41" t="inlineStr">
-        <is>
-          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="C120" s="41" t="inlineStr">
         <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="C121" s="41" t="inlineStr">
         <is>
+          <t>必要権限: `dokusya.view`</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="36" customHeight="1">
+      <c r="C122" s="41" t="inlineStr">
+        <is>
+          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="C123" s="41" t="inlineStr">
+        <is>
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="C124" s="41" t="inlineStr">
+        <is>
           <t>DataScope:</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="D122" s="41" t="inlineStr">
+    <row r="125" ht="18" customHeight="1">
+      <c r="D125" s="41" t="inlineStr">
         <is>
           <t>CHUOKAI（中央会）：自中央会のみ参照可能（管轄JAの読者は不可）</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="D123" s="41" t="inlineStr">
+    <row r="126" ht="18" customHeight="1">
+      <c r="D126" s="41" t="inlineStr">
         <is>
           <t>JA_HONTEN（JA本店）：自JAのみ参照可能（`ja_id = user.ja_id`）</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="36" customHeight="1">
-      <c r="D124" s="41" t="inlineStr">
+    <row r="127" ht="36" customHeight="1">
+      <c r="D127" s="41" t="inlineStr">
         <is>
           <t>JA_KANRI_SHITEN（JA管理支店）：自管理支店のみ参照可能（`ja_id = user.ja_id AND kanri_shiten_id = user.kanri_shiten_id`）</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="36" customHeight="1">
-      <c r="C125" s="41" t="inlineStr">
+    <row r="128" ht="36" customHeight="1">
+      <c r="C128" s="41" t="inlineStr">
         <is>
           <t>DataScope違反（他JAのレコードへのアクセス）の場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="18" customHeight="1">
-      <c r="B126" s="27" t="inlineStr">
+    <row r="129" ht="18" customHeight="1">
+      <c r="B129" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="C127" s="41" t="inlineStr">
+    <row r="130" ht="18" customHeight="1">
+      <c r="C130" s="41" t="inlineStr">
         <is>
           <t>ログインユーザーのスコープを取得する。</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="C128" s="41" t="inlineStr">
-        <is>
-          <t>以下のSQLを実行して購読者情報を取得する（販売店名・単価名を結合）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="162" customHeight="1">
-      <c r="C129" s="42" t="inlineStr">
+    <row r="131" ht="18" customHeight="1">
+      <c r="C131" s="41" t="inlineStr">
+        <is>
+          <t>以下のSQLを実行して購読者情報を取得する（販売店名・単価名・引落口座支店情報を結合）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="90" customHeight="1">
+      <c r="C132" s="41" t="inlineStr">
+        <is>
+          <t>`bank_shiten_id` は `t_dokusya.bank_branch_code` をキーとして、ログインユーザー所属JA内で `kinyu_shiten_flg = TRUE` の `m_shiten` レコードから逆引きする（プルダウン再ハイドレーション用）。`jastem_toriatsukai_tenpo_code` および `jastem_tenpo_name` も同じ JOIN から取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="288" customHeight="1">
+      <c r="C133" s="42" t="inlineStr">
         <is>
           <t>SELECT d.*,
        h.hanbaiten_name,
-       t.tanka_name
+       t.tanka_name,
+       bs.shiten_id                       AS bank_shiten_id,
+       bs.jastem_toriatsukai_tenpo_code   AS jastem_toriatsukai_tenpo_code,
+       bs.jastem_tenpo_name               AS jastem_tenpo_name
 FROM t_dokusya d
 LEFT JOIN m_hanbaiten h ON h.hanbaiten_id = d.hanbaiten_id AND h.deleted_at IS NULL
 LEFT JOIN m_tanka t ON t.tanka_id = d.tanka_id AND t.deleted_at IS NULL
+LEFT JOIN m_shiten bs ON bs.ja_id = d.ja_id
+                     AND bs.jastem_toriatsukai_tenpo_code = d.bank_branch_code
+                     AND bs.kinyu_shiten_flg = TRUE
+                     AND bs.deleted_at IS NULL
 WHERE d.dokusya_id = :dokusya_id
   AND d.ja_id = :ja_id
   AND d.deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D129" s="10" t="n"/>
-      <c r="E129" s="10" t="n"/>
-      <c r="F129" s="10" t="n"/>
-      <c r="G129" s="10" t="n"/>
-      <c r="H129" s="10" t="n"/>
-      <c r="I129" s="10" t="n"/>
-      <c r="J129" s="10" t="n"/>
-      <c r="K129" s="10" t="n"/>
-      <c r="L129" s="10" t="n"/>
-      <c r="M129" s="10" t="n"/>
-      <c r="N129" s="10" t="n"/>
-      <c r="O129" s="10" t="n"/>
-      <c r="P129" s="10" t="n"/>
-      <c r="Q129" s="10" t="n"/>
-      <c r="R129" s="10" t="n"/>
-      <c r="S129" s="10" t="n"/>
-      <c r="T129" s="10" t="n"/>
-      <c r="U129" s="10" t="n"/>
-      <c r="V129" s="10" t="n"/>
-      <c r="W129" s="10" t="n"/>
-      <c r="X129" s="10" t="n"/>
-      <c r="Y129" s="10" t="n"/>
-      <c r="Z129" s="10" t="n"/>
-      <c r="AA129" s="10" t="n"/>
-      <c r="AB129" s="10" t="n"/>
-      <c r="AC129" s="10" t="n"/>
-      <c r="AD129" s="10" t="n"/>
-      <c r="AE129" s="10" t="n"/>
-      <c r="AF129" s="10" t="n"/>
-      <c r="AG129" s="10" t="n"/>
-      <c r="AH129" s="10" t="n"/>
-      <c r="AI129" s="10" t="n"/>
-      <c r="AJ129" s="10" t="n"/>
-      <c r="AK129" s="11" t="n"/>
-    </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="C130" s="41" t="inlineStr">
+      <c r="D133" s="10" t="n"/>
+      <c r="E133" s="10" t="n"/>
+      <c r="F133" s="10" t="n"/>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="10" t="n"/>
+      <c r="J133" s="10" t="n"/>
+      <c r="K133" s="10" t="n"/>
+      <c r="L133" s="10" t="n"/>
+      <c r="M133" s="10" t="n"/>
+      <c r="N133" s="10" t="n"/>
+      <c r="O133" s="10" t="n"/>
+      <c r="P133" s="10" t="n"/>
+      <c r="Q133" s="10" t="n"/>
+      <c r="R133" s="10" t="n"/>
+      <c r="S133" s="10" t="n"/>
+      <c r="T133" s="10" t="n"/>
+      <c r="U133" s="10" t="n"/>
+      <c r="V133" s="10" t="n"/>
+      <c r="W133" s="10" t="n"/>
+      <c r="X133" s="10" t="n"/>
+      <c r="Y133" s="10" t="n"/>
+      <c r="Z133" s="10" t="n"/>
+      <c r="AA133" s="10" t="n"/>
+      <c r="AB133" s="10" t="n"/>
+      <c r="AC133" s="10" t="n"/>
+      <c r="AD133" s="10" t="n"/>
+      <c r="AE133" s="10" t="n"/>
+      <c r="AF133" s="10" t="n"/>
+      <c r="AG133" s="10" t="n"/>
+      <c r="AH133" s="10" t="n"/>
+      <c r="AI133" s="10" t="n"/>
+      <c r="AJ133" s="10" t="n"/>
+      <c r="AK133" s="11" t="n"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="C134" s="41" t="inlineStr">
         <is>
           <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="C131" s="41" t="inlineStr">
-        <is>
-          <t>DataScope違反の場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="B132" s="27" t="inlineStr">
-        <is>
-          <t>4.4 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="C133" s="41" t="inlineStr">
-        <is>
-          <t>data オブジェクトを含むJSONを返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="B134" s="27" t="inlineStr">
-        <is>
-          <t>4.5 例外処理</t>
         </is>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="C135" s="41" t="inlineStr">
         <is>
+          <t>DataScope違反の場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="B136" s="27" t="inlineStr">
+        <is>
+          <t>4.4 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="C137" s="41" t="inlineStr">
+        <is>
+          <t>data オブジェクトを含むJSONを返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="B138" s="27" t="inlineStr">
+        <is>
+          <t>4.5 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="C139" s="41" t="inlineStr">
+        <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="468">
+  <mergeCells count="487">
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="Y27:AE27"/>
     <mergeCell ref="Y45:AE45"/>
@@ -13404,12 +14112,13 @@
     <mergeCell ref="D62:L62"/>
     <mergeCell ref="T68:X68"/>
     <mergeCell ref="D56:L56"/>
+    <mergeCell ref="C29:C91"/>
     <mergeCell ref="C128:AK128"/>
     <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
-    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="C100:AK100"/>
+    <mergeCell ref="AF91:AK91"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="D64:L64"/>
@@ -13420,17 +14129,19 @@
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="AF84:AK84"/>
     <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="C129:AK129"/>
+    <mergeCell ref="Q91:S91"/>
     <mergeCell ref="M54:P54"/>
+    <mergeCell ref="M90:P90"/>
     <mergeCell ref="AF86:AK86"/>
     <mergeCell ref="Q77:S77"/>
-    <mergeCell ref="D124:AK124"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="B138:AK138"/>
     <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="B113:AK113"/>
     <mergeCell ref="T37:X37"/>
+    <mergeCell ref="D126:AK126"/>
     <mergeCell ref="M85:P85"/>
-    <mergeCell ref="B115:AK115"/>
     <mergeCell ref="C131:AK131"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="D75:L75"/>
@@ -13451,14 +14162,15 @@
     <mergeCell ref="Y68:AE68"/>
     <mergeCell ref="Y55:AE55"/>
     <mergeCell ref="AF81:AK81"/>
-    <mergeCell ref="C117:AK117"/>
     <mergeCell ref="T40:X40"/>
+    <mergeCell ref="D89:L89"/>
     <mergeCell ref="T76:X76"/>
     <mergeCell ref="T69:X69"/>
     <mergeCell ref="D65:L65"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="M91:P91"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
@@ -13474,7 +14186,9 @@
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="D83:L83"/>
+    <mergeCell ref="T89:X89"/>
     <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="C134:AK134"/>
     <mergeCell ref="T88:X88"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="Y74:AE74"/>
@@ -13492,11 +14206,9 @@
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
-    <mergeCell ref="B134:AK134"/>
     <mergeCell ref="Q64:S64"/>
     <mergeCell ref="T77:X77"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B90:I90"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="M66:P66"/>
@@ -13504,16 +14216,18 @@
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="Y87:AE87"/>
     <mergeCell ref="AF75:AK75"/>
+    <mergeCell ref="Y89:AE89"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="B108:I108"/>
     <mergeCell ref="T61:X61"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="Y82:AE82"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="AF70:AK70"/>
-    <mergeCell ref="B126:AK126"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="D84:L84"/>
+    <mergeCell ref="T90:X90"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
@@ -13525,7 +14239,6 @@
     <mergeCell ref="Y77:AE77"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="B96:I96"/>
-    <mergeCell ref="A109:AK109"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="M56:P56"/>
     <mergeCell ref="M43:P43"/>
@@ -13533,6 +14246,7 @@
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="Q70:S70"/>
     <mergeCell ref="Y72:AE72"/>
+    <mergeCell ref="D115:AK115"/>
     <mergeCell ref="D33:L33"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="D35:L35"/>
@@ -13546,6 +14260,7 @@
     <mergeCell ref="T86:X86"/>
     <mergeCell ref="Q83:S83"/>
     <mergeCell ref="D36:L36"/>
+    <mergeCell ref="Y90:AE90"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="Q58:S58"/>
     <mergeCell ref="AF78:AK78"/>
@@ -13557,12 +14272,10 @@
     <mergeCell ref="M62:P62"/>
     <mergeCell ref="AF80:AK80"/>
     <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="B132:AK132"/>
     <mergeCell ref="M87:P87"/>
     <mergeCell ref="C103:AK103"/>
     <mergeCell ref="D29:L29"/>
     <mergeCell ref="M64:P64"/>
-    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="AF71:AK71"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="AF37:AK37"/>
@@ -13583,6 +14296,7 @@
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q84:S84"/>
     <mergeCell ref="C116:AK116"/>
+    <mergeCell ref="Y91:AE91"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="M83:P83"/>
     <mergeCell ref="AF79:AK79"/>
@@ -13601,25 +14315,28 @@
     <mergeCell ref="D57:L57"/>
     <mergeCell ref="AF63:AK63"/>
     <mergeCell ref="Q79:S79"/>
-    <mergeCell ref="C111:AK111"/>
     <mergeCell ref="D32:L32"/>
     <mergeCell ref="Y61:AE61"/>
     <mergeCell ref="Y48:AE48"/>
     <mergeCell ref="AF74:AK74"/>
     <mergeCell ref="Q81:S81"/>
+    <mergeCell ref="D117:AK117"/>
     <mergeCell ref="M58:P58"/>
     <mergeCell ref="AF76:AK76"/>
     <mergeCell ref="Q74:S74"/>
     <mergeCell ref="T62:X62"/>
     <mergeCell ref="Q76:S76"/>
+    <mergeCell ref="C137:AK137"/>
     <mergeCell ref="T64:X64"/>
+    <mergeCell ref="C124:AK124"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D44:L44"/>
+    <mergeCell ref="C139:AK139"/>
     <mergeCell ref="D60:L60"/>
-    <mergeCell ref="B110:AK110"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M84:P84"/>
     <mergeCell ref="M22:P22"/>
+    <mergeCell ref="C132:AK132"/>
     <mergeCell ref="Y59:AE59"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="D45:L45"/>
@@ -13637,18 +14354,21 @@
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="T82:X82"/>
     <mergeCell ref="D70:L70"/>
-    <mergeCell ref="D122:AK122"/>
+    <mergeCell ref="AF89:AK89"/>
     <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="B136:AK136"/>
     <mergeCell ref="D78:L78"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="Q89:S89"/>
     <mergeCell ref="D71:L71"/>
+    <mergeCell ref="C109:AK109"/>
     <mergeCell ref="Y62:AE62"/>
     <mergeCell ref="D73:L73"/>
     <mergeCell ref="C133:AK133"/>
     <mergeCell ref="M70:P70"/>
-    <mergeCell ref="C127:AK127"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="M35:P35"/>
+    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="Y64:AE64"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="AF77:AK77"/>
@@ -13677,6 +14397,7 @@
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="T83:X83"/>
     <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="AF90:AK90"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="D79:L79"/>
@@ -13688,9 +14409,9 @@
     <mergeCell ref="C130:AK130"/>
     <mergeCell ref="D81:L81"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C122:AK122"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M36:P36"/>
-    <mergeCell ref="C125:AK125"/>
     <mergeCell ref="Q63:S63"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Y70:AE70"/>
@@ -13720,12 +14441,14 @@
     <mergeCell ref="C120:AK120"/>
     <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
+    <mergeCell ref="M89:P89"/>
     <mergeCell ref="Q55:S55"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="D87:L87"/>
     <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="A112:AK112"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="Y71:AE71"/>
@@ -13745,7 +14468,6 @@
     <mergeCell ref="Q68:S68"/>
     <mergeCell ref="T81:X81"/>
     <mergeCell ref="D31:L31"/>
-    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="D77:L77"/>
     <mergeCell ref="Q72:S72"/>
@@ -13774,26 +14496,28 @@
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="Y79:AE79"/>
+    <mergeCell ref="D90:L90"/>
     <mergeCell ref="AF67:AK67"/>
     <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y81:AE81"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
     <mergeCell ref="Q67:S67"/>
+    <mergeCell ref="D125:AK125"/>
     <mergeCell ref="AF62:AK62"/>
-    <mergeCell ref="D112:AK112"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="Q69:S69"/>
     <mergeCell ref="B102:I102"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y76:AE76"/>
+    <mergeCell ref="D127:AK127"/>
     <mergeCell ref="AF64:AK64"/>
-    <mergeCell ref="D114:AK114"/>
     <mergeCell ref="D37:L37"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="Y63:AE63"/>
     <mergeCell ref="M44:P44"/>
+    <mergeCell ref="B118:AK118"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="M79:P79"/>
@@ -13806,6 +14530,7 @@
     <mergeCell ref="D63:L63"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="AF82:AK82"/>
+    <mergeCell ref="B129:AK129"/>
     <mergeCell ref="Y31:AE31"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="D52:L52"/>
@@ -13813,6 +14538,7 @@
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="T32:X32"/>
+    <mergeCell ref="D91:L91"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
@@ -13828,7 +14554,6 @@
     <mergeCell ref="M69:P69"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="C29:C88"/>
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
     <mergeCell ref="D40:L40"/>
@@ -13837,6 +14562,7 @@
     <mergeCell ref="T27:X27"/>
     <mergeCell ref="C135:AK135"/>
     <mergeCell ref="AF54:AK54"/>
+    <mergeCell ref="T91:X91"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="Q88:S88"/>
     <mergeCell ref="D41:L41"/>
@@ -13844,6 +14570,7 @@
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="M76:P76"/>
     <mergeCell ref="AF83:AK83"/>
+    <mergeCell ref="Q90:S90"/>
     <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="AF58:AK58"/>
@@ -13851,12 +14578,12 @@
     <mergeCell ref="C97:AK97"/>
     <mergeCell ref="AF85:AK85"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="D123:AK123"/>
     <mergeCell ref="AF60:AK60"/>
     <mergeCell ref="D74:L74"/>
     <mergeCell ref="D68:L68"/>
     <mergeCell ref="D59:L59"/>
     <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="M77:P77"/>
     <mergeCell ref="Y52:AE52"/>
@@ -13871,7 +14598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK211"/>
+  <dimension ref="A1:AK226"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -14032,7 +14759,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -17047,7 +17774,7 @@
       <c r="AE60" s="11" t="n"/>
       <c r="AF60" s="19" t="inlineStr">
         <is>
-          <t>郵送区分 ※m_code.code_category='YUBIN_KUBUN'を参照（0:空, 1:郵送）。デフォルト: '0'</t>
+          <t>郵送区分 ※m_code.code_category='YUBIN_KUBUN'を参照（0:空, 1:郵送）。プルダウン入力。デフォルト: '0'</t>
         </is>
       </c>
       <c r="AG60" s="10" t="n"/>
@@ -17162,7 +17889,9 @@
       <c r="Z62" s="10" t="n"/>
       <c r="AA62" s="10" t="n"/>
       <c r="AB62" s="11" t="n"/>
-      <c r="AC62" s="17" t="inlineStr"/>
+      <c r="AC62" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="AD62" s="10" t="n"/>
       <c r="AE62" s="11" t="n"/>
       <c r="AF62" s="19" t="inlineStr">
@@ -17176,13 +17905,13 @@
       <c r="AJ62" s="10" t="n"/>
       <c r="AK62" s="11" t="n"/>
     </row>
-    <row r="63" ht="18" customHeight="1">
+    <row r="63" ht="108" customHeight="1">
       <c r="B63" s="31" t="n">
         <v>40</v>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t>bank_branch_code</t>
+          <t>bank_shiten_id</t>
         </is>
       </c>
       <c r="D63" s="10" t="n"/>
@@ -17196,7 +17925,7 @@
       <c r="L63" s="11" t="n"/>
       <c r="M63" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N63" s="10" t="n"/>
@@ -17218,20 +17947,16 @@
       <c r="V63" s="10" t="n"/>
       <c r="W63" s="10" t="n"/>
       <c r="X63" s="11" t="n"/>
-      <c r="Y63" s="17" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y63" s="17" t="inlineStr"/>
       <c r="Z63" s="10" t="n"/>
       <c r="AA63" s="10" t="n"/>
       <c r="AB63" s="11" t="n"/>
-      <c r="AC63" s="17" t="n">
-        <v>3</v>
-      </c>
+      <c r="AC63" s="17" t="inlineStr"/>
       <c r="AD63" s="10" t="n"/>
       <c r="AE63" s="11" t="n"/>
       <c r="AF63" s="19" t="inlineStr">
         <is>
-          <t>引落口座支店コード（口座引落時は必須）</t>
+          <t>引落口座支店ID（口座引落時は必須、他の支払方法では任意）。`m_shiten.shiten_id` を `kinyu_shiten_flg=TRUE` で絞り込んだ値。指定された場合は支払方法を問わずサーバ側で `jastem_toriatsukai_tenpo_code` / `jastem_tenpo_name` を逆引きし `t_dokusya.bank_branch_code` / `bank_branch_name` に非正規化保存する</t>
         </is>
       </c>
       <c r="AG63" s="10" t="n"/>
@@ -17240,13 +17965,13 @@
       <c r="AJ63" s="10" t="n"/>
       <c r="AK63" s="11" t="n"/>
     </row>
-    <row r="64" ht="18" customHeight="1">
+    <row r="64" ht="36" customHeight="1">
       <c r="B64" s="31" t="n">
         <v>41</v>
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>bank_branch_name</t>
+          <t>hikiotoshi_yokin_shubetsu</t>
         </is>
       </c>
       <c r="D64" s="10" t="n"/>
@@ -17260,7 +17985,7 @@
       <c r="L64" s="11" t="n"/>
       <c r="M64" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N64" s="10" t="n"/>
@@ -17282,20 +18007,16 @@
       <c r="V64" s="10" t="n"/>
       <c r="W64" s="10" t="n"/>
       <c r="X64" s="11" t="n"/>
-      <c r="Y64" s="17" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y64" s="17" t="inlineStr"/>
       <c r="Z64" s="10" t="n"/>
       <c r="AA64" s="10" t="n"/>
       <c r="AB64" s="11" t="n"/>
-      <c r="AC64" s="17" t="n">
-        <v>100</v>
-      </c>
+      <c r="AC64" s="17" t="inlineStr"/>
       <c r="AD64" s="10" t="n"/>
       <c r="AE64" s="11" t="n"/>
       <c r="AF64" s="19" t="inlineStr">
         <is>
-          <t>引落口座支店名</t>
+          <t>引落口座貯金種目 ※m_code.code_category='YOKIN_SHUBETSU'を参照（1:普通, 2:当座）</t>
         </is>
       </c>
       <c r="AG64" s="10" t="n"/>
@@ -17304,13 +18025,13 @@
       <c r="AJ64" s="10" t="n"/>
       <c r="AK64" s="11" t="n"/>
     </row>
-    <row r="65" ht="36" customHeight="1">
+    <row r="65" ht="18" customHeight="1">
       <c r="B65" s="31" t="n">
         <v>42</v>
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t>hikiotoshi_yokin_shubetsu</t>
+          <t>hikiotoshi_koza_no</t>
         </is>
       </c>
       <c r="D65" s="10" t="n"/>
@@ -17324,7 +18045,7 @@
       <c r="L65" s="11" t="n"/>
       <c r="M65" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N65" s="10" t="n"/>
@@ -17346,16 +18067,20 @@
       <c r="V65" s="10" t="n"/>
       <c r="W65" s="10" t="n"/>
       <c r="X65" s="11" t="n"/>
-      <c r="Y65" s="17" t="inlineStr"/>
+      <c r="Y65" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="Z65" s="10" t="n"/>
       <c r="AA65" s="10" t="n"/>
       <c r="AB65" s="11" t="n"/>
-      <c r="AC65" s="17" t="inlineStr"/>
+      <c r="AC65" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="AD65" s="10" t="n"/>
       <c r="AE65" s="11" t="n"/>
       <c r="AF65" s="19" t="inlineStr">
         <is>
-          <t>引落口座貯金種目 ※m_code.code_category='YOKIN_SHUBETSU'を参照（1:普通, 2:当座）</t>
+          <t>引落口座番号</t>
         </is>
       </c>
       <c r="AG65" s="10" t="n"/>
@@ -17370,7 +18095,7 @@
       </c>
       <c r="C66" s="19" t="inlineStr">
         <is>
-          <t>hikiotoshi_koza_no</t>
+          <t>hikiotoshi_koza_meigi</t>
         </is>
       </c>
       <c r="D66" s="10" t="n"/>
@@ -17413,13 +18138,13 @@
       <c r="AA66" s="10" t="n"/>
       <c r="AB66" s="11" t="n"/>
       <c r="AC66" s="17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AD66" s="10" t="n"/>
       <c r="AE66" s="11" t="n"/>
       <c r="AF66" s="19" t="inlineStr">
         <is>
-          <t>引落口座番号</t>
+          <t>引落口座名義</t>
         </is>
       </c>
       <c r="AG66" s="10" t="n"/>
@@ -17434,7 +18159,7 @@
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>hikiotoshi_koza_meigi</t>
+          <t>dokusyaso_bunrui</t>
         </is>
       </c>
       <c r="D67" s="10" t="n"/>
@@ -17463,7 +18188,7 @@
       <c r="S67" s="11" t="n"/>
       <c r="T67" s="17" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U67" s="10" t="n"/>
@@ -17483,7 +18208,7 @@
       <c r="AE67" s="11" t="n"/>
       <c r="AF67" s="19" t="inlineStr">
         <is>
-          <t>引落口座名義</t>
+          <t>購読者層分類（カンマ区切り）</t>
         </is>
       </c>
       <c r="AG67" s="10" t="n"/>
@@ -17498,7 +18223,7 @@
       </c>
       <c r="C68" s="19" t="inlineStr">
         <is>
-          <t>dokusyaso_bunrui</t>
+          <t>nogyosya_bunrui</t>
         </is>
       </c>
       <c r="D68" s="10" t="n"/>
@@ -17527,7 +18252,7 @@
       <c r="S68" s="11" t="n"/>
       <c r="T68" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>△</t>
         </is>
       </c>
       <c r="U68" s="10" t="n"/>
@@ -17547,7 +18272,7 @@
       <c r="AE68" s="11" t="n"/>
       <c r="AF68" s="19" t="inlineStr">
         <is>
-          <t>購読者層分類（カンマ区切り）</t>
+          <t>農業者分類（カンマ区切り）。購読者層分類で「農業者」を選択した場合は必須</t>
         </is>
       </c>
       <c r="AG68" s="10" t="n"/>
@@ -17562,7 +18287,7 @@
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t>nogyosya_bunrui</t>
+          <t>dokusya_kaishi_date</t>
         </is>
       </c>
       <c r="D69" s="10" t="n"/>
@@ -17591,27 +18316,23 @@
       <c r="S69" s="11" t="n"/>
       <c r="T69" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="U69" s="10" t="n"/>
       <c r="V69" s="10" t="n"/>
       <c r="W69" s="10" t="n"/>
       <c r="X69" s="11" t="n"/>
-      <c r="Y69" s="17" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y69" s="17" t="inlineStr"/>
       <c r="Z69" s="10" t="n"/>
       <c r="AA69" s="10" t="n"/>
       <c r="AB69" s="11" t="n"/>
-      <c r="AC69" s="17" t="n">
-        <v>50</v>
-      </c>
+      <c r="AC69" s="17" t="inlineStr"/>
       <c r="AD69" s="10" t="n"/>
       <c r="AE69" s="11" t="n"/>
       <c r="AF69" s="19" t="inlineStr">
         <is>
-          <t>農業者分類（カンマ区切り）</t>
+          <t>購読開始日（YYYY-MM-DD）</t>
         </is>
       </c>
       <c r="AG69" s="10" t="n"/>
@@ -17626,7 +18347,7 @@
       </c>
       <c r="C70" s="19" t="inlineStr">
         <is>
-          <t>dokusya_kaishi_date</t>
+          <t>dokusya_chushi_date</t>
         </is>
       </c>
       <c r="D70" s="10" t="n"/>
@@ -17655,7 +18376,7 @@
       <c r="S70" s="11" t="n"/>
       <c r="T70" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U70" s="10" t="n"/>
@@ -17671,7 +18392,7 @@
       <c r="AE70" s="11" t="n"/>
       <c r="AF70" s="19" t="inlineStr">
         <is>
-          <t>購読開始日（YYYY-MM-DD）</t>
+          <t>購読中止日（YYYY-MM-DD、解約時のみ）</t>
         </is>
       </c>
       <c r="AG70" s="10" t="n"/>
@@ -17686,7 +18407,7 @@
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date</t>
+          <t>joho_henko_tekiyo_date</t>
         </is>
       </c>
       <c r="D71" s="10" t="n"/>
@@ -17731,7 +18452,7 @@
       <c r="AE71" s="11" t="n"/>
       <c r="AF71" s="19" t="inlineStr">
         <is>
-          <t>購読中止日（YYYY-MM-DD、解約時のみ）</t>
+          <t>読者情報変更適用日（YYYY-MM-DD）。入力時は未来日であること</t>
         </is>
       </c>
       <c r="AG71" s="10" t="n"/>
@@ -20270,7 +20991,7 @@
       <c r="AE117" s="11" t="n"/>
       <c r="AF117" s="19" t="inlineStr">
         <is>
-          <t>郵送区分</t>
+          <t>郵送区分（0:空, 1:郵送）</t>
         </is>
       </c>
       <c r="AG117" s="10" t="n"/>
@@ -20399,14 +21120,14 @@
       <c r="AJ119" s="10" t="n"/>
       <c r="AK119" s="11" t="n"/>
     </row>
-    <row r="120" ht="18" customHeight="1">
+    <row r="120" ht="36" customHeight="1">
       <c r="B120" s="31" t="n">
         <v>43</v>
       </c>
       <c r="C120" s="38" t="n"/>
       <c r="D120" s="19" t="inlineStr">
         <is>
-          <t>bank_branch_code</t>
+          <t>bank_shiten_id</t>
         </is>
       </c>
       <c r="E120" s="10" t="n"/>
@@ -20419,7 +21140,7 @@
       <c r="L120" s="11" t="n"/>
       <c r="M120" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N120" s="10" t="n"/>
@@ -20439,7 +21160,7 @@
       <c r="X120" s="11" t="n"/>
       <c r="Y120" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z120" s="10" t="n"/>
@@ -20450,7 +21171,7 @@
       <c r="AE120" s="11" t="n"/>
       <c r="AF120" s="19" t="inlineStr">
         <is>
-          <t>引落口座支店コード</t>
+          <t>引落口座支店ID（プルダウン再ハイドレーション用）。口座引落以外の場合は null</t>
         </is>
       </c>
       <c r="AG120" s="10" t="n"/>
@@ -20459,14 +21180,14 @@
       <c r="AJ120" s="10" t="n"/>
       <c r="AK120" s="11" t="n"/>
     </row>
-    <row r="121" ht="18" customHeight="1">
+    <row r="121" ht="36" customHeight="1">
       <c r="B121" s="31" t="n">
         <v>44</v>
       </c>
       <c r="C121" s="38" t="n"/>
       <c r="D121" s="19" t="inlineStr">
         <is>
-          <t>bank_branch_name</t>
+          <t>jastem_toriatsukai_tenpo_code</t>
         </is>
       </c>
       <c r="E121" s="10" t="n"/>
@@ -20497,11 +21218,7 @@
       <c r="V121" s="10" t="n"/>
       <c r="W121" s="10" t="n"/>
       <c r="X121" s="11" t="n"/>
-      <c r="Y121" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y121" s="17" t="inlineStr"/>
       <c r="Z121" s="10" t="n"/>
       <c r="AA121" s="10" t="n"/>
       <c r="AB121" s="10" t="n"/>
@@ -20510,7 +21227,7 @@
       <c r="AE121" s="11" t="n"/>
       <c r="AF121" s="19" t="inlineStr">
         <is>
-          <t>引落口座支店名</t>
+          <t>引落元口座店舗コード（m_shiten結合取得、自動表示ラベル、空文字許容）</t>
         </is>
       </c>
       <c r="AG121" s="10" t="n"/>
@@ -20519,14 +21236,14 @@
       <c r="AJ121" s="10" t="n"/>
       <c r="AK121" s="11" t="n"/>
     </row>
-    <row r="122" ht="18" customHeight="1">
+    <row r="122" ht="36" customHeight="1">
       <c r="B122" s="31" t="n">
         <v>45</v>
       </c>
       <c r="C122" s="38" t="n"/>
       <c r="D122" s="19" t="inlineStr">
         <is>
-          <t>hikiotoshi_yokin_shubetsu</t>
+          <t>jastem_tenpo_name</t>
         </is>
       </c>
       <c r="E122" s="10" t="n"/>
@@ -20539,7 +21256,7 @@
       <c r="L122" s="11" t="n"/>
       <c r="M122" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N122" s="10" t="n"/>
@@ -20557,11 +21274,7 @@
       <c r="V122" s="10" t="n"/>
       <c r="W122" s="10" t="n"/>
       <c r="X122" s="11" t="n"/>
-      <c r="Y122" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="Y122" s="17" t="inlineStr"/>
       <c r="Z122" s="10" t="n"/>
       <c r="AA122" s="10" t="n"/>
       <c r="AB122" s="10" t="n"/>
@@ -20570,7 +21283,7 @@
       <c r="AE122" s="11" t="n"/>
       <c r="AF122" s="19" t="inlineStr">
         <is>
-          <t>引落口座貯金種目</t>
+          <t>引落元口座店舗名（m_shiten結合取得、自動表示ラベル、空文字許容）</t>
         </is>
       </c>
       <c r="AG122" s="10" t="n"/>
@@ -20586,7 +21299,7 @@
       <c r="C123" s="38" t="n"/>
       <c r="D123" s="19" t="inlineStr">
         <is>
-          <t>hikiotoshi_koza_no</t>
+          <t>bank_branch_code</t>
         </is>
       </c>
       <c r="E123" s="10" t="n"/>
@@ -20617,7 +21330,11 @@
       <c r="V123" s="10" t="n"/>
       <c r="W123" s="10" t="n"/>
       <c r="X123" s="11" t="n"/>
-      <c r="Y123" s="17" t="inlineStr"/>
+      <c r="Y123" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z123" s="10" t="n"/>
       <c r="AA123" s="10" t="n"/>
       <c r="AB123" s="10" t="n"/>
@@ -20626,7 +21343,7 @@
       <c r="AE123" s="11" t="n"/>
       <c r="AF123" s="19" t="inlineStr">
         <is>
-          <t>引落口座番号（空文字許容）</t>
+          <t>引落口座支店コード（t_dokusya 永続列）</t>
         </is>
       </c>
       <c r="AG123" s="10" t="n"/>
@@ -20642,7 +21359,7 @@
       <c r="C124" s="38" t="n"/>
       <c r="D124" s="19" t="inlineStr">
         <is>
-          <t>hikiotoshi_koza_meigi</t>
+          <t>bank_branch_name</t>
         </is>
       </c>
       <c r="E124" s="10" t="n"/>
@@ -20673,7 +21390,11 @@
       <c r="V124" s="10" t="n"/>
       <c r="W124" s="10" t="n"/>
       <c r="X124" s="11" t="n"/>
-      <c r="Y124" s="17" t="inlineStr"/>
+      <c r="Y124" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z124" s="10" t="n"/>
       <c r="AA124" s="10" t="n"/>
       <c r="AB124" s="10" t="n"/>
@@ -20682,7 +21403,7 @@
       <c r="AE124" s="11" t="n"/>
       <c r="AF124" s="19" t="inlineStr">
         <is>
-          <t>引落口座名義（空文字許容）</t>
+          <t>引落口座支店名（t_dokusya 永続列）</t>
         </is>
       </c>
       <c r="AG124" s="10" t="n"/>
@@ -20698,7 +21419,7 @@
       <c r="C125" s="38" t="n"/>
       <c r="D125" s="19" t="inlineStr">
         <is>
-          <t>dokusyaso_bunrui</t>
+          <t>hikiotoshi_yokin_shubetsu</t>
         </is>
       </c>
       <c r="E125" s="10" t="n"/>
@@ -20711,7 +21432,7 @@
       <c r="L125" s="11" t="n"/>
       <c r="M125" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N125" s="10" t="n"/>
@@ -20729,7 +21450,11 @@
       <c r="V125" s="10" t="n"/>
       <c r="W125" s="10" t="n"/>
       <c r="X125" s="11" t="n"/>
-      <c r="Y125" s="17" t="inlineStr"/>
+      <c r="Y125" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="Z125" s="10" t="n"/>
       <c r="AA125" s="10" t="n"/>
       <c r="AB125" s="10" t="n"/>
@@ -20738,7 +21463,7 @@
       <c r="AE125" s="11" t="n"/>
       <c r="AF125" s="19" t="inlineStr">
         <is>
-          <t>購読者層分類（空文字許容）</t>
+          <t>引落口座貯金種目</t>
         </is>
       </c>
       <c r="AG125" s="10" t="n"/>
@@ -20754,7 +21479,7 @@
       <c r="C126" s="38" t="n"/>
       <c r="D126" s="19" t="inlineStr">
         <is>
-          <t>nogyosya_bunrui</t>
+          <t>hikiotoshi_koza_no</t>
         </is>
       </c>
       <c r="E126" s="10" t="n"/>
@@ -20794,7 +21519,7 @@
       <c r="AE126" s="11" t="n"/>
       <c r="AF126" s="19" t="inlineStr">
         <is>
-          <t>農業者分類（空文字許容）</t>
+          <t>引落口座番号（空文字許容）</t>
         </is>
       </c>
       <c r="AG126" s="10" t="n"/>
@@ -20810,7 +21535,7 @@
       <c r="C127" s="38" t="n"/>
       <c r="D127" s="19" t="inlineStr">
         <is>
-          <t>shoki_dokusya_kaishi_date</t>
+          <t>hikiotoshi_koza_meigi</t>
         </is>
       </c>
       <c r="E127" s="10" t="n"/>
@@ -20836,20 +21561,12 @@
       </c>
       <c r="R127" s="10" t="n"/>
       <c r="S127" s="11" t="n"/>
-      <c r="T127" s="17" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+      <c r="T127" s="17" t="inlineStr"/>
       <c r="U127" s="10" t="n"/>
       <c r="V127" s="10" t="n"/>
       <c r="W127" s="10" t="n"/>
       <c r="X127" s="11" t="n"/>
-      <c r="Y127" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y127" s="17" t="inlineStr"/>
       <c r="Z127" s="10" t="n"/>
       <c r="AA127" s="10" t="n"/>
       <c r="AB127" s="10" t="n"/>
@@ -20858,7 +21575,7 @@
       <c r="AE127" s="11" t="n"/>
       <c r="AF127" s="19" t="inlineStr">
         <is>
-          <t>初回購読開始日</t>
+          <t>引落口座名義（空文字許容）</t>
         </is>
       </c>
       <c r="AG127" s="10" t="n"/>
@@ -20874,7 +21591,7 @@
       <c r="C128" s="38" t="n"/>
       <c r="D128" s="19" t="inlineStr">
         <is>
-          <t>dokusya_kaishi_date</t>
+          <t>dokusyaso_bunrui</t>
         </is>
       </c>
       <c r="E128" s="10" t="n"/>
@@ -20900,20 +21617,12 @@
       </c>
       <c r="R128" s="10" t="n"/>
       <c r="S128" s="11" t="n"/>
-      <c r="T128" s="17" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+      <c r="T128" s="17" t="inlineStr"/>
       <c r="U128" s="10" t="n"/>
       <c r="V128" s="10" t="n"/>
       <c r="W128" s="10" t="n"/>
       <c r="X128" s="11" t="n"/>
-      <c r="Y128" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y128" s="17" t="inlineStr"/>
       <c r="Z128" s="10" t="n"/>
       <c r="AA128" s="10" t="n"/>
       <c r="AB128" s="10" t="n"/>
@@ -20922,7 +21631,7 @@
       <c r="AE128" s="11" t="n"/>
       <c r="AF128" s="19" t="inlineStr">
         <is>
-          <t>購読開始日</t>
+          <t>購読者層分類（空文字許容）</t>
         </is>
       </c>
       <c r="AG128" s="10" t="n"/>
@@ -20938,7 +21647,7 @@
       <c r="C129" s="38" t="n"/>
       <c r="D129" s="19" t="inlineStr">
         <is>
-          <t>dokusya_chushi_date</t>
+          <t>nogyosya_bunrui</t>
         </is>
       </c>
       <c r="E129" s="10" t="n"/>
@@ -20964,20 +21673,12 @@
       </c>
       <c r="R129" s="10" t="n"/>
       <c r="S129" s="11" t="n"/>
-      <c r="T129" s="17" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+      <c r="T129" s="17" t="inlineStr"/>
       <c r="U129" s="10" t="n"/>
       <c r="V129" s="10" t="n"/>
       <c r="W129" s="10" t="n"/>
       <c r="X129" s="11" t="n"/>
-      <c r="Y129" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="Y129" s="17" t="inlineStr"/>
       <c r="Z129" s="10" t="n"/>
       <c r="AA129" s="10" t="n"/>
       <c r="AB129" s="10" t="n"/>
@@ -20986,7 +21687,7 @@
       <c r="AE129" s="11" t="n"/>
       <c r="AF129" s="19" t="inlineStr">
         <is>
-          <t>購読中止日</t>
+          <t>農業者分類（空文字許容）</t>
         </is>
       </c>
       <c r="AG129" s="10" t="n"/>
@@ -21002,7 +21703,7 @@
       <c r="C130" s="38" t="n"/>
       <c r="D130" s="19" t="inlineStr">
         <is>
-          <t>joho_henko_tekiyo_date</t>
+          <t>shoki_dokusya_kaishi_date</t>
         </is>
       </c>
       <c r="E130" s="10" t="n"/>
@@ -21039,7 +21740,7 @@
       <c r="X130" s="11" t="n"/>
       <c r="Y130" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z130" s="10" t="n"/>
@@ -21050,7 +21751,7 @@
       <c r="AE130" s="11" t="n"/>
       <c r="AF130" s="19" t="inlineStr">
         <is>
-          <t>読者情報変更適用日</t>
+          <t>初回購読開始日</t>
         </is>
       </c>
       <c r="AG130" s="10" t="n"/>
@@ -21066,7 +21767,7 @@
       <c r="C131" s="38" t="n"/>
       <c r="D131" s="19" t="inlineStr">
         <is>
-          <t>seikyu_kaishi_month</t>
+          <t>dokusya_kaishi_date</t>
         </is>
       </c>
       <c r="E131" s="10" t="n"/>
@@ -21094,14 +21795,18 @@
       <c r="S131" s="11" t="n"/>
       <c r="T131" s="17" t="inlineStr">
         <is>
-          <t>YYYYMM</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="U131" s="10" t="n"/>
       <c r="V131" s="10" t="n"/>
       <c r="W131" s="10" t="n"/>
       <c r="X131" s="11" t="n"/>
-      <c r="Y131" s="17" t="inlineStr"/>
+      <c r="Y131" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z131" s="10" t="n"/>
       <c r="AA131" s="10" t="n"/>
       <c r="AB131" s="10" t="n"/>
@@ -21110,7 +21815,7 @@
       <c r="AE131" s="11" t="n"/>
       <c r="AF131" s="19" t="inlineStr">
         <is>
-          <t>請求開始月（空文字許容）</t>
+          <t>購読開始日</t>
         </is>
       </c>
       <c r="AG131" s="10" t="n"/>
@@ -21126,7 +21831,7 @@
       <c r="C132" s="38" t="n"/>
       <c r="D132" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>dokusya_chushi_date</t>
         </is>
       </c>
       <c r="E132" s="10" t="n"/>
@@ -21152,12 +21857,20 @@
       </c>
       <c r="R132" s="10" t="n"/>
       <c r="S132" s="11" t="n"/>
-      <c r="T132" s="17" t="inlineStr"/>
+      <c r="T132" s="17" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="U132" s="10" t="n"/>
       <c r="V132" s="10" t="n"/>
       <c r="W132" s="10" t="n"/>
       <c r="X132" s="11" t="n"/>
-      <c r="Y132" s="17" t="inlineStr"/>
+      <c r="Y132" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="Z132" s="10" t="n"/>
       <c r="AA132" s="10" t="n"/>
       <c r="AB132" s="10" t="n"/>
@@ -21166,7 +21879,7 @@
       <c r="AE132" s="11" t="n"/>
       <c r="AF132" s="19" t="inlineStr">
         <is>
-          <t>備考（空文字許容）</t>
+          <t>購読中止日</t>
         </is>
       </c>
       <c r="AG132" s="10" t="n"/>
@@ -21182,7 +21895,7 @@
       <c r="C133" s="38" t="n"/>
       <c r="D133" s="19" t="inlineStr">
         <is>
-          <t>rireki_no</t>
+          <t>joho_henko_tekiyo_date</t>
         </is>
       </c>
       <c r="E133" s="10" t="n"/>
@@ -21195,7 +21908,7 @@
       <c r="L133" s="11" t="n"/>
       <c r="M133" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N133" s="10" t="n"/>
@@ -21208,14 +21921,18 @@
       </c>
       <c r="R133" s="10" t="n"/>
       <c r="S133" s="11" t="n"/>
-      <c r="T133" s="17" t="inlineStr"/>
+      <c r="T133" s="17" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="U133" s="10" t="n"/>
       <c r="V133" s="10" t="n"/>
       <c r="W133" s="10" t="n"/>
       <c r="X133" s="11" t="n"/>
       <c r="Y133" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z133" s="10" t="n"/>
@@ -21226,7 +21943,7 @@
       <c r="AE133" s="11" t="n"/>
       <c r="AF133" s="19" t="inlineStr">
         <is>
-          <t>履歴No</t>
+          <t>読者情報変更適用日</t>
         </is>
       </c>
       <c r="AG133" s="10" t="n"/>
@@ -21242,7 +21959,7 @@
       <c r="C134" s="38" t="n"/>
       <c r="D134" s="19" t="inlineStr">
         <is>
-          <t>denshi_shonin_status</t>
+          <t>seikyu_kaishi_month</t>
         </is>
       </c>
       <c r="E134" s="10" t="n"/>
@@ -21255,7 +21972,7 @@
       <c r="L134" s="11" t="n"/>
       <c r="M134" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N134" s="10" t="n"/>
@@ -21268,16 +21985,16 @@
       </c>
       <c r="R134" s="10" t="n"/>
       <c r="S134" s="11" t="n"/>
-      <c r="T134" s="17" t="inlineStr"/>
+      <c r="T134" s="17" t="inlineStr">
+        <is>
+          <t>YYYYMM</t>
+        </is>
+      </c>
       <c r="U134" s="10" t="n"/>
       <c r="V134" s="10" t="n"/>
       <c r="W134" s="10" t="n"/>
       <c r="X134" s="11" t="n"/>
-      <c r="Y134" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="Y134" s="17" t="inlineStr"/>
       <c r="Z134" s="10" t="n"/>
       <c r="AA134" s="10" t="n"/>
       <c r="AB134" s="10" t="n"/>
@@ -21286,7 +22003,7 @@
       <c r="AE134" s="11" t="n"/>
       <c r="AF134" s="19" t="inlineStr">
         <is>
-          <t>電子申込承認ステータス</t>
+          <t>請求開始月（空文字許容）</t>
         </is>
       </c>
       <c r="AG134" s="10" t="n"/>
@@ -21302,7 +22019,7 @@
       <c r="C135" s="38" t="n"/>
       <c r="D135" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="E135" s="10" t="n"/>
@@ -21328,20 +22045,12 @@
       </c>
       <c r="R135" s="10" t="n"/>
       <c r="S135" s="11" t="n"/>
-      <c r="T135" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T135" s="17" t="inlineStr"/>
       <c r="U135" s="10" t="n"/>
       <c r="V135" s="10" t="n"/>
       <c r="W135" s="10" t="n"/>
       <c r="X135" s="11" t="n"/>
-      <c r="Y135" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y135" s="17" t="inlineStr"/>
       <c r="Z135" s="10" t="n"/>
       <c r="AA135" s="10" t="n"/>
       <c r="AB135" s="10" t="n"/>
@@ -21350,7 +22059,7 @@
       <c r="AE135" s="11" t="n"/>
       <c r="AF135" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>備考（空文字許容）</t>
         </is>
       </c>
       <c r="AG135" s="10" t="n"/>
@@ -21363,10 +22072,10 @@
       <c r="B136" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="C136" s="39" t="n"/>
+      <c r="C136" s="38" t="n"/>
       <c r="D136" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>rireki_no</t>
         </is>
       </c>
       <c r="E136" s="10" t="n"/>
@@ -21379,7 +22088,7 @@
       <c r="L136" s="11" t="n"/>
       <c r="M136" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N136" s="10" t="n"/>
@@ -21392,11 +22101,7 @@
       </c>
       <c r="R136" s="10" t="n"/>
       <c r="S136" s="11" t="n"/>
-      <c r="T136" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T136" s="17" t="inlineStr"/>
       <c r="U136" s="10" t="n"/>
       <c r="V136" s="10" t="n"/>
       <c r="W136" s="10" t="n"/>
@@ -21414,7 +22119,7 @@
       <c r="AE136" s="11" t="n"/>
       <c r="AF136" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>履歴No</t>
         </is>
       </c>
       <c r="AG136" s="10" t="n"/>
@@ -21423,16 +22128,204 @@
       <c r="AJ136" s="10" t="n"/>
       <c r="AK136" s="11" t="n"/>
     </row>
-    <row r="137" ht="19.5" customHeight="1"/>
-    <row r="138" ht="19.5" customHeight="1">
-      <c r="B138" s="40" t="inlineStr">
+    <row r="137" ht="18" customHeight="1">
+      <c r="B137" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="C137" s="38" t="n"/>
+      <c r="D137" s="19" t="inlineStr">
+        <is>
+          <t>denshi_shonin_status</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="n"/>
+      <c r="F137" s="10" t="n"/>
+      <c r="G137" s="10" t="n"/>
+      <c r="H137" s="10" t="n"/>
+      <c r="I137" s="10" t="n"/>
+      <c r="J137" s="10" t="n"/>
+      <c r="K137" s="10" t="n"/>
+      <c r="L137" s="11" t="n"/>
+      <c r="M137" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N137" s="10" t="n"/>
+      <c r="O137" s="10" t="n"/>
+      <c r="P137" s="11" t="n"/>
+      <c r="Q137" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R137" s="10" t="n"/>
+      <c r="S137" s="11" t="n"/>
+      <c r="T137" s="17" t="inlineStr"/>
+      <c r="U137" s="10" t="n"/>
+      <c r="V137" s="10" t="n"/>
+      <c r="W137" s="10" t="n"/>
+      <c r="X137" s="11" t="n"/>
+      <c r="Y137" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z137" s="10" t="n"/>
+      <c r="AA137" s="10" t="n"/>
+      <c r="AB137" s="10" t="n"/>
+      <c r="AC137" s="10" t="n"/>
+      <c r="AD137" s="10" t="n"/>
+      <c r="AE137" s="11" t="n"/>
+      <c r="AF137" s="19" t="inlineStr">
+        <is>
+          <t>電子申込承認ステータス</t>
+        </is>
+      </c>
+      <c r="AG137" s="10" t="n"/>
+      <c r="AH137" s="10" t="n"/>
+      <c r="AI137" s="10" t="n"/>
+      <c r="AJ137" s="10" t="n"/>
+      <c r="AK137" s="11" t="n"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="B138" s="31" t="n">
+        <v>61</v>
+      </c>
+      <c r="C138" s="38" t="n"/>
+      <c r="D138" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="n"/>
+      <c r="F138" s="10" t="n"/>
+      <c r="G138" s="10" t="n"/>
+      <c r="H138" s="10" t="n"/>
+      <c r="I138" s="10" t="n"/>
+      <c r="J138" s="10" t="n"/>
+      <c r="K138" s="10" t="n"/>
+      <c r="L138" s="11" t="n"/>
+      <c r="M138" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N138" s="10" t="n"/>
+      <c r="O138" s="10" t="n"/>
+      <c r="P138" s="11" t="n"/>
+      <c r="Q138" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R138" s="10" t="n"/>
+      <c r="S138" s="11" t="n"/>
+      <c r="T138" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U138" s="10" t="n"/>
+      <c r="V138" s="10" t="n"/>
+      <c r="W138" s="10" t="n"/>
+      <c r="X138" s="11" t="n"/>
+      <c r="Y138" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z138" s="10" t="n"/>
+      <c r="AA138" s="10" t="n"/>
+      <c r="AB138" s="10" t="n"/>
+      <c r="AC138" s="10" t="n"/>
+      <c r="AD138" s="10" t="n"/>
+      <c r="AE138" s="11" t="n"/>
+      <c r="AF138" s="19" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="AG138" s="10" t="n"/>
+      <c r="AH138" s="10" t="n"/>
+      <c r="AI138" s="10" t="n"/>
+      <c r="AJ138" s="10" t="n"/>
+      <c r="AK138" s="11" t="n"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="B139" s="31" t="n">
+        <v>62</v>
+      </c>
+      <c r="C139" s="39" t="n"/>
+      <c r="D139" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E139" s="10" t="n"/>
+      <c r="F139" s="10" t="n"/>
+      <c r="G139" s="10" t="n"/>
+      <c r="H139" s="10" t="n"/>
+      <c r="I139" s="10" t="n"/>
+      <c r="J139" s="10" t="n"/>
+      <c r="K139" s="10" t="n"/>
+      <c r="L139" s="11" t="n"/>
+      <c r="M139" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N139" s="10" t="n"/>
+      <c r="O139" s="10" t="n"/>
+      <c r="P139" s="11" t="n"/>
+      <c r="Q139" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R139" s="10" t="n"/>
+      <c r="S139" s="11" t="n"/>
+      <c r="T139" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U139" s="10" t="n"/>
+      <c r="V139" s="10" t="n"/>
+      <c r="W139" s="10" t="n"/>
+      <c r="X139" s="11" t="n"/>
+      <c r="Y139" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z139" s="10" t="n"/>
+      <c r="AA139" s="10" t="n"/>
+      <c r="AB139" s="10" t="n"/>
+      <c r="AC139" s="10" t="n"/>
+      <c r="AD139" s="10" t="n"/>
+      <c r="AE139" s="11" t="n"/>
+      <c r="AF139" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG139" s="10" t="n"/>
+      <c r="AH139" s="10" t="n"/>
+      <c r="AI139" s="10" t="n"/>
+      <c r="AJ139" s="10" t="n"/>
+      <c r="AK139" s="11" t="n"/>
+    </row>
+    <row r="140" ht="19.5" customHeight="1"/>
+    <row r="141" ht="19.5" customHeight="1">
+      <c r="B141" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="409" customHeight="1">
-      <c r="C139" s="19" t="inlineStr">
+    <row r="142" ht="409" customHeight="1">
+      <c r="C142" s="19" t="inlineStr">
         <is>
           <t>POST /api/v1/dokusya
 Content-Type: application/json
@@ -21475,63 +22368,63 @@
   "yubin_kubun": "0",
   "shiharai_hoho": 1,
   "dokusyaryo_shiharai_cycle": 1,
-  "bank_branch_code": "001",
-  "bank_branch_name": "本店",
+  "bank_shiten_id": 50,
   "hikiotoshi_yokin_shubetsu": 1,
   "hikiotoshi_koza_no": "1234567",
   "hikiotoshi_koza_meigi": "ヤマダタロウ",
   "dokusyaso_bunrui": "農業者",
   "nogyosya_bunrui": "水稲,野菜",
   "dokusya_kaishi_date": "2026-04-01",
+  "joho_henko_tekiyo_date": null,
   "seikyu_kaishi_month": "",
   "biko": ""
 }</t>
         </is>
       </c>
-      <c r="D139" s="10" t="n"/>
-      <c r="E139" s="10" t="n"/>
-      <c r="F139" s="10" t="n"/>
-      <c r="G139" s="10" t="n"/>
-      <c r="H139" s="10" t="n"/>
-      <c r="I139" s="10" t="n"/>
-      <c r="J139" s="10" t="n"/>
-      <c r="K139" s="10" t="n"/>
-      <c r="L139" s="10" t="n"/>
-      <c r="M139" s="10" t="n"/>
-      <c r="N139" s="10" t="n"/>
-      <c r="O139" s="10" t="n"/>
-      <c r="P139" s="10" t="n"/>
-      <c r="Q139" s="10" t="n"/>
-      <c r="R139" s="10" t="n"/>
-      <c r="S139" s="10" t="n"/>
-      <c r="T139" s="10" t="n"/>
-      <c r="U139" s="10" t="n"/>
-      <c r="V139" s="10" t="n"/>
-      <c r="W139" s="10" t="n"/>
-      <c r="X139" s="10" t="n"/>
-      <c r="Y139" s="10" t="n"/>
-      <c r="Z139" s="10" t="n"/>
-      <c r="AA139" s="10" t="n"/>
-      <c r="AB139" s="10" t="n"/>
-      <c r="AC139" s="10" t="n"/>
-      <c r="AD139" s="10" t="n"/>
-      <c r="AE139" s="10" t="n"/>
-      <c r="AF139" s="10" t="n"/>
-      <c r="AG139" s="10" t="n"/>
-      <c r="AH139" s="10" t="n"/>
-      <c r="AI139" s="10" t="n"/>
-      <c r="AJ139" s="10" t="n"/>
-      <c r="AK139" s="11" t="n"/>
-    </row>
-    <row r="141" ht="19.5" customHeight="1">
-      <c r="B141" s="40" t="inlineStr">
+      <c r="D142" s="10" t="n"/>
+      <c r="E142" s="10" t="n"/>
+      <c r="F142" s="10" t="n"/>
+      <c r="G142" s="10" t="n"/>
+      <c r="H142" s="10" t="n"/>
+      <c r="I142" s="10" t="n"/>
+      <c r="J142" s="10" t="n"/>
+      <c r="K142" s="10" t="n"/>
+      <c r="L142" s="10" t="n"/>
+      <c r="M142" s="10" t="n"/>
+      <c r="N142" s="10" t="n"/>
+      <c r="O142" s="10" t="n"/>
+      <c r="P142" s="10" t="n"/>
+      <c r="Q142" s="10" t="n"/>
+      <c r="R142" s="10" t="n"/>
+      <c r="S142" s="10" t="n"/>
+      <c r="T142" s="10" t="n"/>
+      <c r="U142" s="10" t="n"/>
+      <c r="V142" s="10" t="n"/>
+      <c r="W142" s="10" t="n"/>
+      <c r="X142" s="10" t="n"/>
+      <c r="Y142" s="10" t="n"/>
+      <c r="Z142" s="10" t="n"/>
+      <c r="AA142" s="10" t="n"/>
+      <c r="AB142" s="10" t="n"/>
+      <c r="AC142" s="10" t="n"/>
+      <c r="AD142" s="10" t="n"/>
+      <c r="AE142" s="10" t="n"/>
+      <c r="AF142" s="10" t="n"/>
+      <c r="AG142" s="10" t="n"/>
+      <c r="AH142" s="10" t="n"/>
+      <c r="AI142" s="10" t="n"/>
+      <c r="AJ142" s="10" t="n"/>
+      <c r="AK142" s="11" t="n"/>
+    </row>
+    <row r="144" ht="19.5" customHeight="1">
+      <c r="B144" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="409" customHeight="1">
-      <c r="C142" s="19" t="inlineStr">
+    <row r="145" ht="409" customHeight="1">
+      <c r="C145" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -21576,6 +22469,9 @@
     "yubin_kubun": "0",
     "shiharai_hoho": 1,
     "dokusyaryo_shiharai_cycle": 1,
+    "bank_shiten_id": 50,
+    "jastem_toriatsukai_tenpo_code": "001",
+    "jastem_tenpo_name": "本店",
     "bank_branch_code": "001",
     "bank_branch_name": "本店",
     "hikiotoshi_yokin_shubetsu": 1,
@@ -21594,61 +22490,6 @@
     "created_at": "2026-05-07T10:00:00+09:00",
     "updated_at": "2026-05-07T10:00:00+09:00"
   }
-}</t>
-        </is>
-      </c>
-      <c r="D142" s="10" t="n"/>
-      <c r="E142" s="10" t="n"/>
-      <c r="F142" s="10" t="n"/>
-      <c r="G142" s="10" t="n"/>
-      <c r="H142" s="10" t="n"/>
-      <c r="I142" s="10" t="n"/>
-      <c r="J142" s="10" t="n"/>
-      <c r="K142" s="10" t="n"/>
-      <c r="L142" s="10" t="n"/>
-      <c r="M142" s="10" t="n"/>
-      <c r="N142" s="10" t="n"/>
-      <c r="O142" s="10" t="n"/>
-      <c r="P142" s="10" t="n"/>
-      <c r="Q142" s="10" t="n"/>
-      <c r="R142" s="10" t="n"/>
-      <c r="S142" s="10" t="n"/>
-      <c r="T142" s="10" t="n"/>
-      <c r="U142" s="10" t="n"/>
-      <c r="V142" s="10" t="n"/>
-      <c r="W142" s="10" t="n"/>
-      <c r="X142" s="10" t="n"/>
-      <c r="Y142" s="10" t="n"/>
-      <c r="Z142" s="10" t="n"/>
-      <c r="AA142" s="10" t="n"/>
-      <c r="AB142" s="10" t="n"/>
-      <c r="AC142" s="10" t="n"/>
-      <c r="AD142" s="10" t="n"/>
-      <c r="AE142" s="10" t="n"/>
-      <c r="AF142" s="10" t="n"/>
-      <c r="AG142" s="10" t="n"/>
-      <c r="AH142" s="10" t="n"/>
-      <c r="AI142" s="10" t="n"/>
-      <c r="AJ142" s="10" t="n"/>
-      <c r="AK142" s="11" t="n"/>
-    </row>
-    <row r="144" ht="19.5" customHeight="1">
-      <c r="B144" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 400 Bad Request（バリデーションエラー））</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="144" customHeight="1">
-      <c r="C145" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "error_code": "VALIDATION_ERROR",
-  "message": "入力値が不正です。詳細はerrorsフィールドを確認してください。",
-  "errors": [
-    { "field": "shimei_sei", "message": "必須項目です。" },
-    { "field": "yubin_no", "message": "郵便番号は7桁で入力してください。" }
-  ]
 }</t>
         </is>
       </c>
@@ -21690,16 +22531,20 @@
     <row r="147" ht="19.5" customHeight="1">
       <c r="B147" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 400 Bad Request（メールアドレス重複））</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="72" customHeight="1">
+          <t>レスポンス（失敗 400 Bad Request（バリデーションエラー））</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="144" customHeight="1">
       <c r="C148" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "DUPLICATE_EMAIL",
-  "message": "このメールアドレスは既に登録されています。"
+  "error_code": "VALIDATION_ERROR",
+  "message": "入力値が不正です。詳細はerrorsフィールドを確認してください。",
+  "errors": [
+    { "field": "shimei_sei", "message": "必須項目です。" },
+    { "field": "yubin_no", "message": "郵便番号は7桁で入力してください。" }
+  ]
 }</t>
         </is>
       </c>
@@ -21741,7 +22586,7 @@
     <row r="150" ht="19.5" customHeight="1">
       <c r="B150" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 401 Unauthorized）</t>
+          <t>レスポンス（失敗 400 Bad Request（メールアドレス重複））</t>
         </is>
       </c>
     </row>
@@ -21749,8 +22594,8 @@
       <c r="C151" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください。"
+  "error_code": "DUPLICATE_EMAIL",
+  "message": "このメールアドレスは既に登録されています。"
 }</t>
         </is>
       </c>
@@ -21792,7 +22637,7 @@
     <row r="153" ht="19.5" customHeight="1">
       <c r="B153" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
+          <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
@@ -21800,8 +22645,8 @@
       <c r="C154" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません。"
+  "error_code": "UNAUTHORIZED",
+  "message": "セッションが切れました。再度ログインしてください。"
 }</t>
         </is>
       </c>
@@ -21843,7 +22688,7 @@
     <row r="156" ht="19.5" customHeight="1">
       <c r="B156" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
+          <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
@@ -21851,8 +22696,8 @@
       <c r="C157" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください。"
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません。"
 }</t>
         </is>
       </c>
@@ -21891,242 +22736,328 @@
       <c r="AJ157" s="10" t="n"/>
       <c r="AK157" s="11" t="n"/>
     </row>
-    <row r="159" ht="19.5" customHeight="1"/>
-    <row r="160" ht="19.5" customHeight="1">
-      <c r="A160" s="27" t="inlineStr">
+    <row r="159" ht="19.5" customHeight="1">
+      <c r="B159" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="72" customHeight="1">
+      <c r="C160" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください。"
+}</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="n"/>
+      <c r="E160" s="10" t="n"/>
+      <c r="F160" s="10" t="n"/>
+      <c r="G160" s="10" t="n"/>
+      <c r="H160" s="10" t="n"/>
+      <c r="I160" s="10" t="n"/>
+      <c r="J160" s="10" t="n"/>
+      <c r="K160" s="10" t="n"/>
+      <c r="L160" s="10" t="n"/>
+      <c r="M160" s="10" t="n"/>
+      <c r="N160" s="10" t="n"/>
+      <c r="O160" s="10" t="n"/>
+      <c r="P160" s="10" t="n"/>
+      <c r="Q160" s="10" t="n"/>
+      <c r="R160" s="10" t="n"/>
+      <c r="S160" s="10" t="n"/>
+      <c r="T160" s="10" t="n"/>
+      <c r="U160" s="10" t="n"/>
+      <c r="V160" s="10" t="n"/>
+      <c r="W160" s="10" t="n"/>
+      <c r="X160" s="10" t="n"/>
+      <c r="Y160" s="10" t="n"/>
+      <c r="Z160" s="10" t="n"/>
+      <c r="AA160" s="10" t="n"/>
+      <c r="AB160" s="10" t="n"/>
+      <c r="AC160" s="10" t="n"/>
+      <c r="AD160" s="10" t="n"/>
+      <c r="AE160" s="10" t="n"/>
+      <c r="AF160" s="10" t="n"/>
+      <c r="AG160" s="10" t="n"/>
+      <c r="AH160" s="10" t="n"/>
+      <c r="AI160" s="10" t="n"/>
+      <c r="AJ160" s="10" t="n"/>
+      <c r="AK160" s="11" t="n"/>
+    </row>
+    <row r="162" ht="19.5" customHeight="1"/>
+    <row r="163" ht="19.5" customHeight="1">
+      <c r="A163" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="54" customHeight="1">
-      <c r="B161" s="42" t="inlineStr">
+    <row r="164" ht="54" customHeight="1">
+      <c r="B164" s="42" t="inlineStr">
         <is>
           <t>※ 4.4 データ登録 と 4.5 操作ログ記録 は単一トランザクション内で実行する。
 いずれかが失敗した場合は全てロールバックすること。
 例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
         </is>
       </c>
-      <c r="C161" s="10" t="n"/>
-      <c r="D161" s="10" t="n"/>
-      <c r="E161" s="10" t="n"/>
-      <c r="F161" s="10" t="n"/>
-      <c r="G161" s="10" t="n"/>
-      <c r="H161" s="10" t="n"/>
-      <c r="I161" s="10" t="n"/>
-      <c r="J161" s="10" t="n"/>
-      <c r="K161" s="10" t="n"/>
-      <c r="L161" s="10" t="n"/>
-      <c r="M161" s="10" t="n"/>
-      <c r="N161" s="10" t="n"/>
-      <c r="O161" s="10" t="n"/>
-      <c r="P161" s="10" t="n"/>
-      <c r="Q161" s="10" t="n"/>
-      <c r="R161" s="10" t="n"/>
-      <c r="S161" s="10" t="n"/>
-      <c r="T161" s="10" t="n"/>
-      <c r="U161" s="10" t="n"/>
-      <c r="V161" s="10" t="n"/>
-      <c r="W161" s="10" t="n"/>
-      <c r="X161" s="10" t="n"/>
-      <c r="Y161" s="10" t="n"/>
-      <c r="Z161" s="10" t="n"/>
-      <c r="AA161" s="10" t="n"/>
-      <c r="AB161" s="10" t="n"/>
-      <c r="AC161" s="10" t="n"/>
-      <c r="AD161" s="10" t="n"/>
-      <c r="AE161" s="10" t="n"/>
-      <c r="AF161" s="10" t="n"/>
-      <c r="AG161" s="10" t="n"/>
-      <c r="AH161" s="10" t="n"/>
-      <c r="AI161" s="10" t="n"/>
-      <c r="AJ161" s="10" t="n"/>
-      <c r="AK161" s="11" t="n"/>
-    </row>
-    <row r="162" ht="18" customHeight="1">
-      <c r="B162" s="27" t="inlineStr">
+      <c r="C164" s="10" t="n"/>
+      <c r="D164" s="10" t="n"/>
+      <c r="E164" s="10" t="n"/>
+      <c r="F164" s="10" t="n"/>
+      <c r="G164" s="10" t="n"/>
+      <c r="H164" s="10" t="n"/>
+      <c r="I164" s="10" t="n"/>
+      <c r="J164" s="10" t="n"/>
+      <c r="K164" s="10" t="n"/>
+      <c r="L164" s="10" t="n"/>
+      <c r="M164" s="10" t="n"/>
+      <c r="N164" s="10" t="n"/>
+      <c r="O164" s="10" t="n"/>
+      <c r="P164" s="10" t="n"/>
+      <c r="Q164" s="10" t="n"/>
+      <c r="R164" s="10" t="n"/>
+      <c r="S164" s="10" t="n"/>
+      <c r="T164" s="10" t="n"/>
+      <c r="U164" s="10" t="n"/>
+      <c r="V164" s="10" t="n"/>
+      <c r="W164" s="10" t="n"/>
+      <c r="X164" s="10" t="n"/>
+      <c r="Y164" s="10" t="n"/>
+      <c r="Z164" s="10" t="n"/>
+      <c r="AA164" s="10" t="n"/>
+      <c r="AB164" s="10" t="n"/>
+      <c r="AC164" s="10" t="n"/>
+      <c r="AD164" s="10" t="n"/>
+      <c r="AE164" s="10" t="n"/>
+      <c r="AF164" s="10" t="n"/>
+      <c r="AG164" s="10" t="n"/>
+      <c r="AH164" s="10" t="n"/>
+      <c r="AI164" s="10" t="n"/>
+      <c r="AJ164" s="10" t="n"/>
+      <c r="AK164" s="11" t="n"/>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="B165" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="18" customHeight="1">
-      <c r="C163" s="41" t="inlineStr">
+    <row r="166" ht="18" customHeight="1">
+      <c r="C166" s="41" t="inlineStr">
         <is>
           <t>リクエストボディの検証：</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="18" customHeight="1">
-      <c r="D164" s="41" t="inlineStr">
-        <is>
-          <t>shimei_sei / shimei_mei：必須、最大50文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="36" customHeight="1">
-      <c r="D165" s="41" t="inlineStr">
-        <is>
-          <t>shimei_kana_sei / shimei_kana_mei：必須、最大100文字、ひらがな/カタカナ形式</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="18" customHeight="1">
-      <c r="D166" s="41" t="inlineStr">
-        <is>
-          <t>dokusya_busu：必須、半角数字。解約時は0</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="18" customHeight="1">
+    <row r="167" ht="108" customHeight="1">
       <c r="D167" s="41" t="inlineStr">
         <is>
-          <t>yubin_no：必須、半角数字7桁</t>
+          <t>dokusya_shubetsu：必須。**3:併読（紙版＋電子版）は新規登録不可**（顧客要件）。併読データは外部の電子版読者管理システムがバッチ連携で管理するため、本システムでは作成・編集・停止・削除いずれも不可。作成は `VALIDATION_ERROR`（field=`dokusya_shubetsu`、メッセージ「併読（紙版＋電子版）はバッチ連携で管理されるため、新規登録できません。」）、編集/停止/削除は `DOKUSYA_READ_ONLY`（403）、Excel取込は取込不可。FEは新規作成モードで併読ラジオを非活性化。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="D168" s="41" t="inlineStr">
         <is>
-          <t>todofuken_code / shikuchoson / chome_banchi：必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="18" customHeight="1">
+          <t>shimei_sei / shimei_mei：必須、最大50文字</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="36" customHeight="1">
       <c r="D169" s="41" t="inlineStr">
         <is>
-          <t>renrakusaki_1：必須、半角数字</t>
+          <t>shimei_kana_sei / shimei_kana_mei：必須、最大100文字、ひらがな/カタカナ形式</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="D170" s="41" t="inlineStr">
         <is>
-          <t>email：電子版/併読の場合は必須、形式チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="72" customHeight="1">
+          <t>dokusya_busu：必須、半角数字。解約時は0</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
       <c r="D171" s="41" t="inlineStr">
         <is>
-          <t>haitatsu_same_flg=falseの場合：haitatsu_yubin_no, haitatsu_todofuken_code, haitatsu_shikuchoson, haitatsu_chome_banchi, haitatsu_shimei_*, haitatsu_shimei_kana_* が必須</t>
+          <t>yubin_no：必須、半角数字7桁</t>
         </is>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="D172" s="41" t="inlineStr">
         <is>
-          <t>hanbaiten_id / tanka_id：必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="54" customHeight="1">
+          <t>todofuken_code / shikuchoson / chome_banchi：必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
       <c r="D173" s="41" t="inlineStr">
         <is>
-          <t>shiharai_hoho：必須。1（口座引落）の場合：bank_branch_code, hikiotoshi_yokin_shubetsu, hikiotoshi_koza_no, hikiotoshi_koza_meigi が必須</t>
+          <t>renrakusaki_1：必須、半角数字</t>
         </is>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="D174" s="41" t="inlineStr">
         <is>
-          <t>dokusya_kaishi_date：必須、YYYY-MM-DD</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="18" customHeight="1">
+          <t>email：電子版/併読の場合は必須、形式チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="72" customHeight="1">
       <c r="D175" s="41" t="inlineStr">
         <is>
-          <t>seikyu_kaishi_month：電子版/併読の場合、YYYYMM形式</t>
+          <t>haitatsu_same_flg=falseの場合：haitatsu_yubin_no, haitatsu_todofuken_code, haitatsu_shikuchoson, haitatsu_chome_banchi, haitatsu_shimei_*, haitatsu_shimei_kana_* が必須</t>
         </is>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="D176" s="41" t="inlineStr">
         <is>
+          <t>hanbaiten_id / tanka_id：必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="54" customHeight="1">
+      <c r="D177" s="41" t="inlineStr">
+        <is>
+          <t>shiharai_hoho：必須。1（口座引落）の場合：bank_shiten_id, hikiotoshi_yokin_shubetsu, hikiotoshi_koza_no, hikiotoshi_koza_meigi が必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="72" customHeight="1">
+      <c r="D178" s="41" t="inlineStr">
+        <is>
+          <t>bank_shiten_id：口座引落時は必須、他の支払方法では任意。指定された場合は `m_shiten` に存在し、かつ ログインユーザー所属JA内（`m_shiten.ja_id = user.ja_id`）かつ `kinyu_shiten_flg = TRUE` であること（不正値は支払方法を問わず VALIDATION_ERROR）</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="36" customHeight="1">
+      <c r="D179" s="41" t="inlineStr">
+        <is>
+          <t>yubin_kubun：任意。入力時は `m_code.code_category='YUBIN_KUBUN'`（0:空, 1:郵送）に存在する値であること</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="D180" s="41" t="inlineStr">
+        <is>
+          <t>dokusya_kaishi_date：必須、YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="D181" s="41" t="inlineStr">
+        <is>
+          <t>joho_henko_tekiyo_date：任意、YYYY-MM-DD。入力時は未来日であること</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="D182" s="41" t="inlineStr">
+        <is>
+          <t>nogyosya_bunrui：購読者層分類で「農業者」を選択した場合は必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="D183" s="41" t="inlineStr">
+        <is>
+          <t>seikyu_kaishi_month：電子版/併読の場合、YYYYMM形式</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="D184" s="41" t="inlineStr">
+        <is>
           <t>biko：500文字以内</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="36" customHeight="1">
-      <c r="C177" s="41" t="inlineStr">
-        <is>
-          <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="18" customHeight="1">
-      <c r="B178" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="C179" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="18" customHeight="1">
-      <c r="C180" s="41" t="inlineStr">
-        <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="18" customHeight="1">
-      <c r="C181" s="41" t="inlineStr">
-        <is>
-          <t>必要権限: `dokusya.create`</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="36" customHeight="1">
-      <c r="C182" s="41" t="inlineStr">
-        <is>
-          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="18" customHeight="1">
-      <c r="C183" s="41" t="inlineStr">
-        <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="36" customHeight="1">
-      <c r="C184" s="41" t="inlineStr">
-        <is>
-          <t>DataScope: `ja_id = user.ja_id`（サーバ側で自動設定。リクエストボディの ja_id は信頼しない）</t>
         </is>
       </c>
     </row>
     <row r="185" ht="36" customHeight="1">
       <c r="C185" s="41" t="inlineStr">
         <is>
-          <t>DataScope違反（他JAのレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+          <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="B186" s="27" t="inlineStr">
         <is>
-          <t>4.3 重複チェック（メールアドレス）</t>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="C187" s="41" t="inlineStr">
         <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="C188" s="41" t="inlineStr">
+        <is>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="C189" s="41" t="inlineStr">
+        <is>
+          <t>必要権限: `dokusya.create`</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="36" customHeight="1">
+      <c r="C190" s="41" t="inlineStr">
+        <is>
+          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="18" customHeight="1">
+      <c r="C191" s="41" t="inlineStr">
+        <is>
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="36" customHeight="1">
+      <c r="C192" s="41" t="inlineStr">
+        <is>
+          <t>DataScope: `ja_id = user.ja_id`（サーバ側で自動設定。リクエストボディの ja_id は信頼しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="36" customHeight="1">
+      <c r="C193" s="41" t="inlineStr">
+        <is>
+          <t>DataScope違反（他JAのレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="B194" s="27" t="inlineStr">
+        <is>
+          <t>4.3 重複チェック（メールアドレス）</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="C195" s="41" t="inlineStr">
+        <is>
           <t>メールアドレスが入力されている場合、以下の条件で重複を確認する。</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="90" customHeight="1">
-      <c r="C188" s="42" t="inlineStr">
+    <row r="196" ht="90" customHeight="1">
+      <c r="C196" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) FROM t_dokusya
 WHERE email = :email
@@ -22135,113 +23066,203 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D188" s="10" t="n"/>
-      <c r="E188" s="10" t="n"/>
-      <c r="F188" s="10" t="n"/>
-      <c r="G188" s="10" t="n"/>
-      <c r="H188" s="10" t="n"/>
-      <c r="I188" s="10" t="n"/>
-      <c r="J188" s="10" t="n"/>
-      <c r="K188" s="10" t="n"/>
-      <c r="L188" s="10" t="n"/>
-      <c r="M188" s="10" t="n"/>
-      <c r="N188" s="10" t="n"/>
-      <c r="O188" s="10" t="n"/>
-      <c r="P188" s="10" t="n"/>
-      <c r="Q188" s="10" t="n"/>
-      <c r="R188" s="10" t="n"/>
-      <c r="S188" s="10" t="n"/>
-      <c r="T188" s="10" t="n"/>
-      <c r="U188" s="10" t="n"/>
-      <c r="V188" s="10" t="n"/>
-      <c r="W188" s="10" t="n"/>
-      <c r="X188" s="10" t="n"/>
-      <c r="Y188" s="10" t="n"/>
-      <c r="Z188" s="10" t="n"/>
-      <c r="AA188" s="10" t="n"/>
-      <c r="AB188" s="10" t="n"/>
-      <c r="AC188" s="10" t="n"/>
-      <c r="AD188" s="10" t="n"/>
-      <c r="AE188" s="10" t="n"/>
-      <c r="AF188" s="10" t="n"/>
-      <c r="AG188" s="10" t="n"/>
-      <c r="AH188" s="10" t="n"/>
-      <c r="AI188" s="10" t="n"/>
-      <c r="AJ188" s="10" t="n"/>
-      <c r="AK188" s="11" t="n"/>
-    </row>
-    <row r="189" ht="18" customHeight="1">
-      <c r="C189" s="41" t="inlineStr">
+      <c r="D196" s="10" t="n"/>
+      <c r="E196" s="10" t="n"/>
+      <c r="F196" s="10" t="n"/>
+      <c r="G196" s="10" t="n"/>
+      <c r="H196" s="10" t="n"/>
+      <c r="I196" s="10" t="n"/>
+      <c r="J196" s="10" t="n"/>
+      <c r="K196" s="10" t="n"/>
+      <c r="L196" s="10" t="n"/>
+      <c r="M196" s="10" t="n"/>
+      <c r="N196" s="10" t="n"/>
+      <c r="O196" s="10" t="n"/>
+      <c r="P196" s="10" t="n"/>
+      <c r="Q196" s="10" t="n"/>
+      <c r="R196" s="10" t="n"/>
+      <c r="S196" s="10" t="n"/>
+      <c r="T196" s="10" t="n"/>
+      <c r="U196" s="10" t="n"/>
+      <c r="V196" s="10" t="n"/>
+      <c r="W196" s="10" t="n"/>
+      <c r="X196" s="10" t="n"/>
+      <c r="Y196" s="10" t="n"/>
+      <c r="Z196" s="10" t="n"/>
+      <c r="AA196" s="10" t="n"/>
+      <c r="AB196" s="10" t="n"/>
+      <c r="AC196" s="10" t="n"/>
+      <c r="AD196" s="10" t="n"/>
+      <c r="AE196" s="10" t="n"/>
+      <c r="AF196" s="10" t="n"/>
+      <c r="AG196" s="10" t="n"/>
+      <c r="AH196" s="10" t="n"/>
+      <c r="AI196" s="10" t="n"/>
+      <c r="AJ196" s="10" t="n"/>
+      <c r="AK196" s="11" t="n"/>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="C197" s="41" t="inlineStr">
         <is>
           <t>重複がある場合：HTTP 400 (`DUPLICATE_EMAIL`)</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="18" customHeight="1">
-      <c r="B190" s="27" t="inlineStr">
+    <row r="198" ht="18" customHeight="1">
+      <c r="B198" s="27" t="inlineStr">
         <is>
           <t>4.4 データ登録</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="18" customHeight="1">
-      <c r="C191" s="41" t="inlineStr">
+    <row r="199" ht="18" customHeight="1">
+      <c r="C199" s="41" t="inlineStr">
+        <is>
+          <t>`denshi_shonin_status`（電子申込承認ステータス）の初期値:</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="D200" s="41" t="inlineStr">
+        <is>
+          <t>紙版（dokusya_shubetsu=1）: `NULL`（承認ワークフロー対象外）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="D201" s="41" t="inlineStr">
+        <is>
+          <t>電子版（2）/ 併読（3）: `1`（承認済）。画面からの新規登録は職員操作のため</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="72" customHeight="1">
+      <c r="C202" s="41" t="inlineStr">
+        <is>
+          <t>支払方法=1（口座引落）の場合、`bank_shiten_id` を以下のSQLで解決し、`jastem_toriatsukai_tenpo_code` および `jastem_tenpo_name` を取得して `t_dokusya.bank_branch_code` / `bank_branch_name` に非正規化保存する（画面設計書 機能定義 §10.1）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="144" customHeight="1">
+      <c r="C203" s="42" t="inlineStr">
+        <is>
+          <t>SELECT shiten_id,
+       jastem_toriatsukai_tenpo_code,
+       jastem_tenpo_name
+FROM m_shiten
+WHERE shiten_id = :bank_shiten_id
+  AND ja_id = :ja_id
+  AND kinyu_shiten_flg = TRUE
+  AND deleted_at IS NULL</t>
+        </is>
+      </c>
+      <c r="D203" s="10" t="n"/>
+      <c r="E203" s="10" t="n"/>
+      <c r="F203" s="10" t="n"/>
+      <c r="G203" s="10" t="n"/>
+      <c r="H203" s="10" t="n"/>
+      <c r="I203" s="10" t="n"/>
+      <c r="J203" s="10" t="n"/>
+      <c r="K203" s="10" t="n"/>
+      <c r="L203" s="10" t="n"/>
+      <c r="M203" s="10" t="n"/>
+      <c r="N203" s="10" t="n"/>
+      <c r="O203" s="10" t="n"/>
+      <c r="P203" s="10" t="n"/>
+      <c r="Q203" s="10" t="n"/>
+      <c r="R203" s="10" t="n"/>
+      <c r="S203" s="10" t="n"/>
+      <c r="T203" s="10" t="n"/>
+      <c r="U203" s="10" t="n"/>
+      <c r="V203" s="10" t="n"/>
+      <c r="W203" s="10" t="n"/>
+      <c r="X203" s="10" t="n"/>
+      <c r="Y203" s="10" t="n"/>
+      <c r="Z203" s="10" t="n"/>
+      <c r="AA203" s="10" t="n"/>
+      <c r="AB203" s="10" t="n"/>
+      <c r="AC203" s="10" t="n"/>
+      <c r="AD203" s="10" t="n"/>
+      <c r="AE203" s="10" t="n"/>
+      <c r="AF203" s="10" t="n"/>
+      <c r="AG203" s="10" t="n"/>
+      <c r="AH203" s="10" t="n"/>
+      <c r="AI203" s="10" t="n"/>
+      <c r="AJ203" s="10" t="n"/>
+      <c r="AK203" s="11" t="n"/>
+    </row>
+    <row r="204" ht="36" customHeight="1">
+      <c r="C204" s="41" t="inlineStr">
+        <is>
+          <t>該当レコードがない場合：HTTP 400 (`VALIDATION_ERROR`)（`field: 'bank_shiten_id'`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="36" customHeight="1">
+      <c r="C205" s="41" t="inlineStr">
+        <is>
+          <t>支払方法 ≠ 1 の場合、`bank_branch_code = ''` / `bank_branch_name = ''` を設定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="C206" s="41" t="inlineStr">
         <is>
           <t>t_dokusya にレコードを INSERT する。</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="36" customHeight="1">
-      <c r="C192" s="41" t="inlineStr">
+    <row r="207" ht="36" customHeight="1">
+      <c r="C207" s="41" t="inlineStr">
         <is>
           <t>t_dokusya_rireki に履歴レコードを INSERT する（rireki_no=1, saishin_data_flg=true）。</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="18" customHeight="1">
-      <c r="C193" s="41" t="inlineStr">
+    <row r="208" ht="18" customHeight="1">
+      <c r="C208" s="41" t="inlineStr">
         <is>
           <t>フラグ設定ルール：</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="18" customHeight="1">
-      <c r="D194" s="41" t="inlineStr">
+    <row r="209" ht="18" customHeight="1">
+      <c r="D209" s="41" t="inlineStr">
         <is>
           <t>saishin_data_flg = true</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="18" customHeight="1">
-      <c r="D195" s="41" t="inlineStr">
+    <row r="210" ht="18" customHeight="1">
+      <c r="D210" s="41" t="inlineStr">
         <is>
           <t>shinki_flg = (tetsuzuki_shurui=1) ? true : false</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="18" customHeight="1">
-      <c r="D196" s="41" t="inlineStr">
+    <row r="211" ht="18" customHeight="1">
+      <c r="D211" s="41" t="inlineStr">
         <is>
           <t>kaiyaku_flg = (tetsuzuki_shurui=0) ? true : false</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="18" customHeight="1">
-      <c r="D197" s="41" t="inlineStr">
+    <row r="212" ht="18" customHeight="1">
+      <c r="D212" s="41" t="inlineStr">
         <is>
           <t>zougen_hokoku_flg = true（新規登録は増減対象）</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="18" customHeight="1">
-      <c r="C198" s="41" t="inlineStr">
+    <row r="213" ht="18" customHeight="1">
+      <c r="C213" s="41" t="inlineStr">
         <is>
           <t>解約時は dokusya_busu=0 を強制する。</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="409" customHeight="1">
-      <c r="C199" s="42" t="inlineStr">
+    <row r="214" ht="409" customHeight="1">
+      <c r="C214" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya (
   ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -22280,50 +23301,50 @@
   :hikiotoshi_yokin_shubetsu, :hikiotoshi_koza_no, :hikiotoshi_koza_meigi,
   :dokusyaso_bunrui, :nogyosya_bunrui,
   :dokusya_kaishi_date, :dokusya_kaishi_date, :dokusya_chushi_date,
-  NULL, :seikyu_kaishi_month, :biko, 1,
-  NULL,
+  :joho_henko_tekiyo_date, :seikyu_kaishi_month, :biko, 1,
+  :denshi_shonin_status,  -- 紙版:NULL / 電子版・併読:1(承認済)
   NOW(), :user_account_id, NOW(), :user_account_id
 )
 RETURNING *</t>
         </is>
       </c>
-      <c r="D199" s="10" t="n"/>
-      <c r="E199" s="10" t="n"/>
-      <c r="F199" s="10" t="n"/>
-      <c r="G199" s="10" t="n"/>
-      <c r="H199" s="10" t="n"/>
-      <c r="I199" s="10" t="n"/>
-      <c r="J199" s="10" t="n"/>
-      <c r="K199" s="10" t="n"/>
-      <c r="L199" s="10" t="n"/>
-      <c r="M199" s="10" t="n"/>
-      <c r="N199" s="10" t="n"/>
-      <c r="O199" s="10" t="n"/>
-      <c r="P199" s="10" t="n"/>
-      <c r="Q199" s="10" t="n"/>
-      <c r="R199" s="10" t="n"/>
-      <c r="S199" s="10" t="n"/>
-      <c r="T199" s="10" t="n"/>
-      <c r="U199" s="10" t="n"/>
-      <c r="V199" s="10" t="n"/>
-      <c r="W199" s="10" t="n"/>
-      <c r="X199" s="10" t="n"/>
-      <c r="Y199" s="10" t="n"/>
-      <c r="Z199" s="10" t="n"/>
-      <c r="AA199" s="10" t="n"/>
-      <c r="AB199" s="10" t="n"/>
-      <c r="AC199" s="10" t="n"/>
-      <c r="AD199" s="10" t="n"/>
-      <c r="AE199" s="10" t="n"/>
-      <c r="AF199" s="10" t="n"/>
-      <c r="AG199" s="10" t="n"/>
-      <c r="AH199" s="10" t="n"/>
-      <c r="AI199" s="10" t="n"/>
-      <c r="AJ199" s="10" t="n"/>
-      <c r="AK199" s="11" t="n"/>
-    </row>
-    <row r="200" ht="409" customHeight="1">
-      <c r="C200" s="42" t="inlineStr">
+      <c r="D214" s="10" t="n"/>
+      <c r="E214" s="10" t="n"/>
+      <c r="F214" s="10" t="n"/>
+      <c r="G214" s="10" t="n"/>
+      <c r="H214" s="10" t="n"/>
+      <c r="I214" s="10" t="n"/>
+      <c r="J214" s="10" t="n"/>
+      <c r="K214" s="10" t="n"/>
+      <c r="L214" s="10" t="n"/>
+      <c r="M214" s="10" t="n"/>
+      <c r="N214" s="10" t="n"/>
+      <c r="O214" s="10" t="n"/>
+      <c r="P214" s="10" t="n"/>
+      <c r="Q214" s="10" t="n"/>
+      <c r="R214" s="10" t="n"/>
+      <c r="S214" s="10" t="n"/>
+      <c r="T214" s="10" t="n"/>
+      <c r="U214" s="10" t="n"/>
+      <c r="V214" s="10" t="n"/>
+      <c r="W214" s="10" t="n"/>
+      <c r="X214" s="10" t="n"/>
+      <c r="Y214" s="10" t="n"/>
+      <c r="Z214" s="10" t="n"/>
+      <c r="AA214" s="10" t="n"/>
+      <c r="AB214" s="10" t="n"/>
+      <c r="AC214" s="10" t="n"/>
+      <c r="AD214" s="10" t="n"/>
+      <c r="AE214" s="10" t="n"/>
+      <c r="AF214" s="10" t="n"/>
+      <c r="AG214" s="10" t="n"/>
+      <c r="AH214" s="10" t="n"/>
+      <c r="AI214" s="10" t="n"/>
+      <c r="AJ214" s="10" t="n"/>
+      <c r="AK214" s="11" t="n"/>
+    </row>
+    <row r="215" ht="409" customHeight="1">
+      <c r="C215" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya_rireki (
   dokusya_id, rireki_no, ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -22365,7 +23386,7 @@
   :hikiotoshi_yokin_shubetsu, :hikiotoshi_koza_no, :hikiotoshi_koza_meigi,
   :dokusyaso_bunrui, :nogyosya_bunrui,
   :dokusya_kaishi_date, :dokusya_kaishi_date, :dokusya_chushi_date,
-  NULL, :seikyu_kaishi_month, :biko, '',
+  :joho_henko_tekiyo_date, :seikyu_kaishi_month, :biko, '',
   TRUE, TRUE, :shinki_flg, :kaiyaku_flg,
   NULL, NULL, NULL,
   NULL, NULL, NULL,
@@ -22374,57 +23395,57 @@
 )</t>
         </is>
       </c>
-      <c r="D200" s="10" t="n"/>
-      <c r="E200" s="10" t="n"/>
-      <c r="F200" s="10" t="n"/>
-      <c r="G200" s="10" t="n"/>
-      <c r="H200" s="10" t="n"/>
-      <c r="I200" s="10" t="n"/>
-      <c r="J200" s="10" t="n"/>
-      <c r="K200" s="10" t="n"/>
-      <c r="L200" s="10" t="n"/>
-      <c r="M200" s="10" t="n"/>
-      <c r="N200" s="10" t="n"/>
-      <c r="O200" s="10" t="n"/>
-      <c r="P200" s="10" t="n"/>
-      <c r="Q200" s="10" t="n"/>
-      <c r="R200" s="10" t="n"/>
-      <c r="S200" s="10" t="n"/>
-      <c r="T200" s="10" t="n"/>
-      <c r="U200" s="10" t="n"/>
-      <c r="V200" s="10" t="n"/>
-      <c r="W200" s="10" t="n"/>
-      <c r="X200" s="10" t="n"/>
-      <c r="Y200" s="10" t="n"/>
-      <c r="Z200" s="10" t="n"/>
-      <c r="AA200" s="10" t="n"/>
-      <c r="AB200" s="10" t="n"/>
-      <c r="AC200" s="10" t="n"/>
-      <c r="AD200" s="10" t="n"/>
-      <c r="AE200" s="10" t="n"/>
-      <c r="AF200" s="10" t="n"/>
-      <c r="AG200" s="10" t="n"/>
-      <c r="AH200" s="10" t="n"/>
-      <c r="AI200" s="10" t="n"/>
-      <c r="AJ200" s="10" t="n"/>
-      <c r="AK200" s="11" t="n"/>
-    </row>
-    <row r="201" ht="18" customHeight="1">
-      <c r="B201" s="27" t="inlineStr">
+      <c r="D215" s="10" t="n"/>
+      <c r="E215" s="10" t="n"/>
+      <c r="F215" s="10" t="n"/>
+      <c r="G215" s="10" t="n"/>
+      <c r="H215" s="10" t="n"/>
+      <c r="I215" s="10" t="n"/>
+      <c r="J215" s="10" t="n"/>
+      <c r="K215" s="10" t="n"/>
+      <c r="L215" s="10" t="n"/>
+      <c r="M215" s="10" t="n"/>
+      <c r="N215" s="10" t="n"/>
+      <c r="O215" s="10" t="n"/>
+      <c r="P215" s="10" t="n"/>
+      <c r="Q215" s="10" t="n"/>
+      <c r="R215" s="10" t="n"/>
+      <c r="S215" s="10" t="n"/>
+      <c r="T215" s="10" t="n"/>
+      <c r="U215" s="10" t="n"/>
+      <c r="V215" s="10" t="n"/>
+      <c r="W215" s="10" t="n"/>
+      <c r="X215" s="10" t="n"/>
+      <c r="Y215" s="10" t="n"/>
+      <c r="Z215" s="10" t="n"/>
+      <c r="AA215" s="10" t="n"/>
+      <c r="AB215" s="10" t="n"/>
+      <c r="AC215" s="10" t="n"/>
+      <c r="AD215" s="10" t="n"/>
+      <c r="AE215" s="10" t="n"/>
+      <c r="AF215" s="10" t="n"/>
+      <c r="AG215" s="10" t="n"/>
+      <c r="AH215" s="10" t="n"/>
+      <c r="AI215" s="10" t="n"/>
+      <c r="AJ215" s="10" t="n"/>
+      <c r="AK215" s="11" t="n"/>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="B216" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="18" customHeight="1">
-      <c r="C202" s="41" t="inlineStr">
+    <row r="217" ht="18" customHeight="1">
+      <c r="C217" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="216" customHeight="1">
-      <c r="C203" s="42" t="inlineStr">
+    <row r="218" ht="216" customHeight="1">
+      <c r="C218" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -22440,92 +23461,92 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D203" s="10" t="n"/>
-      <c r="E203" s="10" t="n"/>
-      <c r="F203" s="10" t="n"/>
-      <c r="G203" s="10" t="n"/>
-      <c r="H203" s="10" t="n"/>
-      <c r="I203" s="10" t="n"/>
-      <c r="J203" s="10" t="n"/>
-      <c r="K203" s="10" t="n"/>
-      <c r="L203" s="10" t="n"/>
-      <c r="M203" s="10" t="n"/>
-      <c r="N203" s="10" t="n"/>
-      <c r="O203" s="10" t="n"/>
-      <c r="P203" s="10" t="n"/>
-      <c r="Q203" s="10" t="n"/>
-      <c r="R203" s="10" t="n"/>
-      <c r="S203" s="10" t="n"/>
-      <c r="T203" s="10" t="n"/>
-      <c r="U203" s="10" t="n"/>
-      <c r="V203" s="10" t="n"/>
-      <c r="W203" s="10" t="n"/>
-      <c r="X203" s="10" t="n"/>
-      <c r="Y203" s="10" t="n"/>
-      <c r="Z203" s="10" t="n"/>
-      <c r="AA203" s="10" t="n"/>
-      <c r="AB203" s="10" t="n"/>
-      <c r="AC203" s="10" t="n"/>
-      <c r="AD203" s="10" t="n"/>
-      <c r="AE203" s="10" t="n"/>
-      <c r="AF203" s="10" t="n"/>
-      <c r="AG203" s="10" t="n"/>
-      <c r="AH203" s="10" t="n"/>
-      <c r="AI203" s="10" t="n"/>
-      <c r="AJ203" s="10" t="n"/>
-      <c r="AK203" s="11" t="n"/>
-    </row>
-    <row r="204" ht="18" customHeight="1">
-      <c r="C204" s="41" t="inlineStr">
+      <c r="D218" s="10" t="n"/>
+      <c r="E218" s="10" t="n"/>
+      <c r="F218" s="10" t="n"/>
+      <c r="G218" s="10" t="n"/>
+      <c r="H218" s="10" t="n"/>
+      <c r="I218" s="10" t="n"/>
+      <c r="J218" s="10" t="n"/>
+      <c r="K218" s="10" t="n"/>
+      <c r="L218" s="10" t="n"/>
+      <c r="M218" s="10" t="n"/>
+      <c r="N218" s="10" t="n"/>
+      <c r="O218" s="10" t="n"/>
+      <c r="P218" s="10" t="n"/>
+      <c r="Q218" s="10" t="n"/>
+      <c r="R218" s="10" t="n"/>
+      <c r="S218" s="10" t="n"/>
+      <c r="T218" s="10" t="n"/>
+      <c r="U218" s="10" t="n"/>
+      <c r="V218" s="10" t="n"/>
+      <c r="W218" s="10" t="n"/>
+      <c r="X218" s="10" t="n"/>
+      <c r="Y218" s="10" t="n"/>
+      <c r="Z218" s="10" t="n"/>
+      <c r="AA218" s="10" t="n"/>
+      <c r="AB218" s="10" t="n"/>
+      <c r="AC218" s="10" t="n"/>
+      <c r="AD218" s="10" t="n"/>
+      <c r="AE218" s="10" t="n"/>
+      <c r="AF218" s="10" t="n"/>
+      <c r="AG218" s="10" t="n"/>
+      <c r="AH218" s="10" t="n"/>
+      <c r="AI218" s="10" t="n"/>
+      <c r="AJ218" s="10" t="n"/>
+      <c r="AK218" s="11" t="n"/>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="C219" s="41" t="inlineStr">
         <is>
           <t>`before_value`：INSERT のため空文字列を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="36" customHeight="1">
-      <c r="C205" s="41" t="inlineStr">
+    <row r="220" ht="36" customHeight="1">
+      <c r="C220" s="41" t="inlineStr">
         <is>
           <t>`after_value`：登録されたデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="18" customHeight="1">
-      <c r="B206" s="27" t="inlineStr">
+    <row r="221" ht="18" customHeight="1">
+      <c r="B221" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="18" customHeight="1">
-      <c r="C207" s="41" t="inlineStr">
+    <row r="222" ht="18" customHeight="1">
+      <c r="C222" s="41" t="inlineStr">
         <is>
           <t>登録されたデータを data オブジェクトとして返却する。HTTP 201。</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="18" customHeight="1">
-      <c r="B208" s="27" t="inlineStr">
+    <row r="223" ht="18" customHeight="1">
+      <c r="B223" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="18" customHeight="1">
-      <c r="C209" s="41" t="inlineStr">
+    <row r="224" ht="18" customHeight="1">
+      <c r="C224" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="18" customHeight="1">
-      <c r="C210" s="41" t="inlineStr">
+    <row r="225" ht="18" customHeight="1">
+      <c r="C225" s="41" t="inlineStr">
         <is>
           <t>エラー発生時はエラーログを記録する（`log_type = 3`、トランザクション外で記録）。</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="216" customHeight="1">
-      <c r="C211" s="42" t="inlineStr">
+    <row r="226" ht="216" customHeight="1">
+      <c r="C226" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -22541,46 +23562,47 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D211" s="10" t="n"/>
-      <c r="E211" s="10" t="n"/>
-      <c r="F211" s="10" t="n"/>
-      <c r="G211" s="10" t="n"/>
-      <c r="H211" s="10" t="n"/>
-      <c r="I211" s="10" t="n"/>
-      <c r="J211" s="10" t="n"/>
-      <c r="K211" s="10" t="n"/>
-      <c r="L211" s="10" t="n"/>
-      <c r="M211" s="10" t="n"/>
-      <c r="N211" s="10" t="n"/>
-      <c r="O211" s="10" t="n"/>
-      <c r="P211" s="10" t="n"/>
-      <c r="Q211" s="10" t="n"/>
-      <c r="R211" s="10" t="n"/>
-      <c r="S211" s="10" t="n"/>
-      <c r="T211" s="10" t="n"/>
-      <c r="U211" s="10" t="n"/>
-      <c r="V211" s="10" t="n"/>
-      <c r="W211" s="10" t="n"/>
-      <c r="X211" s="10" t="n"/>
-      <c r="Y211" s="10" t="n"/>
-      <c r="Z211" s="10" t="n"/>
-      <c r="AA211" s="10" t="n"/>
-      <c r="AB211" s="10" t="n"/>
-      <c r="AC211" s="10" t="n"/>
-      <c r="AD211" s="10" t="n"/>
-      <c r="AE211" s="10" t="n"/>
-      <c r="AF211" s="10" t="n"/>
-      <c r="AG211" s="10" t="n"/>
-      <c r="AH211" s="10" t="n"/>
-      <c r="AI211" s="10" t="n"/>
-      <c r="AJ211" s="10" t="n"/>
-      <c r="AK211" s="11" t="n"/>
+      <c r="D226" s="10" t="n"/>
+      <c r="E226" s="10" t="n"/>
+      <c r="F226" s="10" t="n"/>
+      <c r="G226" s="10" t="n"/>
+      <c r="H226" s="10" t="n"/>
+      <c r="I226" s="10" t="n"/>
+      <c r="J226" s="10" t="n"/>
+      <c r="K226" s="10" t="n"/>
+      <c r="L226" s="10" t="n"/>
+      <c r="M226" s="10" t="n"/>
+      <c r="N226" s="10" t="n"/>
+      <c r="O226" s="10" t="n"/>
+      <c r="P226" s="10" t="n"/>
+      <c r="Q226" s="10" t="n"/>
+      <c r="R226" s="10" t="n"/>
+      <c r="S226" s="10" t="n"/>
+      <c r="T226" s="10" t="n"/>
+      <c r="U226" s="10" t="n"/>
+      <c r="V226" s="10" t="n"/>
+      <c r="W226" s="10" t="n"/>
+      <c r="X226" s="10" t="n"/>
+      <c r="Y226" s="10" t="n"/>
+      <c r="Z226" s="10" t="n"/>
+      <c r="AA226" s="10" t="n"/>
+      <c r="AB226" s="10" t="n"/>
+      <c r="AC226" s="10" t="n"/>
+      <c r="AD226" s="10" t="n"/>
+      <c r="AE226" s="10" t="n"/>
+      <c r="AF226" s="10" t="n"/>
+      <c r="AG226" s="10" t="n"/>
+      <c r="AH226" s="10" t="n"/>
+      <c r="AI226" s="10" t="n"/>
+      <c r="AJ226" s="10" t="n"/>
+      <c r="AK226" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="828">
+  <mergeCells count="858">
     <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="B144:I144"/>
+    <mergeCell ref="D200:AK200"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="M135:P135"/>
     <mergeCell ref="Y61:AB61"/>
@@ -22590,6 +23612,7 @@
     <mergeCell ref="Q78:S78"/>
     <mergeCell ref="M72:P72"/>
     <mergeCell ref="Q114:S114"/>
+    <mergeCell ref="T137:X137"/>
     <mergeCell ref="D125:L125"/>
     <mergeCell ref="T53:X53"/>
     <mergeCell ref="T124:X124"/>
@@ -22613,6 +23636,7 @@
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="M113:P113"/>
     <mergeCell ref="T132:X132"/>
+    <mergeCell ref="Q138:S138"/>
     <mergeCell ref="C205:AK205"/>
     <mergeCell ref="Y118:AE118"/>
     <mergeCell ref="M88:P88"/>
@@ -22626,6 +23650,7 @@
     <mergeCell ref="M54:P54"/>
     <mergeCell ref="Y98:AE98"/>
     <mergeCell ref="M90:P90"/>
+    <mergeCell ref="D138:L138"/>
     <mergeCell ref="AF86:AK86"/>
     <mergeCell ref="Q106:S106"/>
     <mergeCell ref="Q77:S77"/>
@@ -22637,6 +23662,7 @@
     <mergeCell ref="AF101:AK101"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="B165:AK165"/>
     <mergeCell ref="Q135:S135"/>
     <mergeCell ref="M85:P85"/>
     <mergeCell ref="Y36:AB36"/>
@@ -22645,9 +23671,11 @@
     <mergeCell ref="T112:X112"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="B150:I150"/>
+    <mergeCell ref="C220:AK220"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="C38:L38"/>
     <mergeCell ref="Q109:S109"/>
+    <mergeCell ref="C195:AK195"/>
     <mergeCell ref="T122:X122"/>
     <mergeCell ref="M103:P103"/>
     <mergeCell ref="Y116:AE116"/>
@@ -22656,6 +23684,7 @@
     <mergeCell ref="AF104:AK104"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="M118:P118"/>
+    <mergeCell ref="C197:AK197"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
     <mergeCell ref="Q86:S86"/>
@@ -22666,26 +23695,27 @@
     <mergeCell ref="Y130:AE130"/>
     <mergeCell ref="Y62:AB62"/>
     <mergeCell ref="Y117:AE117"/>
+    <mergeCell ref="T139:X139"/>
     <mergeCell ref="AF81:AK81"/>
     <mergeCell ref="Q128:S128"/>
     <mergeCell ref="C73:L73"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="D89:L89"/>
     <mergeCell ref="AF99:AK99"/>
+    <mergeCell ref="T138:X138"/>
     <mergeCell ref="AC70:AE70"/>
     <mergeCell ref="C35:L35"/>
     <mergeCell ref="Y64:AB64"/>
     <mergeCell ref="Y51:AB51"/>
-    <mergeCell ref="C79:C136"/>
     <mergeCell ref="T69:X69"/>
+    <mergeCell ref="C213:AK213"/>
     <mergeCell ref="D128:L128"/>
     <mergeCell ref="AC71:AE71"/>
     <mergeCell ref="Y119:AE119"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="B138:I138"/>
+    <mergeCell ref="C208:AK208"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="A160:AK160"/>
     <mergeCell ref="M91:P91"/>
     <mergeCell ref="C145:AK145"/>
     <mergeCell ref="T45:X45"/>
@@ -22696,9 +23726,7 @@
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C72:L72"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="D165:AK165"/>
     <mergeCell ref="Q99:S99"/>
-    <mergeCell ref="C210:AK210"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="M93:P93"/>
     <mergeCell ref="T87:X87"/>
@@ -22726,7 +23754,7 @@
     <mergeCell ref="AF105:AK105"/>
     <mergeCell ref="Q125:S125"/>
     <mergeCell ref="AF43:AK43"/>
-    <mergeCell ref="C163:AK163"/>
+    <mergeCell ref="Y138:AE138"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="C41:L41"/>
     <mergeCell ref="Q112:S112"/>
@@ -22747,26 +23775,27 @@
     <mergeCell ref="M104:P104"/>
     <mergeCell ref="Q64:S64"/>
     <mergeCell ref="B153:I153"/>
+    <mergeCell ref="D209:AK209"/>
     <mergeCell ref="T77:X77"/>
     <mergeCell ref="Y65:AB65"/>
     <mergeCell ref="M41:P41"/>
     <mergeCell ref="D136:L136"/>
-    <mergeCell ref="B161:AK161"/>
     <mergeCell ref="M106:P106"/>
     <mergeCell ref="Q131:S131"/>
     <mergeCell ref="Y57:AB57"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="AC73:AE73"/>
     <mergeCell ref="Y135:AE135"/>
+    <mergeCell ref="D211:AK211"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
+    <mergeCell ref="C79:C139"/>
     <mergeCell ref="M66:P66"/>
-    <mergeCell ref="B162:AK162"/>
     <mergeCell ref="Y87:AE87"/>
     <mergeCell ref="M130:P130"/>
+    <mergeCell ref="C218:AK218"/>
     <mergeCell ref="Y89:AE89"/>
     <mergeCell ref="Q57:S57"/>
-    <mergeCell ref="C211:AK211"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="Q100:S100"/>
@@ -22778,6 +23807,7 @@
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="AF70:AK70"/>
     <mergeCell ref="Q115:S115"/>
+    <mergeCell ref="B216:AK216"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="Y60:AB60"/>
     <mergeCell ref="T96:X96"/>
@@ -22793,20 +23823,22 @@
     <mergeCell ref="M37:P37"/>
     <mergeCell ref="T98:X98"/>
     <mergeCell ref="AC30:AE30"/>
-    <mergeCell ref="B190:AK190"/>
     <mergeCell ref="D86:L86"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC67:AE67"/>
     <mergeCell ref="AF128:AK128"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="B159:I159"/>
     <mergeCell ref="Y77:AE77"/>
+    <mergeCell ref="D184:AK184"/>
     <mergeCell ref="M125:P125"/>
     <mergeCell ref="AC69:AE69"/>
-    <mergeCell ref="C179:AK179"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M112:P112"/>
     <mergeCell ref="AF121:AK121"/>
     <mergeCell ref="C57:L57"/>
+    <mergeCell ref="C166:AK166"/>
+    <mergeCell ref="C160:AK160"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="C49:L49"/>
     <mergeCell ref="M56:P56"/>
@@ -22829,21 +23861,21 @@
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="Y73:AB73"/>
     <mergeCell ref="T109:X109"/>
-    <mergeCell ref="B201:AK201"/>
+    <mergeCell ref="B164:AK164"/>
+    <mergeCell ref="M138:P138"/>
     <mergeCell ref="T84:X84"/>
     <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="B206:AK206"/>
     <mergeCell ref="Y88:AE88"/>
     <mergeCell ref="D99:L99"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="T86:X86"/>
+    <mergeCell ref="C219:AK219"/>
     <mergeCell ref="Q83:S83"/>
     <mergeCell ref="Y90:AE90"/>
     <mergeCell ref="D101:L101"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="Q58:S58"/>
-    <mergeCell ref="D166:AK166"/>
     <mergeCell ref="AF103:AK103"/>
     <mergeCell ref="AF78:AK78"/>
     <mergeCell ref="C39:L39"/>
@@ -22857,6 +23889,7 @@
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="AC42:AE42"/>
     <mergeCell ref="AF80:AK80"/>
+    <mergeCell ref="D180:AK180"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="D167:AK167"/>
     <mergeCell ref="AF55:AK55"/>
@@ -22867,7 +23900,6 @@
     <mergeCell ref="AC31:AE31"/>
     <mergeCell ref="D169:AK169"/>
     <mergeCell ref="M64:P64"/>
-    <mergeCell ref="C180:AK180"/>
     <mergeCell ref="AF71:AK71"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="AF131:AK131"/>
@@ -22876,13 +23908,11 @@
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="M128:P128"/>
-    <mergeCell ref="C182:AK182"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="AF73:AK73"/>
     <mergeCell ref="Q71:S71"/>
     <mergeCell ref="M65:P65"/>
     <mergeCell ref="Y78:AE78"/>
-    <mergeCell ref="D195:AK195"/>
     <mergeCell ref="T130:X130"/>
     <mergeCell ref="T46:X46"/>
     <mergeCell ref="AF66:AK66"/>
@@ -22891,7 +23921,6 @@
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
     <mergeCell ref="Y80:AE80"/>
-    <mergeCell ref="D197:AK197"/>
     <mergeCell ref="Y49:AB49"/>
     <mergeCell ref="D120:L120"/>
     <mergeCell ref="T48:X48"/>
@@ -22909,10 +23938,12 @@
     <mergeCell ref="M83:P83"/>
     <mergeCell ref="AF79:AK79"/>
     <mergeCell ref="Y106:AE106"/>
+    <mergeCell ref="D182:AK182"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="Y93:AE93"/>
     <mergeCell ref="AF119:AK119"/>
+    <mergeCell ref="C226:AK226"/>
     <mergeCell ref="D133:L133"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="Q101:S101"/>
@@ -22923,7 +23954,9 @@
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="C222:AK222"/>
     <mergeCell ref="AC45:AE45"/>
+    <mergeCell ref="D183:AK183"/>
     <mergeCell ref="T56:X56"/>
     <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="T105:X105"/>
@@ -22937,6 +23970,7 @@
     <mergeCell ref="T107:X107"/>
     <mergeCell ref="T101:X101"/>
     <mergeCell ref="M136:P136"/>
+    <mergeCell ref="C190:AK190"/>
     <mergeCell ref="Y111:AE111"/>
     <mergeCell ref="AF63:AK63"/>
     <mergeCell ref="Q79:S79"/>
@@ -22945,12 +23979,15 @@
     <mergeCell ref="Y104:AE104"/>
     <mergeCell ref="C66:L66"/>
     <mergeCell ref="Q81:S81"/>
+    <mergeCell ref="Q137:S137"/>
     <mergeCell ref="C53:L53"/>
     <mergeCell ref="AC63:AE63"/>
     <mergeCell ref="M131:P131"/>
+    <mergeCell ref="D201:AK201"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
     <mergeCell ref="AC50:AE50"/>
+    <mergeCell ref="AF138:AK138"/>
     <mergeCell ref="C185:AK185"/>
     <mergeCell ref="Q123:S123"/>
     <mergeCell ref="C68:L68"/>
@@ -22965,7 +24002,6 @@
     <mergeCell ref="D123:L123"/>
     <mergeCell ref="D110:L110"/>
     <mergeCell ref="Y44:AB44"/>
-    <mergeCell ref="C139:AK139"/>
     <mergeCell ref="C188:AK188"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M84:P84"/>
@@ -22977,6 +24013,7 @@
     <mergeCell ref="Y99:AE99"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="M80:P80"/>
+    <mergeCell ref="D210:AK210"/>
     <mergeCell ref="T67:X67"/>
     <mergeCell ref="AF87:AK87"/>
     <mergeCell ref="J11:AK11"/>
@@ -23009,7 +24046,6 @@
     <mergeCell ref="Y112:AE112"/>
     <mergeCell ref="AF113:AK113"/>
     <mergeCell ref="T123:X123"/>
-    <mergeCell ref="C183:AK183"/>
     <mergeCell ref="T110:X110"/>
     <mergeCell ref="AF100:AK100"/>
     <mergeCell ref="Q120:S120"/>
@@ -23038,7 +24074,6 @@
     <mergeCell ref="D131:L131"/>
     <mergeCell ref="Q126:S126"/>
     <mergeCell ref="Y52:AB52"/>
-    <mergeCell ref="C209:AK209"/>
     <mergeCell ref="T136:X136"/>
     <mergeCell ref="AC68:AE68"/>
     <mergeCell ref="D124:L124"/>
@@ -23067,6 +24102,7 @@
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="Y121:AE121"/>
     <mergeCell ref="C24:L24"/>
+    <mergeCell ref="C206:AK206"/>
     <mergeCell ref="Q95:S95"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="Y115:AE115"/>
@@ -23088,6 +24124,7 @@
     <mergeCell ref="Q96:S96"/>
     <mergeCell ref="T60:X60"/>
     <mergeCell ref="T131:X131"/>
+    <mergeCell ref="Q139:S139"/>
     <mergeCell ref="C55:L55"/>
     <mergeCell ref="D81:L81"/>
     <mergeCell ref="AC62:AE62"/>
@@ -23095,7 +24132,10 @@
     <mergeCell ref="M105:P105"/>
     <mergeCell ref="Q121:S121"/>
     <mergeCell ref="A75:AK75"/>
+    <mergeCell ref="C224:AK224"/>
+    <mergeCell ref="D139:L139"/>
     <mergeCell ref="M120:P120"/>
+    <mergeCell ref="D179:AK179"/>
     <mergeCell ref="C199:AK199"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="AF116:AK116"/>
@@ -23103,10 +24143,12 @@
     <mergeCell ref="M101:P101"/>
     <mergeCell ref="C52:L52"/>
     <mergeCell ref="Q63:S63"/>
+    <mergeCell ref="C217:AK217"/>
     <mergeCell ref="AF108:AK108"/>
     <mergeCell ref="Y136:AE136"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="B156:I156"/>
+    <mergeCell ref="D212:AK212"/>
     <mergeCell ref="M100:P100"/>
     <mergeCell ref="AF118:AK118"/>
     <mergeCell ref="T42:X42"/>
@@ -23138,6 +24180,7 @@
     <mergeCell ref="D94:L94"/>
     <mergeCell ref="AF96:AK96"/>
     <mergeCell ref="Q116:S116"/>
+    <mergeCell ref="C214:AK214"/>
     <mergeCell ref="Q134:S134"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="Y85:AE85"/>
@@ -23154,6 +24197,7 @@
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="Y124:AE124"/>
+    <mergeCell ref="A163:AK163"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M97:P97"/>
@@ -23163,8 +24207,8 @@
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="D87:L87"/>
     <mergeCell ref="AF124:AK124"/>
+    <mergeCell ref="C225:AK225"/>
     <mergeCell ref="AC65:AE65"/>
-    <mergeCell ref="C200:AK200"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="Y63:AB63"/>
     <mergeCell ref="AF126:AK126"/>
@@ -23175,7 +24219,6 @@
     <mergeCell ref="C45:L45"/>
     <mergeCell ref="M123:P123"/>
     <mergeCell ref="C202:AK202"/>
-    <mergeCell ref="C177:AK177"/>
     <mergeCell ref="M110:P110"/>
     <mergeCell ref="T104:X104"/>
     <mergeCell ref="AF46:AK46"/>
@@ -23190,8 +24233,10 @@
     <mergeCell ref="AF61:AK61"/>
     <mergeCell ref="M108:P108"/>
     <mergeCell ref="D100:L100"/>
+    <mergeCell ref="B198:AK198"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="Q68:S68"/>
+    <mergeCell ref="Y137:AE137"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="T81:X81"/>
     <mergeCell ref="Y69:AB69"/>
@@ -23204,6 +24249,7 @@
     <mergeCell ref="Y84:AE84"/>
     <mergeCell ref="D95:L95"/>
     <mergeCell ref="M57:P57"/>
+    <mergeCell ref="AF137:AK137"/>
     <mergeCell ref="D135:L135"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="Y86:AE86"/>
@@ -23214,16 +24260,17 @@
     <mergeCell ref="C157:AK157"/>
     <mergeCell ref="C151:AK151"/>
     <mergeCell ref="M121:P121"/>
+    <mergeCell ref="AF139:AK139"/>
     <mergeCell ref="Y126:AE126"/>
+    <mergeCell ref="D177:AK177"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="T63:X63"/>
     <mergeCell ref="M96:P96"/>
     <mergeCell ref="M71:P71"/>
     <mergeCell ref="AF114:AK114"/>
-    <mergeCell ref="D164:AK164"/>
     <mergeCell ref="Y38:AB38"/>
     <mergeCell ref="C77:L77"/>
-    <mergeCell ref="B178:AK178"/>
+    <mergeCell ref="C215:AK215"/>
     <mergeCell ref="M111:P111"/>
     <mergeCell ref="T71:X71"/>
     <mergeCell ref="N19:AK19"/>
@@ -23232,6 +24279,7 @@
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="B147:I147"/>
     <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="D178:AK178"/>
     <mergeCell ref="D113:L113"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="D172:AK172"/>
@@ -23249,6 +24297,7 @@
     <mergeCell ref="AF117:AK117"/>
     <mergeCell ref="Y79:AE79"/>
     <mergeCell ref="D90:L90"/>
+    <mergeCell ref="B221:AK221"/>
     <mergeCell ref="AF67:AK67"/>
     <mergeCell ref="AF132:AK132"/>
     <mergeCell ref="C59:L59"/>
@@ -23271,6 +24320,7 @@
     <mergeCell ref="C48:L48"/>
     <mergeCell ref="M126:P126"/>
     <mergeCell ref="T120:X120"/>
+    <mergeCell ref="Y139:AE139"/>
     <mergeCell ref="AF62:AK62"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="AF127:AK127"/>
@@ -23284,6 +24334,7 @@
     <mergeCell ref="Y72:AB72"/>
     <mergeCell ref="D118:L118"/>
     <mergeCell ref="M44:P44"/>
+    <mergeCell ref="C196:AK196"/>
     <mergeCell ref="AC51:AE51"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="M129:P129"/>
@@ -23291,10 +24342,10 @@
     <mergeCell ref="Y92:AE92"/>
     <mergeCell ref="M73:P73"/>
     <mergeCell ref="M60:P60"/>
-    <mergeCell ref="C198:AK198"/>
     <mergeCell ref="Q87:S87"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="Y94:AE94"/>
+    <mergeCell ref="M137:P137"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="AF82:AK82"/>
@@ -23302,6 +24353,8 @@
     <mergeCell ref="T115:X115"/>
     <mergeCell ref="D96:L96"/>
     <mergeCell ref="T102:X102"/>
+    <mergeCell ref="M139:P139"/>
+    <mergeCell ref="B194:AK194"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="Q82:S82"/>
@@ -23311,7 +24364,9 @@
     <mergeCell ref="Q118:S118"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
+    <mergeCell ref="B223:AK223"/>
     <mergeCell ref="Q93:S93"/>
+    <mergeCell ref="D181:AK181"/>
     <mergeCell ref="D116:L116"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="C67:L67"/>
@@ -23321,7 +24376,6 @@
     <mergeCell ref="D91:L91"/>
     <mergeCell ref="T97:X97"/>
     <mergeCell ref="Y120:AE120"/>
-    <mergeCell ref="D196:AK196"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
@@ -23334,7 +24388,6 @@
     <mergeCell ref="C191:AK191"/>
     <mergeCell ref="D93:L93"/>
     <mergeCell ref="M68:P68"/>
-    <mergeCell ref="C184:AK184"/>
     <mergeCell ref="M117:P117"/>
     <mergeCell ref="M92:P92"/>
     <mergeCell ref="M55:P55"/>
@@ -23362,9 +24415,7 @@
     <mergeCell ref="M81:P81"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="D194:AK194"/>
     <mergeCell ref="T116:X116"/>
-    <mergeCell ref="B208:AK208"/>
     <mergeCell ref="D104:L104"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="T91:X91"/>
@@ -23383,6 +24434,7 @@
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="Y97:AE97"/>
     <mergeCell ref="Q65:S65"/>
+    <mergeCell ref="D137:L137"/>
     <mergeCell ref="AF85:AK85"/>
     <mergeCell ref="AC56:AE56"/>
     <mergeCell ref="T118:X118"/>
@@ -23402,7 +24454,6 @@
     <mergeCell ref="Y129:AE129"/>
     <mergeCell ref="Y123:AE123"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="C181:AK181"/>
     <mergeCell ref="M77:P77"/>
     <mergeCell ref="M133:P133"/>
     <mergeCell ref="AF29:AK29"/>
@@ -23417,7 +24468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK102"/>
+  <dimension ref="A1:AK110"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -23578,7 +24629,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -24511,14 +25562,14 @@
   "yubin_kubun": "0",
   "shiharai_hoho": 1,
   "dokusyaryo_shiharai_cycle": 1,
-  "bank_branch_code": "001",
-  "bank_branch_name": "本店",
+  "bank_shiten_id": 50,
   "hikiotoshi_yokin_shubetsu": 1,
   "hikiotoshi_koza_no": "1234567",
   "hikiotoshi_koza_meigi": "ヤマダタロウ",
   "dokusyaso_bunrui": "農業者",
   "nogyosya_bunrui": "水稲,野菜",
   "dokusya_kaishi_date": "2026-04-01",
+  "joho_henko_tekiyo_date": null,
   "seikyu_kaishi_month": "",
   "biko": ""
 }</t>
@@ -24612,6 +25663,9 @@
     "yubin_kubun": "0",
     "shiharai_hoho": 1,
     "dokusyaryo_shiharai_cycle": 1,
+    "bank_shiten_id": 50,
+    "jastem_toriatsukai_tenpo_code": "001",
+    "jastem_tenpo_name": "本店",
     "bank_branch_code": "001",
     "bank_branch_name": "本店",
     "hikiotoshi_yokin_shubetsu": 1,
@@ -25271,8 +26325,84 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="72" customHeight="1">
-      <c r="C82" s="42" t="inlineStr">
+    <row r="82" ht="90" customHeight="1">
+      <c r="C82" s="41" t="inlineStr">
+        <is>
+          <t>`bank_shiten_id` が指定された場合、支払方法を問わず `m_shiten` を逆引きし、`jastem_toriatsukai_tenpo_code` および `jastem_tenpo_name` を取得して `t_dokusya.bank_branch_code` / `bank_branch_name` に非正規化保存する（画面設計書 機能定義 §10.1 / §10.2、顧客要件 2026-06）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="72" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>支払方法=1（口座引落）では `bank_shiten_id` 必須（未指定→VALIDATION_ERROR）。他の支払方法では任意で、未指定なら bank_branch_code/name は空で保存する。指定値が不正（非存在 / 他JA / 金融機関支店でない）の場合は支払方法を問わず VALIDATION_ERROR。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="144" customHeight="1">
+      <c r="C84" s="42" t="inlineStr">
+        <is>
+          <t>SELECT shiten_id,
+       jastem_toriatsukai_tenpo_code,
+       jastem_tenpo_name
+FROM m_shiten
+WHERE shiten_id = :bank_shiten_id
+  AND ja_id = :ja_id
+  AND kinyu_shiten_flg = TRUE
+  AND deleted_at IS NULL</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="10" t="n"/>
+      <c r="K84" s="10" t="n"/>
+      <c r="L84" s="10" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="10" t="n"/>
+      <c r="U84" s="10" t="n"/>
+      <c r="V84" s="10" t="n"/>
+      <c r="W84" s="10" t="n"/>
+      <c r="X84" s="10" t="n"/>
+      <c r="Y84" s="10" t="n"/>
+      <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
+      <c r="AB84" s="10" t="n"/>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="10" t="n"/>
+      <c r="AF84" s="10" t="n"/>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="10" t="n"/>
+      <c r="AK84" s="11" t="n"/>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
+        <is>
+          <t>該当レコードがない場合：HTTP 400 (`VALIDATION_ERROR`)（`field: 'bank_shiten_id'`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>支払方法 ≠ 1 の場合、`bank_branch_code = ''` / `bank_branch_name = ''` を設定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="72" customHeight="1">
+      <c r="C87" s="42" t="inlineStr">
         <is>
           <t>UPDATE t_dokusya_rireki
 SET saishin_data_flg = FALSE
@@ -25280,128 +26410,149 @@
   AND saishin_data_flg = TRUE</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="10" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
-      <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="n"/>
-      <c r="J82" s="10" t="n"/>
-      <c r="K82" s="10" t="n"/>
-      <c r="L82" s="10" t="n"/>
-      <c r="M82" s="10" t="n"/>
-      <c r="N82" s="10" t="n"/>
-      <c r="O82" s="10" t="n"/>
-      <c r="P82" s="10" t="n"/>
-      <c r="Q82" s="10" t="n"/>
-      <c r="R82" s="10" t="n"/>
-      <c r="S82" s="10" t="n"/>
-      <c r="T82" s="10" t="n"/>
-      <c r="U82" s="10" t="n"/>
-      <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n"/>
-      <c r="X82" s="10" t="n"/>
-      <c r="Y82" s="10" t="n"/>
-      <c r="Z82" s="10" t="n"/>
-      <c r="AA82" s="10" t="n"/>
-      <c r="AB82" s="10" t="n"/>
-      <c r="AC82" s="10" t="n"/>
-      <c r="AD82" s="10" t="n"/>
-      <c r="AE82" s="10" t="n"/>
-      <c r="AF82" s="10" t="n"/>
-      <c r="AG82" s="10" t="n"/>
-      <c r="AH82" s="10" t="n"/>
-      <c r="AI82" s="10" t="n"/>
-      <c r="AJ82" s="10" t="n"/>
-      <c r="AK82" s="11" t="n"/>
-    </row>
-    <row r="83" ht="54" customHeight="1">
-      <c r="C83" s="42" t="inlineStr">
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="10" t="n"/>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="10" t="n"/>
+      <c r="Y87" s="10" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="10" t="n"/>
+      <c r="AC87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="10" t="n"/>
+      <c r="AF87" s="10" t="n"/>
+      <c r="AG87" s="10" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="11" t="n"/>
+    </row>
+    <row r="88" ht="54" customHeight="1">
+      <c r="C88" s="42" t="inlineStr">
         <is>
           <t>SELECT COALESCE(MAX(rireki_no), 0) + 1 AS new_rireki_no
 FROM t_dokusya_rireki
 WHERE dokusya_id = :dokusya_id</t>
         </is>
       </c>
-      <c r="D83" s="10" t="n"/>
-      <c r="E83" s="10" t="n"/>
-      <c r="F83" s="10" t="n"/>
-      <c r="G83" s="10" t="n"/>
-      <c r="H83" s="10" t="n"/>
-      <c r="I83" s="10" t="n"/>
-      <c r="J83" s="10" t="n"/>
-      <c r="K83" s="10" t="n"/>
-      <c r="L83" s="10" t="n"/>
-      <c r="M83" s="10" t="n"/>
-      <c r="N83" s="10" t="n"/>
-      <c r="O83" s="10" t="n"/>
-      <c r="P83" s="10" t="n"/>
-      <c r="Q83" s="10" t="n"/>
-      <c r="R83" s="10" t="n"/>
-      <c r="S83" s="10" t="n"/>
-      <c r="T83" s="10" t="n"/>
-      <c r="U83" s="10" t="n"/>
-      <c r="V83" s="10" t="n"/>
-      <c r="W83" s="10" t="n"/>
-      <c r="X83" s="10" t="n"/>
-      <c r="Y83" s="10" t="n"/>
-      <c r="Z83" s="10" t="n"/>
-      <c r="AA83" s="10" t="n"/>
-      <c r="AB83" s="10" t="n"/>
-      <c r="AC83" s="10" t="n"/>
-      <c r="AD83" s="10" t="n"/>
-      <c r="AE83" s="10" t="n"/>
-      <c r="AF83" s="10" t="n"/>
-      <c r="AG83" s="10" t="n"/>
-      <c r="AH83" s="10" t="n"/>
-      <c r="AI83" s="10" t="n"/>
-      <c r="AJ83" s="10" t="n"/>
-      <c r="AK83" s="11" t="n"/>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
-        <is>
-          <t>フラグ設定ルール（機能定義 14.2）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="D85" s="41" t="inlineStr">
-        <is>
-          <t>saishin_data_flg = TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="36" customHeight="1">
-      <c r="D86" s="41" t="inlineStr">
-        <is>
-          <t>shinki_flg = (tetsuzuki_shurui=1) ? TRUE : FALSE（再読時もTRUE）</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="D87" s="41" t="inlineStr">
-        <is>
-          <t>kaiyaku_flg = (tetsuzuki_shurui=0) ? TRUE : FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="36" customHeight="1">
-      <c r="D88" s="41" t="inlineStr">
-        <is>
-          <t>zougen_hokoku_flg = (購読部数/販売店/住所変更時) ? TRUE : FALSE</t>
-        </is>
-      </c>
+      <c r="D88" s="10" t="n"/>
+      <c r="E88" s="10" t="n"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
+      <c r="H88" s="10" t="n"/>
+      <c r="I88" s="10" t="n"/>
+      <c r="J88" s="10" t="n"/>
+      <c r="K88" s="10" t="n"/>
+      <c r="L88" s="10" t="n"/>
+      <c r="M88" s="10" t="n"/>
+      <c r="N88" s="10" t="n"/>
+      <c r="O88" s="10" t="n"/>
+      <c r="P88" s="10" t="n"/>
+      <c r="Q88" s="10" t="n"/>
+      <c r="R88" s="10" t="n"/>
+      <c r="S88" s="10" t="n"/>
+      <c r="T88" s="10" t="n"/>
+      <c r="U88" s="10" t="n"/>
+      <c r="V88" s="10" t="n"/>
+      <c r="W88" s="10" t="n"/>
+      <c r="X88" s="10" t="n"/>
+      <c r="Y88" s="10" t="n"/>
+      <c r="Z88" s="10" t="n"/>
+      <c r="AA88" s="10" t="n"/>
+      <c r="AB88" s="10" t="n"/>
+      <c r="AC88" s="10" t="n"/>
+      <c r="AD88" s="10" t="n"/>
+      <c r="AE88" s="10" t="n"/>
+      <c r="AF88" s="10" t="n"/>
+      <c r="AG88" s="10" t="n"/>
+      <c r="AH88" s="10" t="n"/>
+      <c r="AI88" s="10" t="n"/>
+      <c r="AJ88" s="10" t="n"/>
+      <c r="AK88" s="11" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="C89" s="41" t="inlineStr">
         <is>
+          <t>フラグ設定ルール（機能定義 14.2 / 増減報告フラグの正準仕様は</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="D90" s="41" t="inlineStr">
+        <is>
+          <t>saishin_data_flg = TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>shinki_flg = (tetsuzuki_shurui=1) ? TRUE : FALSE（再読時もTRUE）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="D92" s="41" t="inlineStr">
+        <is>
+          <t>kaiyaku_flg = (tetsuzuki_shurui=0) ? TRUE : FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="D93" s="41" t="inlineStr">
+        <is>
+          <t>zougen_hokoku_flg = 次のいずれかが更新前後で変わったとき TRUE、それ以外の</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="C94" s="41" t="inlineStr">
+        <is>
           <t>zenkai_* 列：更新前の対応する値を格納する（増減比較用）。</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="409" customHeight="1">
-      <c r="C90" s="42" t="inlineStr">
+    <row r="95" ht="36" customHeight="1">
+      <c r="D95" s="41" t="inlineStr">
+        <is>
+          <t>住所5項目の zenkai_*（zenkai_yubin_no / zenkai_todofuken_code /</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
+      <c r="D96" s="41" t="inlineStr">
+        <is>
+          <t>購読部数（zenkai_dokusya_busu）・販売店（zenkai_hanbaiten_id）は変更時のみ退避。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="D97" s="41" t="inlineStr">
+        <is>
+          <t>zenkai_* の退避有無と zougen_hokoku_flg は独立（same_flg=TRUE で住所無変更でも</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="409" customHeight="1">
+      <c r="C98" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya_rireki (
   dokusya_id, rireki_no, ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -25452,43 +26603,43 @@
 )</t>
         </is>
       </c>
-      <c r="D90" s="10" t="n"/>
-      <c r="E90" s="10" t="n"/>
-      <c r="F90" s="10" t="n"/>
-      <c r="G90" s="10" t="n"/>
-      <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="n"/>
-      <c r="J90" s="10" t="n"/>
-      <c r="K90" s="10" t="n"/>
-      <c r="L90" s="10" t="n"/>
-      <c r="M90" s="10" t="n"/>
-      <c r="N90" s="10" t="n"/>
-      <c r="O90" s="10" t="n"/>
-      <c r="P90" s="10" t="n"/>
-      <c r="Q90" s="10" t="n"/>
-      <c r="R90" s="10" t="n"/>
-      <c r="S90" s="10" t="n"/>
-      <c r="T90" s="10" t="n"/>
-      <c r="U90" s="10" t="n"/>
-      <c r="V90" s="10" t="n"/>
-      <c r="W90" s="10" t="n"/>
-      <c r="X90" s="10" t="n"/>
-      <c r="Y90" s="10" t="n"/>
-      <c r="Z90" s="10" t="n"/>
-      <c r="AA90" s="10" t="n"/>
-      <c r="AB90" s="10" t="n"/>
-      <c r="AC90" s="10" t="n"/>
-      <c r="AD90" s="10" t="n"/>
-      <c r="AE90" s="10" t="n"/>
-      <c r="AF90" s="10" t="n"/>
-      <c r="AG90" s="10" t="n"/>
-      <c r="AH90" s="10" t="n"/>
-      <c r="AI90" s="10" t="n"/>
-      <c r="AJ90" s="10" t="n"/>
-      <c r="AK90" s="11" t="n"/>
-    </row>
-    <row r="91" ht="409" customHeight="1">
-      <c r="C91" s="42" t="inlineStr">
+      <c r="D98" s="10" t="n"/>
+      <c r="E98" s="10" t="n"/>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="10" t="n"/>
+      <c r="H98" s="10" t="n"/>
+      <c r="I98" s="10" t="n"/>
+      <c r="J98" s="10" t="n"/>
+      <c r="K98" s="10" t="n"/>
+      <c r="L98" s="10" t="n"/>
+      <c r="M98" s="10" t="n"/>
+      <c r="N98" s="10" t="n"/>
+      <c r="O98" s="10" t="n"/>
+      <c r="P98" s="10" t="n"/>
+      <c r="Q98" s="10" t="n"/>
+      <c r="R98" s="10" t="n"/>
+      <c r="S98" s="10" t="n"/>
+      <c r="T98" s="10" t="n"/>
+      <c r="U98" s="10" t="n"/>
+      <c r="V98" s="10" t="n"/>
+      <c r="W98" s="10" t="n"/>
+      <c r="X98" s="10" t="n"/>
+      <c r="Y98" s="10" t="n"/>
+      <c r="Z98" s="10" t="n"/>
+      <c r="AA98" s="10" t="n"/>
+      <c r="AB98" s="10" t="n"/>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="10" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="10" t="n"/>
+      <c r="AK98" s="11" t="n"/>
+    </row>
+    <row r="99" ht="409" customHeight="1">
+      <c r="C99" s="42" t="inlineStr">
         <is>
           <t>UPDATE t_dokusya
 SET kanri_shiten_id = :kanri_shiten_id,
@@ -25551,57 +26702,57 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D91" s="10" t="n"/>
-      <c r="E91" s="10" t="n"/>
-      <c r="F91" s="10" t="n"/>
-      <c r="G91" s="10" t="n"/>
-      <c r="H91" s="10" t="n"/>
-      <c r="I91" s="10" t="n"/>
-      <c r="J91" s="10" t="n"/>
-      <c r="K91" s="10" t="n"/>
-      <c r="L91" s="10" t="n"/>
-      <c r="M91" s="10" t="n"/>
-      <c r="N91" s="10" t="n"/>
-      <c r="O91" s="10" t="n"/>
-      <c r="P91" s="10" t="n"/>
-      <c r="Q91" s="10" t="n"/>
-      <c r="R91" s="10" t="n"/>
-      <c r="S91" s="10" t="n"/>
-      <c r="T91" s="10" t="n"/>
-      <c r="U91" s="10" t="n"/>
-      <c r="V91" s="10" t="n"/>
-      <c r="W91" s="10" t="n"/>
-      <c r="X91" s="10" t="n"/>
-      <c r="Y91" s="10" t="n"/>
-      <c r="Z91" s="10" t="n"/>
-      <c r="AA91" s="10" t="n"/>
-      <c r="AB91" s="10" t="n"/>
-      <c r="AC91" s="10" t="n"/>
-      <c r="AD91" s="10" t="n"/>
-      <c r="AE91" s="10" t="n"/>
-      <c r="AF91" s="10" t="n"/>
-      <c r="AG91" s="10" t="n"/>
-      <c r="AH91" s="10" t="n"/>
-      <c r="AI91" s="10" t="n"/>
-      <c r="AJ91" s="10" t="n"/>
-      <c r="AK91" s="11" t="n"/>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="B92" s="27" t="inlineStr">
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="10" t="n"/>
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="10" t="n"/>
+      <c r="I99" s="10" t="n"/>
+      <c r="J99" s="10" t="n"/>
+      <c r="K99" s="10" t="n"/>
+      <c r="L99" s="10" t="n"/>
+      <c r="M99" s="10" t="n"/>
+      <c r="N99" s="10" t="n"/>
+      <c r="O99" s="10" t="n"/>
+      <c r="P99" s="10" t="n"/>
+      <c r="Q99" s="10" t="n"/>
+      <c r="R99" s="10" t="n"/>
+      <c r="S99" s="10" t="n"/>
+      <c r="T99" s="10" t="n"/>
+      <c r="U99" s="10" t="n"/>
+      <c r="V99" s="10" t="n"/>
+      <c r="W99" s="10" t="n"/>
+      <c r="X99" s="10" t="n"/>
+      <c r="Y99" s="10" t="n"/>
+      <c r="Z99" s="10" t="n"/>
+      <c r="AA99" s="10" t="n"/>
+      <c r="AB99" s="10" t="n"/>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="10" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="10" t="n"/>
+      <c r="AK99" s="11" t="n"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="B100" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="C93" s="41" t="inlineStr">
+    <row r="101" ht="18" customHeight="1">
+      <c r="C101" s="41" t="inlineStr">
         <is>
           <t>更新前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="216" customHeight="1">
-      <c r="C94" s="42" t="inlineStr">
+    <row r="102" ht="216" customHeight="1">
+      <c r="C102" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -25614,107 +26765,6 @@
         :dokusya_id, 't_dokusya',
         :before_value_json, :after_value_json,
         '', '',
-        :ip_address, :user_agent)</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
-      <c r="J94" s="10" t="n"/>
-      <c r="K94" s="10" t="n"/>
-      <c r="L94" s="10" t="n"/>
-      <c r="M94" s="10" t="n"/>
-      <c r="N94" s="10" t="n"/>
-      <c r="O94" s="10" t="n"/>
-      <c r="P94" s="10" t="n"/>
-      <c r="Q94" s="10" t="n"/>
-      <c r="R94" s="10" t="n"/>
-      <c r="S94" s="10" t="n"/>
-      <c r="T94" s="10" t="n"/>
-      <c r="U94" s="10" t="n"/>
-      <c r="V94" s="10" t="n"/>
-      <c r="W94" s="10" t="n"/>
-      <c r="X94" s="10" t="n"/>
-      <c r="Y94" s="10" t="n"/>
-      <c r="Z94" s="10" t="n"/>
-      <c r="AA94" s="10" t="n"/>
-      <c r="AB94" s="10" t="n"/>
-      <c r="AC94" s="10" t="n"/>
-      <c r="AD94" s="10" t="n"/>
-      <c r="AE94" s="10" t="n"/>
-      <c r="AF94" s="10" t="n"/>
-      <c r="AG94" s="10" t="n"/>
-      <c r="AH94" s="10" t="n"/>
-      <c r="AI94" s="10" t="n"/>
-      <c r="AJ94" s="10" t="n"/>
-      <c r="AK94" s="11" t="n"/>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="C95" s="41" t="inlineStr">
-        <is>
-          <t>`before_value`：更新前のデータをJSON形式で格納する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="C96" s="41" t="inlineStr">
-        <is>
-          <t>`after_value`：更新後のデータをJSON形式で格納する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="B97" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
-        <is>
-          <t>更新されたデータを data オブジェクトとして返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="B99" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="C100" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="C101" s="41" t="inlineStr">
-        <is>
-          <t>エラー発生時はエラーログを記録する（`log_type = 3`、トランザクション外で記録）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="216" customHeight="1">
-      <c r="C102" s="42" t="inlineStr">
-        <is>
-          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
-                   gamen_name, operation, result_status,
-                   target_id, target_table,
-                   before_value, after_value,
-                   error_message, stack_trace,
-                   ip_address, user_agent)
-VALUES (3, NOW(), :account_id, :ja_id,
-        '購読者情報登録画面 (ACSMS-SCR-011)', 'UPDATE', 2,
-        :dokusya_id, 't_dokusya',
-        '', '',
-        :error_message, :stack_trace,
         :ip_address, :user_agent)</t>
         </is>
       </c>
@@ -25753,13 +26803,113 @@
       <c r="AJ102" s="10" t="n"/>
       <c r="AK102" s="11" t="n"/>
     </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="C103" s="41" t="inlineStr">
+        <is>
+          <t>`before_value`：更新前のデータをJSON形式で格納する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="C104" s="41" t="inlineStr">
+        <is>
+          <t>`after_value`：更新後のデータをJSON形式で格納する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="C106" s="41" t="inlineStr">
+        <is>
+          <t>更新されたデータを data オブジェクトとして返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="B107" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="C108" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="C109" s="41" t="inlineStr">
+        <is>
+          <t>エラー発生時はエラーログを記録する（`log_type = 3`、トランザクション外で記録）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="216" customHeight="1">
+      <c r="C110" s="42" t="inlineStr">
+        <is>
+          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
+                   gamen_name, operation, result_status,
+                   target_id, target_table,
+                   before_value, after_value,
+                   error_message, stack_trace,
+                   ip_address, user_agent)
+VALUES (3, NOW(), :account_id, :ja_id,
+        '購読者情報登録画面 (ACSMS-SCR-011)', 'UPDATE', 2,
+        :dokusya_id, 't_dokusya',
+        '', '',
+        :error_message, :stack_trace,
+        :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="n"/>
+      <c r="E110" s="10" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="10" t="n"/>
+      <c r="J110" s="10" t="n"/>
+      <c r="K110" s="10" t="n"/>
+      <c r="L110" s="10" t="n"/>
+      <c r="M110" s="10" t="n"/>
+      <c r="N110" s="10" t="n"/>
+      <c r="O110" s="10" t="n"/>
+      <c r="P110" s="10" t="n"/>
+      <c r="Q110" s="10" t="n"/>
+      <c r="R110" s="10" t="n"/>
+      <c r="S110" s="10" t="n"/>
+      <c r="T110" s="10" t="n"/>
+      <c r="U110" s="10" t="n"/>
+      <c r="V110" s="10" t="n"/>
+      <c r="W110" s="10" t="n"/>
+      <c r="X110" s="10" t="n"/>
+      <c r="Y110" s="10" t="n"/>
+      <c r="Z110" s="10" t="n"/>
+      <c r="AA110" s="10" t="n"/>
+      <c r="AB110" s="10" t="n"/>
+      <c r="AC110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="10" t="n"/>
+      <c r="AF110" s="10" t="n"/>
+      <c r="AG110" s="10" t="n"/>
+      <c r="AH110" s="10" t="n"/>
+      <c r="AI110" s="10" t="n"/>
+      <c r="AJ110" s="10" t="n"/>
+      <c r="AK110" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="129">
+  <mergeCells count="137">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="C66:AK66"/>
     <mergeCell ref="T24:X24"/>
-    <mergeCell ref="D87:AK87"/>
     <mergeCell ref="C53:AK53"/>
     <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D71:AK71"/>
@@ -25768,18 +26918,21 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="C68:AK68"/>
+    <mergeCell ref="C86:AK86"/>
+    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C100:AK100"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="C65:AK65"/>
     <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="C109:AK109"/>
     <mergeCell ref="C44:AK44"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="C75:AK75"/>
@@ -25789,9 +26942,9 @@
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="C95:AK95"/>
     <mergeCell ref="N20:AK20"/>
     <mergeCell ref="M25:P25"/>
+    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="C38:AK38"/>
     <mergeCell ref="T29:X29"/>
@@ -25801,12 +26954,16 @@
     <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="C104:AK104"/>
+    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="D88:AK88"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="C103:AK103"/>
+    <mergeCell ref="C99:AK99"/>
+    <mergeCell ref="D90:AK90"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="B14:I20"/>
     <mergeCell ref="B49:I49"/>
@@ -25815,7 +26972,6 @@
     <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
-    <mergeCell ref="B97:AK97"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="J20:M20"/>
@@ -25826,13 +26982,14 @@
     <mergeCell ref="B58:AK58"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="C82:AK82"/>
     <mergeCell ref="B57:AK57"/>
+    <mergeCell ref="D92:AK92"/>
+    <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="C98:AK98"/>
-    <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="C89:AK89"/>
     <mergeCell ref="Q2:U3"/>
@@ -25842,33 +26999,35 @@
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C63:AK63"/>
     <mergeCell ref="C41:AK41"/>
-    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="C50:AK50"/>
-    <mergeCell ref="B92:AK92"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="D96:AK96"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="A56:AK56"/>
     <mergeCell ref="A27:AK27"/>
     <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="D97:AK97"/>
+    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B105:AK105"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="C83:AK83"/>
+    <mergeCell ref="D93:AK93"/>
     <mergeCell ref="A22:AK22"/>
     <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B107:AK107"/>
     <mergeCell ref="B52:I52"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="D85:AK85"/>
     <mergeCell ref="C47:AK47"/>
-    <mergeCell ref="B99:AK99"/>
     <mergeCell ref="D69:AK69"/>
     <mergeCell ref="B74:AK74"/>
     <mergeCell ref="B34:I34"/>
@@ -25876,13 +27035,13 @@
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="C60:AK60"/>
-    <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="D95:AK95"/>
     <mergeCell ref="C76:AK76"/>
+    <mergeCell ref="B100:AK100"/>
+    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="B62:AK62"/>
     <mergeCell ref="D70:AK70"/>
-    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26056,7 +27215,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/07</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
@@ -1517,7 +1517,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3579,7 +3579,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6011,7 +6011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG9"/>
+  <dimension ref="A1:AG11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6584,71 +6584,203 @@
       <c r="AF9" s="10" t="n"/>
       <c r="AG9" s="11" t="n"/>
     </row>
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="11" t="n"/>
+      <c r="R10" s="19" t="inlineStr">
+        <is>
+          <t>不具合修正（増減報告フラグ）：更新時の `zougen_hokoku_flg` 判定が購読者住所しか見ておらず、`haitatsu_same_flg=FALSE` で別配達先住所を入力しても FALSE のままだった。**実効配達先住所**（same_flg=TRUE→購読者住所 / FALSE→配達先住所）の変更、および `haitatsu_same_flg` の切替を増減トリガに追加し、配達先変更が正しく TRUE になるよう修正（BE: computeZougen）。</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="n"/>
+      <c r="V10" s="11" t="n"/>
+      <c r="W10" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X10" s="10" t="n"/>
+      <c r="Y10" s="10" t="n"/>
+      <c r="Z10" s="10" t="n"/>
+      <c r="AA10" s="11" t="n"/>
+      <c r="AB10" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC10" s="10" t="n"/>
+      <c r="AD10" s="10" t="n"/>
+      <c r="AE10" s="10" t="n"/>
+      <c r="AF10" s="10" t="n"/>
+      <c r="AG10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="11" t="n"/>
+      <c r="R11" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07 改訂：氏名（購読者氏名_氏 `shimei_sei`・購読者氏名_名 `shimei_mei`・配達先氏名 `haitatsu_shimei_sei`/`haitatsu_shimei_mei`）の形式チェックを **漢字のみ → 漢字・ひらがな・カタカナ許容** に緩和（ひらがな/カタカナ表記の氏名の方に対応）。半角カナ・英数字は引き続き不可。形式不正メッセージを「漢字で入力してください。」→「漢字・ひらがな・カタカナで入力してください。」に変更。かな項目（`shimei_kana_*`）の全角ひらがな形式は変更なし。</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="n"/>
+      <c r="V11" s="11" t="n"/>
+      <c r="W11" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X11" s="10" t="n"/>
+      <c r="Y11" s="10" t="n"/>
+      <c r="Z11" s="10" t="n"/>
+      <c r="AA11" s="11" t="n"/>
+      <c r="AB11" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC11" s="10" t="n"/>
+      <c r="AD11" s="10" t="n"/>
+      <c r="AE11" s="10" t="n"/>
+      <c r="AF11" s="10" t="n"/>
+      <c r="AG11" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="63">
-    <mergeCell ref="R1:V1"/>
+  <mergeCells count="77">
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="W6:AA6"/>
-    <mergeCell ref="AB9:AG9"/>
     <mergeCell ref="C5:G5"/>
-    <mergeCell ref="K7:Q7"/>
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="R10:V10"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="W5:AA5"/>
-    <mergeCell ref="R4:V4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="H11:J11"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="R7:V7"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="K6:Q6"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="K3:Q3"/>
-    <mergeCell ref="W4:AA4"/>
-    <mergeCell ref="W1:AA1"/>
-    <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
-    <mergeCell ref="AB8:AG8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="K9:Q9"/>
-    <mergeCell ref="AB7:AG7"/>
-    <mergeCell ref="K5:Q5"/>
-    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="AB10:AG10"/>
     <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="C2:G2"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="R3:V3"/>
     <mergeCell ref="AB3:AG3"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:G8"/>
     <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="AB6:AG6"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="W9:AA9"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="AB4:AG4"/>
+    <mergeCell ref="R1:V1"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="R4:V4"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K10:Q10"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="AB8:AG8"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="K11:Q11"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K8:Q8"/>
+    <mergeCell ref="R9:V9"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="W4:AA4"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="W10:AA10"/>
+    <mergeCell ref="R11:V11"/>
+    <mergeCell ref="K7:Q7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="W3:AA3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="AB7:AG7"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="W9:AA9"/>
+    <mergeCell ref="H10:J10"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K8:Q8"/>
-    <mergeCell ref="AB4:AG4"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="AB9:AG9"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="AB11:AG11"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="AB6:AG6"/>
+    <mergeCell ref="W11:AA11"/>
     <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="R9:V9"/>
     <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6821,7 +6953,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7292,7 +7424,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8221,7 +8353,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8908,7 +9040,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -14598,7 +14730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK226"/>
+  <dimension ref="A1:AK227"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -14759,7 +14891,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -22860,204 +22992,211 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="18" customHeight="1">
+    <row r="168" ht="72" customHeight="1">
       <c r="D168" s="41" t="inlineStr">
         <is>
-          <t>shimei_sei / shimei_mei：必須、最大50文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="36" customHeight="1">
+          <t>shimei_sei / shimei_mei：必須、最大50文字、**漢字・ひらがな・カタカナ形式**（半角カナ・英数字不可。顧客要件 2026-07 でひらがな/カタカナ表記の氏名に対応するため漢字のみから緩和）。形式不正時は `VALIDATION_ERROR`（メッセージ「漢字・ひらがな・カタカナで入力してください。」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="54" customHeight="1">
       <c r="D169" s="41" t="inlineStr">
         <is>
+          <t>haitatsu_shimei_sei / haitatsu_shimei_mei：haitatsu_same_flg=false 時必須、shimei_sei/mei と同じ漢字・ひらがな・カタカナ形式</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="36" customHeight="1">
+      <c r="D170" s="41" t="inlineStr">
+        <is>
           <t>shimei_kana_sei / shimei_kana_mei：必須、最大100文字、ひらがな/カタカナ形式</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="18" customHeight="1">
-      <c r="D170" s="41" t="inlineStr">
-        <is>
-          <t>dokusya_busu：必須、半角数字。解約時は0</t>
         </is>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="D171" s="41" t="inlineStr">
         <is>
-          <t>yubin_no：必須、半角数字7桁</t>
+          <t>dokusya_busu：必須、半角数字。解約時は0</t>
         </is>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="D172" s="41" t="inlineStr">
         <is>
-          <t>todofuken_code / shikuchoson / chome_banchi：必須</t>
+          <t>yubin_no：必須、半角数字7桁</t>
         </is>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="D173" s="41" t="inlineStr">
         <is>
-          <t>renrakusaki_1：必須、半角数字</t>
+          <t>todofuken_code / shikuchoson / chome_banchi：必須</t>
         </is>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="D174" s="41" t="inlineStr">
         <is>
+          <t>renrakusaki_1：必須、半角数字</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="D175" s="41" t="inlineStr">
+        <is>
           <t>email：電子版/併読の場合は必須、形式チェック</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="72" customHeight="1">
-      <c r="D175" s="41" t="inlineStr">
+    <row r="176" ht="72" customHeight="1">
+      <c r="D176" s="41" t="inlineStr">
         <is>
           <t>haitatsu_same_flg=falseの場合：haitatsu_yubin_no, haitatsu_todofuken_code, haitatsu_shikuchoson, haitatsu_chome_banchi, haitatsu_shimei_*, haitatsu_shimei_kana_* が必須</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="18" customHeight="1">
-      <c r="D176" s="41" t="inlineStr">
+    <row r="177" ht="18" customHeight="1">
+      <c r="D177" s="41" t="inlineStr">
         <is>
           <t>hanbaiten_id / tanka_id：必須</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="54" customHeight="1">
-      <c r="D177" s="41" t="inlineStr">
+    <row r="178" ht="54" customHeight="1">
+      <c r="D178" s="41" t="inlineStr">
         <is>
           <t>shiharai_hoho：必須。1（口座引落）の場合：bank_shiten_id, hikiotoshi_yokin_shubetsu, hikiotoshi_koza_no, hikiotoshi_koza_meigi が必須</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="72" customHeight="1">
-      <c r="D178" s="41" t="inlineStr">
+    <row r="179" ht="72" customHeight="1">
+      <c r="D179" s="41" t="inlineStr">
         <is>
           <t>bank_shiten_id：口座引落時は必須、他の支払方法では任意。指定された場合は `m_shiten` に存在し、かつ ログインユーザー所属JA内（`m_shiten.ja_id = user.ja_id`）かつ `kinyu_shiten_flg = TRUE` であること（不正値は支払方法を問わず VALIDATION_ERROR）</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="36" customHeight="1">
-      <c r="D179" s="41" t="inlineStr">
+    <row r="180" ht="36" customHeight="1">
+      <c r="D180" s="41" t="inlineStr">
         <is>
           <t>yubin_kubun：任意。入力時は `m_code.code_category='YUBIN_KUBUN'`（0:空, 1:郵送）に存在する値であること</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="18" customHeight="1">
-      <c r="D180" s="41" t="inlineStr">
-        <is>
-          <t>dokusya_kaishi_date：必須、YYYY-MM-DD</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="D181" s="41" t="inlineStr">
         <is>
-          <t>joho_henko_tekiyo_date：任意、YYYY-MM-DD。入力時は未来日であること</t>
+          <t>dokusya_kaishi_date：必須、YYYY-MM-DD</t>
         </is>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="D182" s="41" t="inlineStr">
         <is>
-          <t>nogyosya_bunrui：購読者層分類で「農業者」を選択した場合は必須</t>
+          <t>joho_henko_tekiyo_date：任意、YYYY-MM-DD。入力時は未来日であること</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="D183" s="41" t="inlineStr">
         <is>
-          <t>seikyu_kaishi_month：電子版/併読の場合、YYYYMM形式</t>
+          <t>nogyosya_bunrui：購読者層分類で「農業者」を選択した場合は必須</t>
         </is>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="D184" s="41" t="inlineStr">
         <is>
+          <t>seikyu_kaishi_month：電子版/併読の場合、YYYYMM形式</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="D185" s="41" t="inlineStr">
+        <is>
           <t>biko：500文字以内</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="36" customHeight="1">
-      <c r="C185" s="41" t="inlineStr">
+    <row r="186" ht="36" customHeight="1">
+      <c r="C186" s="41" t="inlineStr">
         <is>
           <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="18" customHeight="1">
-      <c r="B186" s="27" t="inlineStr">
+    <row r="187" ht="18" customHeight="1">
+      <c r="B187" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="18" customHeight="1">
-      <c r="C187" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="C188" s="41" t="inlineStr">
         <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="C189" s="41" t="inlineStr">
         <is>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="C190" s="41" t="inlineStr">
+        <is>
           <t>必要権限: `dokusya.create`</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="36" customHeight="1">
-      <c r="C190" s="41" t="inlineStr">
+    <row r="191" ht="36" customHeight="1">
+      <c r="C191" s="41" t="inlineStr">
         <is>
           <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="18" customHeight="1">
-      <c r="C191" s="41" t="inlineStr">
+    <row r="192" ht="18" customHeight="1">
+      <c r="C192" s="41" t="inlineStr">
         <is>
           <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="36" customHeight="1">
-      <c r="C192" s="41" t="inlineStr">
-        <is>
-          <t>DataScope: `ja_id = user.ja_id`（サーバ側で自動設定。リクエストボディの ja_id は信頼しない）</t>
         </is>
       </c>
     </row>
     <row r="193" ht="36" customHeight="1">
       <c r="C193" s="41" t="inlineStr">
         <is>
+          <t>DataScope: `ja_id = user.ja_id`（サーバ側で自動設定。リクエストボディの ja_id は信頼しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="36" customHeight="1">
+      <c r="C194" s="41" t="inlineStr">
+        <is>
           <t>DataScope違反（他JAのレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="18" customHeight="1">
-      <c r="B194" s="27" t="inlineStr">
+    <row r="195" ht="18" customHeight="1">
+      <c r="B195" s="27" t="inlineStr">
         <is>
           <t>4.3 重複チェック（メールアドレス）</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="18" customHeight="1">
-      <c r="C195" s="41" t="inlineStr">
+    <row r="196" ht="18" customHeight="1">
+      <c r="C196" s="41" t="inlineStr">
         <is>
           <t>メールアドレスが入力されている場合、以下の条件で重複を確認する。</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="90" customHeight="1">
-      <c r="C196" s="42" t="inlineStr">
+    <row r="197" ht="90" customHeight="1">
+      <c r="C197" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) FROM t_dokusya
 WHERE email = :email
@@ -23066,85 +23205,85 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D196" s="10" t="n"/>
-      <c r="E196" s="10" t="n"/>
-      <c r="F196" s="10" t="n"/>
-      <c r="G196" s="10" t="n"/>
-      <c r="H196" s="10" t="n"/>
-      <c r="I196" s="10" t="n"/>
-      <c r="J196" s="10" t="n"/>
-      <c r="K196" s="10" t="n"/>
-      <c r="L196" s="10" t="n"/>
-      <c r="M196" s="10" t="n"/>
-      <c r="N196" s="10" t="n"/>
-      <c r="O196" s="10" t="n"/>
-      <c r="P196" s="10" t="n"/>
-      <c r="Q196" s="10" t="n"/>
-      <c r="R196" s="10" t="n"/>
-      <c r="S196" s="10" t="n"/>
-      <c r="T196" s="10" t="n"/>
-      <c r="U196" s="10" t="n"/>
-      <c r="V196" s="10" t="n"/>
-      <c r="W196" s="10" t="n"/>
-      <c r="X196" s="10" t="n"/>
-      <c r="Y196" s="10" t="n"/>
-      <c r="Z196" s="10" t="n"/>
-      <c r="AA196" s="10" t="n"/>
-      <c r="AB196" s="10" t="n"/>
-      <c r="AC196" s="10" t="n"/>
-      <c r="AD196" s="10" t="n"/>
-      <c r="AE196" s="10" t="n"/>
-      <c r="AF196" s="10" t="n"/>
-      <c r="AG196" s="10" t="n"/>
-      <c r="AH196" s="10" t="n"/>
-      <c r="AI196" s="10" t="n"/>
-      <c r="AJ196" s="10" t="n"/>
-      <c r="AK196" s="11" t="n"/>
-    </row>
-    <row r="197" ht="18" customHeight="1">
-      <c r="C197" s="41" t="inlineStr">
+      <c r="D197" s="10" t="n"/>
+      <c r="E197" s="10" t="n"/>
+      <c r="F197" s="10" t="n"/>
+      <c r="G197" s="10" t="n"/>
+      <c r="H197" s="10" t="n"/>
+      <c r="I197" s="10" t="n"/>
+      <c r="J197" s="10" t="n"/>
+      <c r="K197" s="10" t="n"/>
+      <c r="L197" s="10" t="n"/>
+      <c r="M197" s="10" t="n"/>
+      <c r="N197" s="10" t="n"/>
+      <c r="O197" s="10" t="n"/>
+      <c r="P197" s="10" t="n"/>
+      <c r="Q197" s="10" t="n"/>
+      <c r="R197" s="10" t="n"/>
+      <c r="S197" s="10" t="n"/>
+      <c r="T197" s="10" t="n"/>
+      <c r="U197" s="10" t="n"/>
+      <c r="V197" s="10" t="n"/>
+      <c r="W197" s="10" t="n"/>
+      <c r="X197" s="10" t="n"/>
+      <c r="Y197" s="10" t="n"/>
+      <c r="Z197" s="10" t="n"/>
+      <c r="AA197" s="10" t="n"/>
+      <c r="AB197" s="10" t="n"/>
+      <c r="AC197" s="10" t="n"/>
+      <c r="AD197" s="10" t="n"/>
+      <c r="AE197" s="10" t="n"/>
+      <c r="AF197" s="10" t="n"/>
+      <c r="AG197" s="10" t="n"/>
+      <c r="AH197" s="10" t="n"/>
+      <c r="AI197" s="10" t="n"/>
+      <c r="AJ197" s="10" t="n"/>
+      <c r="AK197" s="11" t="n"/>
+    </row>
+    <row r="198" ht="18" customHeight="1">
+      <c r="C198" s="41" t="inlineStr">
         <is>
           <t>重複がある場合：HTTP 400 (`DUPLICATE_EMAIL`)</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="18" customHeight="1">
-      <c r="B198" s="27" t="inlineStr">
+    <row r="199" ht="18" customHeight="1">
+      <c r="B199" s="27" t="inlineStr">
         <is>
           <t>4.4 データ登録</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="18" customHeight="1">
-      <c r="C199" s="41" t="inlineStr">
+    <row r="200" ht="18" customHeight="1">
+      <c r="C200" s="41" t="inlineStr">
         <is>
           <t>`denshi_shonin_status`（電子申込承認ステータス）の初期値:</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="18" customHeight="1">
-      <c r="D200" s="41" t="inlineStr">
-        <is>
-          <t>紙版（dokusya_shubetsu=1）: `NULL`（承認ワークフロー対象外）。</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="D201" s="41" t="inlineStr">
         <is>
+          <t>紙版（dokusya_shubetsu=1）: `NULL`（承認ワークフロー対象外）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="D202" s="41" t="inlineStr">
+        <is>
           <t>電子版（2）/ 併読（3）: `1`（承認済）。画面からの新規登録は職員操作のため</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="72" customHeight="1">
-      <c r="C202" s="41" t="inlineStr">
+    <row r="203" ht="72" customHeight="1">
+      <c r="C203" s="41" t="inlineStr">
         <is>
           <t>支払方法=1（口座引落）の場合、`bank_shiten_id` を以下のSQLで解決し、`jastem_toriatsukai_tenpo_code` および `jastem_tenpo_name` を取得して `t_dokusya.bank_branch_code` / `bank_branch_name` に非正規化保存する（画面設計書 機能定義 §10.1）。</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="144" customHeight="1">
-      <c r="C203" s="42" t="inlineStr">
+    <row r="204" ht="144" customHeight="1">
+      <c r="C204" s="42" t="inlineStr">
         <is>
           <t>SELECT shiten_id,
        jastem_toriatsukai_tenpo_code,
@@ -23156,113 +23295,113 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D203" s="10" t="n"/>
-      <c r="E203" s="10" t="n"/>
-      <c r="F203" s="10" t="n"/>
-      <c r="G203" s="10" t="n"/>
-      <c r="H203" s="10" t="n"/>
-      <c r="I203" s="10" t="n"/>
-      <c r="J203" s="10" t="n"/>
-      <c r="K203" s="10" t="n"/>
-      <c r="L203" s="10" t="n"/>
-      <c r="M203" s="10" t="n"/>
-      <c r="N203" s="10" t="n"/>
-      <c r="O203" s="10" t="n"/>
-      <c r="P203" s="10" t="n"/>
-      <c r="Q203" s="10" t="n"/>
-      <c r="R203" s="10" t="n"/>
-      <c r="S203" s="10" t="n"/>
-      <c r="T203" s="10" t="n"/>
-      <c r="U203" s="10" t="n"/>
-      <c r="V203" s="10" t="n"/>
-      <c r="W203" s="10" t="n"/>
-      <c r="X203" s="10" t="n"/>
-      <c r="Y203" s="10" t="n"/>
-      <c r="Z203" s="10" t="n"/>
-      <c r="AA203" s="10" t="n"/>
-      <c r="AB203" s="10" t="n"/>
-      <c r="AC203" s="10" t="n"/>
-      <c r="AD203" s="10" t="n"/>
-      <c r="AE203" s="10" t="n"/>
-      <c r="AF203" s="10" t="n"/>
-      <c r="AG203" s="10" t="n"/>
-      <c r="AH203" s="10" t="n"/>
-      <c r="AI203" s="10" t="n"/>
-      <c r="AJ203" s="10" t="n"/>
-      <c r="AK203" s="11" t="n"/>
-    </row>
-    <row r="204" ht="36" customHeight="1">
-      <c r="C204" s="41" t="inlineStr">
-        <is>
-          <t>該当レコードがない場合：HTTP 400 (`VALIDATION_ERROR`)（`field: 'bank_shiten_id'`）。</t>
-        </is>
-      </c>
+      <c r="D204" s="10" t="n"/>
+      <c r="E204" s="10" t="n"/>
+      <c r="F204" s="10" t="n"/>
+      <c r="G204" s="10" t="n"/>
+      <c r="H204" s="10" t="n"/>
+      <c r="I204" s="10" t="n"/>
+      <c r="J204" s="10" t="n"/>
+      <c r="K204" s="10" t="n"/>
+      <c r="L204" s="10" t="n"/>
+      <c r="M204" s="10" t="n"/>
+      <c r="N204" s="10" t="n"/>
+      <c r="O204" s="10" t="n"/>
+      <c r="P204" s="10" t="n"/>
+      <c r="Q204" s="10" t="n"/>
+      <c r="R204" s="10" t="n"/>
+      <c r="S204" s="10" t="n"/>
+      <c r="T204" s="10" t="n"/>
+      <c r="U204" s="10" t="n"/>
+      <c r="V204" s="10" t="n"/>
+      <c r="W204" s="10" t="n"/>
+      <c r="X204" s="10" t="n"/>
+      <c r="Y204" s="10" t="n"/>
+      <c r="Z204" s="10" t="n"/>
+      <c r="AA204" s="10" t="n"/>
+      <c r="AB204" s="10" t="n"/>
+      <c r="AC204" s="10" t="n"/>
+      <c r="AD204" s="10" t="n"/>
+      <c r="AE204" s="10" t="n"/>
+      <c r="AF204" s="10" t="n"/>
+      <c r="AG204" s="10" t="n"/>
+      <c r="AH204" s="10" t="n"/>
+      <c r="AI204" s="10" t="n"/>
+      <c r="AJ204" s="10" t="n"/>
+      <c r="AK204" s="11" t="n"/>
     </row>
     <row r="205" ht="36" customHeight="1">
       <c r="C205" s="41" t="inlineStr">
         <is>
+          <t>該当レコードがない場合：HTTP 400 (`VALIDATION_ERROR`)（`field: 'bank_shiten_id'`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="36" customHeight="1">
+      <c r="C206" s="41" t="inlineStr">
+        <is>
           <t>支払方法 ≠ 1 の場合、`bank_branch_code = ''` / `bank_branch_name = ''` を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="18" customHeight="1">
-      <c r="C206" s="41" t="inlineStr">
+    <row r="207" ht="18" customHeight="1">
+      <c r="C207" s="41" t="inlineStr">
         <is>
           <t>t_dokusya にレコードを INSERT する。</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="36" customHeight="1">
-      <c r="C207" s="41" t="inlineStr">
+    <row r="208" ht="36" customHeight="1">
+      <c r="C208" s="41" t="inlineStr">
         <is>
           <t>t_dokusya_rireki に履歴レコードを INSERT する（rireki_no=1, saishin_data_flg=true）。</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="18" customHeight="1">
-      <c r="C208" s="41" t="inlineStr">
+    <row r="209" ht="18" customHeight="1">
+      <c r="C209" s="41" t="inlineStr">
         <is>
           <t>フラグ設定ルール：</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="18" customHeight="1">
-      <c r="D209" s="41" t="inlineStr">
-        <is>
-          <t>saishin_data_flg = true</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="D210" s="41" t="inlineStr">
         <is>
-          <t>shinki_flg = (tetsuzuki_shurui=1) ? true : false</t>
+          <t>saishin_data_flg = true</t>
         </is>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="D211" s="41" t="inlineStr">
         <is>
-          <t>kaiyaku_flg = (tetsuzuki_shurui=0) ? true : false</t>
+          <t>shinki_flg = (tetsuzuki_shurui=1) ? true : false</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="D212" s="41" t="inlineStr">
         <is>
+          <t>kaiyaku_flg = (tetsuzuki_shurui=0) ? true : false</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="D213" s="41" t="inlineStr">
+        <is>
           <t>zougen_hokoku_flg = true（新規登録は増減対象）</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="18" customHeight="1">
-      <c r="C213" s="41" t="inlineStr">
+    <row r="214" ht="18" customHeight="1">
+      <c r="C214" s="41" t="inlineStr">
         <is>
           <t>解約時は dokusya_busu=0 を強制する。</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="409" customHeight="1">
-      <c r="C214" s="42" t="inlineStr">
+    <row r="215" ht="409" customHeight="1">
+      <c r="C215" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya (
   ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -23308,43 +23447,43 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D214" s="10" t="n"/>
-      <c r="E214" s="10" t="n"/>
-      <c r="F214" s="10" t="n"/>
-      <c r="G214" s="10" t="n"/>
-      <c r="H214" s="10" t="n"/>
-      <c r="I214" s="10" t="n"/>
-      <c r="J214" s="10" t="n"/>
-      <c r="K214" s="10" t="n"/>
-      <c r="L214" s="10" t="n"/>
-      <c r="M214" s="10" t="n"/>
-      <c r="N214" s="10" t="n"/>
-      <c r="O214" s="10" t="n"/>
-      <c r="P214" s="10" t="n"/>
-      <c r="Q214" s="10" t="n"/>
-      <c r="R214" s="10" t="n"/>
-      <c r="S214" s="10" t="n"/>
-      <c r="T214" s="10" t="n"/>
-      <c r="U214" s="10" t="n"/>
-      <c r="V214" s="10" t="n"/>
-      <c r="W214" s="10" t="n"/>
-      <c r="X214" s="10" t="n"/>
-      <c r="Y214" s="10" t="n"/>
-      <c r="Z214" s="10" t="n"/>
-      <c r="AA214" s="10" t="n"/>
-      <c r="AB214" s="10" t="n"/>
-      <c r="AC214" s="10" t="n"/>
-      <c r="AD214" s="10" t="n"/>
-      <c r="AE214" s="10" t="n"/>
-      <c r="AF214" s="10" t="n"/>
-      <c r="AG214" s="10" t="n"/>
-      <c r="AH214" s="10" t="n"/>
-      <c r="AI214" s="10" t="n"/>
-      <c r="AJ214" s="10" t="n"/>
-      <c r="AK214" s="11" t="n"/>
-    </row>
-    <row r="215" ht="409" customHeight="1">
-      <c r="C215" s="42" t="inlineStr">
+      <c r="D215" s="10" t="n"/>
+      <c r="E215" s="10" t="n"/>
+      <c r="F215" s="10" t="n"/>
+      <c r="G215" s="10" t="n"/>
+      <c r="H215" s="10" t="n"/>
+      <c r="I215" s="10" t="n"/>
+      <c r="J215" s="10" t="n"/>
+      <c r="K215" s="10" t="n"/>
+      <c r="L215" s="10" t="n"/>
+      <c r="M215" s="10" t="n"/>
+      <c r="N215" s="10" t="n"/>
+      <c r="O215" s="10" t="n"/>
+      <c r="P215" s="10" t="n"/>
+      <c r="Q215" s="10" t="n"/>
+      <c r="R215" s="10" t="n"/>
+      <c r="S215" s="10" t="n"/>
+      <c r="T215" s="10" t="n"/>
+      <c r="U215" s="10" t="n"/>
+      <c r="V215" s="10" t="n"/>
+      <c r="W215" s="10" t="n"/>
+      <c r="X215" s="10" t="n"/>
+      <c r="Y215" s="10" t="n"/>
+      <c r="Z215" s="10" t="n"/>
+      <c r="AA215" s="10" t="n"/>
+      <c r="AB215" s="10" t="n"/>
+      <c r="AC215" s="10" t="n"/>
+      <c r="AD215" s="10" t="n"/>
+      <c r="AE215" s="10" t="n"/>
+      <c r="AF215" s="10" t="n"/>
+      <c r="AG215" s="10" t="n"/>
+      <c r="AH215" s="10" t="n"/>
+      <c r="AI215" s="10" t="n"/>
+      <c r="AJ215" s="10" t="n"/>
+      <c r="AK215" s="11" t="n"/>
+    </row>
+    <row r="216" ht="409" customHeight="1">
+      <c r="C216" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya_rireki (
   dokusya_id, rireki_no, ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -23395,57 +23534,57 @@
 )</t>
         </is>
       </c>
-      <c r="D215" s="10" t="n"/>
-      <c r="E215" s="10" t="n"/>
-      <c r="F215" s="10" t="n"/>
-      <c r="G215" s="10" t="n"/>
-      <c r="H215" s="10" t="n"/>
-      <c r="I215" s="10" t="n"/>
-      <c r="J215" s="10" t="n"/>
-      <c r="K215" s="10" t="n"/>
-      <c r="L215" s="10" t="n"/>
-      <c r="M215" s="10" t="n"/>
-      <c r="N215" s="10" t="n"/>
-      <c r="O215" s="10" t="n"/>
-      <c r="P215" s="10" t="n"/>
-      <c r="Q215" s="10" t="n"/>
-      <c r="R215" s="10" t="n"/>
-      <c r="S215" s="10" t="n"/>
-      <c r="T215" s="10" t="n"/>
-      <c r="U215" s="10" t="n"/>
-      <c r="V215" s="10" t="n"/>
-      <c r="W215" s="10" t="n"/>
-      <c r="X215" s="10" t="n"/>
-      <c r="Y215" s="10" t="n"/>
-      <c r="Z215" s="10" t="n"/>
-      <c r="AA215" s="10" t="n"/>
-      <c r="AB215" s="10" t="n"/>
-      <c r="AC215" s="10" t="n"/>
-      <c r="AD215" s="10" t="n"/>
-      <c r="AE215" s="10" t="n"/>
-      <c r="AF215" s="10" t="n"/>
-      <c r="AG215" s="10" t="n"/>
-      <c r="AH215" s="10" t="n"/>
-      <c r="AI215" s="10" t="n"/>
-      <c r="AJ215" s="10" t="n"/>
-      <c r="AK215" s="11" t="n"/>
-    </row>
-    <row r="216" ht="18" customHeight="1">
-      <c r="B216" s="27" t="inlineStr">
+      <c r="D216" s="10" t="n"/>
+      <c r="E216" s="10" t="n"/>
+      <c r="F216" s="10" t="n"/>
+      <c r="G216" s="10" t="n"/>
+      <c r="H216" s="10" t="n"/>
+      <c r="I216" s="10" t="n"/>
+      <c r="J216" s="10" t="n"/>
+      <c r="K216" s="10" t="n"/>
+      <c r="L216" s="10" t="n"/>
+      <c r="M216" s="10" t="n"/>
+      <c r="N216" s="10" t="n"/>
+      <c r="O216" s="10" t="n"/>
+      <c r="P216" s="10" t="n"/>
+      <c r="Q216" s="10" t="n"/>
+      <c r="R216" s="10" t="n"/>
+      <c r="S216" s="10" t="n"/>
+      <c r="T216" s="10" t="n"/>
+      <c r="U216" s="10" t="n"/>
+      <c r="V216" s="10" t="n"/>
+      <c r="W216" s="10" t="n"/>
+      <c r="X216" s="10" t="n"/>
+      <c r="Y216" s="10" t="n"/>
+      <c r="Z216" s="10" t="n"/>
+      <c r="AA216" s="10" t="n"/>
+      <c r="AB216" s="10" t="n"/>
+      <c r="AC216" s="10" t="n"/>
+      <c r="AD216" s="10" t="n"/>
+      <c r="AE216" s="10" t="n"/>
+      <c r="AF216" s="10" t="n"/>
+      <c r="AG216" s="10" t="n"/>
+      <c r="AH216" s="10" t="n"/>
+      <c r="AI216" s="10" t="n"/>
+      <c r="AJ216" s="10" t="n"/>
+      <c r="AK216" s="11" t="n"/>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="B217" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="18" customHeight="1">
-      <c r="C217" s="41" t="inlineStr">
+    <row r="218" ht="18" customHeight="1">
+      <c r="C218" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="216" customHeight="1">
-      <c r="C218" s="42" t="inlineStr">
+    <row r="219" ht="216" customHeight="1">
+      <c r="C219" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -23461,92 +23600,92 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D218" s="10" t="n"/>
-      <c r="E218" s="10" t="n"/>
-      <c r="F218" s="10" t="n"/>
-      <c r="G218" s="10" t="n"/>
-      <c r="H218" s="10" t="n"/>
-      <c r="I218" s="10" t="n"/>
-      <c r="J218" s="10" t="n"/>
-      <c r="K218" s="10" t="n"/>
-      <c r="L218" s="10" t="n"/>
-      <c r="M218" s="10" t="n"/>
-      <c r="N218" s="10" t="n"/>
-      <c r="O218" s="10" t="n"/>
-      <c r="P218" s="10" t="n"/>
-      <c r="Q218" s="10" t="n"/>
-      <c r="R218" s="10" t="n"/>
-      <c r="S218" s="10" t="n"/>
-      <c r="T218" s="10" t="n"/>
-      <c r="U218" s="10" t="n"/>
-      <c r="V218" s="10" t="n"/>
-      <c r="W218" s="10" t="n"/>
-      <c r="X218" s="10" t="n"/>
-      <c r="Y218" s="10" t="n"/>
-      <c r="Z218" s="10" t="n"/>
-      <c r="AA218" s="10" t="n"/>
-      <c r="AB218" s="10" t="n"/>
-      <c r="AC218" s="10" t="n"/>
-      <c r="AD218" s="10" t="n"/>
-      <c r="AE218" s="10" t="n"/>
-      <c r="AF218" s="10" t="n"/>
-      <c r="AG218" s="10" t="n"/>
-      <c r="AH218" s="10" t="n"/>
-      <c r="AI218" s="10" t="n"/>
-      <c r="AJ218" s="10" t="n"/>
-      <c r="AK218" s="11" t="n"/>
-    </row>
-    <row r="219" ht="18" customHeight="1">
-      <c r="C219" s="41" t="inlineStr">
+      <c r="D219" s="10" t="n"/>
+      <c r="E219" s="10" t="n"/>
+      <c r="F219" s="10" t="n"/>
+      <c r="G219" s="10" t="n"/>
+      <c r="H219" s="10" t="n"/>
+      <c r="I219" s="10" t="n"/>
+      <c r="J219" s="10" t="n"/>
+      <c r="K219" s="10" t="n"/>
+      <c r="L219" s="10" t="n"/>
+      <c r="M219" s="10" t="n"/>
+      <c r="N219" s="10" t="n"/>
+      <c r="O219" s="10" t="n"/>
+      <c r="P219" s="10" t="n"/>
+      <c r="Q219" s="10" t="n"/>
+      <c r="R219" s="10" t="n"/>
+      <c r="S219" s="10" t="n"/>
+      <c r="T219" s="10" t="n"/>
+      <c r="U219" s="10" t="n"/>
+      <c r="V219" s="10" t="n"/>
+      <c r="W219" s="10" t="n"/>
+      <c r="X219" s="10" t="n"/>
+      <c r="Y219" s="10" t="n"/>
+      <c r="Z219" s="10" t="n"/>
+      <c r="AA219" s="10" t="n"/>
+      <c r="AB219" s="10" t="n"/>
+      <c r="AC219" s="10" t="n"/>
+      <c r="AD219" s="10" t="n"/>
+      <c r="AE219" s="10" t="n"/>
+      <c r="AF219" s="10" t="n"/>
+      <c r="AG219" s="10" t="n"/>
+      <c r="AH219" s="10" t="n"/>
+      <c r="AI219" s="10" t="n"/>
+      <c r="AJ219" s="10" t="n"/>
+      <c r="AK219" s="11" t="n"/>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="C220" s="41" t="inlineStr">
         <is>
           <t>`before_value`：INSERT のため空文字列を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="36" customHeight="1">
-      <c r="C220" s="41" t="inlineStr">
+    <row r="221" ht="36" customHeight="1">
+      <c r="C221" s="41" t="inlineStr">
         <is>
           <t>`after_value`：登録されたデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="18" customHeight="1">
-      <c r="B221" s="27" t="inlineStr">
+    <row r="222" ht="18" customHeight="1">
+      <c r="B222" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="18" customHeight="1">
-      <c r="C222" s="41" t="inlineStr">
+    <row r="223" ht="18" customHeight="1">
+      <c r="C223" s="41" t="inlineStr">
         <is>
           <t>登録されたデータを data オブジェクトとして返却する。HTTP 201。</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="18" customHeight="1">
-      <c r="B223" s="27" t="inlineStr">
+    <row r="224" ht="18" customHeight="1">
+      <c r="B224" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="18" customHeight="1">
-      <c r="C224" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="C225" s="41" t="inlineStr">
         <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="18" customHeight="1">
+      <c r="C226" s="41" t="inlineStr">
+        <is>
           <t>エラー発生時はエラーログを記録する（`log_type = 3`、トランザクション外で記録）。</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="216" customHeight="1">
-      <c r="C226" s="42" t="inlineStr">
+    <row r="227" ht="216" customHeight="1">
+      <c r="C227" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -23562,47 +23701,46 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D226" s="10" t="n"/>
-      <c r="E226" s="10" t="n"/>
-      <c r="F226" s="10" t="n"/>
-      <c r="G226" s="10" t="n"/>
-      <c r="H226" s="10" t="n"/>
-      <c r="I226" s="10" t="n"/>
-      <c r="J226" s="10" t="n"/>
-      <c r="K226" s="10" t="n"/>
-      <c r="L226" s="10" t="n"/>
-      <c r="M226" s="10" t="n"/>
-      <c r="N226" s="10" t="n"/>
-      <c r="O226" s="10" t="n"/>
-      <c r="P226" s="10" t="n"/>
-      <c r="Q226" s="10" t="n"/>
-      <c r="R226" s="10" t="n"/>
-      <c r="S226" s="10" t="n"/>
-      <c r="T226" s="10" t="n"/>
-      <c r="U226" s="10" t="n"/>
-      <c r="V226" s="10" t="n"/>
-      <c r="W226" s="10" t="n"/>
-      <c r="X226" s="10" t="n"/>
-      <c r="Y226" s="10" t="n"/>
-      <c r="Z226" s="10" t="n"/>
-      <c r="AA226" s="10" t="n"/>
-      <c r="AB226" s="10" t="n"/>
-      <c r="AC226" s="10" t="n"/>
-      <c r="AD226" s="10" t="n"/>
-      <c r="AE226" s="10" t="n"/>
-      <c r="AF226" s="10" t="n"/>
-      <c r="AG226" s="10" t="n"/>
-      <c r="AH226" s="10" t="n"/>
-      <c r="AI226" s="10" t="n"/>
-      <c r="AJ226" s="10" t="n"/>
-      <c r="AK226" s="11" t="n"/>
+      <c r="D227" s="10" t="n"/>
+      <c r="E227" s="10" t="n"/>
+      <c r="F227" s="10" t="n"/>
+      <c r="G227" s="10" t="n"/>
+      <c r="H227" s="10" t="n"/>
+      <c r="I227" s="10" t="n"/>
+      <c r="J227" s="10" t="n"/>
+      <c r="K227" s="10" t="n"/>
+      <c r="L227" s="10" t="n"/>
+      <c r="M227" s="10" t="n"/>
+      <c r="N227" s="10" t="n"/>
+      <c r="O227" s="10" t="n"/>
+      <c r="P227" s="10" t="n"/>
+      <c r="Q227" s="10" t="n"/>
+      <c r="R227" s="10" t="n"/>
+      <c r="S227" s="10" t="n"/>
+      <c r="T227" s="10" t="n"/>
+      <c r="U227" s="10" t="n"/>
+      <c r="V227" s="10" t="n"/>
+      <c r="W227" s="10" t="n"/>
+      <c r="X227" s="10" t="n"/>
+      <c r="Y227" s="10" t="n"/>
+      <c r="Z227" s="10" t="n"/>
+      <c r="AA227" s="10" t="n"/>
+      <c r="AB227" s="10" t="n"/>
+      <c r="AC227" s="10" t="n"/>
+      <c r="AD227" s="10" t="n"/>
+      <c r="AE227" s="10" t="n"/>
+      <c r="AF227" s="10" t="n"/>
+      <c r="AG227" s="10" t="n"/>
+      <c r="AH227" s="10" t="n"/>
+      <c r="AI227" s="10" t="n"/>
+      <c r="AJ227" s="10" t="n"/>
+      <c r="AK227" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="858">
+  <mergeCells count="859">
     <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="B144:I144"/>
-    <mergeCell ref="D200:AK200"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="M135:P135"/>
     <mergeCell ref="Y61:AB61"/>
@@ -23612,6 +23750,7 @@
     <mergeCell ref="Q78:S78"/>
     <mergeCell ref="M72:P72"/>
     <mergeCell ref="Q114:S114"/>
+    <mergeCell ref="D202:AK202"/>
     <mergeCell ref="T137:X137"/>
     <mergeCell ref="D125:L125"/>
     <mergeCell ref="T53:X53"/>
@@ -23658,6 +23797,7 @@
     <mergeCell ref="AC57:AE57"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Y59:AB59"/>
+    <mergeCell ref="D213:AK213"/>
     <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="AF101:AK101"/>
     <mergeCell ref="T37:X37"/>
@@ -23675,7 +23815,6 @@
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="C38:L38"/>
     <mergeCell ref="Q109:S109"/>
-    <mergeCell ref="C195:AK195"/>
     <mergeCell ref="T122:X122"/>
     <mergeCell ref="M103:P103"/>
     <mergeCell ref="Y116:AE116"/>
@@ -23708,7 +23847,6 @@
     <mergeCell ref="Y64:AB64"/>
     <mergeCell ref="Y51:AB51"/>
     <mergeCell ref="T69:X69"/>
-    <mergeCell ref="C213:AK213"/>
     <mergeCell ref="D128:L128"/>
     <mergeCell ref="AC71:AE71"/>
     <mergeCell ref="Y119:AE119"/>
@@ -23775,7 +23913,6 @@
     <mergeCell ref="M104:P104"/>
     <mergeCell ref="Q64:S64"/>
     <mergeCell ref="B153:I153"/>
-    <mergeCell ref="D209:AK209"/>
     <mergeCell ref="T77:X77"/>
     <mergeCell ref="Y65:AB65"/>
     <mergeCell ref="M41:P41"/>
@@ -23791,9 +23928,11 @@
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="C79:C139"/>
     <mergeCell ref="M66:P66"/>
+    <mergeCell ref="C216:AK216"/>
     <mergeCell ref="Y87:AE87"/>
     <mergeCell ref="M130:P130"/>
     <mergeCell ref="C218:AK218"/>
+    <mergeCell ref="B187:AK187"/>
     <mergeCell ref="Y89:AE89"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="AF28:AK28"/>
@@ -23807,7 +23946,6 @@
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="AF70:AK70"/>
     <mergeCell ref="Q115:S115"/>
-    <mergeCell ref="B216:AK216"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="Y60:AB60"/>
     <mergeCell ref="T96:X96"/>
@@ -23931,7 +24069,6 @@
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q84:S84"/>
     <mergeCell ref="C78:L78"/>
-    <mergeCell ref="C187:AK187"/>
     <mergeCell ref="Y91:AE91"/>
     <mergeCell ref="D102:L102"/>
     <mergeCell ref="M34:P34"/>
@@ -23954,7 +24091,6 @@
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
-    <mergeCell ref="C222:AK222"/>
     <mergeCell ref="AC45:AE45"/>
     <mergeCell ref="D183:AK183"/>
     <mergeCell ref="T56:X56"/>
@@ -23965,9 +24101,12 @@
     <mergeCell ref="T99:X99"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="AC47:AE47"/>
+    <mergeCell ref="D185:AK185"/>
     <mergeCell ref="Y109:AE109"/>
+    <mergeCell ref="B224:AK224"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="T107:X107"/>
+    <mergeCell ref="B199:AK199"/>
     <mergeCell ref="T101:X101"/>
     <mergeCell ref="M136:P136"/>
     <mergeCell ref="C190:AK190"/>
@@ -23988,7 +24127,6 @@
     <mergeCell ref="M58:P58"/>
     <mergeCell ref="AC50:AE50"/>
     <mergeCell ref="AF138:AK138"/>
-    <mergeCell ref="C185:AK185"/>
     <mergeCell ref="Q123:S123"/>
     <mergeCell ref="C68:L68"/>
     <mergeCell ref="T62:X62"/>
@@ -23996,6 +24134,7 @@
     <mergeCell ref="T133:X133"/>
     <mergeCell ref="D121:L121"/>
     <mergeCell ref="T127:X127"/>
+    <mergeCell ref="B217:AK217"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="T64:X64"/>
     <mergeCell ref="T135:X135"/>
@@ -24074,6 +24213,7 @@
     <mergeCell ref="D131:L131"/>
     <mergeCell ref="Q126:S126"/>
     <mergeCell ref="Y52:AB52"/>
+    <mergeCell ref="C209:AK209"/>
     <mergeCell ref="T136:X136"/>
     <mergeCell ref="AC68:AE68"/>
     <mergeCell ref="D124:L124"/>
@@ -24132,18 +24272,16 @@
     <mergeCell ref="M105:P105"/>
     <mergeCell ref="Q121:S121"/>
     <mergeCell ref="A75:AK75"/>
-    <mergeCell ref="C224:AK224"/>
     <mergeCell ref="D139:L139"/>
     <mergeCell ref="M120:P120"/>
     <mergeCell ref="D179:AK179"/>
-    <mergeCell ref="C199:AK199"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="AF116:AK116"/>
     <mergeCell ref="T126:X126"/>
     <mergeCell ref="M101:P101"/>
     <mergeCell ref="C52:L52"/>
     <mergeCell ref="Q63:S63"/>
-    <mergeCell ref="C217:AK217"/>
+    <mergeCell ref="C186:AK186"/>
     <mergeCell ref="AF108:AK108"/>
     <mergeCell ref="Y136:AE136"/>
     <mergeCell ref="Q50:S50"/>
@@ -24169,7 +24307,6 @@
     <mergeCell ref="Y68:AB68"/>
     <mergeCell ref="D117:L117"/>
     <mergeCell ref="D92:L92"/>
-    <mergeCell ref="B186:AK186"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="Y55:AB55"/>
     <mergeCell ref="T79:X79"/>
@@ -24209,16 +24346,17 @@
     <mergeCell ref="AF124:AK124"/>
     <mergeCell ref="C225:AK225"/>
     <mergeCell ref="AC65:AE65"/>
+    <mergeCell ref="C200:AK200"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="Y63:AB63"/>
     <mergeCell ref="AF126:AK126"/>
     <mergeCell ref="AF109:AK109"/>
+    <mergeCell ref="C227:AK227"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="D82:L82"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="C45:L45"/>
     <mergeCell ref="M123:P123"/>
-    <mergeCell ref="C202:AK202"/>
     <mergeCell ref="M110:P110"/>
     <mergeCell ref="T104:X104"/>
     <mergeCell ref="AF46:AK46"/>
@@ -24233,7 +24371,6 @@
     <mergeCell ref="AF61:AK61"/>
     <mergeCell ref="M108:P108"/>
     <mergeCell ref="D100:L100"/>
-    <mergeCell ref="B198:AK198"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="Q68:S68"/>
     <mergeCell ref="Y137:AE137"/>
@@ -24288,6 +24425,7 @@
     <mergeCell ref="T94:X94"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="B222:AK222"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="T66:X66"/>
     <mergeCell ref="D115:L115"/>
@@ -24297,7 +24435,6 @@
     <mergeCell ref="AF117:AK117"/>
     <mergeCell ref="Y79:AE79"/>
     <mergeCell ref="D90:L90"/>
-    <mergeCell ref="B221:AK221"/>
     <mergeCell ref="AF67:AK67"/>
     <mergeCell ref="AF132:AK132"/>
     <mergeCell ref="C59:L59"/>
@@ -24334,6 +24471,7 @@
     <mergeCell ref="Y72:AB72"/>
     <mergeCell ref="D118:L118"/>
     <mergeCell ref="M44:P44"/>
+    <mergeCell ref="C221:AK221"/>
     <mergeCell ref="C196:AK196"/>
     <mergeCell ref="AC51:AE51"/>
     <mergeCell ref="AF38:AK38"/>
@@ -24341,7 +24479,9 @@
     <mergeCell ref="M79:P79"/>
     <mergeCell ref="Y92:AE92"/>
     <mergeCell ref="M73:P73"/>
+    <mergeCell ref="C223:AK223"/>
     <mergeCell ref="M60:P60"/>
+    <mergeCell ref="C198:AK198"/>
     <mergeCell ref="Q87:S87"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="Y94:AE94"/>
@@ -24354,7 +24494,6 @@
     <mergeCell ref="D96:L96"/>
     <mergeCell ref="T102:X102"/>
     <mergeCell ref="M139:P139"/>
-    <mergeCell ref="B194:AK194"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="Q82:S82"/>
@@ -24364,7 +24503,6 @@
     <mergeCell ref="Q118:S118"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="B223:AK223"/>
     <mergeCell ref="Q93:S93"/>
     <mergeCell ref="D181:AK181"/>
     <mergeCell ref="D116:L116"/>
@@ -24375,6 +24513,7 @@
     <mergeCell ref="Q113:S113"/>
     <mergeCell ref="D91:L91"/>
     <mergeCell ref="T97:X97"/>
+    <mergeCell ref="B195:AK195"/>
     <mergeCell ref="Y120:AE120"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="T47:X47"/>
@@ -24454,6 +24593,7 @@
     <mergeCell ref="Y129:AE129"/>
     <mergeCell ref="Y123:AE123"/>
     <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="C194:AK194"/>
     <mergeCell ref="M77:P77"/>
     <mergeCell ref="M133:P133"/>
     <mergeCell ref="AF29:AK29"/>
@@ -24629,7 +24769,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -27215,7 +27355,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
@@ -1517,7 +1517,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3579,7 +3579,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6011,7 +6011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AG13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6702,8 +6702,126 @@
       <c r="AF11" s="10" t="n"/>
       <c r="AG11" s="11" t="n"/>
     </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="11" t="n"/>
+      <c r="R12" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07：氏名4項目（`shimei_sei`/`shimei_mei`/`haitatsu_shimei_sei`/`haitatsu_shimei_mei`）の形式チェックを **漢字・ひらがな・カタカナ → 漢字・ひらがな・カタカナ・アルファベット許容** に拡張（半角A-Za-z・全角Ａ-Ｚ/ａ-ｚ可、半角カナ・数字不可）。メッセージを「漢字・ひらがな・カタカナ・アルファベットで入力してください。」に変更。かな項目は変更なし。</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n"/>
+      <c r="V12" s="11" t="n"/>
+      <c r="W12" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X12" s="10" t="n"/>
+      <c r="Y12" s="10" t="n"/>
+      <c r="Z12" s="10" t="n"/>
+      <c r="AA12" s="11" t="n"/>
+      <c r="AB12" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC12" s="10" t="n"/>
+      <c r="AD12" s="10" t="n"/>
+      <c r="AE12" s="10" t="n"/>
+      <c r="AF12" s="10" t="n"/>
+      <c r="AG12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="11" t="n"/>
+      <c r="R13" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07：電子版承認(API-011-004)にリクエストボディ任意 `tanka_id` を追加。承認待ち画面では新聞単価のみ編集可のため、承認時に編集後の単価を保存してから `denshi_shonin_status=1` へ確定する。指定時はテナント跨ぎ FK 検証（`m_tanka` 存在＋自JA）を行う（他JA単価は `DATA_SCOPE_VIOLATION`）。あわせて電子版の編集画面挙動を承認ステータス別に明記：承認待ち(0)=単価のみ編集可＋承認/否認ボタン、承認済(1)=通常編集、否認(2)=全項目読取専用（紙版は本ワークフロー対象外）。</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="11" t="n"/>
+      <c r="W13" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="11" t="n"/>
+      <c r="AB13" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC13" s="10" t="n"/>
+      <c r="AD13" s="10" t="n"/>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" s="10" t="n"/>
+      <c r="AG13" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="77">
+  <mergeCells count="91">
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="C5:G5"/>
@@ -6733,9 +6851,12 @@
     <mergeCell ref="K10:Q10"/>
     <mergeCell ref="K6:Q6"/>
     <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="AB13:AG13"/>
     <mergeCell ref="AB8:AG8"/>
     <mergeCell ref="K9:Q9"/>
     <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="W12:AA12"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="K11:Q11"/>
     <mergeCell ref="A8:B8"/>
@@ -6750,11 +6871,15 @@
     <mergeCell ref="R11:V11"/>
     <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="R13:V13"/>
+    <mergeCell ref="AB12:AG12"/>
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H13:J13"/>
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C9:G9"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="A5:B5"/>
@@ -6766,19 +6891,26 @@
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K12:Q12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="W13:AA13"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB9:AG9"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="K13:Q13"/>
     <mergeCell ref="AB11:AG11"/>
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="R12:V12"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="W11:AA11"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
@@ -6953,7 +7085,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7424,7 +7556,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8353,7 +8485,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8669,7 +8801,7 @@
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="19" t="inlineStr">
         <is>
-          <t>電子版申込の購読者を承認する（denshi_shonin_status 0→1）。新規履歴レコードを作成。</t>
+          <t>電子版申込の購読者を承認する（denshi_shonin_status 0→1）。承認待ち画面で編集した新聞単価（tanka_id）を任意で同時保存してから承認確定する。</t>
         </is>
       </c>
       <c r="T9" s="10" t="n"/>
@@ -9040,7 +9172,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -14891,7 +15023,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -22995,14 +23127,14 @@
     <row r="168" ht="72" customHeight="1">
       <c r="D168" s="41" t="inlineStr">
         <is>
-          <t>shimei_sei / shimei_mei：必須、最大50文字、**漢字・ひらがな・カタカナ形式**（半角カナ・英数字不可。顧客要件 2026-07 でひらがな/カタカナ表記の氏名に対応するため漢字のみから緩和）。形式不正時は `VALIDATION_ERROR`（メッセージ「漢字・ひらがな・カタカナで入力してください。」）</t>
+          <t>shimei_sei / shimei_mei：必須、最大50文字、**漢字・ひらがな・カタカナ・アルファベット形式**（半角英字A-Za-z・全角英字Ａ-Ｚ/ａ-ｚ可、半角カナ・数字不可。顧客要件 2026-07 でひらがな/カタカナ/アルファベット表記の氏名に対応）。形式不正時は `VALIDATION_ERROR`（メッセージ「漢字・ひらがな・カタカナ・アルファベットで入力してください。」）</t>
         </is>
       </c>
     </row>
     <row r="169" ht="54" customHeight="1">
       <c r="D169" s="41" t="inlineStr">
         <is>
-          <t>haitatsu_shimei_sei / haitatsu_shimei_mei：haitatsu_same_flg=false 時必須、shimei_sei/mei と同じ漢字・ひらがな・カタカナ形式</t>
+          <t>haitatsu_shimei_sei / haitatsu_shimei_mei：haitatsu_same_flg=false 時必須、shimei_sei/mei と同じ漢字・ひらがな・カタカナ・アルファベット形式</t>
         </is>
       </c>
     </row>
@@ -23506,7 +23638,7 @@
   saishin_data_flg, zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
   zenkai_hanbaiten_id, zenkai_dokusya_busu, zenkai_yubin_no,
   zenkai_todofuken_code, zenkai_shikuchoson, zenkai_chome_banchi,
-  zenkai_tatemono_mei, denshi_shonin_status, hanbaiten_tekiyo_date,
+  zenkai_tatemono_mei, denshi_shonin_status,
   created_at, created_by
 ) VALUES (
   :dokusya_id, 1, :ja_id, :kanri_shiten_id, :shiten_id, :kumiaiin_code,
@@ -23529,7 +23661,7 @@
   TRUE, TRUE, :shinki_flg, :kaiyaku_flg,
   NULL, NULL, NULL,
   NULL, NULL, NULL,
-  NULL, NULL, NULL,
+  NULL, NULL,
   NOW(), :user_account_id
 )</t>
         </is>
@@ -24769,7 +24901,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -26715,7 +26847,7 @@
   saishin_data_flg, zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
   zenkai_hanbaiten_id, zenkai_dokusya_busu, zenkai_yubin_no,
   zenkai_todofuken_code, zenkai_shikuchoson, zenkai_chome_banchi,
-  zenkai_tatemono_mei, denshi_shonin_status, hanbaiten_tekiyo_date,
+  zenkai_tatemono_mei, denshi_shonin_status,
   created_at, created_by
 ) VALUES (
   :dokusya_id, :new_rireki_no, :ja_id, :kanri_shiten_id, :shiten_id, :kumiaiin_code,
@@ -26738,7 +26870,7 @@
   TRUE, :zougen_hokoku_flg, :shinki_flg, :kaiyaku_flg,
   :zenkai_hanbaiten_id, :zenkai_dokusya_busu, :zenkai_yubin_no,
   :zenkai_todofuken_code, :zenkai_shikuchoson, :zenkai_chome_banchi,
-  :zenkai_tatemono_mei, :denshi_shonin_status, NULL,
+  :zenkai_tatemono_mei, :denshi_shonin_status,
   NOW(), :user_account_id
 )</t>
         </is>
@@ -27194,7 +27326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK87"/>
+  <dimension ref="A1:AK90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -27355,7 +27487,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -27479,7 +27611,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>電子版申込の購読者を承認する（denshi_shonin_status 0→1）。新規履歴レコードを作成。</t>
+          <t>電子版申込の購読者を承認する（denshi_shonin_status 0→1）。承認待ち画面で編集した新聞単価（tanka_id）を任意で同時保存してから承認確定する。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -27617,7 +27749,7 @@
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>JSON（任意）。承認待ち画面は新聞単価のみ編集可のため、編集された tanka_id を送信する（省略時は単価変更なし）。</t>
         </is>
       </c>
       <c r="K11" s="10" t="n"/>
@@ -28123,139 +28255,203 @@
       <c r="AJ24" s="10" t="n"/>
       <c r="AK24" s="11" t="n"/>
     </row>
-    <row r="25" ht="19.5" customHeight="1"/>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="27" t="inlineStr">
+    <row r="25" ht="36" customHeight="1">
+      <c r="B25" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>tanka_id</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="n"/>
+      <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="n"/>
+      <c r="S25" s="11" t="n"/>
+      <c r="T25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U25" s="10" t="n"/>
+      <c r="V25" s="10" t="n"/>
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="11" t="n"/>
+      <c r="Y25" s="17" t="inlineStr"/>
+      <c r="Z25" s="10" t="n"/>
+      <c r="AA25" s="10" t="n"/>
+      <c r="AB25" s="11" t="n"/>
+      <c r="AC25" s="17" t="inlineStr"/>
+      <c r="AD25" s="10" t="n"/>
+      <c r="AE25" s="11" t="n"/>
+      <c r="AF25" s="19" t="inlineStr">
+        <is>
+          <t>新聞単価ID（リクエストボディ・任意）。指定時のみ承認と同時に単価を更新する。1以上の整数。</t>
+        </is>
+      </c>
+      <c r="AG25" s="10" t="n"/>
+      <c r="AH25" s="10" t="n"/>
+      <c r="AI25" s="10" t="n"/>
+      <c r="AJ25" s="10" t="n"/>
+      <c r="AK25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="19.5" customHeight="1"/>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="19.5" customHeight="1"/>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="B28" s="30" t="inlineStr">
+    <row r="28" ht="19.5" customHeight="1"/>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="10" t="n"/>
-      <c r="K28" s="10" t="n"/>
-      <c r="L28" s="11" t="n"/>
-      <c r="M28" s="16" t="inlineStr">
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="10" t="n"/>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="16" t="inlineStr">
         <is>
           <t>タイプ</t>
         </is>
       </c>
-      <c r="N28" s="10" t="n"/>
-      <c r="O28" s="10" t="n"/>
-      <c r="P28" s="11" t="n"/>
-      <c r="Q28" s="16" t="inlineStr">
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="n"/>
+      <c r="P29" s="11" t="n"/>
+      <c r="Q29" s="16" t="inlineStr">
         <is>
           <t>繰り返し</t>
         </is>
       </c>
-      <c r="R28" s="10" t="n"/>
-      <c r="S28" s="11" t="n"/>
-      <c r="T28" s="16" t="inlineStr">
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="11" t="n"/>
+      <c r="T29" s="16" t="inlineStr">
         <is>
           <t>フォーマット</t>
         </is>
       </c>
-      <c r="U28" s="10" t="n"/>
-      <c r="V28" s="10" t="n"/>
-      <c r="W28" s="10" t="n"/>
-      <c r="X28" s="11" t="n"/>
-      <c r="Y28" s="16" t="inlineStr">
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="10" t="n"/>
+      <c r="W29" s="10" t="n"/>
+      <c r="X29" s="11" t="n"/>
+      <c r="Y29" s="16" t="inlineStr">
         <is>
           <t>Nullable</t>
         </is>
       </c>
-      <c r="Z28" s="10" t="n"/>
-      <c r="AA28" s="10" t="n"/>
-      <c r="AB28" s="10" t="n"/>
-      <c r="AC28" s="10" t="n"/>
-      <c r="AD28" s="10" t="n"/>
-      <c r="AE28" s="11" t="n"/>
-      <c r="AF28" s="16" t="inlineStr">
+      <c r="Z29" s="10" t="n"/>
+      <c r="AA29" s="10" t="n"/>
+      <c r="AB29" s="10" t="n"/>
+      <c r="AC29" s="10" t="n"/>
+      <c r="AD29" s="10" t="n"/>
+      <c r="AE29" s="11" t="n"/>
+      <c r="AF29" s="16" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="AG28" s="10" t="n"/>
-      <c r="AH28" s="10" t="n"/>
-      <c r="AI28" s="10" t="n"/>
-      <c r="AJ28" s="10" t="n"/>
-      <c r="AK28" s="11" t="n"/>
-    </row>
-    <row r="29" ht="19.5" customHeight="1"/>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="B30" s="40" t="inlineStr">
+      <c r="AG29" s="10" t="n"/>
+      <c r="AH29" s="10" t="n"/>
+      <c r="AI29" s="10" t="n"/>
+      <c r="AJ29" s="10" t="n"/>
+      <c r="AK29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="19.5" customHeight="1"/>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="B31" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>PUT /api/v1/dokusya/100/approve</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="10" t="n"/>
-      <c r="L31" s="10" t="n"/>
-      <c r="M31" s="10" t="n"/>
-      <c r="N31" s="10" t="n"/>
-      <c r="O31" s="10" t="n"/>
-      <c r="P31" s="10" t="n"/>
-      <c r="Q31" s="10" t="n"/>
-      <c r="R31" s="10" t="n"/>
-      <c r="S31" s="10" t="n"/>
-      <c r="T31" s="10" t="n"/>
-      <c r="U31" s="10" t="n"/>
-      <c r="V31" s="10" t="n"/>
-      <c r="W31" s="10" t="n"/>
-      <c r="X31" s="10" t="n"/>
-      <c r="Y31" s="10" t="n"/>
-      <c r="Z31" s="10" t="n"/>
-      <c r="AA31" s="10" t="n"/>
-      <c r="AB31" s="10" t="n"/>
-      <c r="AC31" s="10" t="n"/>
-      <c r="AD31" s="10" t="n"/>
-      <c r="AE31" s="10" t="n"/>
-      <c r="AF31" s="10" t="n"/>
-      <c r="AG31" s="10" t="n"/>
-      <c r="AH31" s="10" t="n"/>
-      <c r="AI31" s="10" t="n"/>
-      <c r="AJ31" s="10" t="n"/>
-      <c r="AK31" s="11" t="n"/>
-    </row>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="B33" s="40" t="inlineStr">
+    <row r="32" ht="108" customHeight="1">
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>PUT /api/v1/dokusya/100/approve
+Content-Type: application/json
+{
+  "tanka_id": 5
+}</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="10" t="n"/>
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="n"/>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="10" t="n"/>
+      <c r="Y32" s="10" t="n"/>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="10" t="n"/>
+      <c r="AC32" s="10" t="n"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="10" t="n"/>
+      <c r="AF32" s="10" t="n"/>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="11" t="n"/>
+    </row>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="180" customHeight="1">
-      <c r="C34" s="19" t="inlineStr">
+    <row r="35" ht="180" customHeight="1">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -28269,50 +28465,50 @@
 }</t>
         </is>
       </c>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="10" t="n"/>
-      <c r="M34" s="10" t="n"/>
-      <c r="N34" s="10" t="n"/>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="10" t="n"/>
-      <c r="Q34" s="10" t="n"/>
-      <c r="R34" s="10" t="n"/>
-      <c r="S34" s="10" t="n"/>
-      <c r="T34" s="10" t="n"/>
-      <c r="U34" s="10" t="n"/>
-      <c r="V34" s="10" t="n"/>
-      <c r="W34" s="10" t="n"/>
-      <c r="X34" s="10" t="n"/>
-      <c r="Y34" s="10" t="n"/>
-      <c r="Z34" s="10" t="n"/>
-      <c r="AA34" s="10" t="n"/>
-      <c r="AB34" s="10" t="n"/>
-      <c r="AC34" s="10" t="n"/>
-      <c r="AD34" s="10" t="n"/>
-      <c r="AE34" s="10" t="n"/>
-      <c r="AF34" s="10" t="n"/>
-      <c r="AG34" s="10" t="n"/>
-      <c r="AH34" s="10" t="n"/>
-      <c r="AI34" s="10" t="n"/>
-      <c r="AJ34" s="10" t="n"/>
-      <c r="AK34" s="11" t="n"/>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="B36" s="40" t="inlineStr">
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="10" t="n"/>
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="10" t="n"/>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="10" t="n"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="10" t="n"/>
+      <c r="Y35" s="10" t="n"/>
+      <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n"/>
+      <c r="AB35" s="10" t="n"/>
+      <c r="AC35" s="10" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="10" t="n"/>
+      <c r="AF35" s="10" t="n"/>
+      <c r="AG35" s="10" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="10" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="11" t="n"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request（ステータス不正））</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="72" customHeight="1">
-      <c r="C37" s="19" t="inlineStr">
+    <row r="38" ht="72" customHeight="1">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INVALID_STATUS",
@@ -28320,50 +28516,50 @@
 }</t>
         </is>
       </c>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="10" t="n"/>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="10" t="n"/>
-      <c r="Q37" s="10" t="n"/>
-      <c r="R37" s="10" t="n"/>
-      <c r="S37" s="10" t="n"/>
-      <c r="T37" s="10" t="n"/>
-      <c r="U37" s="10" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
-      <c r="X37" s="10" t="n"/>
-      <c r="Y37" s="10" t="n"/>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="10" t="n"/>
-      <c r="AB37" s="10" t="n"/>
-      <c r="AC37" s="10" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="10" t="n"/>
-      <c r="AF37" s="10" t="n"/>
-      <c r="AG37" s="10" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="10" t="n"/>
-      <c r="AK37" s="11" t="n"/>
-    </row>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="B39" s="40" t="inlineStr">
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="10" t="n"/>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="n"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="10" t="n"/>
+      <c r="Y38" s="10" t="n"/>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="10" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="10" t="n"/>
+      <c r="AF38" s="10" t="n"/>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="11" t="n"/>
+    </row>
+    <row r="40" ht="19.5" customHeight="1">
+      <c r="B40" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="72" customHeight="1">
-      <c r="C40" s="19" t="inlineStr">
+    <row r="41" ht="72" customHeight="1">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -28371,50 +28567,50 @@
 }</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n"/>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="10" t="n"/>
-      <c r="O40" s="10" t="n"/>
-      <c r="P40" s="10" t="n"/>
-      <c r="Q40" s="10" t="n"/>
-      <c r="R40" s="10" t="n"/>
-      <c r="S40" s="10" t="n"/>
-      <c r="T40" s="10" t="n"/>
-      <c r="U40" s="10" t="n"/>
-      <c r="V40" s="10" t="n"/>
-      <c r="W40" s="10" t="n"/>
-      <c r="X40" s="10" t="n"/>
-      <c r="Y40" s="10" t="n"/>
-      <c r="Z40" s="10" t="n"/>
-      <c r="AA40" s="10" t="n"/>
-      <c r="AB40" s="10" t="n"/>
-      <c r="AC40" s="10" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="10" t="n"/>
-      <c r="AF40" s="10" t="n"/>
-      <c r="AG40" s="10" t="n"/>
-      <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="10" t="n"/>
-      <c r="AJ40" s="10" t="n"/>
-      <c r="AK40" s="11" t="n"/>
-    </row>
-    <row r="42" ht="19.5" customHeight="1">
-      <c r="B42" s="40" t="inlineStr">
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="10" t="n"/>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="10" t="n"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="10" t="n"/>
+      <c r="W41" s="10" t="n"/>
+      <c r="X41" s="10" t="n"/>
+      <c r="Y41" s="10" t="n"/>
+      <c r="Z41" s="10" t="n"/>
+      <c r="AA41" s="10" t="n"/>
+      <c r="AB41" s="10" t="n"/>
+      <c r="AC41" s="10" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="10" t="n"/>
+      <c r="AF41" s="10" t="n"/>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="10" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41" s="10" t="n"/>
+      <c r="AK41" s="11" t="n"/>
+    </row>
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="72" customHeight="1">
-      <c r="C43" s="19" t="inlineStr">
+    <row r="44" ht="72" customHeight="1">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -28422,50 +28618,50 @@
 }</t>
         </is>
       </c>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="10" t="n"/>
-      <c r="G43" s="10" t="n"/>
-      <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
-      <c r="J43" s="10" t="n"/>
-      <c r="K43" s="10" t="n"/>
-      <c r="L43" s="10" t="n"/>
-      <c r="M43" s="10" t="n"/>
-      <c r="N43" s="10" t="n"/>
-      <c r="O43" s="10" t="n"/>
-      <c r="P43" s="10" t="n"/>
-      <c r="Q43" s="10" t="n"/>
-      <c r="R43" s="10" t="n"/>
-      <c r="S43" s="10" t="n"/>
-      <c r="T43" s="10" t="n"/>
-      <c r="U43" s="10" t="n"/>
-      <c r="V43" s="10" t="n"/>
-      <c r="W43" s="10" t="n"/>
-      <c r="X43" s="10" t="n"/>
-      <c r="Y43" s="10" t="n"/>
-      <c r="Z43" s="10" t="n"/>
-      <c r="AA43" s="10" t="n"/>
-      <c r="AB43" s="10" t="n"/>
-      <c r="AC43" s="10" t="n"/>
-      <c r="AD43" s="10" t="n"/>
-      <c r="AE43" s="10" t="n"/>
-      <c r="AF43" s="10" t="n"/>
-      <c r="AG43" s="10" t="n"/>
-      <c r="AH43" s="10" t="n"/>
-      <c r="AI43" s="10" t="n"/>
-      <c r="AJ43" s="10" t="n"/>
-      <c r="AK43" s="11" t="n"/>
-    </row>
-    <row r="45" ht="19.5" customHeight="1">
-      <c r="B45" s="40" t="inlineStr">
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="10" t="n"/>
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="n"/>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="n"/>
+      <c r="U44" s="10" t="n"/>
+      <c r="V44" s="10" t="n"/>
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="10" t="n"/>
+      <c r="Y44" s="10" t="n"/>
+      <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="10" t="n"/>
+      <c r="AB44" s="10" t="n"/>
+      <c r="AC44" s="10" t="n"/>
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="10" t="n"/>
+      <c r="AF44" s="10" t="n"/>
+      <c r="AG44" s="10" t="n"/>
+      <c r="AH44" s="10" t="n"/>
+      <c r="AI44" s="10" t="n"/>
+      <c r="AJ44" s="10" t="n"/>
+      <c r="AK44" s="11" t="n"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="72" customHeight="1">
-      <c r="C46" s="19" t="inlineStr">
+    <row r="47" ht="72" customHeight="1">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "NOT_FOUND",
@@ -28473,50 +28669,50 @@
 }</t>
         </is>
       </c>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
-      <c r="K46" s="10" t="n"/>
-      <c r="L46" s="10" t="n"/>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="10" t="n"/>
-      <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
-      <c r="R46" s="10" t="n"/>
-      <c r="S46" s="10" t="n"/>
-      <c r="T46" s="10" t="n"/>
-      <c r="U46" s="10" t="n"/>
-      <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="n"/>
-      <c r="Y46" s="10" t="n"/>
-      <c r="Z46" s="10" t="n"/>
-      <c r="AA46" s="10" t="n"/>
-      <c r="AB46" s="10" t="n"/>
-      <c r="AC46" s="10" t="n"/>
-      <c r="AD46" s="10" t="n"/>
-      <c r="AE46" s="10" t="n"/>
-      <c r="AF46" s="10" t="n"/>
-      <c r="AG46" s="10" t="n"/>
-      <c r="AH46" s="10" t="n"/>
-      <c r="AI46" s="10" t="n"/>
-      <c r="AJ46" s="10" t="n"/>
-      <c r="AK46" s="11" t="n"/>
-    </row>
-    <row r="48" ht="19.5" customHeight="1">
-      <c r="B48" s="40" t="inlineStr">
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n"/>
+      <c r="J47" s="10" t="n"/>
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="10" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="10" t="n"/>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n"/>
+      <c r="U47" s="10" t="n"/>
+      <c r="V47" s="10" t="n"/>
+      <c r="W47" s="10" t="n"/>
+      <c r="X47" s="10" t="n"/>
+      <c r="Y47" s="10" t="n"/>
+      <c r="Z47" s="10" t="n"/>
+      <c r="AA47" s="10" t="n"/>
+      <c r="AB47" s="10" t="n"/>
+      <c r="AC47" s="10" t="n"/>
+      <c r="AD47" s="10" t="n"/>
+      <c r="AE47" s="10" t="n"/>
+      <c r="AF47" s="10" t="n"/>
+      <c r="AG47" s="10" t="n"/>
+      <c r="AH47" s="10" t="n"/>
+      <c r="AI47" s="10" t="n"/>
+      <c r="AJ47" s="10" t="n"/>
+      <c r="AK47" s="11" t="n"/>
+    </row>
+    <row r="49" ht="19.5" customHeight="1">
+      <c r="B49" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="72" customHeight="1">
-      <c r="C49" s="19" t="inlineStr">
+    <row r="50" ht="72" customHeight="1">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -28524,200 +28720,207 @@
 }</t>
         </is>
       </c>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n"/>
-      <c r="J49" s="10" t="n"/>
-      <c r="K49" s="10" t="n"/>
-      <c r="L49" s="10" t="n"/>
-      <c r="M49" s="10" t="n"/>
-      <c r="N49" s="10" t="n"/>
-      <c r="O49" s="10" t="n"/>
-      <c r="P49" s="10" t="n"/>
-      <c r="Q49" s="10" t="n"/>
-      <c r="R49" s="10" t="n"/>
-      <c r="S49" s="10" t="n"/>
-      <c r="T49" s="10" t="n"/>
-      <c r="U49" s="10" t="n"/>
-      <c r="V49" s="10" t="n"/>
-      <c r="W49" s="10" t="n"/>
-      <c r="X49" s="10" t="n"/>
-      <c r="Y49" s="10" t="n"/>
-      <c r="Z49" s="10" t="n"/>
-      <c r="AA49" s="10" t="n"/>
-      <c r="AB49" s="10" t="n"/>
-      <c r="AC49" s="10" t="n"/>
-      <c r="AD49" s="10" t="n"/>
-      <c r="AE49" s="10" t="n"/>
-      <c r="AF49" s="10" t="n"/>
-      <c r="AG49" s="10" t="n"/>
-      <c r="AH49" s="10" t="n"/>
-      <c r="AI49" s="10" t="n"/>
-      <c r="AJ49" s="10" t="n"/>
-      <c r="AK49" s="11" t="n"/>
-    </row>
-    <row r="51" ht="19.5" customHeight="1"/>
-    <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="27" t="inlineStr">
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="10" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="10" t="n"/>
+      <c r="Y50" s="10" t="n"/>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="10" t="n"/>
+      <c r="AC50" s="10" t="n"/>
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="10" t="n"/>
+      <c r="AF50" s="10" t="n"/>
+      <c r="AG50" s="10" t="n"/>
+      <c r="AH50" s="10" t="n"/>
+      <c r="AI50" s="10" t="n"/>
+      <c r="AJ50" s="10" t="n"/>
+      <c r="AK50" s="11" t="n"/>
+    </row>
+    <row r="52" ht="19.5" customHeight="1"/>
+    <row r="53" ht="19.5" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="54" customHeight="1">
-      <c r="B53" s="42" t="inlineStr">
+    <row r="54" ht="54" customHeight="1">
+      <c r="B54" s="42" t="inlineStr">
         <is>
           <t>※ 4.4 ステータス更新 と 4.5 操作ログ記録 は単一トランザクション内で実行する。
 いずれかが失敗した場合は全てロールバックすること。
 例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
         </is>
       </c>
-      <c r="C53" s="10" t="n"/>
-      <c r="D53" s="10" t="n"/>
-      <c r="E53" s="10" t="n"/>
-      <c r="F53" s="10" t="n"/>
-      <c r="G53" s="10" t="n"/>
-      <c r="H53" s="10" t="n"/>
-      <c r="I53" s="10" t="n"/>
-      <c r="J53" s="10" t="n"/>
-      <c r="K53" s="10" t="n"/>
-      <c r="L53" s="10" t="n"/>
-      <c r="M53" s="10" t="n"/>
-      <c r="N53" s="10" t="n"/>
-      <c r="O53" s="10" t="n"/>
-      <c r="P53" s="10" t="n"/>
-      <c r="Q53" s="10" t="n"/>
-      <c r="R53" s="10" t="n"/>
-      <c r="S53" s="10" t="n"/>
-      <c r="T53" s="10" t="n"/>
-      <c r="U53" s="10" t="n"/>
-      <c r="V53" s="10" t="n"/>
-      <c r="W53" s="10" t="n"/>
-      <c r="X53" s="10" t="n"/>
-      <c r="Y53" s="10" t="n"/>
-      <c r="Z53" s="10" t="n"/>
-      <c r="AA53" s="10" t="n"/>
-      <c r="AB53" s="10" t="n"/>
-      <c r="AC53" s="10" t="n"/>
-      <c r="AD53" s="10" t="n"/>
-      <c r="AE53" s="10" t="n"/>
-      <c r="AF53" s="10" t="n"/>
-      <c r="AG53" s="10" t="n"/>
-      <c r="AH53" s="10" t="n"/>
-      <c r="AI53" s="10" t="n"/>
-      <c r="AJ53" s="10" t="n"/>
-      <c r="AK53" s="11" t="n"/>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="B54" s="27" t="inlineStr">
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="10" t="n"/>
+      <c r="AF54" s="10" t="n"/>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="C55" s="41" t="inlineStr">
-        <is>
-          <t>パスパラメータ：dokusya_id 数値型チェック、必須</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="C56" s="41" t="inlineStr">
         <is>
-          <t>不正なパラメータが存在する場合：HTTP 400 (`BAD_REQUEST`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="B57" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+          <t>パスパラメータ：dokusya_id 数値型チェック、必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="C57" s="41" t="inlineStr">
+        <is>
+          <t>リクエストボディ `tanka_id`（任意）：指定時は整数・1以上。形式不正は HTTP 400 (`VALIDATION_ERROR`, field=`tanka_id`)。</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="C58" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+          <t>不正なパラメータが存在する場合：HTTP 400 (`BAD_REQUEST`)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="C59" s="41" t="inlineStr">
-        <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="C60" s="41" t="inlineStr">
         <is>
-          <t>必要権限: `dokusya.update`</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1">
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
       <c r="C61" s="41" t="inlineStr">
         <is>
-          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="C62" s="41" t="inlineStr">
         <is>
+          <t>必要権限: `dokusya.update`</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="C63" s="41" t="inlineStr">
+        <is>
+          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="C64" s="41" t="inlineStr">
+        <is>
           <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="C63" s="41" t="inlineStr">
+    <row r="65" ht="18" customHeight="1">
+      <c r="C65" s="41" t="inlineStr">
         <is>
           <t>DataScope:</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="D64" s="41" t="inlineStr">
-        <is>
-          <t>CHUOKAI（中央会）：自中央会のみ承認可能</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="D65" s="41" t="inlineStr">
-        <is>
-          <t>JA_HONTEN（JA本店）：自JAのみ承認可能（`ja_id = user.ja_id`）</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="D66" s="41" t="inlineStr">
         <is>
+          <t>CHUOKAI（中央会）：自中央会のみ承認可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="D67" s="41" t="inlineStr">
+        <is>
+          <t>JA_HONTEN（JA本店）：自JAのみ承認可能（`ja_id = user.ja_id`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="D68" s="41" t="inlineStr">
+        <is>
           <t>JA_KANRI_SHITEN（JA管理支店）：自管理支店のみ承認可能</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="C67" s="41" t="inlineStr">
+    <row r="69" ht="18" customHeight="1">
+      <c r="C69" s="41" t="inlineStr">
         <is>
           <t>DataScope違反の場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="B68" s="27" t="inlineStr">
+    <row r="70" ht="18" customHeight="1">
+      <c r="B70" s="27" t="inlineStr">
         <is>
           <t>4.3 対象レコードの存在確認 + ステータスチェック</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="72" customHeight="1">
-      <c r="C69" s="42" t="inlineStr">
+    <row r="71" ht="72" customHeight="1">
+      <c r="C71" s="42" t="inlineStr">
         <is>
           <t>SELECT * FROM t_dokusya
 WHERE dokusya_id = :dokusya_id
@@ -28725,172 +28928,76 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D69" s="10" t="n"/>
-      <c r="E69" s="10" t="n"/>
-      <c r="F69" s="10" t="n"/>
-      <c r="G69" s="10" t="n"/>
-      <c r="H69" s="10" t="n"/>
-      <c r="I69" s="10" t="n"/>
-      <c r="J69" s="10" t="n"/>
-      <c r="K69" s="10" t="n"/>
-      <c r="L69" s="10" t="n"/>
-      <c r="M69" s="10" t="n"/>
-      <c r="N69" s="10" t="n"/>
-      <c r="O69" s="10" t="n"/>
-      <c r="P69" s="10" t="n"/>
-      <c r="Q69" s="10" t="n"/>
-      <c r="R69" s="10" t="n"/>
-      <c r="S69" s="10" t="n"/>
-      <c r="T69" s="10" t="n"/>
-      <c r="U69" s="10" t="n"/>
-      <c r="V69" s="10" t="n"/>
-      <c r="W69" s="10" t="n"/>
-      <c r="X69" s="10" t="n"/>
-      <c r="Y69" s="10" t="n"/>
-      <c r="Z69" s="10" t="n"/>
-      <c r="AA69" s="10" t="n"/>
-      <c r="AB69" s="10" t="n"/>
-      <c r="AC69" s="10" t="n"/>
-      <c r="AD69" s="10" t="n"/>
-      <c r="AE69" s="10" t="n"/>
-      <c r="AF69" s="10" t="n"/>
-      <c r="AG69" s="10" t="n"/>
-      <c r="AH69" s="10" t="n"/>
-      <c r="AI69" s="10" t="n"/>
-      <c r="AJ69" s="10" t="n"/>
-      <c r="AK69" s="11" t="n"/>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="C70" s="41" t="inlineStr">
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="10" t="n"/>
+      <c r="J71" s="10" t="n"/>
+      <c r="K71" s="10" t="n"/>
+      <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="10" t="n"/>
+      <c r="Q71" s="10" t="n"/>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
+      <c r="U71" s="10" t="n"/>
+      <c r="V71" s="10" t="n"/>
+      <c r="W71" s="10" t="n"/>
+      <c r="X71" s="10" t="n"/>
+      <c r="Y71" s="10" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
+      <c r="AB71" s="10" t="n"/>
+      <c r="AC71" s="10" t="n"/>
+      <c r="AD71" s="10" t="n"/>
+      <c r="AE71" s="10" t="n"/>
+      <c r="AF71" s="10" t="n"/>
+      <c r="AG71" s="10" t="n"/>
+      <c r="AH71" s="10" t="n"/>
+      <c r="AI71" s="10" t="n"/>
+      <c r="AJ71" s="10" t="n"/>
+      <c r="AK71" s="11" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="C72" s="41" t="inlineStr">
         <is>
           <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="36" customHeight="1">
-      <c r="C71" s="41" t="inlineStr">
+    <row r="73" ht="36" customHeight="1">
+      <c r="C73" s="41" t="inlineStr">
         <is>
           <t>denshi_shonin_status が 0 でない場合：HTTP 400 (`INVALID_STATUS`)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="B72" s="27" t="inlineStr">
+    <row r="74" ht="72" customHeight="1">
+      <c r="C74" s="41" t="inlineStr">
+        <is>
+          <t>リクエストボディに `tanka_id` が指定された場合、承認前にテナント跨ぎ FK 検証を行う（`m_tanka` に存在し、かつ対象レコードの `ja_id` に属すること）。存在しない → HTTP 400、他 JA の単価 → HTTP 403 (`DATA_SCOPE_VIOLATION`)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="B75" s="27" t="inlineStr">
         <is>
           <t>4.4 ステータス更新（履歴追記方式）</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="72" customHeight="1">
-      <c r="C73" s="42" t="inlineStr">
+    <row r="76" ht="72" customHeight="1">
+      <c r="C76" s="42" t="inlineStr">
         <is>
           <t>UPDATE t_dokusya_rireki
 SET saishin_data_flg = FALSE
 WHERE dokusya_id = :dokusya_id
   AND saishin_data_flg = TRUE</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="n"/>
-      <c r="E73" s="10" t="n"/>
-      <c r="F73" s="10" t="n"/>
-      <c r="G73" s="10" t="n"/>
-      <c r="H73" s="10" t="n"/>
-      <c r="I73" s="10" t="n"/>
-      <c r="J73" s="10" t="n"/>
-      <c r="K73" s="10" t="n"/>
-      <c r="L73" s="10" t="n"/>
-      <c r="M73" s="10" t="n"/>
-      <c r="N73" s="10" t="n"/>
-      <c r="O73" s="10" t="n"/>
-      <c r="P73" s="10" t="n"/>
-      <c r="Q73" s="10" t="n"/>
-      <c r="R73" s="10" t="n"/>
-      <c r="S73" s="10" t="n"/>
-      <c r="T73" s="10" t="n"/>
-      <c r="U73" s="10" t="n"/>
-      <c r="V73" s="10" t="n"/>
-      <c r="W73" s="10" t="n"/>
-      <c r="X73" s="10" t="n"/>
-      <c r="Y73" s="10" t="n"/>
-      <c r="Z73" s="10" t="n"/>
-      <c r="AA73" s="10" t="n"/>
-      <c r="AB73" s="10" t="n"/>
-      <c r="AC73" s="10" t="n"/>
-      <c r="AD73" s="10" t="n"/>
-      <c r="AE73" s="10" t="n"/>
-      <c r="AF73" s="10" t="n"/>
-      <c r="AG73" s="10" t="n"/>
-      <c r="AH73" s="10" t="n"/>
-      <c r="AI73" s="10" t="n"/>
-      <c r="AJ73" s="10" t="n"/>
-      <c r="AK73" s="11" t="n"/>
-    </row>
-    <row r="74" ht="54" customHeight="1">
-      <c r="C74" s="42" t="inlineStr">
-        <is>
-          <t>SELECT COALESCE(MAX(rireki_no), 0) + 1 AS new_rireki_no
-FROM t_dokusya_rireki
-WHERE dokusya_id = :dokusya_id</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="n"/>
-      <c r="E74" s="10" t="n"/>
-      <c r="F74" s="10" t="n"/>
-      <c r="G74" s="10" t="n"/>
-      <c r="H74" s="10" t="n"/>
-      <c r="I74" s="10" t="n"/>
-      <c r="J74" s="10" t="n"/>
-      <c r="K74" s="10" t="n"/>
-      <c r="L74" s="10" t="n"/>
-      <c r="M74" s="10" t="n"/>
-      <c r="N74" s="10" t="n"/>
-      <c r="O74" s="10" t="n"/>
-      <c r="P74" s="10" t="n"/>
-      <c r="Q74" s="10" t="n"/>
-      <c r="R74" s="10" t="n"/>
-      <c r="S74" s="10" t="n"/>
-      <c r="T74" s="10" t="n"/>
-      <c r="U74" s="10" t="n"/>
-      <c r="V74" s="10" t="n"/>
-      <c r="W74" s="10" t="n"/>
-      <c r="X74" s="10" t="n"/>
-      <c r="Y74" s="10" t="n"/>
-      <c r="Z74" s="10" t="n"/>
-      <c r="AA74" s="10" t="n"/>
-      <c r="AB74" s="10" t="n"/>
-      <c r="AC74" s="10" t="n"/>
-      <c r="AD74" s="10" t="n"/>
-      <c r="AE74" s="10" t="n"/>
-      <c r="AF74" s="10" t="n"/>
-      <c r="AG74" s="10" t="n"/>
-      <c r="AH74" s="10" t="n"/>
-      <c r="AI74" s="10" t="n"/>
-      <c r="AJ74" s="10" t="n"/>
-      <c r="AK74" s="11" t="n"/>
-    </row>
-    <row r="75" ht="36" customHeight="1">
-      <c r="C75" s="41" t="inlineStr">
-        <is>
-          <t>履歴レコードは現在の購読者情報をコピーし、denshi_shonin_status=1 に設定。saishin_data_flg=TRUE。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="234" customHeight="1">
-      <c r="C76" s="42" t="inlineStr">
-        <is>
-          <t>INSERT INTO t_dokusya_rireki (
-  dokusya_id, rireki_no, ja_id, ...,  -- 4.3 で取得した現データを全コピー
-  denshi_shonin_status,
-  saishin_data_flg, zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
-  henko_riyu,
-  created_at, created_by
-) VALUES (
-  :dokusya_id, :new_rireki_no, :ja_id, ...,
-  1,
-  TRUE, FALSE, FALSE, FALSE,
-  '電子版承認',
-  NOW(), :user_account_id
-)</t>
         </is>
       </c>
       <c r="D76" s="10" t="n"/>
@@ -28928,18 +29035,12 @@
       <c r="AJ76" s="10" t="n"/>
       <c r="AK76" s="11" t="n"/>
     </row>
-    <row r="77" ht="162" customHeight="1">
+    <row r="77" ht="54" customHeight="1">
       <c r="C77" s="42" t="inlineStr">
         <is>
-          <t>UPDATE t_dokusya
-SET denshi_shonin_status = 1,
-    rireki_no = :new_rireki_no,
-    updated_at = NOW(),
-    updated_by = :user_account_id
-WHERE dokusya_id = :dokusya_id
-  AND ja_id = :ja_id
-  AND deleted_at IS NULL
-RETURNING *</t>
+          <t>SELECT COALESCE(MAX(rireki_no), 0) + 1 AS new_rireki_no
+FROM t_dokusya_rireki
+WHERE dokusya_id = :dokusya_id</t>
         </is>
       </c>
       <c r="D77" s="10" t="n"/>
@@ -28977,28 +29078,29 @@
       <c r="AJ77" s="10" t="n"/>
       <c r="AK77" s="11" t="n"/>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="B78" s="27" t="inlineStr">
-        <is>
-          <t>4.5 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="216" customHeight="1">
+    <row r="78" ht="36" customHeight="1">
+      <c r="C78" s="41" t="inlineStr">
+        <is>
+          <t>履歴レコードは現在の購読者情報をコピーし、denshi_shonin_status=1 に設定。saishin_data_flg=TRUE。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="234" customHeight="1">
       <c r="C79" s="42" t="inlineStr">
         <is>
-          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
-                   gamen_name, operation, result_status,
-                   target_id, target_table,
-                   before_value, after_value,
-                   error_message, stack_trace,
-                   ip_address, user_agent)
-VALUES (1, NOW(), :account_id, :ja_id,
-        '購読者情報登録画面 (ACSMS-SCR-011)', 'UPDATE', 1,
-        :dokusya_id, 't_dokusya',
-        :before_value_json, :after_value_json,
-        '', '',
-        :ip_address, :user_agent)</t>
+          <t>INSERT INTO t_dokusya_rireki (
+  dokusya_id, rireki_no, ja_id, ...,  -- 4.3 で取得した現データを全コピー
+  denshi_shonin_status,
+  saishin_data_flg, zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
+  henko_riyu,
+  created_at, created_by
+) VALUES (
+  :dokusya_id, :new_rireki_no, :ja_id, ...,
+  1,
+  TRUE, FALSE, FALSE, FALSE,
+  '電子版承認',
+  NOW(), :user_account_id
+)</t>
         </is>
       </c>
       <c r="D79" s="10" t="n"/>
@@ -29036,57 +29138,166 @@
       <c r="AJ79" s="10" t="n"/>
       <c r="AK79" s="11" t="n"/>
     </row>
-    <row r="80" ht="36" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
+    <row r="80" ht="180" customHeight="1">
+      <c r="C80" s="42" t="inlineStr">
+        <is>
+          <t>UPDATE t_dokusya
+SET denshi_shonin_status = 1,
+    tanka_id = :tanka_id,          -- リクエストボディに tanka_id 指定時のみ更新（未指定は据置）
+    rireki_no = :new_rireki_no,
+    updated_at = NOW(),
+    updated_by = :user_account_id
+WHERE dokusya_id = :dokusya_id
+  AND ja_id = :ja_id
+  AND deleted_at IS NULL
+RETURNING *</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="10" t="n"/>
+      <c r="J80" s="10" t="n"/>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="10" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="10" t="n"/>
+      <c r="Q80" s="10" t="n"/>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="10" t="n"/>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="10" t="n"/>
+      <c r="X80" s="10" t="n"/>
+      <c r="Y80" s="10" t="n"/>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="10" t="n"/>
+      <c r="AC80" s="10" t="n"/>
+      <c r="AD80" s="10" t="n"/>
+      <c r="AE80" s="10" t="n"/>
+      <c r="AF80" s="10" t="n"/>
+      <c r="AG80" s="10" t="n"/>
+      <c r="AH80" s="10" t="n"/>
+      <c r="AI80" s="10" t="n"/>
+      <c r="AJ80" s="10" t="n"/>
+      <c r="AK80" s="11" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="B81" s="27" t="inlineStr">
+        <is>
+          <t>4.5 操作ログ記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="216" customHeight="1">
+      <c r="C82" s="42" t="inlineStr">
+        <is>
+          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
+                   gamen_name, operation, result_status,
+                   target_id, target_table,
+                   before_value, after_value,
+                   error_message, stack_trace,
+                   ip_address, user_agent)
+VALUES (1, NOW(), :account_id, :ja_id,
+        '購読者情報登録画面 (ACSMS-SCR-011)', 'UPDATE', 1,
+        :dokusya_id, 't_dokusya',
+        :before_value_json, :after_value_json,
+        '', '',
+        :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="10" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
+      <c r="H82" s="10" t="n"/>
+      <c r="I82" s="10" t="n"/>
+      <c r="J82" s="10" t="n"/>
+      <c r="K82" s="10" t="n"/>
+      <c r="L82" s="10" t="n"/>
+      <c r="M82" s="10" t="n"/>
+      <c r="N82" s="10" t="n"/>
+      <c r="O82" s="10" t="n"/>
+      <c r="P82" s="10" t="n"/>
+      <c r="Q82" s="10" t="n"/>
+      <c r="R82" s="10" t="n"/>
+      <c r="S82" s="10" t="n"/>
+      <c r="T82" s="10" t="n"/>
+      <c r="U82" s="10" t="n"/>
+      <c r="V82" s="10" t="n"/>
+      <c r="W82" s="10" t="n"/>
+      <c r="X82" s="10" t="n"/>
+      <c r="Y82" s="10" t="n"/>
+      <c r="Z82" s="10" t="n"/>
+      <c r="AA82" s="10" t="n"/>
+      <c r="AB82" s="10" t="n"/>
+      <c r="AC82" s="10" t="n"/>
+      <c r="AD82" s="10" t="n"/>
+      <c r="AE82" s="10" t="n"/>
+      <c r="AF82" s="10" t="n"/>
+      <c r="AG82" s="10" t="n"/>
+      <c r="AH82" s="10" t="n"/>
+      <c r="AI82" s="10" t="n"/>
+      <c r="AJ82" s="10" t="n"/>
+      <c r="AK82" s="11" t="n"/>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
         <is>
           <t>`before_value`：承認前のデータ（denshi_shonin_status=0）をJSON形式で格納する。</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="36" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
+    <row r="84" ht="36" customHeight="1">
+      <c r="C84" s="41" t="inlineStr">
         <is>
           <t>`after_value`：承認後のデータ（denshi_shonin_status=1）をJSON形式で格納する。</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="B82" s="27" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="B85" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="C83" s="41" t="inlineStr">
-        <is>
-          <t>承認後のデータを data オブジェクトとして返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="B84" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="C85" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="C86" s="41" t="inlineStr">
         <is>
+          <t>承認後のデータを data オブジェクトとして返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="B87" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="C88" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
+        <is>
           <t>エラー発生時はエラーログを記録する（`log_type = 3`、トランザクション外で記録）。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="216" customHeight="1">
-      <c r="C87" s="42" t="inlineStr">
+    <row r="90" ht="216" customHeight="1">
+      <c r="C90" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -29102,157 +29313,166 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D87" s="10" t="n"/>
-      <c r="E87" s="10" t="n"/>
-      <c r="F87" s="10" t="n"/>
-      <c r="G87" s="10" t="n"/>
-      <c r="H87" s="10" t="n"/>
-      <c r="I87" s="10" t="n"/>
-      <c r="J87" s="10" t="n"/>
-      <c r="K87" s="10" t="n"/>
-      <c r="L87" s="10" t="n"/>
-      <c r="M87" s="10" t="n"/>
-      <c r="N87" s="10" t="n"/>
-      <c r="O87" s="10" t="n"/>
-      <c r="P87" s="10" t="n"/>
-      <c r="Q87" s="10" t="n"/>
-      <c r="R87" s="10" t="n"/>
-      <c r="S87" s="10" t="n"/>
-      <c r="T87" s="10" t="n"/>
-      <c r="U87" s="10" t="n"/>
-      <c r="V87" s="10" t="n"/>
-      <c r="W87" s="10" t="n"/>
-      <c r="X87" s="10" t="n"/>
-      <c r="Y87" s="10" t="n"/>
-      <c r="Z87" s="10" t="n"/>
-      <c r="AA87" s="10" t="n"/>
-      <c r="AB87" s="10" t="n"/>
-      <c r="AC87" s="10" t="n"/>
-      <c r="AD87" s="10" t="n"/>
-      <c r="AE87" s="10" t="n"/>
-      <c r="AF87" s="10" t="n"/>
-      <c r="AG87" s="10" t="n"/>
-      <c r="AH87" s="10" t="n"/>
-      <c r="AI87" s="10" t="n"/>
-      <c r="AJ87" s="10" t="n"/>
-      <c r="AK87" s="11" t="n"/>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
+      <c r="AF90" s="10" t="n"/>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="114">
+  <mergeCells count="123">
     <mergeCell ref="J11:AK11"/>
-    <mergeCell ref="A26:AK26"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="C77:AK77"/>
-    <mergeCell ref="C34:AK34"/>
     <mergeCell ref="N18:AK18"/>
-    <mergeCell ref="C86:AK86"/>
+    <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
+    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="A53:AK53"/>
+    <mergeCell ref="N17:AK17"/>
     <mergeCell ref="C58:AK58"/>
-    <mergeCell ref="N17:AK17"/>
-    <mergeCell ref="D64:AK64"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C75:AK75"/>
+    <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="C44:AK44"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="C31:AK31"/>
     <mergeCell ref="C80:AK80"/>
-    <mergeCell ref="C46:AK46"/>
+    <mergeCell ref="Q25:S25"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="C70:AK70"/>
-    <mergeCell ref="T28:X28"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="C38:AK38"/>
     <mergeCell ref="A21:AK21"/>
-    <mergeCell ref="C49:AK49"/>
+    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B39:I39"/>
     <mergeCell ref="C74:AK74"/>
-    <mergeCell ref="A52:AK52"/>
-    <mergeCell ref="B78:AK78"/>
+    <mergeCell ref="C88:AK88"/>
+    <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C55:AK55"/>
+    <mergeCell ref="B55:AK55"/>
     <mergeCell ref="J13:AK13"/>
-    <mergeCell ref="D65:AK65"/>
-    <mergeCell ref="C59:AK59"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="Y29:AE29"/>
+    <mergeCell ref="C25:L25"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
-    <mergeCell ref="B33:I33"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="D66:AK66"/>
-    <mergeCell ref="Y28:AE28"/>
-    <mergeCell ref="C81:AK81"/>
-    <mergeCell ref="C37:AK37"/>
+    <mergeCell ref="C72:AK72"/>
+    <mergeCell ref="C32:AK32"/>
+    <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="C87:AK87"/>
+    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="C62:AK62"/>
-    <mergeCell ref="C28:L28"/>
-    <mergeCell ref="B57:AK57"/>
+    <mergeCell ref="C82:AK82"/>
+    <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
+    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="Q2:U3"/>
-    <mergeCell ref="B53:AK53"/>
+    <mergeCell ref="C64:AK64"/>
     <mergeCell ref="C79:AK79"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C63:AK63"/>
-    <mergeCell ref="B84:AK84"/>
+    <mergeCell ref="C41:AK41"/>
+    <mergeCell ref="C50:AK50"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="C56:AK56"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="C43:AK43"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="B54:AK54"/>
-    <mergeCell ref="B72:AK72"/>
-    <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="A27:AK27"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B70:AK70"/>
     <mergeCell ref="B14:I19"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="C69:AK69"/>
     <mergeCell ref="C83:AK83"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="B82:AK82"/>
-    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="D68:AK68"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="D67:AK67"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B68:AK68"/>
-    <mergeCell ref="C40:AK40"/>
-    <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="C47:AK47"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="B37:I37"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="C60:AK60"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="C76:AK76"/>
-    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="B75:AK75"/>
+    <mergeCell ref="B59:AK59"/>
+    <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
@@ -1517,7 +1517,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3579,7 +3579,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6011,7 +6011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG13"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6820,14 +6820,74 @@
       <c r="AF13" s="10" t="n"/>
       <c r="AG13" s="11" t="n"/>
     </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="11" t="n"/>
+      <c r="R14" s="19" t="inlineStr">
+        <is>
+          <t>実装是正：承認(API-011-004)/否認(API-011-005) を §4.4 の**履歴追記方式**（旧 saishin 降格 → rireki_no 採番 → 現行行コピー＋新ステータスで1件 INSERT ＋ 新行を saishin へ昇格し t_dokusya へ即時反映）へ統一。旧実装は t_dokusya と現行履歴行を in-place 更新するだけで履歴が残らなかったため、承認/否認の操作も履歴(t_dokusya_rireki)へ1レコード記録されるよう修正（顧客要件）。承認/否認は電子版(dokusya_shubetsu=2)専用ワークフローであり**電子版は適用日(joho_henko_tekiyo_date)が常に当日**のため、承認/否認イベント行の joho も当日に設定する（現行行の joho を carry-forward しない）。電子版の joho は常に &lt;= 当日なので、当日・最大 rireki_no のこの行が到来日バッチ後も有効行として保たれる。</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="11" t="n"/>
+      <c r="W14" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="10" t="n"/>
+      <c r="Z14" s="10" t="n"/>
+      <c r="AA14" s="11" t="n"/>
+      <c r="AB14" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC14" s="10" t="n"/>
+      <c r="AD14" s="10" t="n"/>
+      <c r="AE14" s="10" t="n"/>
+      <c r="AF14" s="10" t="n"/>
+      <c r="AG14" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="98">
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="R10:V10"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="W5:AA5"/>
+    <mergeCell ref="C14:G14"/>
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="R7:V7"/>
@@ -6842,8 +6902,10 @@
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="AB14:AG14"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="AB4:AG4"/>
+    <mergeCell ref="R14:V14"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="R4:V4"/>
@@ -6885,16 +6947,19 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="C11:G11"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="W9:AA9"/>
     <mergeCell ref="H10:J10"/>
+    <mergeCell ref="W14:AA14"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="K12:Q12"/>
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="W13:AA13"/>
     <mergeCell ref="C6:G6"/>
+    <mergeCell ref="K14:Q14"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB9:AG9"/>
     <mergeCell ref="A6:B6"/>
@@ -6907,6 +6972,7 @@
     <mergeCell ref="H12:J12"/>
     <mergeCell ref="R12:V12"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="H14:J14"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="W11:AA11"/>
@@ -7085,7 +7151,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7556,7 +7622,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8485,7 +8551,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -9172,7 +9238,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -15023,7 +15089,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -24901,7 +24967,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -27487,7 +27553,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
@@ -1517,7 +1517,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3030,20 +3030,18 @@
       <c r="AJ74" s="10" t="n"/>
       <c r="AK74" s="11" t="n"/>
     </row>
-    <row r="75" ht="234" customHeight="1">
+    <row r="75" ht="198" customHeight="1">
       <c r="C75" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya_rireki (
   dokusya_id, rireki_no, ja_id, ...,  -- 4.3 で取得した現データを全コピー
   denshi_shonin_status,
   saishin_data_flg, zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
-  henko_riyu,
   created_at, created_by
 ) VALUES (
   :dokusya_id, :new_rireki_no, :ja_id, ...,
   2,
   TRUE, FALSE, FALSE, FALSE,
-  '電子版否認',
   NOW(), :user_account_id
 )</t>
         </is>
@@ -3418,7 +3416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK86"/>
+  <dimension ref="A1:AK85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3579,7 +3577,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4751,7 +4749,7 @@
       <c r="C34" s="38" t="n"/>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>henko_riyu</t>
+          <t>saishin_data_flg</t>
         </is>
       </c>
       <c r="E34" s="10" t="n"/>
@@ -4764,7 +4762,7 @@
       <c r="L34" s="11" t="n"/>
       <c r="M34" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N34" s="10" t="n"/>
@@ -4782,7 +4780,11 @@
       <c r="V34" s="10" t="n"/>
       <c r="W34" s="10" t="n"/>
       <c r="X34" s="11" t="n"/>
-      <c r="Y34" s="17" t="inlineStr"/>
+      <c r="Y34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z34" s="10" t="n"/>
       <c r="AA34" s="10" t="n"/>
       <c r="AB34" s="10" t="n"/>
@@ -4791,7 +4793,7 @@
       <c r="AE34" s="11" t="n"/>
       <c r="AF34" s="19" t="inlineStr">
         <is>
-          <t>変更理由（空文字許容）</t>
+          <t>最新データフラグ</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -4807,7 +4809,7 @@
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>saishin_data_flg</t>
+          <t>shinki_flg</t>
         </is>
       </c>
       <c r="E35" s="10" t="n"/>
@@ -4851,7 +4853,7 @@
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>最新データフラグ</t>
+          <t>新規フラグ</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -4867,7 +4869,7 @@
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>shinki_flg</t>
+          <t>kaiyaku_flg</t>
         </is>
       </c>
       <c r="E36" s="10" t="n"/>
@@ -4911,7 +4913,7 @@
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>新規フラグ</t>
+          <t>解約フラグ</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -4927,7 +4929,7 @@
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>kaiyaku_flg</t>
+          <t>zougen_hokoku_flg</t>
         </is>
       </c>
       <c r="E37" s="10" t="n"/>
@@ -4971,7 +4973,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>解約フラグ</t>
+          <t>増減報告フラグ</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -4987,7 +4989,7 @@
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>zougen_hokoku_flg</t>
+          <t>denshi_shonin_status</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -5000,7 +5002,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -5020,7 +5022,7 @@
       <c r="X38" s="11" t="n"/>
       <c r="Y38" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z38" s="10" t="n"/>
@@ -5031,7 +5033,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>増減報告フラグ</t>
+          <t>電子申込承認ステータス</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -5047,7 +5049,7 @@
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>denshi_shonin_status</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -5060,7 +5062,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -5073,14 +5075,18 @@
       </c>
       <c r="R39" s="10" t="n"/>
       <c r="S39" s="11" t="n"/>
-      <c r="T39" s="17" t="inlineStr"/>
+      <c r="T39" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
       <c r="W39" s="10" t="n"/>
       <c r="X39" s="11" t="n"/>
       <c r="Y39" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z39" s="10" t="n"/>
@@ -5091,7 +5097,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>電子申込承認ステータス</t>
+          <t>作成日時（履歴登録日時）</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -5104,10 +5110,10 @@
       <c r="B40" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="C40" s="38" t="n"/>
+      <c r="C40" s="39" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -5133,11 +5139,7 @@
       </c>
       <c r="R40" s="10" t="n"/>
       <c r="S40" s="11" t="n"/>
-      <c r="T40" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T40" s="17" t="inlineStr"/>
       <c r="U40" s="10" t="n"/>
       <c r="V40" s="10" t="n"/>
       <c r="W40" s="10" t="n"/>
@@ -5155,7 +5157,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>作成日時（履歴登録日時）</t>
+          <t>作成者（履歴登録者）</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -5164,124 +5166,64 @@
       <c r="AJ40" s="10" t="n"/>
       <c r="AK40" s="11" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="31" t="n">
-        <v>14</v>
-      </c>
-      <c r="C41" s="39" t="n"/>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
-      <c r="G41" s="10" t="n"/>
-      <c r="H41" s="10" t="n"/>
-      <c r="I41" s="10" t="n"/>
-      <c r="J41" s="10" t="n"/>
-      <c r="K41" s="10" t="n"/>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N41" s="10" t="n"/>
-      <c r="O41" s="10" t="n"/>
-      <c r="P41" s="11" t="n"/>
-      <c r="Q41" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R41" s="10" t="n"/>
-      <c r="S41" s="11" t="n"/>
-      <c r="T41" s="17" t="inlineStr"/>
-      <c r="U41" s="10" t="n"/>
-      <c r="V41" s="10" t="n"/>
-      <c r="W41" s="10" t="n"/>
-      <c r="X41" s="11" t="n"/>
-      <c r="Y41" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z41" s="10" t="n"/>
-      <c r="AA41" s="10" t="n"/>
-      <c r="AB41" s="10" t="n"/>
-      <c r="AC41" s="10" t="n"/>
-      <c r="AD41" s="10" t="n"/>
-      <c r="AE41" s="11" t="n"/>
-      <c r="AF41" s="19" t="inlineStr">
-        <is>
-          <t>作成者（履歴登録者）</t>
-        </is>
-      </c>
-      <c r="AG41" s="10" t="n"/>
-      <c r="AH41" s="10" t="n"/>
-      <c r="AI41" s="10" t="n"/>
-      <c r="AJ41" s="10" t="n"/>
-      <c r="AK41" s="11" t="n"/>
-    </row>
-    <row r="42" ht="19.5" customHeight="1"/>
-    <row r="43" ht="19.5" customHeight="1">
-      <c r="B43" s="40" t="inlineStr">
+    <row r="41" ht="19.5" customHeight="1"/>
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="C44" s="19" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/dokusya/100/history</t>
         </is>
       </c>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
-      <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="n"/>
-      <c r="J44" s="10" t="n"/>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="10" t="n"/>
-      <c r="M44" s="10" t="n"/>
-      <c r="N44" s="10" t="n"/>
-      <c r="O44" s="10" t="n"/>
-      <c r="P44" s="10" t="n"/>
-      <c r="Q44" s="10" t="n"/>
-      <c r="R44" s="10" t="n"/>
-      <c r="S44" s="10" t="n"/>
-      <c r="T44" s="10" t="n"/>
-      <c r="U44" s="10" t="n"/>
-      <c r="V44" s="10" t="n"/>
-      <c r="W44" s="10" t="n"/>
-      <c r="X44" s="10" t="n"/>
-      <c r="Y44" s="10" t="n"/>
-      <c r="Z44" s="10" t="n"/>
-      <c r="AA44" s="10" t="n"/>
-      <c r="AB44" s="10" t="n"/>
-      <c r="AC44" s="10" t="n"/>
-      <c r="AD44" s="10" t="n"/>
-      <c r="AE44" s="10" t="n"/>
-      <c r="AF44" s="10" t="n"/>
-      <c r="AG44" s="10" t="n"/>
-      <c r="AH44" s="10" t="n"/>
-      <c r="AI44" s="10" t="n"/>
-      <c r="AJ44" s="10" t="n"/>
-      <c r="AK44" s="11" t="n"/>
-    </row>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="B46" s="40" t="inlineStr">
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="10" t="n"/>
+      <c r="L43" s="10" t="n"/>
+      <c r="M43" s="10" t="n"/>
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="10" t="n"/>
+      <c r="P43" s="10" t="n"/>
+      <c r="Q43" s="10" t="n"/>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="10" t="n"/>
+      <c r="T43" s="10" t="n"/>
+      <c r="U43" s="10" t="n"/>
+      <c r="V43" s="10" t="n"/>
+      <c r="W43" s="10" t="n"/>
+      <c r="X43" s="10" t="n"/>
+      <c r="Y43" s="10" t="n"/>
+      <c r="Z43" s="10" t="n"/>
+      <c r="AA43" s="10" t="n"/>
+      <c r="AB43" s="10" t="n"/>
+      <c r="AC43" s="10" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="10" t="n"/>
+      <c r="AF43" s="10" t="n"/>
+      <c r="AG43" s="10" t="n"/>
+      <c r="AH43" s="10" t="n"/>
+      <c r="AI43" s="10" t="n"/>
+      <c r="AJ43" s="10" t="n"/>
+      <c r="AK43" s="11" t="n"/>
+    </row>
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="409" customHeight="1">
-      <c r="C47" s="19" t="inlineStr">
+    <row r="46" ht="409" customHeight="1">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -5291,7 +5233,6 @@
       "rireki_no": 2,
       "tetsuzuki_shurui": 1,
       "tetsuzuki_shurui_label": "新規",
-      "henko_riyu": "住所変更",
       "saishin_data_flg": true,
       "shinki_flg": false,
       "kaiyaku_flg": false,
@@ -5306,7 +5247,6 @@
       "rireki_no": 1,
       "tetsuzuki_shurui": 1,
       "tetsuzuki_shurui_label": "新規",
-      "henko_riyu": "",
       "saishin_data_flg": false,
       "shinki_flg": true,
       "kaiyaku_flg": false,
@@ -5319,50 +5259,50 @@
 }</t>
         </is>
       </c>
-      <c r="D47" s="10" t="n"/>
-      <c r="E47" s="10" t="n"/>
-      <c r="F47" s="10" t="n"/>
-      <c r="G47" s="10" t="n"/>
-      <c r="H47" s="10" t="n"/>
-      <c r="I47" s="10" t="n"/>
-      <c r="J47" s="10" t="n"/>
-      <c r="K47" s="10" t="n"/>
-      <c r="L47" s="10" t="n"/>
-      <c r="M47" s="10" t="n"/>
-      <c r="N47" s="10" t="n"/>
-      <c r="O47" s="10" t="n"/>
-      <c r="P47" s="10" t="n"/>
-      <c r="Q47" s="10" t="n"/>
-      <c r="R47" s="10" t="n"/>
-      <c r="S47" s="10" t="n"/>
-      <c r="T47" s="10" t="n"/>
-      <c r="U47" s="10" t="n"/>
-      <c r="V47" s="10" t="n"/>
-      <c r="W47" s="10" t="n"/>
-      <c r="X47" s="10" t="n"/>
-      <c r="Y47" s="10" t="n"/>
-      <c r="Z47" s="10" t="n"/>
-      <c r="AA47" s="10" t="n"/>
-      <c r="AB47" s="10" t="n"/>
-      <c r="AC47" s="10" t="n"/>
-      <c r="AD47" s="10" t="n"/>
-      <c r="AE47" s="10" t="n"/>
-      <c r="AF47" s="10" t="n"/>
-      <c r="AG47" s="10" t="n"/>
-      <c r="AH47" s="10" t="n"/>
-      <c r="AI47" s="10" t="n"/>
-      <c r="AJ47" s="10" t="n"/>
-      <c r="AK47" s="11" t="n"/>
-    </row>
-    <row r="49" ht="19.5" customHeight="1">
-      <c r="B49" s="40" t="inlineStr">
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="10" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n"/>
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="10" t="n"/>
+      <c r="Y46" s="10" t="n"/>
+      <c r="Z46" s="10" t="n"/>
+      <c r="AA46" s="10" t="n"/>
+      <c r="AB46" s="10" t="n"/>
+      <c r="AC46" s="10" t="n"/>
+      <c r="AD46" s="10" t="n"/>
+      <c r="AE46" s="10" t="n"/>
+      <c r="AF46" s="10" t="n"/>
+      <c r="AG46" s="10" t="n"/>
+      <c r="AH46" s="10" t="n"/>
+      <c r="AI46" s="10" t="n"/>
+      <c r="AJ46" s="10" t="n"/>
+      <c r="AK46" s="11" t="n"/>
+    </row>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="72" customHeight="1">
-      <c r="C50" s="19" t="inlineStr">
+    <row r="49" ht="72" customHeight="1">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -5370,50 +5310,50 @@
 }</t>
         </is>
       </c>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
-      <c r="G50" s="10" t="n"/>
-      <c r="H50" s="10" t="n"/>
-      <c r="I50" s="10" t="n"/>
-      <c r="J50" s="10" t="n"/>
-      <c r="K50" s="10" t="n"/>
-      <c r="L50" s="10" t="n"/>
-      <c r="M50" s="10" t="n"/>
-      <c r="N50" s="10" t="n"/>
-      <c r="O50" s="10" t="n"/>
-      <c r="P50" s="10" t="n"/>
-      <c r="Q50" s="10" t="n"/>
-      <c r="R50" s="10" t="n"/>
-      <c r="S50" s="10" t="n"/>
-      <c r="T50" s="10" t="n"/>
-      <c r="U50" s="10" t="n"/>
-      <c r="V50" s="10" t="n"/>
-      <c r="W50" s="10" t="n"/>
-      <c r="X50" s="10" t="n"/>
-      <c r="Y50" s="10" t="n"/>
-      <c r="Z50" s="10" t="n"/>
-      <c r="AA50" s="10" t="n"/>
-      <c r="AB50" s="10" t="n"/>
-      <c r="AC50" s="10" t="n"/>
-      <c r="AD50" s="10" t="n"/>
-      <c r="AE50" s="10" t="n"/>
-      <c r="AF50" s="10" t="n"/>
-      <c r="AG50" s="10" t="n"/>
-      <c r="AH50" s="10" t="n"/>
-      <c r="AI50" s="10" t="n"/>
-      <c r="AJ50" s="10" t="n"/>
-      <c r="AK50" s="11" t="n"/>
-    </row>
-    <row r="52" ht="19.5" customHeight="1">
-      <c r="B52" s="40" t="inlineStr">
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="10" t="n"/>
+      <c r="K49" s="10" t="n"/>
+      <c r="L49" s="10" t="n"/>
+      <c r="M49" s="10" t="n"/>
+      <c r="N49" s="10" t="n"/>
+      <c r="O49" s="10" t="n"/>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="n"/>
+      <c r="U49" s="10" t="n"/>
+      <c r="V49" s="10" t="n"/>
+      <c r="W49" s="10" t="n"/>
+      <c r="X49" s="10" t="n"/>
+      <c r="Y49" s="10" t="n"/>
+      <c r="Z49" s="10" t="n"/>
+      <c r="AA49" s="10" t="n"/>
+      <c r="AB49" s="10" t="n"/>
+      <c r="AC49" s="10" t="n"/>
+      <c r="AD49" s="10" t="n"/>
+      <c r="AE49" s="10" t="n"/>
+      <c r="AF49" s="10" t="n"/>
+      <c r="AG49" s="10" t="n"/>
+      <c r="AH49" s="10" t="n"/>
+      <c r="AI49" s="10" t="n"/>
+      <c r="AJ49" s="10" t="n"/>
+      <c r="AK49" s="11" t="n"/>
+    </row>
+    <row r="51" ht="19.5" customHeight="1">
+      <c r="B51" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="72" customHeight="1">
-      <c r="C53" s="19" t="inlineStr">
+    <row r="52" ht="72" customHeight="1">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -5421,50 +5361,50 @@
 }</t>
         </is>
       </c>
-      <c r="D53" s="10" t="n"/>
-      <c r="E53" s="10" t="n"/>
-      <c r="F53" s="10" t="n"/>
-      <c r="G53" s="10" t="n"/>
-      <c r="H53" s="10" t="n"/>
-      <c r="I53" s="10" t="n"/>
-      <c r="J53" s="10" t="n"/>
-      <c r="K53" s="10" t="n"/>
-      <c r="L53" s="10" t="n"/>
-      <c r="M53" s="10" t="n"/>
-      <c r="N53" s="10" t="n"/>
-      <c r="O53" s="10" t="n"/>
-      <c r="P53" s="10" t="n"/>
-      <c r="Q53" s="10" t="n"/>
-      <c r="R53" s="10" t="n"/>
-      <c r="S53" s="10" t="n"/>
-      <c r="T53" s="10" t="n"/>
-      <c r="U53" s="10" t="n"/>
-      <c r="V53" s="10" t="n"/>
-      <c r="W53" s="10" t="n"/>
-      <c r="X53" s="10" t="n"/>
-      <c r="Y53" s="10" t="n"/>
-      <c r="Z53" s="10" t="n"/>
-      <c r="AA53" s="10" t="n"/>
-      <c r="AB53" s="10" t="n"/>
-      <c r="AC53" s="10" t="n"/>
-      <c r="AD53" s="10" t="n"/>
-      <c r="AE53" s="10" t="n"/>
-      <c r="AF53" s="10" t="n"/>
-      <c r="AG53" s="10" t="n"/>
-      <c r="AH53" s="10" t="n"/>
-      <c r="AI53" s="10" t="n"/>
-      <c r="AJ53" s="10" t="n"/>
-      <c r="AK53" s="11" t="n"/>
-    </row>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="B55" s="40" t="inlineStr">
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="10" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="10" t="n"/>
+      <c r="Q52" s="10" t="n"/>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="10" t="n"/>
+      <c r="Y52" s="10" t="n"/>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="10" t="n"/>
+      <c r="AD52" s="10" t="n"/>
+      <c r="AE52" s="10" t="n"/>
+      <c r="AF52" s="10" t="n"/>
+      <c r="AG52" s="10" t="n"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="10" t="n"/>
+      <c r="AJ52" s="10" t="n"/>
+      <c r="AK52" s="11" t="n"/>
+    </row>
+    <row r="54" ht="19.5" customHeight="1">
+      <c r="B54" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="72" customHeight="1">
-      <c r="C56" s="19" t="inlineStr">
+    <row r="55" ht="72" customHeight="1">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "NOT_FOUND",
@@ -5472,50 +5412,50 @@
 }</t>
         </is>
       </c>
-      <c r="D56" s="10" t="n"/>
-      <c r="E56" s="10" t="n"/>
-      <c r="F56" s="10" t="n"/>
-      <c r="G56" s="10" t="n"/>
-      <c r="H56" s="10" t="n"/>
-      <c r="I56" s="10" t="n"/>
-      <c r="J56" s="10" t="n"/>
-      <c r="K56" s="10" t="n"/>
-      <c r="L56" s="10" t="n"/>
-      <c r="M56" s="10" t="n"/>
-      <c r="N56" s="10" t="n"/>
-      <c r="O56" s="10" t="n"/>
-      <c r="P56" s="10" t="n"/>
-      <c r="Q56" s="10" t="n"/>
-      <c r="R56" s="10" t="n"/>
-      <c r="S56" s="10" t="n"/>
-      <c r="T56" s="10" t="n"/>
-      <c r="U56" s="10" t="n"/>
-      <c r="V56" s="10" t="n"/>
-      <c r="W56" s="10" t="n"/>
-      <c r="X56" s="10" t="n"/>
-      <c r="Y56" s="10" t="n"/>
-      <c r="Z56" s="10" t="n"/>
-      <c r="AA56" s="10" t="n"/>
-      <c r="AB56" s="10" t="n"/>
-      <c r="AC56" s="10" t="n"/>
-      <c r="AD56" s="10" t="n"/>
-      <c r="AE56" s="10" t="n"/>
-      <c r="AF56" s="10" t="n"/>
-      <c r="AG56" s="10" t="n"/>
-      <c r="AH56" s="10" t="n"/>
-      <c r="AI56" s="10" t="n"/>
-      <c r="AJ56" s="10" t="n"/>
-      <c r="AK56" s="11" t="n"/>
-    </row>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="B58" s="40" t="inlineStr">
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="10" t="n"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="10" t="n"/>
+      <c r="Y55" s="10" t="n"/>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+      <c r="AC55" s="10" t="n"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="10" t="n"/>
+      <c r="AF55" s="10" t="n"/>
+      <c r="AG55" s="10" t="n"/>
+      <c r="AH55" s="10" t="n"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
+      <c r="AK55" s="11" t="n"/>
+    </row>
+    <row r="57" ht="19.5" customHeight="1">
+      <c r="B57" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="72" customHeight="1">
-      <c r="C59" s="19" t="inlineStr">
+    <row r="58" ht="72" customHeight="1">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -5523,156 +5463,156 @@
 }</t>
         </is>
       </c>
-      <c r="D59" s="10" t="n"/>
-      <c r="E59" s="10" t="n"/>
-      <c r="F59" s="10" t="n"/>
-      <c r="G59" s="10" t="n"/>
-      <c r="H59" s="10" t="n"/>
-      <c r="I59" s="10" t="n"/>
-      <c r="J59" s="10" t="n"/>
-      <c r="K59" s="10" t="n"/>
-      <c r="L59" s="10" t="n"/>
-      <c r="M59" s="10" t="n"/>
-      <c r="N59" s="10" t="n"/>
-      <c r="O59" s="10" t="n"/>
-      <c r="P59" s="10" t="n"/>
-      <c r="Q59" s="10" t="n"/>
-      <c r="R59" s="10" t="n"/>
-      <c r="S59" s="10" t="n"/>
-      <c r="T59" s="10" t="n"/>
-      <c r="U59" s="10" t="n"/>
-      <c r="V59" s="10" t="n"/>
-      <c r="W59" s="10" t="n"/>
-      <c r="X59" s="10" t="n"/>
-      <c r="Y59" s="10" t="n"/>
-      <c r="Z59" s="10" t="n"/>
-      <c r="AA59" s="10" t="n"/>
-      <c r="AB59" s="10" t="n"/>
-      <c r="AC59" s="10" t="n"/>
-      <c r="AD59" s="10" t="n"/>
-      <c r="AE59" s="10" t="n"/>
-      <c r="AF59" s="10" t="n"/>
-      <c r="AG59" s="10" t="n"/>
-      <c r="AH59" s="10" t="n"/>
-      <c r="AI59" s="10" t="n"/>
-      <c r="AJ59" s="10" t="n"/>
-      <c r="AK59" s="11" t="n"/>
-    </row>
-    <row r="61" ht="19.5" customHeight="1"/>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="27" t="inlineStr">
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="10" t="n"/>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="10" t="n"/>
+      <c r="AF58" s="10" t="n"/>
+      <c r="AG58" s="10" t="n"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
+      <c r="AK58" s="11" t="n"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="1"/>
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="B63" s="27" t="inlineStr">
-        <is>
-          <t>4.1 リクエストのバリデーション</t>
+      <c r="C63" s="41" t="inlineStr">
+        <is>
+          <t>パスパラメータ：dokusya_id 数値型チェック、必須</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="C64" s="41" t="inlineStr">
         <is>
-          <t>パスパラメータ：dokusya_id 数値型チェック、必須</t>
+          <t>不正なパラメータが存在する場合：HTTP 400 (`BAD_REQUEST`)</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：HTTP 400 (`BAD_REQUEST`)</t>
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="B66" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="C67" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="C68" s="41" t="inlineStr">
         <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
+          <t>必要権限: `dokusya.view`</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1">
       <c r="C69" s="41" t="inlineStr">
         <is>
-          <t>必要権限: `dokusya.view`</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="36" customHeight="1">
+          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
       <c r="C70" s="41" t="inlineStr">
         <is>
-          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="C71" s="41" t="inlineStr">
         <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+          <t>DataScope:</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="C72" s="41" t="inlineStr">
-        <is>
-          <t>DataScope:</t>
+      <c r="D72" s="41" t="inlineStr">
+        <is>
+          <t>CHUOKAI（中央会）：自中央会のみ参照可能</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="D73" s="41" t="inlineStr">
         <is>
-          <t>CHUOKAI（中央会）：自中央会のみ参照可能</t>
+          <t>JA_HONTEN（JA本店）：自JAのみ参照可能（`ja_id = user.ja_id`）</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="D74" s="41" t="inlineStr">
         <is>
-          <t>JA_HONTEN（JA本店）：自JAのみ参照可能（`ja_id = user.ja_id`）</t>
+          <t>JA_KANRI_SHITEN（JA管理支店）：自管理支店のみ参照可能</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="D75" s="41" t="inlineStr">
-        <is>
-          <t>JA_KANRI_SHITEN（JA管理支店）：自管理支店のみ参照可能</t>
+      <c r="C75" s="41" t="inlineStr">
+        <is>
+          <t>DataScope違反の場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="C76" s="41" t="inlineStr">
-        <is>
-          <t>DataScope違反の場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="B77" s="27" t="inlineStr">
+      <c r="B76" s="27" t="inlineStr">
         <is>
           <t>4.3 購読者の存在確認</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="90" customHeight="1">
-      <c r="C78" s="42" t="inlineStr">
+    <row r="77" ht="90" customHeight="1">
+      <c r="C77" s="42" t="inlineStr">
         <is>
           <t>SELECT dokusya_id, ja_id, kanri_shiten_id
 FROM t_dokusya
@@ -5681,60 +5621,60 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D78" s="10" t="n"/>
-      <c r="E78" s="10" t="n"/>
-      <c r="F78" s="10" t="n"/>
-      <c r="G78" s="10" t="n"/>
-      <c r="H78" s="10" t="n"/>
-      <c r="I78" s="10" t="n"/>
-      <c r="J78" s="10" t="n"/>
-      <c r="K78" s="10" t="n"/>
-      <c r="L78" s="10" t="n"/>
-      <c r="M78" s="10" t="n"/>
-      <c r="N78" s="10" t="n"/>
-      <c r="O78" s="10" t="n"/>
-      <c r="P78" s="10" t="n"/>
-      <c r="Q78" s="10" t="n"/>
-      <c r="R78" s="10" t="n"/>
-      <c r="S78" s="10" t="n"/>
-      <c r="T78" s="10" t="n"/>
-      <c r="U78" s="10" t="n"/>
-      <c r="V78" s="10" t="n"/>
-      <c r="W78" s="10" t="n"/>
-      <c r="X78" s="10" t="n"/>
-      <c r="Y78" s="10" t="n"/>
-      <c r="Z78" s="10" t="n"/>
-      <c r="AA78" s="10" t="n"/>
-      <c r="AB78" s="10" t="n"/>
-      <c r="AC78" s="10" t="n"/>
-      <c r="AD78" s="10" t="n"/>
-      <c r="AE78" s="10" t="n"/>
-      <c r="AF78" s="10" t="n"/>
-      <c r="AG78" s="10" t="n"/>
-      <c r="AH78" s="10" t="n"/>
-      <c r="AI78" s="10" t="n"/>
-      <c r="AJ78" s="10" t="n"/>
-      <c r="AK78" s="11" t="n"/>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="10" t="n"/>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="10" t="n"/>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="10" t="n"/>
+      <c r="Q77" s="10" t="n"/>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
+      <c r="T77" s="10" t="n"/>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="10" t="n"/>
+      <c r="X77" s="10" t="n"/>
+      <c r="Y77" s="10" t="n"/>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="10" t="n"/>
+      <c r="AD77" s="10" t="n"/>
+      <c r="AE77" s="10" t="n"/>
+      <c r="AF77" s="10" t="n"/>
+      <c r="AG77" s="10" t="n"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="10" t="n"/>
+      <c r="AJ77" s="10" t="n"/>
+      <c r="AK77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="C78" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
-        <is>
-          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="B80" s="27" t="inlineStr">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>4.4 履歴データ取得</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="162" customHeight="1">
-      <c r="C81" s="42" t="inlineStr">
+    <row r="80" ht="162" customHeight="1">
+      <c r="C80" s="42" t="inlineStr">
         <is>
           <t>SELECT dokusya_rireki_id, dokusya_id, rireki_no,
-       tetsuzuki_shurui, henko_riyu,
+       tetsuzuki_shurui,
        saishin_data_flg, shinki_flg, kaiyaku_flg, zougen_hokoku_flg,
        denshi_shonin_status,
        created_at, created_by
@@ -5744,117 +5684,120 @@
 ORDER BY rireki_no DESC</t>
         </is>
       </c>
-      <c r="D81" s="10" t="n"/>
-      <c r="E81" s="10" t="n"/>
-      <c r="F81" s="10" t="n"/>
-      <c r="G81" s="10" t="n"/>
-      <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="n"/>
-      <c r="J81" s="10" t="n"/>
-      <c r="K81" s="10" t="n"/>
-      <c r="L81" s="10" t="n"/>
-      <c r="M81" s="10" t="n"/>
-      <c r="N81" s="10" t="n"/>
-      <c r="O81" s="10" t="n"/>
-      <c r="P81" s="10" t="n"/>
-      <c r="Q81" s="10" t="n"/>
-      <c r="R81" s="10" t="n"/>
-      <c r="S81" s="10" t="n"/>
-      <c r="T81" s="10" t="n"/>
-      <c r="U81" s="10" t="n"/>
-      <c r="V81" s="10" t="n"/>
-      <c r="W81" s="10" t="n"/>
-      <c r="X81" s="10" t="n"/>
-      <c r="Y81" s="10" t="n"/>
-      <c r="Z81" s="10" t="n"/>
-      <c r="AA81" s="10" t="n"/>
-      <c r="AB81" s="10" t="n"/>
-      <c r="AC81" s="10" t="n"/>
-      <c r="AD81" s="10" t="n"/>
-      <c r="AE81" s="10" t="n"/>
-      <c r="AF81" s="10" t="n"/>
-      <c r="AG81" s="10" t="n"/>
-      <c r="AH81" s="10" t="n"/>
-      <c r="AI81" s="10" t="n"/>
-      <c r="AJ81" s="10" t="n"/>
-      <c r="AK81" s="11" t="n"/>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="B82" s="27" t="inlineStr">
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="10" t="n"/>
+      <c r="J80" s="10" t="n"/>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="10" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="10" t="n"/>
+      <c r="Q80" s="10" t="n"/>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="10" t="n"/>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="10" t="n"/>
+      <c r="X80" s="10" t="n"/>
+      <c r="Y80" s="10" t="n"/>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="10" t="n"/>
+      <c r="AC80" s="10" t="n"/>
+      <c r="AD80" s="10" t="n"/>
+      <c r="AE80" s="10" t="n"/>
+      <c r="AF80" s="10" t="n"/>
+      <c r="AG80" s="10" t="n"/>
+      <c r="AH80" s="10" t="n"/>
+      <c r="AI80" s="10" t="n"/>
+      <c r="AJ80" s="10" t="n"/>
+      <c r="AK80" s="11" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="B81" s="27" t="inlineStr">
         <is>
           <t>4.5 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="36" customHeight="1">
+    <row r="82" ht="36" customHeight="1">
+      <c r="C82" s="41" t="inlineStr">
+        <is>
+          <t>tetsuzuki_shurui 値をラベル（m_code.code_category='TETSUZUKI_SHURUI'）にマッピング。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
       <c r="C83" s="41" t="inlineStr">
         <is>
-          <t>tetsuzuki_shurui 値をラベル（m_code.code_category='TETSUZUKI_SHURUI'）にマッピング。</t>
+          <t>data 配列を含むJSONを返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
-        <is>
-          <t>data 配列を含むJSONを返却する。HTTP 200。</t>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>4.6 例外処理</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="B85" s="27" t="inlineStr">
-        <is>
-          <t>4.6 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
+      <c r="C85" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="184">
+  <mergeCells count="178">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y27:AE27"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="Y36:AE36"/>
+    <mergeCell ref="C66:AK66"/>
+    <mergeCell ref="B54:I54"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C53:AK53"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
+    <mergeCell ref="C77:AK77"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="C68:AK68"/>
-    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="D73:AK73"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="C65:AK65"/>
     <mergeCell ref="D33:L33"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="C44:AK44"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C84:AK84"/>
+    <mergeCell ref="B65:AK65"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="D35:L35"/>
+    <mergeCell ref="C46:AK46"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
-    <mergeCell ref="B63:AK63"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="AF34:AK34"/>
@@ -5866,15 +5809,14 @@
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T37:X37"/>
+    <mergeCell ref="B45:I45"/>
     <mergeCell ref="D36:L36"/>
-    <mergeCell ref="D75:AK75"/>
-    <mergeCell ref="B66:AK66"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="T30:X30"/>
+    <mergeCell ref="D72:AK72"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="B77:AK77"/>
     <mergeCell ref="T38:X38"/>
-    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="C49:AK49"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y33:AE33"/>
@@ -5884,7 +5826,6 @@
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
-    <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="D39:L39"/>
     <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="AD2:AG3"/>
@@ -5892,6 +5833,7 @@
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="D29:L29"/>
+    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="T40:X40"/>
@@ -5899,33 +5841,32 @@
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="B49:I49"/>
     <mergeCell ref="Y29:AE29"/>
-    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="A25:AK25"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="C52:AK52"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="Y31:AE31"/>
+    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="M37:P37"/>
-    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
-    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="C29:C41"/>
     <mergeCell ref="C78:AK78"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q27:S27"/>
@@ -5934,26 +5875,23 @@
     <mergeCell ref="C64:AK64"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
-    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="D30:L30"/>
     <mergeCell ref="AF40:AK40"/>
+    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="M39:P39"/>
-    <mergeCell ref="C50:AK50"/>
+    <mergeCell ref="B84:AK84"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="C56:AK56"/>
-    <mergeCell ref="T41:X41"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="B80:AK80"/>
+    <mergeCell ref="C43:AK43"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="M40:P40"/>
-    <mergeCell ref="B55:I55"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
@@ -5964,38 +5902,34 @@
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="C67:AK67"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="M41:P41"/>
     <mergeCell ref="D32:L32"/>
-    <mergeCell ref="D41:L41"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="C83:AK83"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B58:I58"/>
     <mergeCell ref="D74:AK74"/>
-    <mergeCell ref="B52:I52"/>
     <mergeCell ref="Y32:AE32"/>
-    <mergeCell ref="A62:AK62"/>
-    <mergeCell ref="B82:AK82"/>
+    <mergeCell ref="B42:I42"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="C47:AK47"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="C29:C40"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="A61:AK61"/>
+    <mergeCell ref="B76:AK76"/>
     <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
-    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="D31:L31"/>
+    <mergeCell ref="B62:AK62"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="M28:P28"/>
@@ -7151,7 +7085,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7622,7 +7556,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8551,7 +8485,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -9238,7 +9172,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -10461,7 +10395,7 @@
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="B35" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="19" t="inlineStr">
@@ -10521,7 +10455,7 @@
     </row>
     <row r="36" ht="54" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="19" t="inlineStr">
@@ -10581,7 +10515,7 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="19" t="inlineStr">
@@ -10641,7 +10575,7 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
@@ -10701,7 +10635,7 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
@@ -10761,7 +10695,7 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
@@ -10821,7 +10755,7 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
@@ -10881,7 +10815,7 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
@@ -10941,7 +10875,7 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
@@ -11001,7 +10935,7 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
@@ -11061,7 +10995,7 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
@@ -11121,7 +11055,7 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
@@ -11177,7 +11111,7 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
@@ -11233,7 +11167,7 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
@@ -11289,7 +11223,7 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
@@ -11345,7 +11279,7 @@
     </row>
     <row r="50" ht="54" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C50" s="38" t="n"/>
       <c r="D50" s="19" t="inlineStr">
@@ -11405,7 +11339,7 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" s="38" t="n"/>
       <c r="D51" s="19" t="inlineStr">
@@ -11465,7 +11399,7 @@
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C52" s="38" t="n"/>
       <c r="D52" s="19" t="inlineStr">
@@ -11525,7 +11459,7 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
@@ -11585,7 +11519,7 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C54" s="38" t="n"/>
       <c r="D54" s="19" t="inlineStr">
@@ -11641,7 +11575,7 @@
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C55" s="38" t="n"/>
       <c r="D55" s="19" t="inlineStr">
@@ -11697,7 +11631,7 @@
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C56" s="38" t="n"/>
       <c r="D56" s="19" t="inlineStr">
@@ -11753,7 +11687,7 @@
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C57" s="38" t="n"/>
       <c r="D57" s="19" t="inlineStr">
@@ -11809,7 +11743,7 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C58" s="38" t="n"/>
       <c r="D58" s="19" t="inlineStr">
@@ -11865,7 +11799,7 @@
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C59" s="38" t="n"/>
       <c r="D59" s="19" t="inlineStr">
@@ -11921,7 +11855,7 @@
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C60" s="38" t="n"/>
       <c r="D60" s="19" t="inlineStr">
@@ -11977,7 +11911,7 @@
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C61" s="38" t="n"/>
       <c r="D61" s="19" t="inlineStr">
@@ -12033,7 +11967,7 @@
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C62" s="38" t="n"/>
       <c r="D62" s="19" t="inlineStr">
@@ -12089,7 +12023,7 @@
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C63" s="38" t="n"/>
       <c r="D63" s="19" t="inlineStr">
@@ -12145,7 +12079,7 @@
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C64" s="38" t="n"/>
       <c r="D64" s="19" t="inlineStr">
@@ -12201,7 +12135,7 @@
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C65" s="38" t="n"/>
       <c r="D65" s="19" t="inlineStr">
@@ -12261,7 +12195,7 @@
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="B66" s="31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C66" s="38" t="n"/>
       <c r="D66" s="19" t="inlineStr">
@@ -12321,7 +12255,7 @@
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="B67" s="31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C67" s="38" t="n"/>
       <c r="D67" s="19" t="inlineStr">
@@ -12381,7 +12315,7 @@
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C68" s="38" t="n"/>
       <c r="D68" s="19" t="inlineStr">
@@ -12441,7 +12375,7 @@
     </row>
     <row r="69" ht="54" customHeight="1">
       <c r="B69" s="31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C69" s="38" t="n"/>
       <c r="D69" s="19" t="inlineStr">
@@ -12501,7 +12435,7 @@
     </row>
     <row r="70" ht="72" customHeight="1">
       <c r="B70" s="31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C70" s="38" t="n"/>
       <c r="D70" s="19" t="inlineStr">
@@ -12561,7 +12495,7 @@
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="B71" s="31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C71" s="38" t="n"/>
       <c r="D71" s="19" t="inlineStr">
@@ -12621,7 +12555,7 @@
     </row>
     <row r="72" ht="72" customHeight="1">
       <c r="B72" s="31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C72" s="38" t="n"/>
       <c r="D72" s="19" t="inlineStr">
@@ -12681,7 +12615,7 @@
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="B73" s="31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C73" s="38" t="n"/>
       <c r="D73" s="19" t="inlineStr">
@@ -12737,7 +12671,7 @@
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="B74" s="31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C74" s="38" t="n"/>
       <c r="D74" s="19" t="inlineStr">
@@ -12793,7 +12727,7 @@
     </row>
     <row r="75" ht="72" customHeight="1">
       <c r="B75" s="31" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C75" s="38" t="n"/>
       <c r="D75" s="19" t="inlineStr">
@@ -12853,7 +12787,7 @@
     </row>
     <row r="76" ht="54" customHeight="1">
       <c r="B76" s="31" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C76" s="38" t="n"/>
       <c r="D76" s="19" t="inlineStr">
@@ -12913,7 +12847,7 @@
     </row>
     <row r="77" ht="54" customHeight="1">
       <c r="B77" s="31" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C77" s="38" t="n"/>
       <c r="D77" s="19" t="inlineStr">
@@ -12973,7 +12907,7 @@
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="B78" s="31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C78" s="38" t="n"/>
       <c r="D78" s="19" t="inlineStr">
@@ -13029,7 +12963,7 @@
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="B79" s="31" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C79" s="38" t="n"/>
       <c r="D79" s="19" t="inlineStr">
@@ -13085,7 +13019,7 @@
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="B80" s="31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C80" s="38" t="n"/>
       <c r="D80" s="19" t="inlineStr">
@@ -13141,7 +13075,7 @@
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="B81" s="31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C81" s="38" t="n"/>
       <c r="D81" s="19" t="inlineStr">
@@ -13197,7 +13131,7 @@
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="B82" s="31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C82" s="38" t="n"/>
       <c r="D82" s="19" t="inlineStr">
@@ -13261,7 +13195,7 @@
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="B83" s="31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C83" s="38" t="n"/>
       <c r="D83" s="19" t="inlineStr">
@@ -13325,7 +13259,7 @@
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="B84" s="31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C84" s="38" t="n"/>
       <c r="D84" s="19" t="inlineStr">
@@ -13389,7 +13323,7 @@
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="B85" s="31" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C85" s="38" t="n"/>
       <c r="D85" s="19" t="inlineStr">
@@ -13453,7 +13387,7 @@
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="B86" s="31" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C86" s="38" t="n"/>
       <c r="D86" s="19" t="inlineStr">
@@ -13513,7 +13447,7 @@
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="B87" s="31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C87" s="38" t="n"/>
       <c r="D87" s="19" t="inlineStr">
@@ -13569,7 +13503,7 @@
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="B88" s="31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C88" s="38" t="n"/>
       <c r="D88" s="19" t="inlineStr">
@@ -13629,7 +13563,7 @@
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="B89" s="31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C89" s="38" t="n"/>
       <c r="D89" s="19" t="inlineStr">
@@ -13689,7 +13623,7 @@
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="B90" s="31" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C90" s="38" t="n"/>
       <c r="D90" s="19" t="inlineStr">
@@ -13753,7 +13687,7 @@
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="B91" s="31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C91" s="39" t="n"/>
       <c r="D91" s="19" t="inlineStr">
@@ -15089,7 +15023,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -19412,7 +19346,7 @@
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="B85" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C85" s="38" t="n"/>
       <c r="D85" s="19" t="inlineStr">
@@ -19472,7 +19406,7 @@
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="B86" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C86" s="38" t="n"/>
       <c r="D86" s="19" t="inlineStr">
@@ -19532,7 +19466,7 @@
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="B87" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C87" s="38" t="n"/>
       <c r="D87" s="19" t="inlineStr">
@@ -19592,7 +19526,7 @@
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="B88" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C88" s="38" t="n"/>
       <c r="D88" s="19" t="inlineStr">
@@ -19652,7 +19586,7 @@
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="B89" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C89" s="38" t="n"/>
       <c r="D89" s="19" t="inlineStr">
@@ -19712,7 +19646,7 @@
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="B90" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C90" s="38" t="n"/>
       <c r="D90" s="19" t="inlineStr">
@@ -19772,7 +19706,7 @@
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="B91" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C91" s="38" t="n"/>
       <c r="D91" s="19" t="inlineStr">
@@ -19832,7 +19766,7 @@
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="B92" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C92" s="38" t="n"/>
       <c r="D92" s="19" t="inlineStr">
@@ -19892,7 +19826,7 @@
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="B93" s="31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C93" s="38" t="n"/>
       <c r="D93" s="19" t="inlineStr">
@@ -19952,7 +19886,7 @@
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="B94" s="31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C94" s="38" t="n"/>
       <c r="D94" s="19" t="inlineStr">
@@ -20012,7 +19946,7 @@
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="B95" s="31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C95" s="38" t="n"/>
       <c r="D95" s="19" t="inlineStr">
@@ -20072,7 +20006,7 @@
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="B96" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C96" s="38" t="n"/>
       <c r="D96" s="19" t="inlineStr">
@@ -20128,7 +20062,7 @@
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="B97" s="31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C97" s="38" t="n"/>
       <c r="D97" s="19" t="inlineStr">
@@ -20184,7 +20118,7 @@
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="B98" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C98" s="38" t="n"/>
       <c r="D98" s="19" t="inlineStr">
@@ -20240,7 +20174,7 @@
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="B99" s="31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C99" s="38" t="n"/>
       <c r="D99" s="19" t="inlineStr">
@@ -20296,7 +20230,7 @@
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="B100" s="31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C100" s="38" t="n"/>
       <c r="D100" s="19" t="inlineStr">
@@ -20356,7 +20290,7 @@
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="B101" s="31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C101" s="38" t="n"/>
       <c r="D101" s="19" t="inlineStr">
@@ -20416,7 +20350,7 @@
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="B102" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C102" s="38" t="n"/>
       <c r="D102" s="19" t="inlineStr">
@@ -20476,7 +20410,7 @@
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="B103" s="31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C103" s="38" t="n"/>
       <c r="D103" s="19" t="inlineStr">
@@ -20536,7 +20470,7 @@
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="B104" s="31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C104" s="38" t="n"/>
       <c r="D104" s="19" t="inlineStr">
@@ -20592,7 +20526,7 @@
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="B105" s="31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C105" s="38" t="n"/>
       <c r="D105" s="19" t="inlineStr">
@@ -20648,7 +20582,7 @@
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="B106" s="31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C106" s="38" t="n"/>
       <c r="D106" s="19" t="inlineStr">
@@ -20704,7 +20638,7 @@
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="B107" s="31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C107" s="38" t="n"/>
       <c r="D107" s="19" t="inlineStr">
@@ -20760,7 +20694,7 @@
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="B108" s="31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C108" s="38" t="n"/>
       <c r="D108" s="19" t="inlineStr">
@@ -20816,7 +20750,7 @@
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="B109" s="31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C109" s="38" t="n"/>
       <c r="D109" s="19" t="inlineStr">
@@ -20872,7 +20806,7 @@
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="B110" s="31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C110" s="38" t="n"/>
       <c r="D110" s="19" t="inlineStr">
@@ -20928,7 +20862,7 @@
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="B111" s="31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C111" s="38" t="n"/>
       <c r="D111" s="19" t="inlineStr">
@@ -20984,7 +20918,7 @@
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="B112" s="31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C112" s="38" t="n"/>
       <c r="D112" s="19" t="inlineStr">
@@ -21040,7 +20974,7 @@
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="B113" s="31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C113" s="38" t="n"/>
       <c r="D113" s="19" t="inlineStr">
@@ -21096,7 +21030,7 @@
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="B114" s="31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C114" s="38" t="n"/>
       <c r="D114" s="19" t="inlineStr">
@@ -21152,7 +21086,7 @@
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="B115" s="31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C115" s="38" t="n"/>
       <c r="D115" s="19" t="inlineStr">
@@ -21212,7 +21146,7 @@
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="B116" s="31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C116" s="38" t="n"/>
       <c r="D116" s="19" t="inlineStr">
@@ -21272,7 +21206,7 @@
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="B117" s="31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C117" s="38" t="n"/>
       <c r="D117" s="19" t="inlineStr">
@@ -21332,7 +21266,7 @@
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="B118" s="31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C118" s="38" t="n"/>
       <c r="D118" s="19" t="inlineStr">
@@ -21392,7 +21326,7 @@
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="B119" s="31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C119" s="38" t="n"/>
       <c r="D119" s="19" t="inlineStr">
@@ -21452,7 +21386,7 @@
     </row>
     <row r="120" ht="36" customHeight="1">
       <c r="B120" s="31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C120" s="38" t="n"/>
       <c r="D120" s="19" t="inlineStr">
@@ -21512,7 +21446,7 @@
     </row>
     <row r="121" ht="36" customHeight="1">
       <c r="B121" s="31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C121" s="38" t="n"/>
       <c r="D121" s="19" t="inlineStr">
@@ -21568,7 +21502,7 @@
     </row>
     <row r="122" ht="36" customHeight="1">
       <c r="B122" s="31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C122" s="38" t="n"/>
       <c r="D122" s="19" t="inlineStr">
@@ -21624,7 +21558,7 @@
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="B123" s="31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C123" s="38" t="n"/>
       <c r="D123" s="19" t="inlineStr">
@@ -21684,7 +21618,7 @@
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="B124" s="31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C124" s="38" t="n"/>
       <c r="D124" s="19" t="inlineStr">
@@ -21744,7 +21678,7 @@
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="B125" s="31" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C125" s="38" t="n"/>
       <c r="D125" s="19" t="inlineStr">
@@ -21804,7 +21738,7 @@
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="B126" s="31" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C126" s="38" t="n"/>
       <c r="D126" s="19" t="inlineStr">
@@ -21860,7 +21794,7 @@
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="B127" s="31" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C127" s="38" t="n"/>
       <c r="D127" s="19" t="inlineStr">
@@ -21916,7 +21850,7 @@
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="B128" s="31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C128" s="38" t="n"/>
       <c r="D128" s="19" t="inlineStr">
@@ -21972,7 +21906,7 @@
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="B129" s="31" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C129" s="38" t="n"/>
       <c r="D129" s="19" t="inlineStr">
@@ -22028,7 +21962,7 @@
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="B130" s="31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C130" s="38" t="n"/>
       <c r="D130" s="19" t="inlineStr">
@@ -22092,7 +22026,7 @@
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="B131" s="31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C131" s="38" t="n"/>
       <c r="D131" s="19" t="inlineStr">
@@ -22156,7 +22090,7 @@
     </row>
     <row r="132" ht="18" customHeight="1">
       <c r="B132" s="31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C132" s="38" t="n"/>
       <c r="D132" s="19" t="inlineStr">
@@ -22220,7 +22154,7 @@
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="B133" s="31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C133" s="38" t="n"/>
       <c r="D133" s="19" t="inlineStr">
@@ -22284,7 +22218,7 @@
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="B134" s="31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C134" s="38" t="n"/>
       <c r="D134" s="19" t="inlineStr">
@@ -22344,7 +22278,7 @@
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="B135" s="31" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C135" s="38" t="n"/>
       <c r="D135" s="19" t="inlineStr">
@@ -22400,7 +22334,7 @@
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="B136" s="31" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C136" s="38" t="n"/>
       <c r="D136" s="19" t="inlineStr">
@@ -22460,7 +22394,7 @@
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="B137" s="31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C137" s="38" t="n"/>
       <c r="D137" s="19" t="inlineStr">
@@ -22520,7 +22454,7 @@
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="B138" s="31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C138" s="38" t="n"/>
       <c r="D138" s="19" t="inlineStr">
@@ -22584,7 +22518,7 @@
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="B139" s="31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C139" s="39" t="n"/>
       <c r="D139" s="19" t="inlineStr">
@@ -23700,7 +23634,7 @@
   hikiotoshi_yokin_shubetsu, hikiotoshi_koza_no, hikiotoshi_koza_meigi,
   dokusyaso_bunrui, nogyosya_bunrui,
   shoki_dokusya_kaishi_date, dokusya_kaishi_date, dokusya_chushi_date,
-  joho_henko_tekiyo_date, seikyu_kaishi_month, biko, henko_riyu,
+  joho_henko_tekiyo_date, seikyu_kaishi_month, biko,
   saishin_data_flg, zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
   zenkai_hanbaiten_id, zenkai_dokusya_busu, zenkai_yubin_no,
   zenkai_todofuken_code, zenkai_shikuchoson, zenkai_chome_banchi,
@@ -23723,7 +23657,7 @@
   :hikiotoshi_yokin_shubetsu, :hikiotoshi_koza_no, :hikiotoshi_koza_meigi,
   :dokusyaso_bunrui, :nogyosya_bunrui,
   :dokusya_kaishi_date, :dokusya_kaishi_date, :dokusya_chushi_date,
-  :joho_henko_tekiyo_date, :seikyu_kaishi_month, :biko, '',
+  :joho_henko_tekiyo_date, :seikyu_kaishi_month, :biko,
   TRUE, TRUE, :shinki_flg, :kaiyaku_flg,
   NULL, NULL, NULL,
   NULL, NULL, NULL,
@@ -24967,7 +24901,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -26909,7 +26843,7 @@
   hikiotoshi_yokin_shubetsu, hikiotoshi_koza_no, hikiotoshi_koza_meigi,
   dokusyaso_bunrui, nogyosya_bunrui,
   shoki_dokusya_kaishi_date, dokusya_kaishi_date, dokusya_chushi_date,
-  joho_henko_tekiyo_date, seikyu_kaishi_month, biko, henko_riyu,
+  joho_henko_tekiyo_date, seikyu_kaishi_month, biko,
   saishin_data_flg, zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
   zenkai_hanbaiten_id, zenkai_dokusya_busu, zenkai_yubin_no,
   zenkai_todofuken_code, zenkai_shikuchoson, zenkai_chome_banchi,
@@ -26932,7 +26866,7 @@
   :hikiotoshi_yokin_shubetsu, :hikiotoshi_koza_no, :hikiotoshi_koza_meigi,
   :dokusyaso_bunrui, :nogyosya_bunrui,
   :shoki_dokusya_kaishi_date, :dokusya_kaishi_date, :dokusya_chushi_date,
-  :joho_henko_tekiyo_date, :seikyu_kaishi_month, :biko, :henko_riyu,
+  :joho_henko_tekiyo_date, :seikyu_kaishi_month, :biko,
   TRUE, :zougen_hokoku_flg, :shinki_flg, :kaiyaku_flg,
   :zenkai_hanbaiten_id, :zenkai_dokusya_busu, :zenkai_yubin_no,
   :zenkai_todofuken_code, :zenkai_shikuchoson, :zenkai_chome_banchi,
@@ -27553,7 +27487,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -29151,20 +29085,18 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="234" customHeight="1">
+    <row r="79" ht="198" customHeight="1">
       <c r="C79" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya_rireki (
   dokusya_id, rireki_no, ja_id, ...,  -- 4.3 で取得した現データを全コピー
   denshi_shonin_status,
   saishin_data_flg, zougen_hokoku_flg, shinki_flg, kaiyaku_flg,
-  henko_riyu,
   created_at, created_by
 ) VALUES (
   :dokusya_id, :new_rireki_no, :ja_id, ...,
   1,
   TRUE, FALSE, FALSE, FALSE,
-  '電子版承認',
   NOW(), :user_account_id
 )</t>
         </is>

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
@@ -1517,7 +1517,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3577,7 +3577,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5945,7 +5945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AG15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6813,10 +6813,70 @@
       <c r="AF14" s="10" t="n"/>
       <c r="AG14" s="11" t="n"/>
     </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="n"/>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="11" t="n"/>
+      <c r="R15" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07 改訂（UI統一）：BE仕様は変更なし（電子版の `change_mode='reserved'` 拒否は従来どおり）。FE側の記述のみ更新 — 電子版でもモードバーを表示し「予約変更」ボタンを非活性にする（従来はモードバー自体を非表示にして当日変更固定で開いていた）。</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="10" t="n"/>
+      <c r="V15" s="11" t="n"/>
+      <c r="W15" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X15" s="10" t="n"/>
+      <c r="Y15" s="10" t="n"/>
+      <c r="Z15" s="10" t="n"/>
+      <c r="AA15" s="11" t="n"/>
+      <c r="AB15" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC15" s="10" t="n"/>
+      <c r="AD15" s="10" t="n"/>
+      <c r="AE15" s="10" t="n"/>
+      <c r="AF15" s="10" t="n"/>
+      <c r="AG15" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="98">
+  <mergeCells count="105">
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="R10:V10"/>
     <mergeCell ref="H2:J2"/>
@@ -6872,11 +6932,13 @@
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="H13:J13"/>
+    <mergeCell ref="R15:V15"/>
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="AB7:AG7"/>
+    <mergeCell ref="H15:J15"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="H8:J8"/>
@@ -6894,8 +6956,10 @@
     <mergeCell ref="W13:AA13"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="K14:Q14"/>
+    <mergeCell ref="C15:G15"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB9:AG9"/>
+    <mergeCell ref="W15:AA15"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="K13:Q13"/>
@@ -6904,11 +6968,13 @@
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="W1:AA1"/>
     <mergeCell ref="H12:J12"/>
+    <mergeCell ref="K15:Q15"/>
     <mergeCell ref="R12:V12"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="AB6:AG6"/>
+    <mergeCell ref="AB15:AG15"/>
     <mergeCell ref="W11:AA11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="K2:Q2"/>
@@ -7085,7 +7151,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7556,7 +7622,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8485,7 +8551,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -9172,7 +9238,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -15023,7 +15089,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -24901,7 +24967,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -27487,7 +27553,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
@@ -1517,7 +1517,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3922,7 +3922,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6222,7 +6222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG17"/>
+  <dimension ref="A1:AG18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -7251,8 +7251,59 @@
       <c r="AF17" s="10" t="n"/>
       <c r="AG17" s="11" t="n"/>
     </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="11" t="n"/>
+      <c r="R18" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-08：①**併読（dokusya_shubetsu=3）の配達先情報を画面に表示する**。従来は電子版と同じ扱いで配達先エリアを非活性化していたが、併読は紙も配達されるため配達先が実在し、読者同期バッチも電子版の `paper_*`（paper_zip / paper_pref_id / paper_addr / paper_city / paper_building）由来の配達先を `haitatsu_*` へ取り込んでいる（`haitatsu_same_flg=false`）。エリアを隠したままでは同期済みの配達先住所を画面から確認できなかった。非活性の対象は電子版のみ。**API のリクエスト/レスポンス仕様に変更は無い**（併読は従来どおり作成 `VALIDATION_ERROR`、編集/停止/削除 `DOKUSYA_READ_ONLY`(403) の参照専用）。②読者同期バッチの販売店割当を電子版・併読とも当該JAのダミー販売店（`hanbaiten_code = 9999999999`）へ統一し、電子版側の `ShopCd` は参照しない。紙の配達担当は cloud 側（SCR-011 / SCR-017）で設定する運用とする。</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="11" t="n"/>
+      <c r="W18" s="17" t="inlineStr"/>
+      <c r="X18" s="10" t="n"/>
+      <c r="Y18" s="10" t="n"/>
+      <c r="Z18" s="10" t="n"/>
+      <c r="AA18" s="11" t="n"/>
+      <c r="AB18" s="17" t="inlineStr"/>
+      <c r="AC18" s="10" t="n"/>
+      <c r="AD18" s="10" t="n"/>
+      <c r="AE18" s="10" t="n"/>
+      <c r="AF18" s="10" t="n"/>
+      <c r="AG18" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="119">
+  <mergeCells count="126">
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="A15:B15"/>
@@ -7276,6 +7327,7 @@
     <mergeCell ref="AB3:AG3"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="W18:AA18"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB5:AG5"/>
@@ -7284,6 +7336,7 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="R14:V14"/>
+    <mergeCell ref="C18:G18"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="K17:Q17"/>
@@ -7300,6 +7353,7 @@
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="W12:AA12"/>
+    <mergeCell ref="AB18:AG18"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="K11:Q11"/>
     <mergeCell ref="A8:B8"/>
@@ -7322,12 +7376,14 @@
     <mergeCell ref="H13:J13"/>
     <mergeCell ref="C16:G16"/>
     <mergeCell ref="R15:V15"/>
+    <mergeCell ref="K18:Q18"/>
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="H8:J8"/>
@@ -7360,6 +7416,7 @@
     <mergeCell ref="W1:AA1"/>
     <mergeCell ref="H12:J12"/>
     <mergeCell ref="K15:Q15"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="R12:V12"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="H14:J14"/>
@@ -7370,6 +7427,7 @@
     <mergeCell ref="W17:AA17"/>
     <mergeCell ref="W11:AA11"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="R18:V18"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
@@ -7544,7 +7602,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8015,7 +8073,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8944,7 +9002,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -9631,7 +9689,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -15734,7 +15792,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -26194,7 +26252,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -28788,7 +28846,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>

--- a/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者情報登録画面_V1.0.xlsx
@@ -18,6 +18,7 @@
     <sheet name="ACSMS-API-011-004" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="ACSMS-API-011-005" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="ACSMS-API-011-006" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ACSMS-API-011-007" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1517,7 +1518,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3922,7 +3923,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6216,13 +6217,1787 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AK80"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="4.25" customWidth="1" min="1" max="1"/>
+    <col width="4.25" customWidth="1" min="2" max="2"/>
+    <col width="4.25" customWidth="1" min="3" max="3"/>
+    <col width="4.25" customWidth="1" min="4" max="4"/>
+    <col width="4.25" customWidth="1" min="5" max="5"/>
+    <col width="4.25" customWidth="1" min="6" max="6"/>
+    <col width="4.25" customWidth="1" min="7" max="7"/>
+    <col width="4.25" customWidth="1" min="8" max="8"/>
+    <col width="4.25" customWidth="1" min="9" max="9"/>
+    <col width="4.25" customWidth="1" min="10" max="10"/>
+    <col width="4.25" customWidth="1" min="11" max="11"/>
+    <col width="4.25" customWidth="1" min="12" max="12"/>
+    <col width="4.25" customWidth="1" min="13" max="13"/>
+    <col width="4.25" customWidth="1" min="14" max="14"/>
+    <col width="4.25" customWidth="1" min="15" max="15"/>
+    <col width="4.25" customWidth="1" min="16" max="16"/>
+    <col width="4.25" customWidth="1" min="17" max="17"/>
+    <col width="4.25" customWidth="1" min="18" max="18"/>
+    <col width="4.25" customWidth="1" min="19" max="19"/>
+    <col width="4.25" customWidth="1" min="20" max="20"/>
+    <col width="4.25" customWidth="1" min="21" max="21"/>
+    <col width="4.25" customWidth="1" min="22" max="22"/>
+    <col width="4.25" customWidth="1" min="23" max="23"/>
+    <col width="4.25" customWidth="1" min="24" max="24"/>
+    <col width="4.25" customWidth="1" min="25" max="25"/>
+    <col width="4.25" customWidth="1" min="26" max="26"/>
+    <col width="4.25" customWidth="1" min="27" max="27"/>
+    <col width="4.25" customWidth="1" min="28" max="28"/>
+    <col width="4.25" customWidth="1" min="29" max="29"/>
+    <col width="4.25" customWidth="1" min="30" max="30"/>
+    <col width="4.25" customWidth="1" min="31" max="31"/>
+    <col width="4.25" customWidth="1" min="32" max="32"/>
+    <col width="4.25" customWidth="1" min="33" max="33"/>
+    <col width="4.25" customWidth="1" min="34" max="34"/>
+    <col width="4.25" customWidth="1" min="35" max="35"/>
+    <col width="4.25" customWidth="1" min="36" max="36"/>
+    <col width="4.25" customWidth="1" min="37" max="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.5" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>システム・アプリケーション名</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="10" t="n"/>
+      <c r="G1" s="10" t="n"/>
+      <c r="H1" s="10" t="n"/>
+      <c r="I1" s="11" t="n"/>
+      <c r="J1" s="16" t="inlineStr">
+        <is>
+          <t>ドキュメント</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="n"/>
+      <c r="L1" s="10" t="n"/>
+      <c r="M1" s="10" t="n"/>
+      <c r="N1" s="10" t="n"/>
+      <c r="O1" s="10" t="n"/>
+      <c r="P1" s="11" t="n"/>
+      <c r="Q1" s="16" t="inlineStr">
+        <is>
+          <t>シート名</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="n"/>
+      <c r="S1" s="10" t="n"/>
+      <c r="T1" s="10" t="n"/>
+      <c r="U1" s="11" t="n"/>
+      <c r="V1" s="16" t="inlineStr">
+        <is>
+          <t>作成日</t>
+        </is>
+      </c>
+      <c r="W1" s="10" t="n"/>
+      <c r="X1" s="10" t="n"/>
+      <c r="Y1" s="11" t="n"/>
+      <c r="Z1" s="16" t="inlineStr">
+        <is>
+          <t>作成者</t>
+        </is>
+      </c>
+      <c r="AA1" s="10" t="n"/>
+      <c r="AB1" s="10" t="n"/>
+      <c r="AC1" s="11" t="n"/>
+      <c r="AD1" s="16" t="inlineStr">
+        <is>
+          <t>更新日</t>
+        </is>
+      </c>
+      <c r="AE1" s="10" t="n"/>
+      <c r="AF1" s="10" t="n"/>
+      <c r="AG1" s="11" t="n"/>
+      <c r="AH1" s="16" t="inlineStr">
+        <is>
+          <t>更新者</t>
+        </is>
+      </c>
+      <c r="AI1" s="10" t="n"/>
+      <c r="AJ1" s="10" t="n"/>
+      <c r="AK1" s="11" t="n"/>
+    </row>
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>クラウド版購読者管理システム</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="n"/>
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="21" t="n"/>
+      <c r="E2" s="21" t="n"/>
+      <c r="F2" s="21" t="n"/>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="21" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="20" t="inlineStr">
+        <is>
+          <t>API設計書</t>
+        </is>
+      </c>
+      <c r="K2" s="21" t="n"/>
+      <c r="L2" s="21" t="n"/>
+      <c r="M2" s="21" t="n"/>
+      <c r="N2" s="21" t="n"/>
+      <c r="O2" s="21" t="n"/>
+      <c r="P2" s="22" t="n"/>
+      <c r="Q2" s="20" t="inlineStr">
+        <is>
+          <t>ACSMS-API-011-007</t>
+        </is>
+      </c>
+      <c r="R2" s="21" t="n"/>
+      <c r="S2" s="21" t="n"/>
+      <c r="T2" s="21" t="n"/>
+      <c r="U2" s="22" t="n"/>
+      <c r="V2" s="23" t="inlineStr">
+        <is>
+          <t>2026/05/07</t>
+        </is>
+      </c>
+      <c r="W2" s="21" t="n"/>
+      <c r="X2" s="21" t="n"/>
+      <c r="Y2" s="22" t="n"/>
+      <c r="Z2" s="20" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="AA2" s="21" t="n"/>
+      <c r="AB2" s="21" t="n"/>
+      <c r="AC2" s="22" t="n"/>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="AE2" s="21" t="n"/>
+      <c r="AF2" s="21" t="n"/>
+      <c r="AG2" s="22" t="n"/>
+      <c r="AH2" s="20" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="AI2" s="21" t="n"/>
+      <c r="AJ2" s="21" t="n"/>
+      <c r="AK2" s="22" t="n"/>
+    </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="24" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="26" t="n"/>
+      <c r="J3" s="24" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="26" t="n"/>
+      <c r="Q3" s="24" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="26" t="n"/>
+      <c r="V3" s="24" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="26" t="n"/>
+      <c r="Z3" s="24" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="26" t="n"/>
+      <c r="AD3" s="24" t="n"/>
+      <c r="AE3" s="25" t="n"/>
+      <c r="AF3" s="25" t="n"/>
+      <c r="AG3" s="26" t="n"/>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="25" t="n"/>
+      <c r="AJ3" s="25" t="n"/>
+      <c r="AK3" s="26" t="n"/>
+    </row>
+    <row r="4" ht="19.5" customHeight="1"/>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>1.概要</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19.5" customHeight="1"/>
+    <row r="7" ht="18" customHeight="1">
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>API名</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>Get Dokusya Effective At</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n"/>
+      <c r="W7" s="10" t="n"/>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="10" t="n"/>
+      <c r="AB7" s="10" t="n"/>
+      <c r="AC7" s="10" t="n"/>
+      <c r="AD7" s="10" t="n"/>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="10" t="n"/>
+      <c r="AG7" s="10" t="n"/>
+      <c r="AH7" s="10" t="n"/>
+      <c r="AI7" s="10" t="n"/>
+      <c r="AJ7" s="10" t="n"/>
+      <c r="AK7" s="11" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>概要</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>指定した情報変更適用日（joho）時点で有効な履歴行を、購読者詳細と同一形式で取得する（予約変更ポップアップの基準行取得用）</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="n"/>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="10" t="n"/>
+      <c r="W8" s="10" t="n"/>
+      <c r="X8" s="10" t="n"/>
+      <c r="Y8" s="10" t="n"/>
+      <c r="Z8" s="10" t="n"/>
+      <c r="AA8" s="10" t="n"/>
+      <c r="AB8" s="10" t="n"/>
+      <c r="AC8" s="10" t="n"/>
+      <c r="AD8" s="10" t="n"/>
+      <c r="AE8" s="10" t="n"/>
+      <c r="AF8" s="10" t="n"/>
+      <c r="AG8" s="10" t="n"/>
+      <c r="AH8" s="10" t="n"/>
+      <c r="AI8" s="10" t="n"/>
+      <c r="AJ8" s="10" t="n"/>
+      <c r="AK8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>URI</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>/api/v1/dokusya/{dokusya_id}/effective-at</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="10" t="n"/>
+      <c r="W9" s="10" t="n"/>
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="10" t="n"/>
+      <c r="Z9" s="10" t="n"/>
+      <c r="AA9" s="10" t="n"/>
+      <c r="AB9" s="10" t="n"/>
+      <c r="AC9" s="10" t="n"/>
+      <c r="AD9" s="10" t="n"/>
+      <c r="AE9" s="10" t="n"/>
+      <c r="AF9" s="10" t="n"/>
+      <c r="AG9" s="10" t="n"/>
+      <c r="AH9" s="10" t="n"/>
+      <c r="AI9" s="10" t="n"/>
+      <c r="AJ9" s="10" t="n"/>
+      <c r="AK9" s="11" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>メソッド</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="10" t="n"/>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="n"/>
+      <c r="V10" s="10" t="n"/>
+      <c r="W10" s="10" t="n"/>
+      <c r="X10" s="10" t="n"/>
+      <c r="Y10" s="10" t="n"/>
+      <c r="Z10" s="10" t="n"/>
+      <c r="AA10" s="10" t="n"/>
+      <c r="AB10" s="10" t="n"/>
+      <c r="AC10" s="10" t="n"/>
+      <c r="AD10" s="10" t="n"/>
+      <c r="AE10" s="10" t="n"/>
+      <c r="AF10" s="10" t="n"/>
+      <c r="AG10" s="10" t="n"/>
+      <c r="AH10" s="10" t="n"/>
+      <c r="AI10" s="10" t="n"/>
+      <c r="AJ10" s="10" t="n"/>
+      <c r="AK10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>リクエストボディー</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="10" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="n"/>
+      <c r="V11" s="10" t="n"/>
+      <c r="W11" s="10" t="n"/>
+      <c r="X11" s="10" t="n"/>
+      <c r="Y11" s="10" t="n"/>
+      <c r="Z11" s="10" t="n"/>
+      <c r="AA11" s="10" t="n"/>
+      <c r="AB11" s="10" t="n"/>
+      <c r="AC11" s="10" t="n"/>
+      <c r="AD11" s="10" t="n"/>
+      <c r="AE11" s="10" t="n"/>
+      <c r="AF11" s="10" t="n"/>
+      <c r="AG11" s="10" t="n"/>
+      <c r="AH11" s="10" t="n"/>
+      <c r="AI11" s="10" t="n"/>
+      <c r="AJ11" s="10" t="n"/>
+      <c r="AK11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>リクエストパラメーター</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>dokusya_id（パスパラメータ）, joho（クエリパラメータ・必須）</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="10" t="n"/>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n"/>
+      <c r="V12" s="10" t="n"/>
+      <c r="W12" s="10" t="n"/>
+      <c r="X12" s="10" t="n"/>
+      <c r="Y12" s="10" t="n"/>
+      <c r="Z12" s="10" t="n"/>
+      <c r="AA12" s="10" t="n"/>
+      <c r="AB12" s="10" t="n"/>
+      <c r="AC12" s="10" t="n"/>
+      <c r="AD12" s="10" t="n"/>
+      <c r="AE12" s="10" t="n"/>
+      <c r="AF12" s="10" t="n"/>
+      <c r="AG12" s="10" t="n"/>
+      <c r="AH12" s="10" t="n"/>
+      <c r="AI12" s="10" t="n"/>
+      <c r="AJ12" s="10" t="n"/>
+      <c r="AK12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>ヘッダ</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="10" t="n"/>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="10" t="n"/>
+      <c r="AB13" s="10" t="n"/>
+      <c r="AC13" s="10" t="n"/>
+      <c r="AD13" s="10" t="n"/>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" s="10" t="n"/>
+      <c r="AG13" s="10" t="n"/>
+      <c r="AH13" s="10" t="n"/>
+      <c r="AI13" s="10" t="n"/>
+      <c r="AJ13" s="10" t="n"/>
+      <c r="AK13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>HTTPレスポンスコード</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="17" t="n">
+        <v>200</v>
+      </c>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="11" t="n"/>
+      <c r="N14" s="19" t="inlineStr">
+        <is>
+          <t>正常に基準行を取得しました</t>
+        </is>
+      </c>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="10" t="n"/>
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="10" t="n"/>
+      <c r="Z14" s="10" t="n"/>
+      <c r="AA14" s="10" t="n"/>
+      <c r="AB14" s="10" t="n"/>
+      <c r="AC14" s="10" t="n"/>
+      <c r="AD14" s="10" t="n"/>
+      <c r="AE14" s="10" t="n"/>
+      <c r="AF14" s="10" t="n"/>
+      <c r="AG14" s="10" t="n"/>
+      <c r="AH14" s="10" t="n"/>
+      <c r="AI14" s="10" t="n"/>
+      <c r="AJ14" s="10" t="n"/>
+      <c r="AK14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="35" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>情報変更適用日の形式が不正です／範囲が不正です</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="10" t="n"/>
+      <c r="V15" s="10" t="n"/>
+      <c r="W15" s="10" t="n"/>
+      <c r="X15" s="10" t="n"/>
+      <c r="Y15" s="10" t="n"/>
+      <c r="Z15" s="10" t="n"/>
+      <c r="AA15" s="10" t="n"/>
+      <c r="AB15" s="10" t="n"/>
+      <c r="AC15" s="10" t="n"/>
+      <c r="AD15" s="10" t="n"/>
+      <c r="AE15" s="10" t="n"/>
+      <c r="AF15" s="10" t="n"/>
+      <c r="AG15" s="10" t="n"/>
+      <c r="AH15" s="10" t="n"/>
+      <c r="AI15" s="10" t="n"/>
+      <c r="AJ15" s="10" t="n"/>
+      <c r="AK15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="35" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="17" t="n">
+        <v>401</v>
+      </c>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n"/>
+      <c r="M16" s="11" t="n"/>
+      <c r="N16" s="19" t="inlineStr">
+        <is>
+          <t>セッションが切れました。再度ログインしてください</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n"/>
+      <c r="R16" s="10" t="n"/>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="n"/>
+      <c r="U16" s="10" t="n"/>
+      <c r="V16" s="10" t="n"/>
+      <c r="W16" s="10" t="n"/>
+      <c r="X16" s="10" t="n"/>
+      <c r="Y16" s="10" t="n"/>
+      <c r="Z16" s="10" t="n"/>
+      <c r="AA16" s="10" t="n"/>
+      <c r="AB16" s="10" t="n"/>
+      <c r="AC16" s="10" t="n"/>
+      <c r="AD16" s="10" t="n"/>
+      <c r="AE16" s="10" t="n"/>
+      <c r="AF16" s="10" t="n"/>
+      <c r="AG16" s="10" t="n"/>
+      <c r="AH16" s="10" t="n"/>
+      <c r="AI16" s="10" t="n"/>
+      <c r="AJ16" s="10" t="n"/>
+      <c r="AK16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="35" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="17" t="n">
+        <v>403</v>
+      </c>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n"/>
+      <c r="M17" s="11" t="n"/>
+      <c r="N17" s="19" t="inlineStr">
+        <is>
+          <t>この画面へのアクセス権限がありません</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="n"/>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="10" t="n"/>
+      <c r="R17" s="10" t="n"/>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="10" t="n"/>
+      <c r="U17" s="10" t="n"/>
+      <c r="V17" s="10" t="n"/>
+      <c r="W17" s="10" t="n"/>
+      <c r="X17" s="10" t="n"/>
+      <c r="Y17" s="10" t="n"/>
+      <c r="Z17" s="10" t="n"/>
+      <c r="AA17" s="10" t="n"/>
+      <c r="AB17" s="10" t="n"/>
+      <c r="AC17" s="10" t="n"/>
+      <c r="AD17" s="10" t="n"/>
+      <c r="AE17" s="10" t="n"/>
+      <c r="AF17" s="10" t="n"/>
+      <c r="AG17" s="10" t="n"/>
+      <c r="AH17" s="10" t="n"/>
+      <c r="AI17" s="10" t="n"/>
+      <c r="AJ17" s="10" t="n"/>
+      <c r="AK17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="35" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="17" t="n">
+        <v>404</v>
+      </c>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="11" t="n"/>
+      <c r="N18" s="19" t="inlineStr">
+        <is>
+          <t>指定された購読者が見つかりません</t>
+        </is>
+      </c>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n"/>
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="10" t="n"/>
+      <c r="Y18" s="10" t="n"/>
+      <c r="Z18" s="10" t="n"/>
+      <c r="AA18" s="10" t="n"/>
+      <c r="AB18" s="10" t="n"/>
+      <c r="AC18" s="10" t="n"/>
+      <c r="AD18" s="10" t="n"/>
+      <c r="AE18" s="10" t="n"/>
+      <c r="AF18" s="10" t="n"/>
+      <c r="AG18" s="10" t="n"/>
+      <c r="AH18" s="10" t="n"/>
+      <c r="AI18" s="10" t="n"/>
+      <c r="AJ18" s="10" t="n"/>
+      <c r="AK18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="26" t="n"/>
+      <c r="J19" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="19" t="inlineStr">
+        <is>
+          <t>システムエラーが発生しました</t>
+        </is>
+      </c>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="10" t="n"/>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="10" t="n"/>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="10" t="n"/>
+      <c r="Y19" s="10" t="n"/>
+      <c r="Z19" s="10" t="n"/>
+      <c r="AA19" s="10" t="n"/>
+      <c r="AB19" s="10" t="n"/>
+      <c r="AC19" s="10" t="n"/>
+      <c r="AD19" s="10" t="n"/>
+      <c r="AE19" s="10" t="n"/>
+      <c r="AF19" s="10" t="n"/>
+      <c r="AG19" s="10" t="n"/>
+      <c r="AH19" s="10" t="n"/>
+      <c r="AI19" s="10" t="n"/>
+      <c r="AJ19" s="10" t="n"/>
+      <c r="AK19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1"/>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>2. リクエストパラメータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19.5" customHeight="1"/>
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>パラメーターID</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="n"/>
+      <c r="O23" s="10" t="n"/>
+      <c r="P23" s="11" t="n"/>
+      <c r="Q23" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R23" s="10" t="n"/>
+      <c r="S23" s="11" t="n"/>
+      <c r="T23" s="16" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="U23" s="10" t="n"/>
+      <c r="V23" s="10" t="n"/>
+      <c r="W23" s="10" t="n"/>
+      <c r="X23" s="11" t="n"/>
+      <c r="Y23" s="16" t="inlineStr">
+        <is>
+          <t>最小長</t>
+        </is>
+      </c>
+      <c r="Z23" s="10" t="n"/>
+      <c r="AA23" s="10" t="n"/>
+      <c r="AB23" s="11" t="n"/>
+      <c r="AC23" s="16" t="inlineStr">
+        <is>
+          <t>最大長</t>
+        </is>
+      </c>
+      <c r="AD23" s="10" t="n"/>
+      <c r="AE23" s="11" t="n"/>
+      <c r="AF23" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG23" s="10" t="n"/>
+      <c r="AH23" s="10" t="n"/>
+      <c r="AI23" s="10" t="n"/>
+      <c r="AJ23" s="10" t="n"/>
+      <c r="AK23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>dokusya_id</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="n"/>
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="11" t="n"/>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="11" t="n"/>
+      <c r="T24" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="10" t="n"/>
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="11" t="n"/>
+      <c r="Y24" s="17" t="inlineStr"/>
+      <c r="Z24" s="10" t="n"/>
+      <c r="AA24" s="10" t="n"/>
+      <c r="AB24" s="11" t="n"/>
+      <c r="AC24" s="17" t="inlineStr"/>
+      <c r="AD24" s="10" t="n"/>
+      <c r="AE24" s="11" t="n"/>
+      <c r="AF24" s="19" t="inlineStr">
+        <is>
+          <t>対象の dokusya_id（パスパラメータ）</t>
+        </is>
+      </c>
+      <c r="AG24" s="10" t="n"/>
+      <c r="AH24" s="10" t="n"/>
+      <c r="AI24" s="10" t="n"/>
+      <c r="AJ24" s="10" t="n"/>
+      <c r="AK24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>joho</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="n"/>
+      <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="n"/>
+      <c r="S25" s="11" t="n"/>
+      <c r="T25" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="U25" s="10" t="n"/>
+      <c r="V25" s="10" t="n"/>
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="11" t="n"/>
+      <c r="Y25" s="17" t="inlineStr"/>
+      <c r="Z25" s="10" t="n"/>
+      <c r="AA25" s="10" t="n"/>
+      <c r="AB25" s="11" t="n"/>
+      <c r="AC25" s="17" t="inlineStr"/>
+      <c r="AD25" s="10" t="n"/>
+      <c r="AE25" s="11" t="n"/>
+      <c r="AF25" s="19" t="inlineStr">
+        <is>
+          <t>情報変更適用日（クエリパラメータ・YYYY-MM-DD）</t>
+        </is>
+      </c>
+      <c r="AG25" s="10" t="n"/>
+      <c r="AH25" s="10" t="n"/>
+      <c r="AI25" s="10" t="n"/>
+      <c r="AJ25" s="10" t="n"/>
+      <c r="AK25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="19.5" customHeight="1"/>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19.5" customHeight="1"/>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="10" t="n"/>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="n"/>
+      <c r="P29" s="11" t="n"/>
+      <c r="Q29" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="11" t="n"/>
+      <c r="T29" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="10" t="n"/>
+      <c r="W29" s="10" t="n"/>
+      <c r="X29" s="11" t="n"/>
+      <c r="Y29" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="Z29" s="10" t="n"/>
+      <c r="AA29" s="10" t="n"/>
+      <c r="AB29" s="10" t="n"/>
+      <c r="AC29" s="10" t="n"/>
+      <c r="AD29" s="10" t="n"/>
+      <c r="AE29" s="11" t="n"/>
+      <c r="AF29" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG29" s="10" t="n"/>
+      <c r="AH29" s="10" t="n"/>
+      <c r="AI29" s="10" t="n"/>
+      <c r="AJ29" s="10" t="n"/>
+      <c r="AK29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="19.5" customHeight="1"/>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="B31" s="40" t="inlineStr">
+        <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/dokusya/100/effective-at?joho=2026-08-23</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="10" t="n"/>
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="n"/>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="10" t="n"/>
+      <c r="Y32" s="10" t="n"/>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="10" t="n"/>
+      <c r="AC32" s="10" t="n"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="10" t="n"/>
+      <c r="AF32" s="10" t="n"/>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="11" t="n"/>
+    </row>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="B34" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 400 Bad Request（適用日の形式不正））</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "VALIDATION_ERROR",
+  "message": "入力値が不正です",
+  "errors": [{ "field": "joho", "message": "情報変更適用日の形式が不正です。" }]
+}</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="10" t="n"/>
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="10" t="n"/>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="10" t="n"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="10" t="n"/>
+      <c r="Y35" s="10" t="n"/>
+      <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n"/>
+      <c r="AB35" s="10" t="n"/>
+      <c r="AC35" s="10" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="10" t="n"/>
+      <c r="AF35" s="10" t="n"/>
+      <c r="AG35" s="10" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="10" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="11" t="n"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="B37" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 400 Bad Request（適用日の範囲不正））</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "VALIDATION_ERROR",
+  "message": "入力値が不正です",
+  "errors": [{ "field": "joho_henko_tekiyo_date", "message": "情報変更適用日は購読開始日（2026-04-01）以降の日付を指定してください。" }]
+}</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="10" t="n"/>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="n"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="10" t="n"/>
+      <c r="Y38" s="10" t="n"/>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="10" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="10" t="n"/>
+      <c r="AF38" s="10" t="n"/>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="11" t="n"/>
+    </row>
+    <row r="40" ht="19.5" customHeight="1">
+      <c r="B40" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 400 Bad Request（同一適用日に既存の変更あり・v1.18））</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "VALIDATION_ERROR",
+  "message": "入力値が不正です",
+  "errors": [{ "field": "joho_henko_tekiyo_date", "message": "この適用日には既に変更履歴が登録されています。購読者履歴情報画面から該当の変更を取消してから、まとめて更新してください。" }]
+}</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="10" t="n"/>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="10" t="n"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="10" t="n"/>
+      <c r="W41" s="10" t="n"/>
+      <c r="X41" s="10" t="n"/>
+      <c r="Y41" s="10" t="n"/>
+      <c r="Z41" s="10" t="n"/>
+      <c r="AA41" s="10" t="n"/>
+      <c r="AB41" s="10" t="n"/>
+      <c r="AC41" s="10" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="10" t="n"/>
+      <c r="AF41" s="10" t="n"/>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="10" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41" s="10" t="n"/>
+      <c r="AK41" s="11" t="n"/>
+    </row>
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="B43" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 401 Unauthorized）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="72" customHeight="1">
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "UNAUTHORIZED",
+  "message": "セッションが切れました。再度ログインしてください。"
+}</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="10" t="n"/>
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="n"/>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="n"/>
+      <c r="U44" s="10" t="n"/>
+      <c r="V44" s="10" t="n"/>
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="10" t="n"/>
+      <c r="Y44" s="10" t="n"/>
+      <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="10" t="n"/>
+      <c r="AB44" s="10" t="n"/>
+      <c r="AC44" s="10" t="n"/>
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="10" t="n"/>
+      <c r="AF44" s="10" t="n"/>
+      <c r="AG44" s="10" t="n"/>
+      <c r="AH44" s="10" t="n"/>
+      <c r="AI44" s="10" t="n"/>
+      <c r="AJ44" s="10" t="n"/>
+      <c r="AK44" s="11" t="n"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="B46" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 403 Forbidden）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="72" customHeight="1">
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません。"
+}</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n"/>
+      <c r="J47" s="10" t="n"/>
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="10" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="10" t="n"/>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n"/>
+      <c r="U47" s="10" t="n"/>
+      <c r="V47" s="10" t="n"/>
+      <c r="W47" s="10" t="n"/>
+      <c r="X47" s="10" t="n"/>
+      <c r="Y47" s="10" t="n"/>
+      <c r="Z47" s="10" t="n"/>
+      <c r="AA47" s="10" t="n"/>
+      <c r="AB47" s="10" t="n"/>
+      <c r="AC47" s="10" t="n"/>
+      <c r="AD47" s="10" t="n"/>
+      <c r="AE47" s="10" t="n"/>
+      <c r="AF47" s="10" t="n"/>
+      <c r="AG47" s="10" t="n"/>
+      <c r="AH47" s="10" t="n"/>
+      <c r="AI47" s="10" t="n"/>
+      <c r="AJ47" s="10" t="n"/>
+      <c r="AK47" s="11" t="n"/>
+    </row>
+    <row r="49" ht="19.5" customHeight="1">
+      <c r="B49" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 404 Not Found）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="72" customHeight="1">
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "NOT_FOUND",
+  "message": "指定された購読者が見つかりません。"
+}</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="10" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="10" t="n"/>
+      <c r="Y50" s="10" t="n"/>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="10" t="n"/>
+      <c r="AC50" s="10" t="n"/>
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="10" t="n"/>
+      <c r="AF50" s="10" t="n"/>
+      <c r="AG50" s="10" t="n"/>
+      <c r="AH50" s="10" t="n"/>
+      <c r="AI50" s="10" t="n"/>
+      <c r="AJ50" s="10" t="n"/>
+      <c r="AK50" s="11" t="n"/>
+    </row>
+    <row r="52" ht="19.5" customHeight="1">
+      <c r="B52" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="72" customHeight="1">
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください。"
+}</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="10" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="10" t="n"/>
+      <c r="Q53" s="10" t="n"/>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="10" t="n"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="10" t="n"/>
+      <c r="Y53" s="10" t="n"/>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+      <c r="AC53" s="10" t="n"/>
+      <c r="AD53" s="10" t="n"/>
+      <c r="AE53" s="10" t="n"/>
+      <c r="AF53" s="10" t="n"/>
+      <c r="AG53" s="10" t="n"/>
+      <c r="AH53" s="10" t="n"/>
+      <c r="AI53" s="10" t="n"/>
+      <c r="AJ53" s="10" t="n"/>
+      <c r="AK53" s="11" t="n"/>
+    </row>
+    <row r="55" ht="19.5" customHeight="1"/>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="C58" s="41" t="inlineStr">
+        <is>
+          <t>パスパラメータ：dokusya_id 数値型チェック、必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="54" customHeight="1">
+      <c r="C59" s="41" t="inlineStr">
+        <is>
+          <t>クエリパラメータ：joho 必須、`YYYY-MM-DD` 形式チェック。不正な場合は `VALIDATION_ERROR`（field=`joho`、メッセージ「情報変更適用日の形式が不正です。」）で HTTP 400。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="C61" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="C62" s="41" t="inlineStr">
+        <is>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="C63" s="41" t="inlineStr">
+        <is>
+          <t>必要権限: `dokusya.view`</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1">
+      <c r="C64" s="41" t="inlineStr">
+        <is>
+          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="C65" s="41" t="inlineStr">
+        <is>
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="54" customHeight="1">
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>DataScope: ACSMS-API-011-001 と同一（CHUOKAI/JA_HONTEN は ja_id、JA_KANRI_SHITEN は kanri_shiten_id も判定）。違反の場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="B67" s="27" t="inlineStr">
+        <is>
+          <t>4.3 適用日の範囲整合性チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="C68" s="41" t="inlineStr">
+        <is>
+          <t>対象購読者を取得（DataScope込み）。レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="C69" s="41" t="inlineStr">
+        <is>
+          <t>指定 joho 時点で有効な解約予定日を履歴から算出し、購読開始日（`dokusya_kaishi_date`）・解約予定日との整合性を検証する：</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="54" customHeight="1">
+      <c r="D70" s="41" t="inlineStr">
+        <is>
+          <t>`joho &gt;= 購読開始日`：満たさない場合 `VALIDATION_ERROR`（field=`joho_henko_tekiyo_date`、メッセージ「情報変更適用日は購読開始日（YYYY-MM-DD）以降の日付を指定してください。」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="54" customHeight="1">
+      <c r="D71" s="41" t="inlineStr">
+        <is>
+          <t>`joho &lt; 解約予定日`（同日不可）：満たさない場合 `VALIDATION_ERROR`（field=`joho_henko_tekiyo_date`、メッセージ「情報変更適用日は解約予定日（YYYY-MM-DD）より前の日付を指定してください。」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="36" customHeight="1">
+      <c r="D72" s="41" t="inlineStr">
+        <is>
+          <t>解約→再購読済み（現在の購読開始日が、履歴上見つかった解約予定日より後）の場合は、その解約予定日は現行の購読サイクルと無関係のため判定から除外する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>4.4 基準行の取得・マッピング</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="36" customHeight="1">
+      <c r="C74" s="41" t="inlineStr">
+        <is>
+          <t>`joho` 時点で有効な履歴行（`joho_henko_tekiyo_date &lt;= joho` の中で `(joho, rireki_no)` 最大・取消行除外）を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="36" customHeight="1">
+      <c r="C75" s="41" t="inlineStr">
+        <is>
+          <t>該当行がなければ、購読者の現行詳細（ACSMS-API-011-001 と同じ取得処理）をそのまま返す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="C76" s="41" t="inlineStr">
+        <is>
+          <t>該当行があれば、その業務値を購読者の識別子（`ja_id` 等）へ重ね合わせ、販売店名・単価名・引落口座支店情報を結合したうえで詳細レスポンス形にマッピングして返す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>4.5 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="C78" s="41" t="inlineStr">
+        <is>
+          <t>data オブジェクトを含むJSONを返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="27" t="inlineStr">
+        <is>
+          <t>4.6 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="112">
+    <mergeCell ref="J11:AK11"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="C66:AK66"/>
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="C53:AK53"/>
+    <mergeCell ref="D71:AK71"/>
+    <mergeCell ref="N18:AK18"/>
+    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="C68:AK68"/>
+    <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="C58:AK58"/>
+    <mergeCell ref="N17:AK17"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="B73:AK73"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="N19:AK19"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="C44:AK44"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C75:AK75"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C80:AK80"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="C38:AK38"/>
+    <mergeCell ref="A21:AK21"/>
+    <mergeCell ref="D72:AK72"/>
+    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="B77:AK77"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="B67:AK67"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="C74:AK74"/>
+    <mergeCell ref="C35:AK35"/>
+    <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="AD2:AG3"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="J13:AK13"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="Y29:AE29"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C59:AK59"/>
+    <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="C32:AK32"/>
+    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="J7:AK7"/>
+    <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="B60:AK60"/>
+    <mergeCell ref="C62:AK62"/>
+    <mergeCell ref="B57:AK57"/>
+    <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="C64:AK64"/>
+    <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="C63:AK63"/>
+    <mergeCell ref="C41:AK41"/>
+    <mergeCell ref="C50:AK50"/>
+    <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="T23:X23"/>
+    <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="V2:Y3"/>
+    <mergeCell ref="N16:AK16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="A56:AK56"/>
+    <mergeCell ref="A27:AK27"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B14:I19"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="C69:AK69"/>
+    <mergeCell ref="Y23:AB23"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="C47:AK47"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="C76:AK76"/>
+    <mergeCell ref="D70:AK70"/>
+    <mergeCell ref="AF29:AK29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG18"/>
+  <dimension ref="A1:AG22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -7302,8 +9077,212 @@
       <c r="AF18" s="10" t="n"/>
       <c r="AG18" s="11" t="n"/>
     </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="11" t="n"/>
+      <c r="R19" s="19" t="inlineStr">
+        <is>
+          <t>コードとの整合確認（スポットチェック）：①更新(API-011-003)の §4.3 メール重複チェックが v1.15（#56568・JA横断化）反映前の自JA限定SQLのまま残っていたのを是正 — `assertEmailUnique`（dokusya.service.ts）は `dokusya_shubetsu IN (2,3)` かつ JAを跨いで全件を対象にすることを明記。②予約変更ポップアップが呼び出す `GET /api/v1/dokusya/{dokusya_id}/effective-at?joho=`（DokusyaController.getEffectiveAt）が本書に未記載だったため ACSMS-API-011-007 として追加。</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="11" t="n"/>
+      <c r="W19" s="17" t="inlineStr"/>
+      <c r="X19" s="10" t="n"/>
+      <c r="Y19" s="10" t="n"/>
+      <c r="Z19" s="10" t="n"/>
+      <c r="AA19" s="11" t="n"/>
+      <c r="AB19" s="17" t="inlineStr"/>
+      <c r="AC19" s="10" t="n"/>
+      <c r="AD19" s="10" t="n"/>
+      <c r="AE19" s="10" t="n"/>
+      <c r="AF19" s="10" t="n"/>
+      <c r="AG19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="n"/>
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="10" t="n"/>
+      <c r="O20" s="10" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="11" t="n"/>
+      <c r="R20" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-08：住所変更と販売店の移動が同一適用日に別々の更新として積み重なると増減連絡票（ACSMS-SCR-028）の同日集計が意図しない出力になるため、**紙版の予約変更（未来日）は同一適用日への変更を1回までに制限**。既存レコードに同一適用日の変更（非取消・非新規）がある場合、更新(API-011-003 §4.3.1)・予約変更ポップアップ確定(API-011-007)の双方で `VALIDATION_ERROR`(field=`joho_henko_tekiyo_date`) を返す。同日に複数項目をまとめて変更したいときは、ACSMS-SCR-013 で該当履歴を取消してから1回でまとめて更新する。当日変更は対象外（当日行は取消不可のため）。電子版は対象外（予約変更自体が不可）。Excel取込(SCR-016)・販売店一括置換(SCR-015)にも同一制限を適用（3経路共通の `dokusya-shubetsu.rules.ts` に集約）。</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n"/>
+      <c r="U20" s="10" t="n"/>
+      <c r="V20" s="11" t="n"/>
+      <c r="W20" s="17" t="inlineStr"/>
+      <c r="X20" s="10" t="n"/>
+      <c r="Y20" s="10" t="n"/>
+      <c r="Z20" s="10" t="n"/>
+      <c r="AA20" s="11" t="n"/>
+      <c r="AB20" s="17" t="inlineStr"/>
+      <c r="AC20" s="10" t="n"/>
+      <c r="AD20" s="10" t="n"/>
+      <c r="AE20" s="10" t="n"/>
+      <c r="AF20" s="10" t="n"/>
+      <c r="AG20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="n"/>
+      <c r="M21" s="10" t="n"/>
+      <c r="N21" s="10" t="n"/>
+      <c r="O21" s="10" t="n"/>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="11" t="n"/>
+      <c r="R21" s="19" t="inlineStr">
+        <is>
+          <t>不具合修正 2026-08：電子版（dokusya_shubetsu=2）は配達先情報エリアが画面上非活性化される（v1.16 参照）が、種別ラジオを紙版/併読→電子版へ切替えた直後に送信すると隠れた入力欄の値がそのまま届き、BE 側にゲートが無かったため配達先情報12項目（`haitatsu_same_flg` + 住所5＋連絡先2＋氏名4）を保存できてしまっていた。新規登録(API-011-002 §4.1)・更新(API-011-003 §4.1) の両方で、電子版の場合は配達先情報12項目をリクエスト値に関わらずサーバ側で強制的に空欄化（`haitatsu_same_flg=true`・残り11列=空文字）するよう修正（BE: `buildHaitatsuPayload`、購読者層分類の従属4項目 `buildBunruiPayload` と同じ方式）。あわせて FE（DokusyaFormView.vue）も新規作成モードで種別を電子版へ切替えた時点で配達先情報を画面上もクリアするよう修正（UX目的のみ・電子版は種別変更不可のため編集モードは対象外）。</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="10" t="n"/>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="11" t="n"/>
+      <c r="W21" s="17" t="inlineStr"/>
+      <c r="X21" s="10" t="n"/>
+      <c r="Y21" s="10" t="n"/>
+      <c r="Z21" s="10" t="n"/>
+      <c r="AA21" s="11" t="n"/>
+      <c r="AB21" s="17" t="inlineStr"/>
+      <c r="AC21" s="10" t="n"/>
+      <c r="AD21" s="10" t="n"/>
+      <c r="AE21" s="10" t="n"/>
+      <c r="AF21" s="10" t="n"/>
+      <c r="AG21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="n"/>
+      <c r="M22" s="10" t="n"/>
+      <c r="N22" s="10" t="n"/>
+      <c r="O22" s="10" t="n"/>
+      <c r="P22" s="10" t="n"/>
+      <c r="Q22" s="11" t="n"/>
+      <c r="R22" s="19" t="inlineStr">
+        <is>
+          <t>不具合修正 2026-08：廃店(`m_hanbaiten.haiten_flg=true`)の販売店・失効(`m_tanka.active_flg=false`)の単価を新規登録(API-011-002)・更新(API-011-003)で選択・変更できてしまう不具合を修正（Excel取込 ACSMS-SCR-016 §4.3.1/4.3.2 で先に修正済みの同一ルールをUIにも適用）。新規登録は常に検証(§4.1)、更新は `hanbaiten_id`/`tanka_id` を実際に変更する場合のみ検証し、既存値のまま（既に廃店/失効へ紐づく既存購読者の他項目編集）は据え置く(§4.3.2新設) — 全項目を毎回送信するUIの性質上、変更なしまで拒否すると当該購読者が永久に編集不能になるため。修正前は取込と同様、購読者詳細画面にも廃店・失効の旨を示す表示が無いため運用が事後に気付けなかった。</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="n"/>
+      <c r="T22" s="10" t="n"/>
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="11" t="n"/>
+      <c r="W22" s="17" t="inlineStr"/>
+      <c r="X22" s="10" t="n"/>
+      <c r="Y22" s="10" t="n"/>
+      <c r="Z22" s="10" t="n"/>
+      <c r="AA22" s="11" t="n"/>
+      <c r="AB22" s="17" t="inlineStr"/>
+      <c r="AC22" s="10" t="n"/>
+      <c r="AD22" s="10" t="n"/>
+      <c r="AE22" s="10" t="n"/>
+      <c r="AF22" s="10" t="n"/>
+      <c r="AG22" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="126">
+  <mergeCells count="154">
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="A15:B15"/>
@@ -7318,46 +9297,65 @@
     <mergeCell ref="R7:V7"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="R16:V16"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
     <mergeCell ref="AB17:AG17"/>
     <mergeCell ref="H3:J3"/>
+    <mergeCell ref="C21:G21"/>
     <mergeCell ref="AB10:AG10"/>
     <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="R20:V20"/>
+    <mergeCell ref="AB19:AG19"/>
     <mergeCell ref="W16:AA16"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K21:Q21"/>
     <mergeCell ref="AB3:AG3"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="R22:V22"/>
     <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="W18:AA18"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="AB5:AG5"/>
+    <mergeCell ref="AB20:AG20"/>
     <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="AB14:AG14"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="R14:V14"/>
     <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H21:J21"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="K17:Q17"/>
     <mergeCell ref="R4:V4"/>
+    <mergeCell ref="AB21:AG21"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="K10:Q10"/>
     <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K19:Q19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="W20:AA20"/>
     <mergeCell ref="K3:Q3"/>
     <mergeCell ref="K16:Q16"/>
     <mergeCell ref="AB13:AG13"/>
     <mergeCell ref="AB8:AG8"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="W22:AA22"/>
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="W12:AA12"/>
+    <mergeCell ref="W21:AA21"/>
     <mergeCell ref="AB18:AG18"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="K11:Q11"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="R17:V17"/>
+    <mergeCell ref="H20:J20"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="K8:Q8"/>
@@ -7366,6 +9364,7 @@
     <mergeCell ref="W4:AA4"/>
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="W10:AA10"/>
+    <mergeCell ref="AB22:AG22"/>
     <mergeCell ref="R11:V11"/>
     <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
@@ -7383,16 +9382,20 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="H15:J15"/>
+    <mergeCell ref="R21:V21"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="K20:Q20"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="W9:AA9"/>
     <mergeCell ref="H10:J10"/>
+    <mergeCell ref="K22:Q22"/>
     <mergeCell ref="W14:AA14"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="H9:J9"/>
@@ -7406,6 +9409,7 @@
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB9:AG9"/>
     <mergeCell ref="W15:AA15"/>
+    <mergeCell ref="R19:V19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="K13:Q13"/>
@@ -7423,10 +9427,13 @@
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="AB6:AG6"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="AB15:AG15"/>
     <mergeCell ref="W17:AA17"/>
     <mergeCell ref="W11:AA11"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="W19:AA19"/>
     <mergeCell ref="R18:V18"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
@@ -7602,7 +9609,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8073,7 +10080,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8841,7 +10848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -9002,7 +11009,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -9458,13 +11465,72 @@
       <c r="AJ11" s="10" t="n"/>
       <c r="AK11" s="11" t="n"/>
     </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>ACSMS-API-011-007</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>Get Dokusya Effective At</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="11" t="n"/>
+      <c r="S12" s="19" t="inlineStr">
+        <is>
+          <t>指定した情報変更適用日（joho）時点で有効な履歴行を、購読者詳細と同一形式で取得する（予約変更ポップアップの基準行取得用）</t>
+        </is>
+      </c>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n"/>
+      <c r="V12" s="10" t="n"/>
+      <c r="W12" s="10" t="n"/>
+      <c r="X12" s="10" t="n"/>
+      <c r="Y12" s="10" t="n"/>
+      <c r="Z12" s="10" t="n"/>
+      <c r="AA12" s="10" t="n"/>
+      <c r="AB12" s="10" t="n"/>
+      <c r="AC12" s="11" t="n"/>
+      <c r="AD12" s="19" t="inlineStr">
+        <is>
+          <t>/api/v1/dokusya/{dokusya_id}/effective-at</t>
+        </is>
+      </c>
+      <c r="AE12" s="10" t="n"/>
+      <c r="AF12" s="10" t="n"/>
+      <c r="AG12" s="10" t="n"/>
+      <c r="AH12" s="10" t="n"/>
+      <c r="AI12" s="10" t="n"/>
+      <c r="AJ12" s="10" t="n"/>
+      <c r="AK12" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="54">
     <mergeCell ref="AD9:AK9"/>
     <mergeCell ref="J6:R6"/>
+    <mergeCell ref="AD12:AK12"/>
     <mergeCell ref="AD8:AK8"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="S12:AC12"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="AD5:AK5"/>
     <mergeCell ref="Z1:AC1"/>
@@ -9482,8 +11548,10 @@
     <mergeCell ref="AD6:AK6"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="C5:I5"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="J12:R12"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="S10:AC10"/>
@@ -9505,6 +11573,7 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="S5:AC5"/>
+    <mergeCell ref="C12:I12"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="J9:R9"/>
@@ -9517,6 +11586,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9528,7 +11598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK143"/>
+  <dimension ref="A1:AK147"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -9689,7 +11759,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -14362,14 +16432,14 @@
       <c r="AJ93" s="10" t="n"/>
       <c r="AK93" s="11" t="n"/>
     </row>
-    <row r="94" ht="18" customHeight="1">
+    <row r="94" ht="36" customHeight="1">
       <c r="B94" s="31" t="n">
         <v>67</v>
       </c>
       <c r="C94" s="38" t="n"/>
       <c r="D94" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>denshi_kaiin_id</t>
         </is>
       </c>
       <c r="E94" s="10" t="n"/>
@@ -14382,7 +16452,7 @@
       <c r="L94" s="11" t="n"/>
       <c r="M94" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N94" s="10" t="n"/>
@@ -14395,18 +16465,14 @@
       </c>
       <c r="R94" s="10" t="n"/>
       <c r="S94" s="11" t="n"/>
-      <c r="T94" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T94" s="17" t="inlineStr"/>
       <c r="U94" s="10" t="n"/>
       <c r="V94" s="10" t="n"/>
       <c r="W94" s="10" t="n"/>
       <c r="X94" s="11" t="n"/>
       <c r="Y94" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z94" s="10" t="n"/>
@@ -14417,7 +16483,7 @@
       <c r="AE94" s="11" t="n"/>
       <c r="AF94" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>電子版会員ID（外部の電子版読者管理システムの会員ID。外部連携機能が設定する読取専用値）</t>
         </is>
       </c>
       <c r="AG94" s="10" t="n"/>
@@ -14426,14 +16492,14 @@
       <c r="AJ94" s="10" t="n"/>
       <c r="AK94" s="11" t="n"/>
     </row>
-    <row r="95" ht="18" customHeight="1">
+    <row r="95" ht="54" customHeight="1">
       <c r="B95" s="31" t="n">
         <v>68</v>
       </c>
-      <c r="C95" s="39" t="n"/>
+      <c r="C95" s="38" t="n"/>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>honshi_kodoku_flg</t>
         </is>
       </c>
       <c r="E95" s="10" t="n"/>
@@ -14446,7 +16512,7 @@
       <c r="L95" s="11" t="n"/>
       <c r="M95" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N95" s="10" t="n"/>
@@ -14459,11 +16525,7 @@
       </c>
       <c r="R95" s="10" t="n"/>
       <c r="S95" s="11" t="n"/>
-      <c r="T95" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T95" s="17" t="inlineStr"/>
       <c r="U95" s="10" t="n"/>
       <c r="V95" s="10" t="n"/>
       <c r="W95" s="10" t="n"/>
@@ -14481,7 +16543,7 @@
       <c r="AE95" s="11" t="n"/>
       <c r="AF95" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>本紙購読フラグ（電子版読者管理システム users.subscribe_flg 連携。購読種別=電子版のとき画面の「紙版購読状況　有り」表示に使用）</t>
         </is>
       </c>
       <c r="AG95" s="10" t="n"/>
@@ -14490,21 +16552,144 @@
       <c r="AJ95" s="10" t="n"/>
       <c r="AK95" s="11" t="n"/>
     </row>
-    <row r="96" ht="19.5" customHeight="1"/>
-    <row r="97" ht="19.5" customHeight="1">
-      <c r="B97" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/dokusya/1</t>
-        </is>
-      </c>
-      <c r="D98" s="10" t="n"/>
+    <row r="96" ht="18" customHeight="1">
+      <c r="B96" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="C96" s="38" t="n"/>
+      <c r="D96" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="10" t="n"/>
+      <c r="I96" s="10" t="n"/>
+      <c r="J96" s="10" t="n"/>
+      <c r="K96" s="10" t="n"/>
+      <c r="L96" s="11" t="n"/>
+      <c r="M96" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N96" s="10" t="n"/>
+      <c r="O96" s="10" t="n"/>
+      <c r="P96" s="11" t="n"/>
+      <c r="Q96" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R96" s="10" t="n"/>
+      <c r="S96" s="11" t="n"/>
+      <c r="T96" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U96" s="10" t="n"/>
+      <c r="V96" s="10" t="n"/>
+      <c r="W96" s="10" t="n"/>
+      <c r="X96" s="11" t="n"/>
+      <c r="Y96" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z96" s="10" t="n"/>
+      <c r="AA96" s="10" t="n"/>
+      <c r="AB96" s="10" t="n"/>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="19" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="10" t="n"/>
+      <c r="AK96" s="11" t="n"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="B97" s="31" t="n">
+        <v>70</v>
+      </c>
+      <c r="C97" s="38" t="n"/>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="n"/>
+      <c r="F97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="10" t="n"/>
+      <c r="J97" s="10" t="n"/>
+      <c r="K97" s="10" t="n"/>
+      <c r="L97" s="11" t="n"/>
+      <c r="M97" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N97" s="10" t="n"/>
+      <c r="O97" s="10" t="n"/>
+      <c r="P97" s="11" t="n"/>
+      <c r="Q97" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R97" s="10" t="n"/>
+      <c r="S97" s="11" t="n"/>
+      <c r="T97" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U97" s="10" t="n"/>
+      <c r="V97" s="10" t="n"/>
+      <c r="W97" s="10" t="n"/>
+      <c r="X97" s="11" t="n"/>
+      <c r="Y97" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z97" s="10" t="n"/>
+      <c r="AA97" s="10" t="n"/>
+      <c r="AB97" s="10" t="n"/>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="10" t="n"/>
+      <c r="AK97" s="11" t="n"/>
+    </row>
+    <row r="98" ht="72" customHeight="1">
+      <c r="B98" s="31" t="n">
+        <v>71</v>
+      </c>
+      <c r="C98" s="38" t="n"/>
+      <c r="D98" s="19" t="inlineStr">
+        <is>
+          <t>has_active_kaiyaku</t>
+        </is>
+      </c>
       <c r="E98" s="10" t="n"/>
       <c r="F98" s="10" t="n"/>
       <c r="G98" s="10" t="n"/>
@@ -14512,42 +16697,171 @@
       <c r="I98" s="10" t="n"/>
       <c r="J98" s="10" t="n"/>
       <c r="K98" s="10" t="n"/>
-      <c r="L98" s="10" t="n"/>
-      <c r="M98" s="10" t="n"/>
+      <c r="L98" s="11" t="n"/>
+      <c r="M98" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
       <c r="N98" s="10" t="n"/>
       <c r="O98" s="10" t="n"/>
-      <c r="P98" s="10" t="n"/>
-      <c r="Q98" s="10" t="n"/>
+      <c r="P98" s="11" t="n"/>
+      <c r="Q98" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R98" s="10" t="n"/>
-      <c r="S98" s="10" t="n"/>
-      <c r="T98" s="10" t="n"/>
+      <c r="S98" s="11" t="n"/>
+      <c r="T98" s="17" t="inlineStr"/>
       <c r="U98" s="10" t="n"/>
       <c r="V98" s="10" t="n"/>
       <c r="W98" s="10" t="n"/>
-      <c r="X98" s="10" t="n"/>
-      <c r="Y98" s="10" t="n"/>
+      <c r="X98" s="11" t="n"/>
+      <c r="Y98" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z98" s="10" t="n"/>
       <c r="AA98" s="10" t="n"/>
       <c r="AB98" s="10" t="n"/>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
-      <c r="AE98" s="10" t="n"/>
-      <c r="AF98" s="10" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="19" t="inlineStr">
+        <is>
+          <t>有効な解約予約（kaiyaku_flg=true・取消除外）が存在するか（顧客要件2026-07。履歴から算出、trueの間は追加の解約予約を禁止し編集画面の購読中止日をdisabled）</t>
+        </is>
+      </c>
       <c r="AG98" s="10" t="n"/>
       <c r="AH98" s="10" t="n"/>
       <c r="AI98" s="10" t="n"/>
       <c r="AJ98" s="10" t="n"/>
       <c r="AK98" s="11" t="n"/>
     </row>
-    <row r="100" ht="19.5" customHeight="1">
-      <c r="B100" s="40" t="inlineStr">
+    <row r="99" ht="54" customHeight="1">
+      <c r="B99" s="31" t="n">
+        <v>72</v>
+      </c>
+      <c r="C99" s="39" t="n"/>
+      <c r="D99" s="19" t="inlineStr">
+        <is>
+          <t>max_joho_date</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="10" t="n"/>
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="10" t="n"/>
+      <c r="I99" s="10" t="n"/>
+      <c r="J99" s="10" t="n"/>
+      <c r="K99" s="10" t="n"/>
+      <c r="L99" s="11" t="n"/>
+      <c r="M99" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N99" s="10" t="n"/>
+      <c r="O99" s="10" t="n"/>
+      <c r="P99" s="11" t="n"/>
+      <c r="Q99" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R99" s="10" t="n"/>
+      <c r="S99" s="11" t="n"/>
+      <c r="T99" s="17" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="U99" s="10" t="n"/>
+      <c r="V99" s="10" t="n"/>
+      <c r="W99" s="10" t="n"/>
+      <c r="X99" s="11" t="n"/>
+      <c r="Y99" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z99" s="10" t="n"/>
+      <c r="AA99" s="10" t="n"/>
+      <c r="AB99" s="10" t="n"/>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="19" t="inlineStr">
+        <is>
+          <t>履歴の最終変更適用日（MAX joho・取消除外）。解約予定日はこの日以降のみ指定可（編集画面の disabled-date 基準）。履歴なしは null</t>
+        </is>
+      </c>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="10" t="n"/>
+      <c r="AK99" s="11" t="n"/>
+    </row>
+    <row r="100" ht="19.5" customHeight="1"/>
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="B101" s="40" t="inlineStr">
+        <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="C102" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/dokusya/1</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="10" t="n"/>
+      <c r="J102" s="10" t="n"/>
+      <c r="K102" s="10" t="n"/>
+      <c r="L102" s="10" t="n"/>
+      <c r="M102" s="10" t="n"/>
+      <c r="N102" s="10" t="n"/>
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
+      <c r="V102" s="10" t="n"/>
+      <c r="W102" s="10" t="n"/>
+      <c r="X102" s="10" t="n"/>
+      <c r="Y102" s="10" t="n"/>
+      <c r="Z102" s="10" t="n"/>
+      <c r="AA102" s="10" t="n"/>
+      <c r="AB102" s="10" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="10" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="10" t="n"/>
+      <c r="AK102" s="11" t="n"/>
+    </row>
+    <row r="104" ht="19.5" customHeight="1">
+      <c r="B104" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="409" customHeight="1">
-      <c r="C101" s="19" t="inlineStr">
+    <row r="105" ht="409" customHeight="1">
+      <c r="C105" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -14616,56 +16930,60 @@
     "biko": "",
     "rireki_no": 1,
     "denshi_shonin_status": null,
+    "denshi_kaiin_id": null,
+    "honshi_kodoku_flg": false,
     "created_at": "2026-04-01T10:00:00+09:00",
-    "updated_at": "2026-04-01T10:00:00+09:00"
+    "updated_at": "2026-04-01T10:00:00+09:00",
+    "has_active_kaiyaku": false,
+    "max_joho_date": null
   }
 }</t>
         </is>
       </c>
-      <c r="D101" s="10" t="n"/>
-      <c r="E101" s="10" t="n"/>
-      <c r="F101" s="10" t="n"/>
-      <c r="G101" s="10" t="n"/>
-      <c r="H101" s="10" t="n"/>
-      <c r="I101" s="10" t="n"/>
-      <c r="J101" s="10" t="n"/>
-      <c r="K101" s="10" t="n"/>
-      <c r="L101" s="10" t="n"/>
-      <c r="M101" s="10" t="n"/>
-      <c r="N101" s="10" t="n"/>
-      <c r="O101" s="10" t="n"/>
-      <c r="P101" s="10" t="n"/>
-      <c r="Q101" s="10" t="n"/>
-      <c r="R101" s="10" t="n"/>
-      <c r="S101" s="10" t="n"/>
-      <c r="T101" s="10" t="n"/>
-      <c r="U101" s="10" t="n"/>
-      <c r="V101" s="10" t="n"/>
-      <c r="W101" s="10" t="n"/>
-      <c r="X101" s="10" t="n"/>
-      <c r="Y101" s="10" t="n"/>
-      <c r="Z101" s="10" t="n"/>
-      <c r="AA101" s="10" t="n"/>
-      <c r="AB101" s="10" t="n"/>
-      <c r="AC101" s="10" t="n"/>
-      <c r="AD101" s="10" t="n"/>
-      <c r="AE101" s="10" t="n"/>
-      <c r="AF101" s="10" t="n"/>
-      <c r="AG101" s="10" t="n"/>
-      <c r="AH101" s="10" t="n"/>
-      <c r="AI101" s="10" t="n"/>
-      <c r="AJ101" s="10" t="n"/>
-      <c r="AK101" s="11" t="n"/>
-    </row>
-    <row r="103" ht="19.5" customHeight="1">
-      <c r="B103" s="40" t="inlineStr">
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="10" t="n"/>
+      <c r="F105" s="10" t="n"/>
+      <c r="G105" s="10" t="n"/>
+      <c r="H105" s="10" t="n"/>
+      <c r="I105" s="10" t="n"/>
+      <c r="J105" s="10" t="n"/>
+      <c r="K105" s="10" t="n"/>
+      <c r="L105" s="10" t="n"/>
+      <c r="M105" s="10" t="n"/>
+      <c r="N105" s="10" t="n"/>
+      <c r="O105" s="10" t="n"/>
+      <c r="P105" s="10" t="n"/>
+      <c r="Q105" s="10" t="n"/>
+      <c r="R105" s="10" t="n"/>
+      <c r="S105" s="10" t="n"/>
+      <c r="T105" s="10" t="n"/>
+      <c r="U105" s="10" t="n"/>
+      <c r="V105" s="10" t="n"/>
+      <c r="W105" s="10" t="n"/>
+      <c r="X105" s="10" t="n"/>
+      <c r="Y105" s="10" t="n"/>
+      <c r="Z105" s="10" t="n"/>
+      <c r="AA105" s="10" t="n"/>
+      <c r="AB105" s="10" t="n"/>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="10" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="10" t="n"/>
+      <c r="AK105" s="11" t="n"/>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
+      <c r="B107" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="72" customHeight="1">
-      <c r="C104" s="19" t="inlineStr">
+    <row r="108" ht="72" customHeight="1">
+      <c r="C108" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -14673,50 +16991,50 @@
 }</t>
         </is>
       </c>
-      <c r="D104" s="10" t="n"/>
-      <c r="E104" s="10" t="n"/>
-      <c r="F104" s="10" t="n"/>
-      <c r="G104" s="10" t="n"/>
-      <c r="H104" s="10" t="n"/>
-      <c r="I104" s="10" t="n"/>
-      <c r="J104" s="10" t="n"/>
-      <c r="K104" s="10" t="n"/>
-      <c r="L104" s="10" t="n"/>
-      <c r="M104" s="10" t="n"/>
-      <c r="N104" s="10" t="n"/>
-      <c r="O104" s="10" t="n"/>
-      <c r="P104" s="10" t="n"/>
-      <c r="Q104" s="10" t="n"/>
-      <c r="R104" s="10" t="n"/>
-      <c r="S104" s="10" t="n"/>
-      <c r="T104" s="10" t="n"/>
-      <c r="U104" s="10" t="n"/>
-      <c r="V104" s="10" t="n"/>
-      <c r="W104" s="10" t="n"/>
-      <c r="X104" s="10" t="n"/>
-      <c r="Y104" s="10" t="n"/>
-      <c r="Z104" s="10" t="n"/>
-      <c r="AA104" s="10" t="n"/>
-      <c r="AB104" s="10" t="n"/>
-      <c r="AC104" s="10" t="n"/>
-      <c r="AD104" s="10" t="n"/>
-      <c r="AE104" s="10" t="n"/>
-      <c r="AF104" s="10" t="n"/>
-      <c r="AG104" s="10" t="n"/>
-      <c r="AH104" s="10" t="n"/>
-      <c r="AI104" s="10" t="n"/>
-      <c r="AJ104" s="10" t="n"/>
-      <c r="AK104" s="11" t="n"/>
-    </row>
-    <row r="106" ht="19.5" customHeight="1">
-      <c r="B106" s="40" t="inlineStr">
+      <c r="D108" s="10" t="n"/>
+      <c r="E108" s="10" t="n"/>
+      <c r="F108" s="10" t="n"/>
+      <c r="G108" s="10" t="n"/>
+      <c r="H108" s="10" t="n"/>
+      <c r="I108" s="10" t="n"/>
+      <c r="J108" s="10" t="n"/>
+      <c r="K108" s="10" t="n"/>
+      <c r="L108" s="10" t="n"/>
+      <c r="M108" s="10" t="n"/>
+      <c r="N108" s="10" t="n"/>
+      <c r="O108" s="10" t="n"/>
+      <c r="P108" s="10" t="n"/>
+      <c r="Q108" s="10" t="n"/>
+      <c r="R108" s="10" t="n"/>
+      <c r="S108" s="10" t="n"/>
+      <c r="T108" s="10" t="n"/>
+      <c r="U108" s="10" t="n"/>
+      <c r="V108" s="10" t="n"/>
+      <c r="W108" s="10" t="n"/>
+      <c r="X108" s="10" t="n"/>
+      <c r="Y108" s="10" t="n"/>
+      <c r="Z108" s="10" t="n"/>
+      <c r="AA108" s="10" t="n"/>
+      <c r="AB108" s="10" t="n"/>
+      <c r="AC108" s="10" t="n"/>
+      <c r="AD108" s="10" t="n"/>
+      <c r="AE108" s="10" t="n"/>
+      <c r="AF108" s="10" t="n"/>
+      <c r="AG108" s="10" t="n"/>
+      <c r="AH108" s="10" t="n"/>
+      <c r="AI108" s="10" t="n"/>
+      <c r="AJ108" s="10" t="n"/>
+      <c r="AK108" s="11" t="n"/>
+    </row>
+    <row r="110" ht="19.5" customHeight="1">
+      <c r="B110" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="72" customHeight="1">
-      <c r="C107" s="19" t="inlineStr">
+    <row r="111" ht="72" customHeight="1">
+      <c r="C111" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -14724,50 +17042,50 @@
 }</t>
         </is>
       </c>
-      <c r="D107" s="10" t="n"/>
-      <c r="E107" s="10" t="n"/>
-      <c r="F107" s="10" t="n"/>
-      <c r="G107" s="10" t="n"/>
-      <c r="H107" s="10" t="n"/>
-      <c r="I107" s="10" t="n"/>
-      <c r="J107" s="10" t="n"/>
-      <c r="K107" s="10" t="n"/>
-      <c r="L107" s="10" t="n"/>
-      <c r="M107" s="10" t="n"/>
-      <c r="N107" s="10" t="n"/>
-      <c r="O107" s="10" t="n"/>
-      <c r="P107" s="10" t="n"/>
-      <c r="Q107" s="10" t="n"/>
-      <c r="R107" s="10" t="n"/>
-      <c r="S107" s="10" t="n"/>
-      <c r="T107" s="10" t="n"/>
-      <c r="U107" s="10" t="n"/>
-      <c r="V107" s="10" t="n"/>
-      <c r="W107" s="10" t="n"/>
-      <c r="X107" s="10" t="n"/>
-      <c r="Y107" s="10" t="n"/>
-      <c r="Z107" s="10" t="n"/>
-      <c r="AA107" s="10" t="n"/>
-      <c r="AB107" s="10" t="n"/>
-      <c r="AC107" s="10" t="n"/>
-      <c r="AD107" s="10" t="n"/>
-      <c r="AE107" s="10" t="n"/>
-      <c r="AF107" s="10" t="n"/>
-      <c r="AG107" s="10" t="n"/>
-      <c r="AH107" s="10" t="n"/>
-      <c r="AI107" s="10" t="n"/>
-      <c r="AJ107" s="10" t="n"/>
-      <c r="AK107" s="11" t="n"/>
-    </row>
-    <row r="109" ht="19.5" customHeight="1">
-      <c r="B109" s="40" t="inlineStr">
+      <c r="D111" s="10" t="n"/>
+      <c r="E111" s="10" t="n"/>
+      <c r="F111" s="10" t="n"/>
+      <c r="G111" s="10" t="n"/>
+      <c r="H111" s="10" t="n"/>
+      <c r="I111" s="10" t="n"/>
+      <c r="J111" s="10" t="n"/>
+      <c r="K111" s="10" t="n"/>
+      <c r="L111" s="10" t="n"/>
+      <c r="M111" s="10" t="n"/>
+      <c r="N111" s="10" t="n"/>
+      <c r="O111" s="10" t="n"/>
+      <c r="P111" s="10" t="n"/>
+      <c r="Q111" s="10" t="n"/>
+      <c r="R111" s="10" t="n"/>
+      <c r="S111" s="10" t="n"/>
+      <c r="T111" s="10" t="n"/>
+      <c r="U111" s="10" t="n"/>
+      <c r="V111" s="10" t="n"/>
+      <c r="W111" s="10" t="n"/>
+      <c r="X111" s="10" t="n"/>
+      <c r="Y111" s="10" t="n"/>
+      <c r="Z111" s="10" t="n"/>
+      <c r="AA111" s="10" t="n"/>
+      <c r="AB111" s="10" t="n"/>
+      <c r="AC111" s="10" t="n"/>
+      <c r="AD111" s="10" t="n"/>
+      <c r="AE111" s="10" t="n"/>
+      <c r="AF111" s="10" t="n"/>
+      <c r="AG111" s="10" t="n"/>
+      <c r="AH111" s="10" t="n"/>
+      <c r="AI111" s="10" t="n"/>
+      <c r="AJ111" s="10" t="n"/>
+      <c r="AK111" s="11" t="n"/>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
+      <c r="B113" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="72" customHeight="1">
-      <c r="C110" s="19" t="inlineStr">
+    <row r="114" ht="72" customHeight="1">
+      <c r="C114" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "NOT_FOUND",
@@ -14775,50 +17093,50 @@
 }</t>
         </is>
       </c>
-      <c r="D110" s="10" t="n"/>
-      <c r="E110" s="10" t="n"/>
-      <c r="F110" s="10" t="n"/>
-      <c r="G110" s="10" t="n"/>
-      <c r="H110" s="10" t="n"/>
-      <c r="I110" s="10" t="n"/>
-      <c r="J110" s="10" t="n"/>
-      <c r="K110" s="10" t="n"/>
-      <c r="L110" s="10" t="n"/>
-      <c r="M110" s="10" t="n"/>
-      <c r="N110" s="10" t="n"/>
-      <c r="O110" s="10" t="n"/>
-      <c r="P110" s="10" t="n"/>
-      <c r="Q110" s="10" t="n"/>
-      <c r="R110" s="10" t="n"/>
-      <c r="S110" s="10" t="n"/>
-      <c r="T110" s="10" t="n"/>
-      <c r="U110" s="10" t="n"/>
-      <c r="V110" s="10" t="n"/>
-      <c r="W110" s="10" t="n"/>
-      <c r="X110" s="10" t="n"/>
-      <c r="Y110" s="10" t="n"/>
-      <c r="Z110" s="10" t="n"/>
-      <c r="AA110" s="10" t="n"/>
-      <c r="AB110" s="10" t="n"/>
-      <c r="AC110" s="10" t="n"/>
-      <c r="AD110" s="10" t="n"/>
-      <c r="AE110" s="10" t="n"/>
-      <c r="AF110" s="10" t="n"/>
-      <c r="AG110" s="10" t="n"/>
-      <c r="AH110" s="10" t="n"/>
-      <c r="AI110" s="10" t="n"/>
-      <c r="AJ110" s="10" t="n"/>
-      <c r="AK110" s="11" t="n"/>
-    </row>
-    <row r="112" ht="19.5" customHeight="1">
-      <c r="B112" s="40" t="inlineStr">
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="10" t="n"/>
+      <c r="J114" s="10" t="n"/>
+      <c r="K114" s="10" t="n"/>
+      <c r="L114" s="10" t="n"/>
+      <c r="M114" s="10" t="n"/>
+      <c r="N114" s="10" t="n"/>
+      <c r="O114" s="10" t="n"/>
+      <c r="P114" s="10" t="n"/>
+      <c r="Q114" s="10" t="n"/>
+      <c r="R114" s="10" t="n"/>
+      <c r="S114" s="10" t="n"/>
+      <c r="T114" s="10" t="n"/>
+      <c r="U114" s="10" t="n"/>
+      <c r="V114" s="10" t="n"/>
+      <c r="W114" s="10" t="n"/>
+      <c r="X114" s="10" t="n"/>
+      <c r="Y114" s="10" t="n"/>
+      <c r="Z114" s="10" t="n"/>
+      <c r="AA114" s="10" t="n"/>
+      <c r="AB114" s="10" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="10" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="10" t="n"/>
+      <c r="AK114" s="11" t="n"/>
+    </row>
+    <row r="116" ht="19.5" customHeight="1">
+      <c r="B116" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="72" customHeight="1">
-      <c r="C113" s="19" t="inlineStr">
+    <row r="117" ht="72" customHeight="1">
+      <c r="C117" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -14826,191 +17144,191 @@
 }</t>
         </is>
       </c>
-      <c r="D113" s="10" t="n"/>
-      <c r="E113" s="10" t="n"/>
-      <c r="F113" s="10" t="n"/>
-      <c r="G113" s="10" t="n"/>
-      <c r="H113" s="10" t="n"/>
-      <c r="I113" s="10" t="n"/>
-      <c r="J113" s="10" t="n"/>
-      <c r="K113" s="10" t="n"/>
-      <c r="L113" s="10" t="n"/>
-      <c r="M113" s="10" t="n"/>
-      <c r="N113" s="10" t="n"/>
-      <c r="O113" s="10" t="n"/>
-      <c r="P113" s="10" t="n"/>
-      <c r="Q113" s="10" t="n"/>
-      <c r="R113" s="10" t="n"/>
-      <c r="S113" s="10" t="n"/>
-      <c r="T113" s="10" t="n"/>
-      <c r="U113" s="10" t="n"/>
-      <c r="V113" s="10" t="n"/>
-      <c r="W113" s="10" t="n"/>
-      <c r="X113" s="10" t="n"/>
-      <c r="Y113" s="10" t="n"/>
-      <c r="Z113" s="10" t="n"/>
-      <c r="AA113" s="10" t="n"/>
-      <c r="AB113" s="10" t="n"/>
-      <c r="AC113" s="10" t="n"/>
-      <c r="AD113" s="10" t="n"/>
-      <c r="AE113" s="10" t="n"/>
-      <c r="AF113" s="10" t="n"/>
-      <c r="AG113" s="10" t="n"/>
-      <c r="AH113" s="10" t="n"/>
-      <c r="AI113" s="10" t="n"/>
-      <c r="AJ113" s="10" t="n"/>
-      <c r="AK113" s="11" t="n"/>
-    </row>
-    <row r="115" ht="19.5" customHeight="1"/>
-    <row r="116" ht="19.5" customHeight="1">
-      <c r="A116" s="27" t="inlineStr">
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="10" t="n"/>
+      <c r="F117" s="10" t="n"/>
+      <c r="G117" s="10" t="n"/>
+      <c r="H117" s="10" t="n"/>
+      <c r="I117" s="10" t="n"/>
+      <c r="J117" s="10" t="n"/>
+      <c r="K117" s="10" t="n"/>
+      <c r="L117" s="10" t="n"/>
+      <c r="M117" s="10" t="n"/>
+      <c r="N117" s="10" t="n"/>
+      <c r="O117" s="10" t="n"/>
+      <c r="P117" s="10" t="n"/>
+      <c r="Q117" s="10" t="n"/>
+      <c r="R117" s="10" t="n"/>
+      <c r="S117" s="10" t="n"/>
+      <c r="T117" s="10" t="n"/>
+      <c r="U117" s="10" t="n"/>
+      <c r="V117" s="10" t="n"/>
+      <c r="W117" s="10" t="n"/>
+      <c r="X117" s="10" t="n"/>
+      <c r="Y117" s="10" t="n"/>
+      <c r="Z117" s="10" t="n"/>
+      <c r="AA117" s="10" t="n"/>
+      <c r="AB117" s="10" t="n"/>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="10" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="10" t="n"/>
+      <c r="AK117" s="11" t="n"/>
+    </row>
+    <row r="119" ht="19.5" customHeight="1"/>
+    <row r="120" ht="19.5" customHeight="1">
+      <c r="A120" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="B117" s="27" t="inlineStr">
+    <row r="121" ht="18" customHeight="1">
+      <c r="B121" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="C118" s="41" t="inlineStr">
+    <row r="122" ht="18" customHeight="1">
+      <c r="C122" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="D119" s="41" t="inlineStr">
+    <row r="123" ht="18" customHeight="1">
+      <c r="D123" s="41" t="inlineStr">
         <is>
           <t>dokusya_id：数値型チェック、必須チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="C120" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="D121" s="41" t="inlineStr">
-        <is>
-          <t>HTTP 400 (`BAD_REQUEST`) を返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="B122" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="C123" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="C124" s="41" t="inlineStr">
         <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="C125" s="41" t="inlineStr">
-        <is>
-          <t>必要権限: `dokusya.view`</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="36" customHeight="1">
-      <c r="C126" s="41" t="inlineStr">
-        <is>
-          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+      <c r="D125" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 400 (`BAD_REQUEST`) を返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="B126" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="C127" s="41" t="inlineStr">
         <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="C128" s="41" t="inlineStr">
         <is>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="C129" s="41" t="inlineStr">
+        <is>
+          <t>必要権限: `dokusya.view`</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="36" customHeight="1">
+      <c r="C130" s="41" t="inlineStr">
+        <is>
+          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="C131" s="41" t="inlineStr">
+        <is>
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="C132" s="41" t="inlineStr">
+        <is>
           <t>DataScope:</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="D129" s="41" t="inlineStr">
+    <row r="133" ht="18" customHeight="1">
+      <c r="D133" s="41" t="inlineStr">
         <is>
           <t>CHUOKAI（中央会）：自中央会のみ参照可能（管轄JAの読者は不可）</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="D130" s="41" t="inlineStr">
+    <row r="134" ht="18" customHeight="1">
+      <c r="D134" s="41" t="inlineStr">
         <is>
           <t>JA_HONTEN（JA本店）：自JAのみ参照可能（`ja_id = user.ja_id`）</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="36" customHeight="1">
-      <c r="D131" s="41" t="inlineStr">
+    <row r="135" ht="36" customHeight="1">
+      <c r="D135" s="41" t="inlineStr">
         <is>
           <t>JA_KANRI_SHITEN（JA管理支店）：自管理支店のみ参照可能（`ja_id = user.ja_id AND kanri_shiten_id = user.kanri_shiten_id`）</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="36" customHeight="1">
-      <c r="C132" s="41" t="inlineStr">
+    <row r="136" ht="36" customHeight="1">
+      <c r="C136" s="41" t="inlineStr">
         <is>
           <t>DataScope違反（他JAのレコードへのアクセス）の場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="B133" s="27" t="inlineStr">
+    <row r="137" ht="18" customHeight="1">
+      <c r="B137" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="C134" s="41" t="inlineStr">
+    <row r="138" ht="18" customHeight="1">
+      <c r="C138" s="41" t="inlineStr">
         <is>
           <t>ログインユーザーのスコープを取得する。</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="C135" s="41" t="inlineStr">
+    <row r="139" ht="18" customHeight="1">
+      <c r="C139" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して購読者情報を取得する（販売店名・単価名・引落口座支店情報を結合）。</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="90" customHeight="1">
-      <c r="C136" s="41" t="inlineStr">
+    <row r="140" ht="90" customHeight="1">
+      <c r="C140" s="41" t="inlineStr">
         <is>
           <t>`bank_shiten_id` は `t_dokusya.bank_branch_code` をキーとして、ログインユーザー所属JA内で `kinyu_shiten_flg = TRUE` の `m_shiten` レコードから逆引きする（プルダウン再ハイドレーション用）。`jastem_toriatsukai_tenpo_code` および `jastem_tenpo_name` も同じ JOIN から取得する。</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="288" customHeight="1">
-      <c r="C137" s="42" t="inlineStr">
+    <row r="141" ht="288" customHeight="1">
+      <c r="C141" s="42" t="inlineStr">
         <is>
           <t>SELECT d.*,
        h.hanbaiten_name,
@@ -15030,87 +17348,88 @@
   AND d.deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D137" s="10" t="n"/>
-      <c r="E137" s="10" t="n"/>
-      <c r="F137" s="10" t="n"/>
-      <c r="G137" s="10" t="n"/>
-      <c r="H137" s="10" t="n"/>
-      <c r="I137" s="10" t="n"/>
-      <c r="J137" s="10" t="n"/>
-      <c r="K137" s="10" t="n"/>
-      <c r="L137" s="10" t="n"/>
-      <c r="M137" s="10" t="n"/>
-      <c r="N137" s="10" t="n"/>
-      <c r="O137" s="10" t="n"/>
-      <c r="P137" s="10" t="n"/>
-      <c r="Q137" s="10" t="n"/>
-      <c r="R137" s="10" t="n"/>
-      <c r="S137" s="10" t="n"/>
-      <c r="T137" s="10" t="n"/>
-      <c r="U137" s="10" t="n"/>
-      <c r="V137" s="10" t="n"/>
-      <c r="W137" s="10" t="n"/>
-      <c r="X137" s="10" t="n"/>
-      <c r="Y137" s="10" t="n"/>
-      <c r="Z137" s="10" t="n"/>
-      <c r="AA137" s="10" t="n"/>
-      <c r="AB137" s="10" t="n"/>
-      <c r="AC137" s="10" t="n"/>
-      <c r="AD137" s="10" t="n"/>
-      <c r="AE137" s="10" t="n"/>
-      <c r="AF137" s="10" t="n"/>
-      <c r="AG137" s="10" t="n"/>
-      <c r="AH137" s="10" t="n"/>
-      <c r="AI137" s="10" t="n"/>
-      <c r="AJ137" s="10" t="n"/>
-      <c r="AK137" s="11" t="n"/>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="C138" s="41" t="inlineStr">
+      <c r="D141" s="10" t="n"/>
+      <c r="E141" s="10" t="n"/>
+      <c r="F141" s="10" t="n"/>
+      <c r="G141" s="10" t="n"/>
+      <c r="H141" s="10" t="n"/>
+      <c r="I141" s="10" t="n"/>
+      <c r="J141" s="10" t="n"/>
+      <c r="K141" s="10" t="n"/>
+      <c r="L141" s="10" t="n"/>
+      <c r="M141" s="10" t="n"/>
+      <c r="N141" s="10" t="n"/>
+      <c r="O141" s="10" t="n"/>
+      <c r="P141" s="10" t="n"/>
+      <c r="Q141" s="10" t="n"/>
+      <c r="R141" s="10" t="n"/>
+      <c r="S141" s="10" t="n"/>
+      <c r="T141" s="10" t="n"/>
+      <c r="U141" s="10" t="n"/>
+      <c r="V141" s="10" t="n"/>
+      <c r="W141" s="10" t="n"/>
+      <c r="X141" s="10" t="n"/>
+      <c r="Y141" s="10" t="n"/>
+      <c r="Z141" s="10" t="n"/>
+      <c r="AA141" s="10" t="n"/>
+      <c r="AB141" s="10" t="n"/>
+      <c r="AC141" s="10" t="n"/>
+      <c r="AD141" s="10" t="n"/>
+      <c r="AE141" s="10" t="n"/>
+      <c r="AF141" s="10" t="n"/>
+      <c r="AG141" s="10" t="n"/>
+      <c r="AH141" s="10" t="n"/>
+      <c r="AI141" s="10" t="n"/>
+      <c r="AJ141" s="10" t="n"/>
+      <c r="AK141" s="11" t="n"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="C142" s="41" t="inlineStr">
         <is>
           <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="C139" s="41" t="inlineStr">
-        <is>
-          <t>DataScope違反の場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="B140" s="27" t="inlineStr">
-        <is>
-          <t>4.4 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="C141" s="41" t="inlineStr">
-        <is>
-          <t>data オブジェクトを含むJSONを返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="B142" s="27" t="inlineStr">
-        <is>
-          <t>4.5 例外処理</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="C143" s="41" t="inlineStr">
         <is>
+          <t>DataScope違反の場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="B144" s="27" t="inlineStr">
+        <is>
+          <t>4.4 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="C145" s="41" t="inlineStr">
+        <is>
+          <t>data オブジェクトを含むJSONを返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="B146" s="27" t="inlineStr">
+        <is>
+          <t>4.5 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="C147" s="41" t="inlineStr">
+        <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="511">
+  <mergeCells count="535">
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="Y27:AE27"/>
+    <mergeCell ref="D134:AK134"/>
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="D61:L61"/>
     <mergeCell ref="D48:L48"/>
@@ -15124,7 +17443,6 @@
     <mergeCell ref="C128:AK128"/>
     <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
-    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="AF91:AK91"/>
     <mergeCell ref="J1:P1"/>
@@ -15133,11 +17451,14 @@
     <mergeCell ref="D51:L51"/>
     <mergeCell ref="M88:P88"/>
     <mergeCell ref="M82:P82"/>
+    <mergeCell ref="C142:AK142"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="AF84:AK84"/>
     <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="C129:AK129"/>
     <mergeCell ref="Q91:S91"/>
     <mergeCell ref="M54:P54"/>
+    <mergeCell ref="Y98:AE98"/>
     <mergeCell ref="M90:P90"/>
     <mergeCell ref="AF86:AK86"/>
     <mergeCell ref="Q77:S77"/>
@@ -15145,8 +17466,8 @@
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="T37:X37"/>
-    <mergeCell ref="B140:AK140"/>
     <mergeCell ref="M85:P85"/>
+    <mergeCell ref="C131:AK131"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="D75:L75"/>
     <mergeCell ref="Z1:AC1"/>
@@ -15154,9 +17475,7 @@
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="Y66:AE66"/>
-    <mergeCell ref="C126:AK126"/>
     <mergeCell ref="Y53:AE53"/>
-    <mergeCell ref="D129:AK129"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
     <mergeCell ref="D39:L39"/>
@@ -15168,8 +17487,10 @@
     <mergeCell ref="Y68:AE68"/>
     <mergeCell ref="Y55:AE55"/>
     <mergeCell ref="AF81:AK81"/>
+    <mergeCell ref="C117:AK117"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="D89:L89"/>
+    <mergeCell ref="AF99:AK99"/>
     <mergeCell ref="T76:X76"/>
     <mergeCell ref="T69:X69"/>
     <mergeCell ref="D65:L65"/>
@@ -15177,12 +17498,14 @@
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="M91:P91"/>
+    <mergeCell ref="C145:AK145"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF92:AK92"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C28:L28"/>
+    <mergeCell ref="Q99:S99"/>
     <mergeCell ref="Y41:AE41"/>
     <mergeCell ref="M93:P93"/>
     <mergeCell ref="T87:X87"/>
@@ -15197,7 +17520,6 @@
     <mergeCell ref="D83:L83"/>
     <mergeCell ref="T89:X89"/>
     <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="C134:AK134"/>
     <mergeCell ref="T88:X88"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="Y74:AE74"/>
@@ -15215,7 +17537,7 @@
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="Q64:S64"/>
-    <mergeCell ref="B97:I97"/>
+    <mergeCell ref="B121:AK121"/>
     <mergeCell ref="T77:X77"/>
     <mergeCell ref="M41:P41"/>
     <mergeCell ref="T35:X35"/>
@@ -15224,6 +17546,7 @@
     <mergeCell ref="D58:L58"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="Y87:AE87"/>
+    <mergeCell ref="C147:AK147"/>
     <mergeCell ref="AF75:AK75"/>
     <mergeCell ref="Y89:AE89"/>
     <mergeCell ref="Q57:S57"/>
@@ -15233,21 +17556,24 @@
     <mergeCell ref="Y82:AE82"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="AF70:AK70"/>
+    <mergeCell ref="T96:X96"/>
+    <mergeCell ref="B126:AK126"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="D84:L84"/>
     <mergeCell ref="T90:X90"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="Q52:S52"/>
+    <mergeCell ref="AF97:AK97"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="M37:P37"/>
+    <mergeCell ref="T98:X98"/>
     <mergeCell ref="D86:L86"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="Y77:AE77"/>
-    <mergeCell ref="A116:AK116"/>
     <mergeCell ref="J18:M18"/>
-    <mergeCell ref="D121:AK121"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="M56:P56"/>
     <mergeCell ref="C141:AK141"/>
@@ -15257,6 +17583,7 @@
     <mergeCell ref="Q70:S70"/>
     <mergeCell ref="Y72:AE72"/>
     <mergeCell ref="C143:AK143"/>
+    <mergeCell ref="B137:AK137"/>
     <mergeCell ref="D33:L33"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="D35:L35"/>
@@ -15266,6 +17593,7 @@
     <mergeCell ref="T75:X75"/>
     <mergeCell ref="D34:L34"/>
     <mergeCell ref="Y88:AE88"/>
+    <mergeCell ref="D99:L99"/>
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="T86:X86"/>
     <mergeCell ref="Q83:S83"/>
@@ -15276,21 +17604,17 @@
     <mergeCell ref="AF78:AK78"/>
     <mergeCell ref="Y65:AE65"/>
     <mergeCell ref="D76:L76"/>
-    <mergeCell ref="B109:I109"/>
     <mergeCell ref="Q85:S85"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="B117:AK117"/>
     <mergeCell ref="M62:P62"/>
     <mergeCell ref="AF80:AK80"/>
     <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="M87:P87"/>
     <mergeCell ref="D29:L29"/>
     <mergeCell ref="M64:P64"/>
-    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="AF71:AK71"/>
     <mergeCell ref="M51:P51"/>
-    <mergeCell ref="D131:AK131"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="AF73:AK73"/>
     <mergeCell ref="Q71:S71"/>
@@ -15301,12 +17625,11 @@
     <mergeCell ref="AF66:AK66"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
-    <mergeCell ref="B122:AK122"/>
     <mergeCell ref="Y80:AE80"/>
     <mergeCell ref="D49:L49"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF68:AK68"/>
-    <mergeCell ref="C98:AK98"/>
+    <mergeCell ref="Y96:AE96"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q84:S84"/>
@@ -15317,36 +17640,35 @@
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="Y93:AE93"/>
-    <mergeCell ref="D119:AK119"/>
     <mergeCell ref="D54:L54"/>
-    <mergeCell ref="B112:I112"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="M78:P78"/>
-    <mergeCell ref="B133:AK133"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="T56:X56"/>
     <mergeCell ref="T43:X43"/>
+    <mergeCell ref="T99:X99"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="Y46:AE46"/>
     <mergeCell ref="D57:L57"/>
     <mergeCell ref="AF63:AK63"/>
     <mergeCell ref="Q79:S79"/>
+    <mergeCell ref="C111:AK111"/>
     <mergeCell ref="D32:L32"/>
     <mergeCell ref="Y61:AE61"/>
+    <mergeCell ref="D97:L97"/>
     <mergeCell ref="Y48:AE48"/>
     <mergeCell ref="AF74:AK74"/>
     <mergeCell ref="Q81:S81"/>
-    <mergeCell ref="D130:AK130"/>
     <mergeCell ref="M58:P58"/>
     <mergeCell ref="AF76:AK76"/>
     <mergeCell ref="Q74:S74"/>
+    <mergeCell ref="B107:I107"/>
     <mergeCell ref="T62:X62"/>
+    <mergeCell ref="B146:AK146"/>
     <mergeCell ref="Q76:S76"/>
-    <mergeCell ref="C137:AK137"/>
     <mergeCell ref="T64:X64"/>
-    <mergeCell ref="C29:C95"/>
     <mergeCell ref="C124:AK124"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D44:L44"/>
@@ -15362,6 +17684,7 @@
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="D45:L45"/>
     <mergeCell ref="M86:P86"/>
+    <mergeCell ref="Y99:AE99"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="M80:P80"/>
     <mergeCell ref="T67:X67"/>
@@ -15378,26 +17701,33 @@
     <mergeCell ref="D70:L70"/>
     <mergeCell ref="AF89:AK89"/>
     <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="D78:L78"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="Q89:S89"/>
     <mergeCell ref="D71:L71"/>
     <mergeCell ref="Y62:AE62"/>
     <mergeCell ref="D73:L73"/>
+    <mergeCell ref="D98:L98"/>
     <mergeCell ref="M70:P70"/>
     <mergeCell ref="C127:AK127"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="M35:P35"/>
+    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="Y64:AE64"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="AF77:AK77"/>
+    <mergeCell ref="M99:P99"/>
     <mergeCell ref="M74:P74"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="T72:X72"/>
     <mergeCell ref="T28:X28"/>
+    <mergeCell ref="B110:I110"/>
+    <mergeCell ref="D135:AK135"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T57:X57"/>
+    <mergeCell ref="C140:AK140"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="D66:L66"/>
     <mergeCell ref="D53:L53"/>
@@ -15407,7 +17737,6 @@
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="AF95:AK95"/>
-    <mergeCell ref="C104:AK104"/>
     <mergeCell ref="T58:X58"/>
     <mergeCell ref="T54:X54"/>
     <mergeCell ref="Y75:AE75"/>
@@ -15427,12 +17756,14 @@
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
     <mergeCell ref="T85:X85"/>
+    <mergeCell ref="Q96:S96"/>
     <mergeCell ref="T60:X60"/>
+    <mergeCell ref="C130:AK130"/>
     <mergeCell ref="D81:L81"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C122:AK122"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M36:P36"/>
-    <mergeCell ref="C125:AK125"/>
     <mergeCell ref="Q63:S63"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Y70:AE70"/>
@@ -15448,6 +17779,7 @@
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="T80:X80"/>
     <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="B101:I101"/>
     <mergeCell ref="D92:L92"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="D30:L30"/>
@@ -15458,18 +17790,21 @@
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="Y83:AE83"/>
     <mergeCell ref="D94:L94"/>
+    <mergeCell ref="C105:AK105"/>
+    <mergeCell ref="AF96:AK96"/>
     <mergeCell ref="D69:L69"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="Y85:AE85"/>
-    <mergeCell ref="C120:AK120"/>
+    <mergeCell ref="AF98:AK98"/>
     <mergeCell ref="Y60:AE60"/>
+    <mergeCell ref="B104:I104"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="M95:P95"/>
     <mergeCell ref="M89:P89"/>
     <mergeCell ref="Q55:S55"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="B106:I106"/>
+    <mergeCell ref="M97:P97"/>
     <mergeCell ref="AF93:AK93"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="D87:L87"/>
@@ -15493,6 +17828,7 @@
     <mergeCell ref="T81:X81"/>
     <mergeCell ref="D31:L31"/>
     <mergeCell ref="M28:P28"/>
+    <mergeCell ref="Q97:S97"/>
     <mergeCell ref="D77:L77"/>
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="Y84:AE84"/>
@@ -15506,9 +17842,11 @@
     <mergeCell ref="D72:L72"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="T63:X63"/>
+    <mergeCell ref="M96:P96"/>
     <mergeCell ref="M71:P71"/>
     <mergeCell ref="AF29:AK29"/>
     <mergeCell ref="T71:X71"/>
+    <mergeCell ref="M98:P98"/>
     <mergeCell ref="T92:X92"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
@@ -15526,19 +17864,21 @@
     <mergeCell ref="AF67:AK67"/>
     <mergeCell ref="T95:X95"/>
     <mergeCell ref="Y81:AE81"/>
+    <mergeCell ref="A120:AK120"/>
+    <mergeCell ref="B113:I113"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
     <mergeCell ref="Q67:S67"/>
-    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="D125:AK125"/>
     <mergeCell ref="AF62:AK62"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="Q69:S69"/>
-    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y76:AE76"/>
     <mergeCell ref="AF64:AK64"/>
     <mergeCell ref="D37:L37"/>
     <mergeCell ref="AF51:AK51"/>
+    <mergeCell ref="Q98:S98"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="Y63:AE63"/>
     <mergeCell ref="M44:P44"/>
@@ -15557,6 +17897,7 @@
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="AF82:AK82"/>
     <mergeCell ref="Y31:AE31"/>
+    <mergeCell ref="D96:L96"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="D52:L52"/>
     <mergeCell ref="Q82:S82"/>
@@ -15565,32 +17906,33 @@
     <mergeCell ref="Q93:S93"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="D91:L91"/>
+    <mergeCell ref="T97:X97"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
     <mergeCell ref="M50:P50"/>
-    <mergeCell ref="C107:AK107"/>
     <mergeCell ref="D93:L93"/>
+    <mergeCell ref="D133:AK133"/>
     <mergeCell ref="M68:P68"/>
     <mergeCell ref="M92:P92"/>
     <mergeCell ref="M55:P55"/>
     <mergeCell ref="M67:P67"/>
+    <mergeCell ref="B116:I116"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="AF72:AK72"/>
-    <mergeCell ref="B103:I103"/>
     <mergeCell ref="Q75:S75"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="M69:P69"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="B142:AK142"/>
     <mergeCell ref="Y44:AE44"/>
+    <mergeCell ref="C29:C99"/>
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
+    <mergeCell ref="B144:AK144"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="M81:P81"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="C135:AK135"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="T91:X91"/>
     <mergeCell ref="B7:I7"/>
@@ -15606,18 +17948,18 @@
     <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="AF58:AK58"/>
+    <mergeCell ref="Y97:AE97"/>
     <mergeCell ref="Q65:S65"/>
     <mergeCell ref="AF85:AK85"/>
     <mergeCell ref="Y47:AE47"/>
+    <mergeCell ref="D123:AK123"/>
     <mergeCell ref="AF60:AK60"/>
     <mergeCell ref="D74:L74"/>
     <mergeCell ref="D68:L68"/>
     <mergeCell ref="D59:L59"/>
     <mergeCell ref="M94:P94"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
-    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="M77:P77"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>
@@ -15631,7 +17973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK239"/>
+  <dimension ref="A1:AK244"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -15792,7 +18134,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -23709,14 +26051,14 @@
       <c r="AJ145" s="10" t="n"/>
       <c r="AK145" s="11" t="n"/>
     </row>
-    <row r="146" ht="18" customHeight="1">
+    <row r="146" ht="36" customHeight="1">
       <c r="B146" s="31" t="n">
         <v>65</v>
       </c>
       <c r="C146" s="38" t="n"/>
       <c r="D146" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>denshi_kaiin_id</t>
         </is>
       </c>
       <c r="E146" s="10" t="n"/>
@@ -23729,7 +26071,7 @@
       <c r="L146" s="11" t="n"/>
       <c r="M146" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N146" s="10" t="n"/>
@@ -23742,18 +26084,14 @@
       </c>
       <c r="R146" s="10" t="n"/>
       <c r="S146" s="11" t="n"/>
-      <c r="T146" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T146" s="17" t="inlineStr"/>
       <c r="U146" s="10" t="n"/>
       <c r="V146" s="10" t="n"/>
       <c r="W146" s="10" t="n"/>
       <c r="X146" s="11" t="n"/>
       <c r="Y146" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z146" s="10" t="n"/>
@@ -23764,7 +26102,7 @@
       <c r="AE146" s="11" t="n"/>
       <c r="AF146" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>電子版会員ID（外部の電子版読者管理システムの会員ID。外部連携機能が設定する読取専用値）</t>
         </is>
       </c>
       <c r="AG146" s="10" t="n"/>
@@ -23773,14 +26111,14 @@
       <c r="AJ146" s="10" t="n"/>
       <c r="AK146" s="11" t="n"/>
     </row>
-    <row r="147" ht="18" customHeight="1">
+    <row r="147" ht="36" customHeight="1">
       <c r="B147" s="31" t="n">
         <v>66</v>
       </c>
-      <c r="C147" s="39" t="n"/>
+      <c r="C147" s="38" t="n"/>
       <c r="D147" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>honshi_kodoku_flg</t>
         </is>
       </c>
       <c r="E147" s="10" t="n"/>
@@ -23793,7 +26131,7 @@
       <c r="L147" s="11" t="n"/>
       <c r="M147" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N147" s="10" t="n"/>
@@ -23806,11 +26144,7 @@
       </c>
       <c r="R147" s="10" t="n"/>
       <c r="S147" s="11" t="n"/>
-      <c r="T147" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T147" s="17" t="inlineStr"/>
       <c r="U147" s="10" t="n"/>
       <c r="V147" s="10" t="n"/>
       <c r="W147" s="10" t="n"/>
@@ -23828,7 +26162,7 @@
       <c r="AE147" s="11" t="n"/>
       <c r="AF147" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>本紙購読フラグ（電子版読者管理システム users.subscribe_flg 連携）</t>
         </is>
       </c>
       <c r="AG147" s="10" t="n"/>
@@ -23837,16 +26171,268 @@
       <c r="AJ147" s="10" t="n"/>
       <c r="AK147" s="11" t="n"/>
     </row>
-    <row r="148" ht="19.5" customHeight="1"/>
-    <row r="149" ht="19.5" customHeight="1">
-      <c r="B149" s="40" t="inlineStr">
+    <row r="148" ht="18" customHeight="1">
+      <c r="B148" s="31" t="n">
+        <v>67</v>
+      </c>
+      <c r="C148" s="38" t="n"/>
+      <c r="D148" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E148" s="10" t="n"/>
+      <c r="F148" s="10" t="n"/>
+      <c r="G148" s="10" t="n"/>
+      <c r="H148" s="10" t="n"/>
+      <c r="I148" s="10" t="n"/>
+      <c r="J148" s="10" t="n"/>
+      <c r="K148" s="10" t="n"/>
+      <c r="L148" s="11" t="n"/>
+      <c r="M148" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N148" s="10" t="n"/>
+      <c r="O148" s="10" t="n"/>
+      <c r="P148" s="11" t="n"/>
+      <c r="Q148" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R148" s="10" t="n"/>
+      <c r="S148" s="11" t="n"/>
+      <c r="T148" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U148" s="10" t="n"/>
+      <c r="V148" s="10" t="n"/>
+      <c r="W148" s="10" t="n"/>
+      <c r="X148" s="11" t="n"/>
+      <c r="Y148" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z148" s="10" t="n"/>
+      <c r="AA148" s="10" t="n"/>
+      <c r="AB148" s="10" t="n"/>
+      <c r="AC148" s="10" t="n"/>
+      <c r="AD148" s="10" t="n"/>
+      <c r="AE148" s="11" t="n"/>
+      <c r="AF148" s="19" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="AG148" s="10" t="n"/>
+      <c r="AH148" s="10" t="n"/>
+      <c r="AI148" s="10" t="n"/>
+      <c r="AJ148" s="10" t="n"/>
+      <c r="AK148" s="11" t="n"/>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="B149" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="C149" s="38" t="n"/>
+      <c r="D149" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="n"/>
+      <c r="F149" s="10" t="n"/>
+      <c r="G149" s="10" t="n"/>
+      <c r="H149" s="10" t="n"/>
+      <c r="I149" s="10" t="n"/>
+      <c r="J149" s="10" t="n"/>
+      <c r="K149" s="10" t="n"/>
+      <c r="L149" s="11" t="n"/>
+      <c r="M149" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N149" s="10" t="n"/>
+      <c r="O149" s="10" t="n"/>
+      <c r="P149" s="11" t="n"/>
+      <c r="Q149" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R149" s="10" t="n"/>
+      <c r="S149" s="11" t="n"/>
+      <c r="T149" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U149" s="10" t="n"/>
+      <c r="V149" s="10" t="n"/>
+      <c r="W149" s="10" t="n"/>
+      <c r="X149" s="11" t="n"/>
+      <c r="Y149" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z149" s="10" t="n"/>
+      <c r="AA149" s="10" t="n"/>
+      <c r="AB149" s="10" t="n"/>
+      <c r="AC149" s="10" t="n"/>
+      <c r="AD149" s="10" t="n"/>
+      <c r="AE149" s="11" t="n"/>
+      <c r="AF149" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG149" s="10" t="n"/>
+      <c r="AH149" s="10" t="n"/>
+      <c r="AI149" s="10" t="n"/>
+      <c r="AJ149" s="10" t="n"/>
+      <c r="AK149" s="11" t="n"/>
+    </row>
+    <row r="150" ht="36" customHeight="1">
+      <c r="B150" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="C150" s="38" t="n"/>
+      <c r="D150" s="19" t="inlineStr">
+        <is>
+          <t>has_active_kaiyaku</t>
+        </is>
+      </c>
+      <c r="E150" s="10" t="n"/>
+      <c r="F150" s="10" t="n"/>
+      <c r="G150" s="10" t="n"/>
+      <c r="H150" s="10" t="n"/>
+      <c r="I150" s="10" t="n"/>
+      <c r="J150" s="10" t="n"/>
+      <c r="K150" s="10" t="n"/>
+      <c r="L150" s="11" t="n"/>
+      <c r="M150" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N150" s="10" t="n"/>
+      <c r="O150" s="10" t="n"/>
+      <c r="P150" s="11" t="n"/>
+      <c r="Q150" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R150" s="10" t="n"/>
+      <c r="S150" s="11" t="n"/>
+      <c r="T150" s="17" t="inlineStr"/>
+      <c r="U150" s="10" t="n"/>
+      <c r="V150" s="10" t="n"/>
+      <c r="W150" s="10" t="n"/>
+      <c r="X150" s="11" t="n"/>
+      <c r="Y150" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z150" s="10" t="n"/>
+      <c r="AA150" s="10" t="n"/>
+      <c r="AB150" s="10" t="n"/>
+      <c r="AC150" s="10" t="n"/>
+      <c r="AD150" s="10" t="n"/>
+      <c r="AE150" s="11" t="n"/>
+      <c r="AF150" s="19" t="inlineStr">
+        <is>
+          <t>有効な解約予約が存在するか（顧客要件2026-07。履歴から算出）</t>
+        </is>
+      </c>
+      <c r="AG150" s="10" t="n"/>
+      <c r="AH150" s="10" t="n"/>
+      <c r="AI150" s="10" t="n"/>
+      <c r="AJ150" s="10" t="n"/>
+      <c r="AK150" s="11" t="n"/>
+    </row>
+    <row r="151" ht="36" customHeight="1">
+      <c r="B151" s="31" t="n">
+        <v>70</v>
+      </c>
+      <c r="C151" s="39" t="n"/>
+      <c r="D151" s="19" t="inlineStr">
+        <is>
+          <t>max_joho_date</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="n"/>
+      <c r="F151" s="10" t="n"/>
+      <c r="G151" s="10" t="n"/>
+      <c r="H151" s="10" t="n"/>
+      <c r="I151" s="10" t="n"/>
+      <c r="J151" s="10" t="n"/>
+      <c r="K151" s="10" t="n"/>
+      <c r="L151" s="11" t="n"/>
+      <c r="M151" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N151" s="10" t="n"/>
+      <c r="O151" s="10" t="n"/>
+      <c r="P151" s="11" t="n"/>
+      <c r="Q151" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R151" s="10" t="n"/>
+      <c r="S151" s="11" t="n"/>
+      <c r="T151" s="17" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="U151" s="10" t="n"/>
+      <c r="V151" s="10" t="n"/>
+      <c r="W151" s="10" t="n"/>
+      <c r="X151" s="11" t="n"/>
+      <c r="Y151" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z151" s="10" t="n"/>
+      <c r="AA151" s="10" t="n"/>
+      <c r="AB151" s="10" t="n"/>
+      <c r="AC151" s="10" t="n"/>
+      <c r="AD151" s="10" t="n"/>
+      <c r="AE151" s="11" t="n"/>
+      <c r="AF151" s="19" t="inlineStr">
+        <is>
+          <t>履歴の最終変更適用日（MAX joho・取消除外）。履歴なしは null</t>
+        </is>
+      </c>
+      <c r="AG151" s="10" t="n"/>
+      <c r="AH151" s="10" t="n"/>
+      <c r="AI151" s="10" t="n"/>
+      <c r="AJ151" s="10" t="n"/>
+      <c r="AK151" s="11" t="n"/>
+    </row>
+    <row r="152" ht="19.5" customHeight="1"/>
+    <row r="153" ht="19.5" customHeight="1">
+      <c r="B153" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="409" customHeight="1">
-      <c r="C150" s="19" t="inlineStr">
+    <row r="154" ht="409" customHeight="1">
+      <c r="C154" s="19" t="inlineStr">
         <is>
           <t>POST /api/v1/dokusya
 Content-Type: application/json
@@ -23906,50 +26492,50 @@
 }</t>
         </is>
       </c>
-      <c r="D150" s="10" t="n"/>
-      <c r="E150" s="10" t="n"/>
-      <c r="F150" s="10" t="n"/>
-      <c r="G150" s="10" t="n"/>
-      <c r="H150" s="10" t="n"/>
-      <c r="I150" s="10" t="n"/>
-      <c r="J150" s="10" t="n"/>
-      <c r="K150" s="10" t="n"/>
-      <c r="L150" s="10" t="n"/>
-      <c r="M150" s="10" t="n"/>
-      <c r="N150" s="10" t="n"/>
-      <c r="O150" s="10" t="n"/>
-      <c r="P150" s="10" t="n"/>
-      <c r="Q150" s="10" t="n"/>
-      <c r="R150" s="10" t="n"/>
-      <c r="S150" s="10" t="n"/>
-      <c r="T150" s="10" t="n"/>
-      <c r="U150" s="10" t="n"/>
-      <c r="V150" s="10" t="n"/>
-      <c r="W150" s="10" t="n"/>
-      <c r="X150" s="10" t="n"/>
-      <c r="Y150" s="10" t="n"/>
-      <c r="Z150" s="10" t="n"/>
-      <c r="AA150" s="10" t="n"/>
-      <c r="AB150" s="10" t="n"/>
-      <c r="AC150" s="10" t="n"/>
-      <c r="AD150" s="10" t="n"/>
-      <c r="AE150" s="10" t="n"/>
-      <c r="AF150" s="10" t="n"/>
-      <c r="AG150" s="10" t="n"/>
-      <c r="AH150" s="10" t="n"/>
-      <c r="AI150" s="10" t="n"/>
-      <c r="AJ150" s="10" t="n"/>
-      <c r="AK150" s="11" t="n"/>
-    </row>
-    <row r="152" ht="19.5" customHeight="1">
-      <c r="B152" s="40" t="inlineStr">
+      <c r="D154" s="10" t="n"/>
+      <c r="E154" s="10" t="n"/>
+      <c r="F154" s="10" t="n"/>
+      <c r="G154" s="10" t="n"/>
+      <c r="H154" s="10" t="n"/>
+      <c r="I154" s="10" t="n"/>
+      <c r="J154" s="10" t="n"/>
+      <c r="K154" s="10" t="n"/>
+      <c r="L154" s="10" t="n"/>
+      <c r="M154" s="10" t="n"/>
+      <c r="N154" s="10" t="n"/>
+      <c r="O154" s="10" t="n"/>
+      <c r="P154" s="10" t="n"/>
+      <c r="Q154" s="10" t="n"/>
+      <c r="R154" s="10" t="n"/>
+      <c r="S154" s="10" t="n"/>
+      <c r="T154" s="10" t="n"/>
+      <c r="U154" s="10" t="n"/>
+      <c r="V154" s="10" t="n"/>
+      <c r="W154" s="10" t="n"/>
+      <c r="X154" s="10" t="n"/>
+      <c r="Y154" s="10" t="n"/>
+      <c r="Z154" s="10" t="n"/>
+      <c r="AA154" s="10" t="n"/>
+      <c r="AB154" s="10" t="n"/>
+      <c r="AC154" s="10" t="n"/>
+      <c r="AD154" s="10" t="n"/>
+      <c r="AE154" s="10" t="n"/>
+      <c r="AF154" s="10" t="n"/>
+      <c r="AG154" s="10" t="n"/>
+      <c r="AH154" s="10" t="n"/>
+      <c r="AI154" s="10" t="n"/>
+      <c r="AJ154" s="10" t="n"/>
+      <c r="AK154" s="11" t="n"/>
+    </row>
+    <row r="156" ht="19.5" customHeight="1">
+      <c r="B156" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="409" customHeight="1">
-      <c r="C153" s="19" t="inlineStr">
+    <row r="157" ht="409" customHeight="1">
+      <c r="C157" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -24016,56 +26602,60 @@
     "biko": "",
     "rireki_no": 1,
     "denshi_shonin_status": null,
+    "denshi_kaiin_id": null,
+    "honshi_kodoku_flg": false,
     "created_at": "2026-05-07T10:00:00+09:00",
-    "updated_at": "2026-05-07T10:00:00+09:00"
+    "updated_at": "2026-05-07T10:00:00+09:00",
+    "has_active_kaiyaku": false,
+    "max_joho_date": null
   }
 }</t>
         </is>
       </c>
-      <c r="D153" s="10" t="n"/>
-      <c r="E153" s="10" t="n"/>
-      <c r="F153" s="10" t="n"/>
-      <c r="G153" s="10" t="n"/>
-      <c r="H153" s="10" t="n"/>
-      <c r="I153" s="10" t="n"/>
-      <c r="J153" s="10" t="n"/>
-      <c r="K153" s="10" t="n"/>
-      <c r="L153" s="10" t="n"/>
-      <c r="M153" s="10" t="n"/>
-      <c r="N153" s="10" t="n"/>
-      <c r="O153" s="10" t="n"/>
-      <c r="P153" s="10" t="n"/>
-      <c r="Q153" s="10" t="n"/>
-      <c r="R153" s="10" t="n"/>
-      <c r="S153" s="10" t="n"/>
-      <c r="T153" s="10" t="n"/>
-      <c r="U153" s="10" t="n"/>
-      <c r="V153" s="10" t="n"/>
-      <c r="W153" s="10" t="n"/>
-      <c r="X153" s="10" t="n"/>
-      <c r="Y153" s="10" t="n"/>
-      <c r="Z153" s="10" t="n"/>
-      <c r="AA153" s="10" t="n"/>
-      <c r="AB153" s="10" t="n"/>
-      <c r="AC153" s="10" t="n"/>
-      <c r="AD153" s="10" t="n"/>
-      <c r="AE153" s="10" t="n"/>
-      <c r="AF153" s="10" t="n"/>
-      <c r="AG153" s="10" t="n"/>
-      <c r="AH153" s="10" t="n"/>
-      <c r="AI153" s="10" t="n"/>
-      <c r="AJ153" s="10" t="n"/>
-      <c r="AK153" s="11" t="n"/>
-    </row>
-    <row r="155" ht="19.5" customHeight="1">
-      <c r="B155" s="40" t="inlineStr">
+      <c r="D157" s="10" t="n"/>
+      <c r="E157" s="10" t="n"/>
+      <c r="F157" s="10" t="n"/>
+      <c r="G157" s="10" t="n"/>
+      <c r="H157" s="10" t="n"/>
+      <c r="I157" s="10" t="n"/>
+      <c r="J157" s="10" t="n"/>
+      <c r="K157" s="10" t="n"/>
+      <c r="L157" s="10" t="n"/>
+      <c r="M157" s="10" t="n"/>
+      <c r="N157" s="10" t="n"/>
+      <c r="O157" s="10" t="n"/>
+      <c r="P157" s="10" t="n"/>
+      <c r="Q157" s="10" t="n"/>
+      <c r="R157" s="10" t="n"/>
+      <c r="S157" s="10" t="n"/>
+      <c r="T157" s="10" t="n"/>
+      <c r="U157" s="10" t="n"/>
+      <c r="V157" s="10" t="n"/>
+      <c r="W157" s="10" t="n"/>
+      <c r="X157" s="10" t="n"/>
+      <c r="Y157" s="10" t="n"/>
+      <c r="Z157" s="10" t="n"/>
+      <c r="AA157" s="10" t="n"/>
+      <c r="AB157" s="10" t="n"/>
+      <c r="AC157" s="10" t="n"/>
+      <c r="AD157" s="10" t="n"/>
+      <c r="AE157" s="10" t="n"/>
+      <c r="AF157" s="10" t="n"/>
+      <c r="AG157" s="10" t="n"/>
+      <c r="AH157" s="10" t="n"/>
+      <c r="AI157" s="10" t="n"/>
+      <c r="AJ157" s="10" t="n"/>
+      <c r="AK157" s="11" t="n"/>
+    </row>
+    <row r="159" ht="19.5" customHeight="1">
+      <c r="B159" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request（バリデーションエラー））</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="144" customHeight="1">
-      <c r="C156" s="19" t="inlineStr">
+    <row r="160" ht="144" customHeight="1">
+      <c r="C160" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -24077,50 +26667,50 @@
 }</t>
         </is>
       </c>
-      <c r="D156" s="10" t="n"/>
-      <c r="E156" s="10" t="n"/>
-      <c r="F156" s="10" t="n"/>
-      <c r="G156" s="10" t="n"/>
-      <c r="H156" s="10" t="n"/>
-      <c r="I156" s="10" t="n"/>
-      <c r="J156" s="10" t="n"/>
-      <c r="K156" s="10" t="n"/>
-      <c r="L156" s="10" t="n"/>
-      <c r="M156" s="10" t="n"/>
-      <c r="N156" s="10" t="n"/>
-      <c r="O156" s="10" t="n"/>
-      <c r="P156" s="10" t="n"/>
-      <c r="Q156" s="10" t="n"/>
-      <c r="R156" s="10" t="n"/>
-      <c r="S156" s="10" t="n"/>
-      <c r="T156" s="10" t="n"/>
-      <c r="U156" s="10" t="n"/>
-      <c r="V156" s="10" t="n"/>
-      <c r="W156" s="10" t="n"/>
-      <c r="X156" s="10" t="n"/>
-      <c r="Y156" s="10" t="n"/>
-      <c r="Z156" s="10" t="n"/>
-      <c r="AA156" s="10" t="n"/>
-      <c r="AB156" s="10" t="n"/>
-      <c r="AC156" s="10" t="n"/>
-      <c r="AD156" s="10" t="n"/>
-      <c r="AE156" s="10" t="n"/>
-      <c r="AF156" s="10" t="n"/>
-      <c r="AG156" s="10" t="n"/>
-      <c r="AH156" s="10" t="n"/>
-      <c r="AI156" s="10" t="n"/>
-      <c r="AJ156" s="10" t="n"/>
-      <c r="AK156" s="11" t="n"/>
-    </row>
-    <row r="158" ht="19.5" customHeight="1">
-      <c r="B158" s="40" t="inlineStr">
+      <c r="D160" s="10" t="n"/>
+      <c r="E160" s="10" t="n"/>
+      <c r="F160" s="10" t="n"/>
+      <c r="G160" s="10" t="n"/>
+      <c r="H160" s="10" t="n"/>
+      <c r="I160" s="10" t="n"/>
+      <c r="J160" s="10" t="n"/>
+      <c r="K160" s="10" t="n"/>
+      <c r="L160" s="10" t="n"/>
+      <c r="M160" s="10" t="n"/>
+      <c r="N160" s="10" t="n"/>
+      <c r="O160" s="10" t="n"/>
+      <c r="P160" s="10" t="n"/>
+      <c r="Q160" s="10" t="n"/>
+      <c r="R160" s="10" t="n"/>
+      <c r="S160" s="10" t="n"/>
+      <c r="T160" s="10" t="n"/>
+      <c r="U160" s="10" t="n"/>
+      <c r="V160" s="10" t="n"/>
+      <c r="W160" s="10" t="n"/>
+      <c r="X160" s="10" t="n"/>
+      <c r="Y160" s="10" t="n"/>
+      <c r="Z160" s="10" t="n"/>
+      <c r="AA160" s="10" t="n"/>
+      <c r="AB160" s="10" t="n"/>
+      <c r="AC160" s="10" t="n"/>
+      <c r="AD160" s="10" t="n"/>
+      <c r="AE160" s="10" t="n"/>
+      <c r="AF160" s="10" t="n"/>
+      <c r="AG160" s="10" t="n"/>
+      <c r="AH160" s="10" t="n"/>
+      <c r="AI160" s="10" t="n"/>
+      <c r="AJ160" s="10" t="n"/>
+      <c r="AK160" s="11" t="n"/>
+    </row>
+    <row r="162" ht="19.5" customHeight="1">
+      <c r="B162" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request（メールアドレス重複））</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="72" customHeight="1">
-      <c r="C159" s="19" t="inlineStr">
+    <row r="163" ht="72" customHeight="1">
+      <c r="C163" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "DUPLICATE_EMAIL",
@@ -24128,50 +26718,50 @@
 }</t>
         </is>
       </c>
-      <c r="D159" s="10" t="n"/>
-      <c r="E159" s="10" t="n"/>
-      <c r="F159" s="10" t="n"/>
-      <c r="G159" s="10" t="n"/>
-      <c r="H159" s="10" t="n"/>
-      <c r="I159" s="10" t="n"/>
-      <c r="J159" s="10" t="n"/>
-      <c r="K159" s="10" t="n"/>
-      <c r="L159" s="10" t="n"/>
-      <c r="M159" s="10" t="n"/>
-      <c r="N159" s="10" t="n"/>
-      <c r="O159" s="10" t="n"/>
-      <c r="P159" s="10" t="n"/>
-      <c r="Q159" s="10" t="n"/>
-      <c r="R159" s="10" t="n"/>
-      <c r="S159" s="10" t="n"/>
-      <c r="T159" s="10" t="n"/>
-      <c r="U159" s="10" t="n"/>
-      <c r="V159" s="10" t="n"/>
-      <c r="W159" s="10" t="n"/>
-      <c r="X159" s="10" t="n"/>
-      <c r="Y159" s="10" t="n"/>
-      <c r="Z159" s="10" t="n"/>
-      <c r="AA159" s="10" t="n"/>
-      <c r="AB159" s="10" t="n"/>
-      <c r="AC159" s="10" t="n"/>
-      <c r="AD159" s="10" t="n"/>
-      <c r="AE159" s="10" t="n"/>
-      <c r="AF159" s="10" t="n"/>
-      <c r="AG159" s="10" t="n"/>
-      <c r="AH159" s="10" t="n"/>
-      <c r="AI159" s="10" t="n"/>
-      <c r="AJ159" s="10" t="n"/>
-      <c r="AK159" s="11" t="n"/>
-    </row>
-    <row r="161" ht="19.5" customHeight="1">
-      <c r="B161" s="40" t="inlineStr">
+      <c r="D163" s="10" t="n"/>
+      <c r="E163" s="10" t="n"/>
+      <c r="F163" s="10" t="n"/>
+      <c r="G163" s="10" t="n"/>
+      <c r="H163" s="10" t="n"/>
+      <c r="I163" s="10" t="n"/>
+      <c r="J163" s="10" t="n"/>
+      <c r="K163" s="10" t="n"/>
+      <c r="L163" s="10" t="n"/>
+      <c r="M163" s="10" t="n"/>
+      <c r="N163" s="10" t="n"/>
+      <c r="O163" s="10" t="n"/>
+      <c r="P163" s="10" t="n"/>
+      <c r="Q163" s="10" t="n"/>
+      <c r="R163" s="10" t="n"/>
+      <c r="S163" s="10" t="n"/>
+      <c r="T163" s="10" t="n"/>
+      <c r="U163" s="10" t="n"/>
+      <c r="V163" s="10" t="n"/>
+      <c r="W163" s="10" t="n"/>
+      <c r="X163" s="10" t="n"/>
+      <c r="Y163" s="10" t="n"/>
+      <c r="Z163" s="10" t="n"/>
+      <c r="AA163" s="10" t="n"/>
+      <c r="AB163" s="10" t="n"/>
+      <c r="AC163" s="10" t="n"/>
+      <c r="AD163" s="10" t="n"/>
+      <c r="AE163" s="10" t="n"/>
+      <c r="AF163" s="10" t="n"/>
+      <c r="AG163" s="10" t="n"/>
+      <c r="AH163" s="10" t="n"/>
+      <c r="AI163" s="10" t="n"/>
+      <c r="AJ163" s="10" t="n"/>
+      <c r="AK163" s="11" t="n"/>
+    </row>
+    <row r="165" ht="19.5" customHeight="1">
+      <c r="B165" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="72" customHeight="1">
-      <c r="C162" s="19" t="inlineStr">
+    <row r="166" ht="72" customHeight="1">
+      <c r="C166" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -24179,50 +26769,50 @@
 }</t>
         </is>
       </c>
-      <c r="D162" s="10" t="n"/>
-      <c r="E162" s="10" t="n"/>
-      <c r="F162" s="10" t="n"/>
-      <c r="G162" s="10" t="n"/>
-      <c r="H162" s="10" t="n"/>
-      <c r="I162" s="10" t="n"/>
-      <c r="J162" s="10" t="n"/>
-      <c r="K162" s="10" t="n"/>
-      <c r="L162" s="10" t="n"/>
-      <c r="M162" s="10" t="n"/>
-      <c r="N162" s="10" t="n"/>
-      <c r="O162" s="10" t="n"/>
-      <c r="P162" s="10" t="n"/>
-      <c r="Q162" s="10" t="n"/>
-      <c r="R162" s="10" t="n"/>
-      <c r="S162" s="10" t="n"/>
-      <c r="T162" s="10" t="n"/>
-      <c r="U162" s="10" t="n"/>
-      <c r="V162" s="10" t="n"/>
-      <c r="W162" s="10" t="n"/>
-      <c r="X162" s="10" t="n"/>
-      <c r="Y162" s="10" t="n"/>
-      <c r="Z162" s="10" t="n"/>
-      <c r="AA162" s="10" t="n"/>
-      <c r="AB162" s="10" t="n"/>
-      <c r="AC162" s="10" t="n"/>
-      <c r="AD162" s="10" t="n"/>
-      <c r="AE162" s="10" t="n"/>
-      <c r="AF162" s="10" t="n"/>
-      <c r="AG162" s="10" t="n"/>
-      <c r="AH162" s="10" t="n"/>
-      <c r="AI162" s="10" t="n"/>
-      <c r="AJ162" s="10" t="n"/>
-      <c r="AK162" s="11" t="n"/>
-    </row>
-    <row r="164" ht="19.5" customHeight="1">
-      <c r="B164" s="40" t="inlineStr">
+      <c r="D166" s="10" t="n"/>
+      <c r="E166" s="10" t="n"/>
+      <c r="F166" s="10" t="n"/>
+      <c r="G166" s="10" t="n"/>
+      <c r="H166" s="10" t="n"/>
+      <c r="I166" s="10" t="n"/>
+      <c r="J166" s="10" t="n"/>
+      <c r="K166" s="10" t="n"/>
+      <c r="L166" s="10" t="n"/>
+      <c r="M166" s="10" t="n"/>
+      <c r="N166" s="10" t="n"/>
+      <c r="O166" s="10" t="n"/>
+      <c r="P166" s="10" t="n"/>
+      <c r="Q166" s="10" t="n"/>
+      <c r="R166" s="10" t="n"/>
+      <c r="S166" s="10" t="n"/>
+      <c r="T166" s="10" t="n"/>
+      <c r="U166" s="10" t="n"/>
+      <c r="V166" s="10" t="n"/>
+      <c r="W166" s="10" t="n"/>
+      <c r="X166" s="10" t="n"/>
+      <c r="Y166" s="10" t="n"/>
+      <c r="Z166" s="10" t="n"/>
+      <c r="AA166" s="10" t="n"/>
+      <c r="AB166" s="10" t="n"/>
+      <c r="AC166" s="10" t="n"/>
+      <c r="AD166" s="10" t="n"/>
+      <c r="AE166" s="10" t="n"/>
+      <c r="AF166" s="10" t="n"/>
+      <c r="AG166" s="10" t="n"/>
+      <c r="AH166" s="10" t="n"/>
+      <c r="AI166" s="10" t="n"/>
+      <c r="AJ166" s="10" t="n"/>
+      <c r="AK166" s="11" t="n"/>
+    </row>
+    <row r="168" ht="19.5" customHeight="1">
+      <c r="B168" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="72" customHeight="1">
-      <c r="C165" s="19" t="inlineStr">
+    <row r="169" ht="72" customHeight="1">
+      <c r="C169" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -24230,50 +26820,50 @@
 }</t>
         </is>
       </c>
-      <c r="D165" s="10" t="n"/>
-      <c r="E165" s="10" t="n"/>
-      <c r="F165" s="10" t="n"/>
-      <c r="G165" s="10" t="n"/>
-      <c r="H165" s="10" t="n"/>
-      <c r="I165" s="10" t="n"/>
-      <c r="J165" s="10" t="n"/>
-      <c r="K165" s="10" t="n"/>
-      <c r="L165" s="10" t="n"/>
-      <c r="M165" s="10" t="n"/>
-      <c r="N165" s="10" t="n"/>
-      <c r="O165" s="10" t="n"/>
-      <c r="P165" s="10" t="n"/>
-      <c r="Q165" s="10" t="n"/>
-      <c r="R165" s="10" t="n"/>
-      <c r="S165" s="10" t="n"/>
-      <c r="T165" s="10" t="n"/>
-      <c r="U165" s="10" t="n"/>
-      <c r="V165" s="10" t="n"/>
-      <c r="W165" s="10" t="n"/>
-      <c r="X165" s="10" t="n"/>
-      <c r="Y165" s="10" t="n"/>
-      <c r="Z165" s="10" t="n"/>
-      <c r="AA165" s="10" t="n"/>
-      <c r="AB165" s="10" t="n"/>
-      <c r="AC165" s="10" t="n"/>
-      <c r="AD165" s="10" t="n"/>
-      <c r="AE165" s="10" t="n"/>
-      <c r="AF165" s="10" t="n"/>
-      <c r="AG165" s="10" t="n"/>
-      <c r="AH165" s="10" t="n"/>
-      <c r="AI165" s="10" t="n"/>
-      <c r="AJ165" s="10" t="n"/>
-      <c r="AK165" s="11" t="n"/>
-    </row>
-    <row r="167" ht="19.5" customHeight="1">
-      <c r="B167" s="40" t="inlineStr">
+      <c r="D169" s="10" t="n"/>
+      <c r="E169" s="10" t="n"/>
+      <c r="F169" s="10" t="n"/>
+      <c r="G169" s="10" t="n"/>
+      <c r="H169" s="10" t="n"/>
+      <c r="I169" s="10" t="n"/>
+      <c r="J169" s="10" t="n"/>
+      <c r="K169" s="10" t="n"/>
+      <c r="L169" s="10" t="n"/>
+      <c r="M169" s="10" t="n"/>
+      <c r="N169" s="10" t="n"/>
+      <c r="O169" s="10" t="n"/>
+      <c r="P169" s="10" t="n"/>
+      <c r="Q169" s="10" t="n"/>
+      <c r="R169" s="10" t="n"/>
+      <c r="S169" s="10" t="n"/>
+      <c r="T169" s="10" t="n"/>
+      <c r="U169" s="10" t="n"/>
+      <c r="V169" s="10" t="n"/>
+      <c r="W169" s="10" t="n"/>
+      <c r="X169" s="10" t="n"/>
+      <c r="Y169" s="10" t="n"/>
+      <c r="Z169" s="10" t="n"/>
+      <c r="AA169" s="10" t="n"/>
+      <c r="AB169" s="10" t="n"/>
+      <c r="AC169" s="10" t="n"/>
+      <c r="AD169" s="10" t="n"/>
+      <c r="AE169" s="10" t="n"/>
+      <c r="AF169" s="10" t="n"/>
+      <c r="AG169" s="10" t="n"/>
+      <c r="AH169" s="10" t="n"/>
+      <c r="AI169" s="10" t="n"/>
+      <c r="AJ169" s="10" t="n"/>
+      <c r="AK169" s="11" t="n"/>
+    </row>
+    <row r="171" ht="19.5" customHeight="1">
+      <c r="B171" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="72" customHeight="1">
-      <c r="C168" s="19" t="inlineStr">
+    <row r="172" ht="72" customHeight="1">
+      <c r="C172" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -24281,58 +26871,6 @@
 }</t>
         </is>
       </c>
-      <c r="D168" s="10" t="n"/>
-      <c r="E168" s="10" t="n"/>
-      <c r="F168" s="10" t="n"/>
-      <c r="G168" s="10" t="n"/>
-      <c r="H168" s="10" t="n"/>
-      <c r="I168" s="10" t="n"/>
-      <c r="J168" s="10" t="n"/>
-      <c r="K168" s="10" t="n"/>
-      <c r="L168" s="10" t="n"/>
-      <c r="M168" s="10" t="n"/>
-      <c r="N168" s="10" t="n"/>
-      <c r="O168" s="10" t="n"/>
-      <c r="P168" s="10" t="n"/>
-      <c r="Q168" s="10" t="n"/>
-      <c r="R168" s="10" t="n"/>
-      <c r="S168" s="10" t="n"/>
-      <c r="T168" s="10" t="n"/>
-      <c r="U168" s="10" t="n"/>
-      <c r="V168" s="10" t="n"/>
-      <c r="W168" s="10" t="n"/>
-      <c r="X168" s="10" t="n"/>
-      <c r="Y168" s="10" t="n"/>
-      <c r="Z168" s="10" t="n"/>
-      <c r="AA168" s="10" t="n"/>
-      <c r="AB168" s="10" t="n"/>
-      <c r="AC168" s="10" t="n"/>
-      <c r="AD168" s="10" t="n"/>
-      <c r="AE168" s="10" t="n"/>
-      <c r="AF168" s="10" t="n"/>
-      <c r="AG168" s="10" t="n"/>
-      <c r="AH168" s="10" t="n"/>
-      <c r="AI168" s="10" t="n"/>
-      <c r="AJ168" s="10" t="n"/>
-      <c r="AK168" s="11" t="n"/>
-    </row>
-    <row r="170" ht="19.5" customHeight="1"/>
-    <row r="171" ht="19.5" customHeight="1">
-      <c r="A171" s="27" t="inlineStr">
-        <is>
-          <t>4. 処理手順</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="54" customHeight="1">
-      <c r="B172" s="42" t="inlineStr">
-        <is>
-          <t>※ 4.4 データ登録 と 4.5 操作ログ記録 は単一トランザクション内で実行する。
-いずれかが失敗した場合は全てロールバックすること。
-例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
-        </is>
-      </c>
-      <c r="C172" s="10" t="n"/>
       <c r="D172" s="10" t="n"/>
       <c r="E172" s="10" t="n"/>
       <c r="F172" s="10" t="n"/>
@@ -24368,260 +26906,319 @@
       <c r="AJ172" s="10" t="n"/>
       <c r="AK172" s="11" t="n"/>
     </row>
-    <row r="173" ht="18" customHeight="1">
-      <c r="B173" s="27" t="inlineStr">
+    <row r="174" ht="19.5" customHeight="1"/>
+    <row r="175" ht="19.5" customHeight="1">
+      <c r="A175" s="27" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="54" customHeight="1">
+      <c r="B176" s="42" t="inlineStr">
+        <is>
+          <t>※ 4.4 データ登録 と 4.5 操作ログ記録 は単一トランザクション内で実行する。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C176" s="10" t="n"/>
+      <c r="D176" s="10" t="n"/>
+      <c r="E176" s="10" t="n"/>
+      <c r="F176" s="10" t="n"/>
+      <c r="G176" s="10" t="n"/>
+      <c r="H176" s="10" t="n"/>
+      <c r="I176" s="10" t="n"/>
+      <c r="J176" s="10" t="n"/>
+      <c r="K176" s="10" t="n"/>
+      <c r="L176" s="10" t="n"/>
+      <c r="M176" s="10" t="n"/>
+      <c r="N176" s="10" t="n"/>
+      <c r="O176" s="10" t="n"/>
+      <c r="P176" s="10" t="n"/>
+      <c r="Q176" s="10" t="n"/>
+      <c r="R176" s="10" t="n"/>
+      <c r="S176" s="10" t="n"/>
+      <c r="T176" s="10" t="n"/>
+      <c r="U176" s="10" t="n"/>
+      <c r="V176" s="10" t="n"/>
+      <c r="W176" s="10" t="n"/>
+      <c r="X176" s="10" t="n"/>
+      <c r="Y176" s="10" t="n"/>
+      <c r="Z176" s="10" t="n"/>
+      <c r="AA176" s="10" t="n"/>
+      <c r="AB176" s="10" t="n"/>
+      <c r="AC176" s="10" t="n"/>
+      <c r="AD176" s="10" t="n"/>
+      <c r="AE176" s="10" t="n"/>
+      <c r="AF176" s="10" t="n"/>
+      <c r="AG176" s="10" t="n"/>
+      <c r="AH176" s="10" t="n"/>
+      <c r="AI176" s="10" t="n"/>
+      <c r="AJ176" s="10" t="n"/>
+      <c r="AK176" s="11" t="n"/>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="B177" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="18" customHeight="1">
-      <c r="C174" s="41" t="inlineStr">
+    <row r="178" ht="18" customHeight="1">
+      <c r="C178" s="41" t="inlineStr">
         <is>
           <t>リクエストボディの検証：</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="108" customHeight="1">
-      <c r="D175" s="41" t="inlineStr">
+    <row r="179" ht="108" customHeight="1">
+      <c r="D179" s="41" t="inlineStr">
         <is>
           <t>dokusya_shubetsu：必須。**3:併読（紙版＋電子版）は新規登録不可**（顧客要件）。併読データは外部の電子版読者管理システムがバッチ連携で管理するため、本システムでは作成・編集・停止・削除いずれも不可。作成は `VALIDATION_ERROR`（field=`dokusya_shubetsu`、メッセージ「併読（紙版＋電子版）はバッチ連携で管理されるため、新規登録できません。」）、編集/停止/削除は `DOKUSYA_READ_ONLY`（403）、Excel取込は取込不可。FEは新規作成モードで併読ラジオを非活性化。</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="72" customHeight="1">
-      <c r="D176" s="41" t="inlineStr">
+    <row r="180" ht="72" customHeight="1">
+      <c r="D180" s="41" t="inlineStr">
         <is>
           <t>shimei_sei / shimei_mei：必須、最大50文字、**漢字・ひらがな・カタカナ・アルファベット形式**（半角英字A-Za-z・全角英字Ａ-Ｚ/ａ-ｚ可、半角カナ・数字不可。顧客要件 2026-07 でひらがな/カタカナ/アルファベット表記の氏名に対応）。形式不正時は `VALIDATION_ERROR`（メッセージ「漢字・ひらがな・カタカナ・アルファベットで入力してください。」）</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="54" customHeight="1">
-      <c r="D177" s="41" t="inlineStr">
+    <row r="181" ht="54" customHeight="1">
+      <c r="D181" s="41" t="inlineStr">
         <is>
           <t>haitatsu_shimei_sei / haitatsu_shimei_mei：haitatsu_same_flg=false 時必須、shimei_sei/mei と同じ漢字・ひらがな・カタカナ・アルファベット形式</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="36" customHeight="1">
-      <c r="D178" s="41" t="inlineStr">
+    <row r="182" ht="36" customHeight="1">
+      <c r="D182" s="41" t="inlineStr">
         <is>
           <t>shimei_kana_sei / shimei_kana_mei：必須、最大100文字、ひらがな/カタカナ形式</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="D179" s="41" t="inlineStr">
-        <is>
-          <t>dokusya_busu：必須、半角数字。解約時は0</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="18" customHeight="1">
-      <c r="D180" s="41" t="inlineStr">
-        <is>
-          <t>yubin_no：必須、半角数字7桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="18" customHeight="1">
-      <c r="D181" s="41" t="inlineStr">
-        <is>
-          <t>todofuken_code / shikuchoson / chome_banchi：必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="18" customHeight="1">
-      <c r="D182" s="41" t="inlineStr">
-        <is>
-          <t>renrakusaki_1：必須、半角数字</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="D183" s="41" t="inlineStr">
         <is>
-          <t>email：電子版/併読の場合は必須、形式チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="72" customHeight="1">
+          <t>dokusya_busu：必須、半角数字。解約時は0</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="18" customHeight="1">
       <c r="D184" s="41" t="inlineStr">
         <is>
-          <t>haitatsu_same_flg=falseの場合：haitatsu_yubin_no, haitatsu_todofuken_code, haitatsu_shikuchoson, haitatsu_chome_banchi, haitatsu_shimei_*, haitatsu_shimei_kana_* が必須</t>
+          <t>yubin_no：必須、半角数字7桁</t>
         </is>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
       <c r="D185" s="41" t="inlineStr">
         <is>
-          <t>hanbaiten_id / tanka_id：必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="54" customHeight="1">
+          <t>todofuken_code / shikuchoson / chome_banchi：必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="18" customHeight="1">
       <c r="D186" s="41" t="inlineStr">
         <is>
+          <t>renrakusaki_1：必須、半角数字</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="D187" s="41" t="inlineStr">
+        <is>
+          <t>email：電子版/併読の場合は必須、形式チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="72" customHeight="1">
+      <c r="D188" s="41" t="inlineStr">
+        <is>
+          <t>haitatsu_same_flg=falseの場合：haitatsu_yubin_no, haitatsu_todofuken_code, haitatsu_shikuchoson, haitatsu_chome_banchi, haitatsu_shimei_*, haitatsu_shimei_kana_* が必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="216" customHeight="1">
+      <c r="D189" s="41" t="inlineStr">
+        <is>
+          <t>**dokusya_shubetsu=2（電子版）の場合：配達先情報12項目（haitatsu_same_flg + haitatsu_yubin_no / haitatsu_todofuken_code / haitatsu_shikuchoson / haitatsu_chome_banchi / haitatsu_tatemono_mei / haitatsu_renrakusaki_1 / haitatsu_renrakusaki_2 / haitatsu_shimei_sei / haitatsu_shimei_mei / haitatsu_shimei_kana_sei / haitatsu_shimei_kana_mei）はリクエストボディの値に関わらずサーバ側で `haitatsu_same_flg=true`・残り11列は空文字に強制する（不具合修正 2026-08）**。画面は電子版で配達先情報エリアを非活性化するが（No.27-38）、種別ラジオを紙版/併読→電子版へ切替えた直後に送信すると隠れた入力欄の値が残ったまま届き得るため、API直叩き・FEのバグ双方に対する防御的措置としてBEでも独立にゲートする。エラーにはせず値を落とすのみ（購読者層分類の従属4項目と同じ方式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="162" customHeight="1">
+      <c r="D190" s="41" t="inlineStr">
+        <is>
+          <t>hanbaiten_id / tanka_id：必須。ログインユーザー所属JA内に存在すること（テナント跨ぎは `DATA_SCOPE_VIOLATION`）。**`hanbaiten_id` が指す `m_hanbaiten.haiten_flg=true`（廃店）の場合、または `tanka_id` が指す `m_tanka.active_flg=false`（失効）の場合は `VALIDATION_ERROR`（field=`hanbaiten_id`, message=「指定された販売店は廃店のため選択できません。」／field=`tanka_id`, message=「指定された新聞単価は失効しています。」）で拒否する（不具合修正 2026-08。Excel取込 ACSMS-SCR-016 §4.3.1/4.3.2 で先に修正済みの同一ルールをUIにも適用）。新規登録は常に検証する — 編集時の据え置きルールは ACSMS-API-011-003 §4.3.2 参照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="54" customHeight="1">
+      <c r="D191" s="41" t="inlineStr">
+        <is>
           <t>shiharai_hoho：必須。1（口座引落）の場合：bank_shiten_id, hikiotoshi_yokin_shubetsu, hikiotoshi_koza_no, hikiotoshi_koza_meigi が必須</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="72" customHeight="1">
-      <c r="D187" s="41" t="inlineStr">
+    <row r="192" ht="72" customHeight="1">
+      <c r="D192" s="41" t="inlineStr">
         <is>
           <t>bank_shiten_id：口座引落時は必須、他の支払方法では任意。指定された場合は `m_shiten` に存在し、かつ ログインユーザー所属JA内（`m_shiten.ja_id = user.ja_id`）かつ `kinyu_shiten_flg = TRUE` であること（不正値は支払方法を問わず VALIDATION_ERROR）</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="36" customHeight="1">
-      <c r="D188" s="41" t="inlineStr">
+    <row r="193" ht="36" customHeight="1">
+      <c r="D193" s="41" t="inlineStr">
         <is>
           <t>yubin_kubun：任意。入力時は `m_code.code_category='YUBIN_KUBUN'`（0:空, 1:郵送）に存在する値であること</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="18" customHeight="1">
-      <c r="D189" s="41" t="inlineStr">
+    <row r="194" ht="18" customHeight="1">
+      <c r="D194" s="41" t="inlineStr">
         <is>
           <t>dokusya_kaishi_date：必須、YYYY-MM-DD</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="18" customHeight="1">
-      <c r="D190" s="41" t="inlineStr">
+    <row r="195" ht="18" customHeight="1">
+      <c r="D195" s="41" t="inlineStr">
         <is>
           <t>joho_henko_tekiyo_date：任意、YYYY-MM-DD。入力時は未来日であること</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="18" customHeight="1">
-      <c r="D191" s="41" t="inlineStr">
+    <row r="196" ht="18" customHeight="1">
+      <c r="D196" s="41" t="inlineStr">
         <is>
           <t>nogyosya_bunrui：購読者層分類で「農業者」を選択した場合は必須</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="18" customHeight="1">
-      <c r="D192" s="41" t="inlineStr">
+    <row r="197" ht="18" customHeight="1">
+      <c r="D197" s="41" t="inlineStr">
         <is>
           <t>seikyu_kaishi_month：電子版/併読の場合、YYYYMM形式</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="18" customHeight="1">
-      <c r="D193" s="41" t="inlineStr">
+    <row r="198" ht="18" customHeight="1">
+      <c r="D198" s="41" t="inlineStr">
         <is>
           <t>biko：500文字以内</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="36" customHeight="1">
-      <c r="C194" s="41" t="inlineStr">
-        <is>
-          <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="18" customHeight="1">
-      <c r="B195" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="18" customHeight="1">
-      <c r="C196" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="18" customHeight="1">
-      <c r="C197" s="41" t="inlineStr">
-        <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="18" customHeight="1">
-      <c r="C198" s="41" t="inlineStr">
-        <is>
-          <t>必要権限: `dokusya.create`</t>
         </is>
       </c>
     </row>
     <row r="199" ht="36" customHeight="1">
       <c r="C199" s="41" t="inlineStr">
         <is>
-          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+          <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
         </is>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
-      <c r="C200" s="41" t="inlineStr">
-        <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="36" customHeight="1">
+      <c r="B200" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="18" customHeight="1">
       <c r="C201" s="41" t="inlineStr">
         <is>
-          <t>DataScope: `ja_id = user.ja_id`（サーバ側で自動設定。リクエストボディの ja_id は信頼しない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="36" customHeight="1">
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="18" customHeight="1">
       <c r="C202" s="41" t="inlineStr">
         <is>
-          <t>DataScope違反（他JAのレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
-      <c r="B203" s="27" t="inlineStr">
-        <is>
-          <t>4.3 重複チェック（メールアドレス）</t>
+      <c r="C203" s="41" t="inlineStr">
+        <is>
+          <t>必要権限: `dokusya.create`</t>
         </is>
       </c>
     </row>
     <row r="204" ht="36" customHeight="1">
       <c r="C204" s="41" t="inlineStr">
         <is>
-          <t>メールアドレスが入力されており、かつ購読種別が電子版(2)・併読(3) の場合、以下の条件で重複を確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="36" customHeight="1">
+          <t>該当権限保持ロール: CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="18" customHeight="1">
       <c r="C205" s="41" t="inlineStr">
         <is>
-          <t>**JA を跨いで全件**を対象とする（顧客要件 2026-08 / #56568）。電子版ではメールアドレスが</t>
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="206" ht="36" customHeight="1">
       <c r="C206" s="41" t="inlineStr">
         <is>
-          <t>紙版(1)は必須でも一意でもないため対象外。既存行側も `dokusya_shubetsu IN (2,3)` に絞るので、</t>
+          <t>DataScope: `ja_id = user.ja_id`（サーバ側で自動設定。リクエストボディの ja_id は信頼しない）</t>
         </is>
       </c>
     </row>
     <row r="207" ht="36" customHeight="1">
       <c r="C207" s="41" t="inlineStr">
         <is>
+          <t>DataScope違反（他JAのレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="18" customHeight="1">
+      <c r="B208" s="27" t="inlineStr">
+        <is>
+          <t>4.3 重複チェック（メールアドレス）</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="36" customHeight="1">
+      <c r="C209" s="41" t="inlineStr">
+        <is>
+          <t>メールアドレスが入力されており、かつ購読種別が電子版(2)・併読(3) の場合、以下の条件で重複を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="36" customHeight="1">
+      <c r="C210" s="41" t="inlineStr">
+        <is>
+          <t>**JA を跨いで全件**を対象とする（顧客要件 2026-08 / #56568）。電子版ではメールアドレスが</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="36" customHeight="1">
+      <c r="C211" s="41" t="inlineStr">
+        <is>
+          <t>紙版(1)は必須でも一意でもないため対象外。既存行側も `dokusya_shubetsu IN (2,3)` に絞るので、</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="36" customHeight="1">
+      <c r="C212" s="41" t="inlineStr">
+        <is>
           <t>論理削除済み（`deleted_at IS NOT NULL`）は対象外 — 削除済みのメールは再利用できる。</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="18" customHeight="1">
-      <c r="C208" s="41" t="inlineStr">
+    <row r="213" ht="18" customHeight="1">
+      <c r="C213" s="41" t="inlineStr">
         <is>
           <t>更新時は自身の行を除外する（`dokusya_id &lt;&gt; :dokusya_id`）。</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="126" customHeight="1">
-      <c r="C209" s="42" t="inlineStr">
+    <row r="214" ht="126" customHeight="1">
+      <c r="C214" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) FROM t_dokusya
 WHERE email = :email
@@ -24632,85 +27229,85 @@
   AND dokusya_id &lt;&gt; :dokusya_id</t>
         </is>
       </c>
-      <c r="D209" s="10" t="n"/>
-      <c r="E209" s="10" t="n"/>
-      <c r="F209" s="10" t="n"/>
-      <c r="G209" s="10" t="n"/>
-      <c r="H209" s="10" t="n"/>
-      <c r="I209" s="10" t="n"/>
-      <c r="J209" s="10" t="n"/>
-      <c r="K209" s="10" t="n"/>
-      <c r="L209" s="10" t="n"/>
-      <c r="M209" s="10" t="n"/>
-      <c r="N209" s="10" t="n"/>
-      <c r="O209" s="10" t="n"/>
-      <c r="P209" s="10" t="n"/>
-      <c r="Q209" s="10" t="n"/>
-      <c r="R209" s="10" t="n"/>
-      <c r="S209" s="10" t="n"/>
-      <c r="T209" s="10" t="n"/>
-      <c r="U209" s="10" t="n"/>
-      <c r="V209" s="10" t="n"/>
-      <c r="W209" s="10" t="n"/>
-      <c r="X209" s="10" t="n"/>
-      <c r="Y209" s="10" t="n"/>
-      <c r="Z209" s="10" t="n"/>
-      <c r="AA209" s="10" t="n"/>
-      <c r="AB209" s="10" t="n"/>
-      <c r="AC209" s="10" t="n"/>
-      <c r="AD209" s="10" t="n"/>
-      <c r="AE209" s="10" t="n"/>
-      <c r="AF209" s="10" t="n"/>
-      <c r="AG209" s="10" t="n"/>
-      <c r="AH209" s="10" t="n"/>
-      <c r="AI209" s="10" t="n"/>
-      <c r="AJ209" s="10" t="n"/>
-      <c r="AK209" s="11" t="n"/>
-    </row>
-    <row r="210" ht="36" customHeight="1">
-      <c r="C210" s="41" t="inlineStr">
+      <c r="D214" s="10" t="n"/>
+      <c r="E214" s="10" t="n"/>
+      <c r="F214" s="10" t="n"/>
+      <c r="G214" s="10" t="n"/>
+      <c r="H214" s="10" t="n"/>
+      <c r="I214" s="10" t="n"/>
+      <c r="J214" s="10" t="n"/>
+      <c r="K214" s="10" t="n"/>
+      <c r="L214" s="10" t="n"/>
+      <c r="M214" s="10" t="n"/>
+      <c r="N214" s="10" t="n"/>
+      <c r="O214" s="10" t="n"/>
+      <c r="P214" s="10" t="n"/>
+      <c r="Q214" s="10" t="n"/>
+      <c r="R214" s="10" t="n"/>
+      <c r="S214" s="10" t="n"/>
+      <c r="T214" s="10" t="n"/>
+      <c r="U214" s="10" t="n"/>
+      <c r="V214" s="10" t="n"/>
+      <c r="W214" s="10" t="n"/>
+      <c r="X214" s="10" t="n"/>
+      <c r="Y214" s="10" t="n"/>
+      <c r="Z214" s="10" t="n"/>
+      <c r="AA214" s="10" t="n"/>
+      <c r="AB214" s="10" t="n"/>
+      <c r="AC214" s="10" t="n"/>
+      <c r="AD214" s="10" t="n"/>
+      <c r="AE214" s="10" t="n"/>
+      <c r="AF214" s="10" t="n"/>
+      <c r="AG214" s="10" t="n"/>
+      <c r="AH214" s="10" t="n"/>
+      <c r="AI214" s="10" t="n"/>
+      <c r="AJ214" s="10" t="n"/>
+      <c r="AK214" s="11" t="n"/>
+    </row>
+    <row r="215" ht="36" customHeight="1">
+      <c r="C215" s="41" t="inlineStr">
         <is>
           <t>重複がある場合：HTTP 400 (`DUPLICATE_EMAIL`) — `このメールアドレスは既に登録されています。`</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="18" customHeight="1">
-      <c r="B211" s="27" t="inlineStr">
+    <row r="216" ht="18" customHeight="1">
+      <c r="B216" s="27" t="inlineStr">
         <is>
           <t>4.4 データ登録</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="18" customHeight="1">
-      <c r="C212" s="41" t="inlineStr">
+    <row r="217" ht="18" customHeight="1">
+      <c r="C217" s="41" t="inlineStr">
         <is>
           <t>`denshi_shonin_status`（電子申込承認ステータス）の初期値:</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="18" customHeight="1">
-      <c r="D213" s="41" t="inlineStr">
+    <row r="218" ht="18" customHeight="1">
+      <c r="D218" s="41" t="inlineStr">
         <is>
           <t>紙版（dokusya_shubetsu=1）: `NULL`（承認ワークフロー対象外）。</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="18" customHeight="1">
-      <c r="D214" s="41" t="inlineStr">
+    <row r="219" ht="18" customHeight="1">
+      <c r="D219" s="41" t="inlineStr">
         <is>
           <t>電子版（2）/ 併読（3）: `1`（承認済）。画面からの新規登録は職員操作のため</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="72" customHeight="1">
-      <c r="C215" s="41" t="inlineStr">
+    <row r="220" ht="72" customHeight="1">
+      <c r="C220" s="41" t="inlineStr">
         <is>
           <t>支払方法=1（口座引落）の場合、`bank_shiten_id` を以下のSQLで解決し、`jastem_toriatsukai_tenpo_code` および `jastem_tenpo_name` を取得して `t_dokusya.bank_branch_code` / `bank_branch_name` に非正規化保存する（画面設計書 機能定義 §10.1）。</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="144" customHeight="1">
-      <c r="C216" s="42" t="inlineStr">
+    <row r="221" ht="144" customHeight="1">
+      <c r="C221" s="42" t="inlineStr">
         <is>
           <t>SELECT shiten_id,
        jastem_toriatsukai_tenpo_code,
@@ -24722,113 +27319,113 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D216" s="10" t="n"/>
-      <c r="E216" s="10" t="n"/>
-      <c r="F216" s="10" t="n"/>
-      <c r="G216" s="10" t="n"/>
-      <c r="H216" s="10" t="n"/>
-      <c r="I216" s="10" t="n"/>
-      <c r="J216" s="10" t="n"/>
-      <c r="K216" s="10" t="n"/>
-      <c r="L216" s="10" t="n"/>
-      <c r="M216" s="10" t="n"/>
-      <c r="N216" s="10" t="n"/>
-      <c r="O216" s="10" t="n"/>
-      <c r="P216" s="10" t="n"/>
-      <c r="Q216" s="10" t="n"/>
-      <c r="R216" s="10" t="n"/>
-      <c r="S216" s="10" t="n"/>
-      <c r="T216" s="10" t="n"/>
-      <c r="U216" s="10" t="n"/>
-      <c r="V216" s="10" t="n"/>
-      <c r="W216" s="10" t="n"/>
-      <c r="X216" s="10" t="n"/>
-      <c r="Y216" s="10" t="n"/>
-      <c r="Z216" s="10" t="n"/>
-      <c r="AA216" s="10" t="n"/>
-      <c r="AB216" s="10" t="n"/>
-      <c r="AC216" s="10" t="n"/>
-      <c r="AD216" s="10" t="n"/>
-      <c r="AE216" s="10" t="n"/>
-      <c r="AF216" s="10" t="n"/>
-      <c r="AG216" s="10" t="n"/>
-      <c r="AH216" s="10" t="n"/>
-      <c r="AI216" s="10" t="n"/>
-      <c r="AJ216" s="10" t="n"/>
-      <c r="AK216" s="11" t="n"/>
-    </row>
-    <row r="217" ht="36" customHeight="1">
-      <c r="C217" s="41" t="inlineStr">
+      <c r="D221" s="10" t="n"/>
+      <c r="E221" s="10" t="n"/>
+      <c r="F221" s="10" t="n"/>
+      <c r="G221" s="10" t="n"/>
+      <c r="H221" s="10" t="n"/>
+      <c r="I221" s="10" t="n"/>
+      <c r="J221" s="10" t="n"/>
+      <c r="K221" s="10" t="n"/>
+      <c r="L221" s="10" t="n"/>
+      <c r="M221" s="10" t="n"/>
+      <c r="N221" s="10" t="n"/>
+      <c r="O221" s="10" t="n"/>
+      <c r="P221" s="10" t="n"/>
+      <c r="Q221" s="10" t="n"/>
+      <c r="R221" s="10" t="n"/>
+      <c r="S221" s="10" t="n"/>
+      <c r="T221" s="10" t="n"/>
+      <c r="U221" s="10" t="n"/>
+      <c r="V221" s="10" t="n"/>
+      <c r="W221" s="10" t="n"/>
+      <c r="X221" s="10" t="n"/>
+      <c r="Y221" s="10" t="n"/>
+      <c r="Z221" s="10" t="n"/>
+      <c r="AA221" s="10" t="n"/>
+      <c r="AB221" s="10" t="n"/>
+      <c r="AC221" s="10" t="n"/>
+      <c r="AD221" s="10" t="n"/>
+      <c r="AE221" s="10" t="n"/>
+      <c r="AF221" s="10" t="n"/>
+      <c r="AG221" s="10" t="n"/>
+      <c r="AH221" s="10" t="n"/>
+      <c r="AI221" s="10" t="n"/>
+      <c r="AJ221" s="10" t="n"/>
+      <c r="AK221" s="11" t="n"/>
+    </row>
+    <row r="222" ht="36" customHeight="1">
+      <c r="C222" s="41" t="inlineStr">
         <is>
           <t>該当レコードがない場合：HTTP 400 (`VALIDATION_ERROR`)（`field: 'bank_shiten_id'`）。</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="36" customHeight="1">
-      <c r="C218" s="41" t="inlineStr">
+    <row r="223" ht="36" customHeight="1">
+      <c r="C223" s="41" t="inlineStr">
         <is>
           <t>支払方法 ≠ 1 の場合、`bank_branch_code = ''` / `bank_branch_name = ''` を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="18" customHeight="1">
-      <c r="C219" s="41" t="inlineStr">
+    <row r="224" ht="18" customHeight="1">
+      <c r="C224" s="41" t="inlineStr">
         <is>
           <t>t_dokusya にレコードを INSERT する。</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="36" customHeight="1">
-      <c r="C220" s="41" t="inlineStr">
+    <row r="225" ht="36" customHeight="1">
+      <c r="C225" s="41" t="inlineStr">
         <is>
           <t>t_dokusya_rireki に履歴レコードを INSERT する（rireki_no=1, saishin_data_flg=true）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="18" customHeight="1">
-      <c r="C221" s="41" t="inlineStr">
-        <is>
-          <t>フラグ設定ルール：</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="18" customHeight="1">
-      <c r="D222" s="41" t="inlineStr">
-        <is>
-          <t>saishin_data_flg = true</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="18" customHeight="1">
-      <c r="D223" s="41" t="inlineStr">
-        <is>
-          <t>shinki_flg = (tetsuzuki_shurui=1) ? true : false</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="18" customHeight="1">
-      <c r="D224" s="41" t="inlineStr">
-        <is>
-          <t>kaiyaku_flg = (tetsuzuki_shurui=0) ? true : false</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="18" customHeight="1">
-      <c r="D225" s="41" t="inlineStr">
-        <is>
-          <t>zougen_hokoku_flg = true（新規登録は増減対象）</t>
         </is>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="C226" s="41" t="inlineStr">
         <is>
+          <t>フラグ設定ルール：</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="18" customHeight="1">
+      <c r="D227" s="41" t="inlineStr">
+        <is>
+          <t>saishin_data_flg = true</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="D228" s="41" t="inlineStr">
+        <is>
+          <t>shinki_flg = (tetsuzuki_shurui=1) ? true : false</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="D229" s="41" t="inlineStr">
+        <is>
+          <t>kaiyaku_flg = (tetsuzuki_shurui=0) ? true : false</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="18" customHeight="1">
+      <c r="D230" s="41" t="inlineStr">
+        <is>
+          <t>zougen_hokoku_flg = true（新規登録は増減対象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="18" customHeight="1">
+      <c r="C231" s="41" t="inlineStr">
+        <is>
           <t>解約時は dokusya_busu=0 を強制する。</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="409" customHeight="1">
-      <c r="C227" s="42" t="inlineStr">
+    <row r="232" ht="409" customHeight="1">
+      <c r="C232" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya (
   ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -24874,43 +27471,43 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D227" s="10" t="n"/>
-      <c r="E227" s="10" t="n"/>
-      <c r="F227" s="10" t="n"/>
-      <c r="G227" s="10" t="n"/>
-      <c r="H227" s="10" t="n"/>
-      <c r="I227" s="10" t="n"/>
-      <c r="J227" s="10" t="n"/>
-      <c r="K227" s="10" t="n"/>
-      <c r="L227" s="10" t="n"/>
-      <c r="M227" s="10" t="n"/>
-      <c r="N227" s="10" t="n"/>
-      <c r="O227" s="10" t="n"/>
-      <c r="P227" s="10" t="n"/>
-      <c r="Q227" s="10" t="n"/>
-      <c r="R227" s="10" t="n"/>
-      <c r="S227" s="10" t="n"/>
-      <c r="T227" s="10" t="n"/>
-      <c r="U227" s="10" t="n"/>
-      <c r="V227" s="10" t="n"/>
-      <c r="W227" s="10" t="n"/>
-      <c r="X227" s="10" t="n"/>
-      <c r="Y227" s="10" t="n"/>
-      <c r="Z227" s="10" t="n"/>
-      <c r="AA227" s="10" t="n"/>
-      <c r="AB227" s="10" t="n"/>
-      <c r="AC227" s="10" t="n"/>
-      <c r="AD227" s="10" t="n"/>
-      <c r="AE227" s="10" t="n"/>
-      <c r="AF227" s="10" t="n"/>
-      <c r="AG227" s="10" t="n"/>
-      <c r="AH227" s="10" t="n"/>
-      <c r="AI227" s="10" t="n"/>
-      <c r="AJ227" s="10" t="n"/>
-      <c r="AK227" s="11" t="n"/>
-    </row>
-    <row r="228" ht="409" customHeight="1">
-      <c r="C228" s="42" t="inlineStr">
+      <c r="D232" s="10" t="n"/>
+      <c r="E232" s="10" t="n"/>
+      <c r="F232" s="10" t="n"/>
+      <c r="G232" s="10" t="n"/>
+      <c r="H232" s="10" t="n"/>
+      <c r="I232" s="10" t="n"/>
+      <c r="J232" s="10" t="n"/>
+      <c r="K232" s="10" t="n"/>
+      <c r="L232" s="10" t="n"/>
+      <c r="M232" s="10" t="n"/>
+      <c r="N232" s="10" t="n"/>
+      <c r="O232" s="10" t="n"/>
+      <c r="P232" s="10" t="n"/>
+      <c r="Q232" s="10" t="n"/>
+      <c r="R232" s="10" t="n"/>
+      <c r="S232" s="10" t="n"/>
+      <c r="T232" s="10" t="n"/>
+      <c r="U232" s="10" t="n"/>
+      <c r="V232" s="10" t="n"/>
+      <c r="W232" s="10" t="n"/>
+      <c r="X232" s="10" t="n"/>
+      <c r="Y232" s="10" t="n"/>
+      <c r="Z232" s="10" t="n"/>
+      <c r="AA232" s="10" t="n"/>
+      <c r="AB232" s="10" t="n"/>
+      <c r="AC232" s="10" t="n"/>
+      <c r="AD232" s="10" t="n"/>
+      <c r="AE232" s="10" t="n"/>
+      <c r="AF232" s="10" t="n"/>
+      <c r="AG232" s="10" t="n"/>
+      <c r="AH232" s="10" t="n"/>
+      <c r="AI232" s="10" t="n"/>
+      <c r="AJ232" s="10" t="n"/>
+      <c r="AK232" s="11" t="n"/>
+    </row>
+    <row r="233" ht="409" customHeight="1">
+      <c r="C233" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya_rireki (
   dokusya_id, rireki_no, ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -24961,57 +27558,57 @@
 )</t>
         </is>
       </c>
-      <c r="D228" s="10" t="n"/>
-      <c r="E228" s="10" t="n"/>
-      <c r="F228" s="10" t="n"/>
-      <c r="G228" s="10" t="n"/>
-      <c r="H228" s="10" t="n"/>
-      <c r="I228" s="10" t="n"/>
-      <c r="J228" s="10" t="n"/>
-      <c r="K228" s="10" t="n"/>
-      <c r="L228" s="10" t="n"/>
-      <c r="M228" s="10" t="n"/>
-      <c r="N228" s="10" t="n"/>
-      <c r="O228" s="10" t="n"/>
-      <c r="P228" s="10" t="n"/>
-      <c r="Q228" s="10" t="n"/>
-      <c r="R228" s="10" t="n"/>
-      <c r="S228" s="10" t="n"/>
-      <c r="T228" s="10" t="n"/>
-      <c r="U228" s="10" t="n"/>
-      <c r="V228" s="10" t="n"/>
-      <c r="W228" s="10" t="n"/>
-      <c r="X228" s="10" t="n"/>
-      <c r="Y228" s="10" t="n"/>
-      <c r="Z228" s="10" t="n"/>
-      <c r="AA228" s="10" t="n"/>
-      <c r="AB228" s="10" t="n"/>
-      <c r="AC228" s="10" t="n"/>
-      <c r="AD228" s="10" t="n"/>
-      <c r="AE228" s="10" t="n"/>
-      <c r="AF228" s="10" t="n"/>
-      <c r="AG228" s="10" t="n"/>
-      <c r="AH228" s="10" t="n"/>
-      <c r="AI228" s="10" t="n"/>
-      <c r="AJ228" s="10" t="n"/>
-      <c r="AK228" s="11" t="n"/>
-    </row>
-    <row r="229" ht="18" customHeight="1">
-      <c r="B229" s="27" t="inlineStr">
+      <c r="D233" s="10" t="n"/>
+      <c r="E233" s="10" t="n"/>
+      <c r="F233" s="10" t="n"/>
+      <c r="G233" s="10" t="n"/>
+      <c r="H233" s="10" t="n"/>
+      <c r="I233" s="10" t="n"/>
+      <c r="J233" s="10" t="n"/>
+      <c r="K233" s="10" t="n"/>
+      <c r="L233" s="10" t="n"/>
+      <c r="M233" s="10" t="n"/>
+      <c r="N233" s="10" t="n"/>
+      <c r="O233" s="10" t="n"/>
+      <c r="P233" s="10" t="n"/>
+      <c r="Q233" s="10" t="n"/>
+      <c r="R233" s="10" t="n"/>
+      <c r="S233" s="10" t="n"/>
+      <c r="T233" s="10" t="n"/>
+      <c r="U233" s="10" t="n"/>
+      <c r="V233" s="10" t="n"/>
+      <c r="W233" s="10" t="n"/>
+      <c r="X233" s="10" t="n"/>
+      <c r="Y233" s="10" t="n"/>
+      <c r="Z233" s="10" t="n"/>
+      <c r="AA233" s="10" t="n"/>
+      <c r="AB233" s="10" t="n"/>
+      <c r="AC233" s="10" t="n"/>
+      <c r="AD233" s="10" t="n"/>
+      <c r="AE233" s="10" t="n"/>
+      <c r="AF233" s="10" t="n"/>
+      <c r="AG233" s="10" t="n"/>
+      <c r="AH233" s="10" t="n"/>
+      <c r="AI233" s="10" t="n"/>
+      <c r="AJ233" s="10" t="n"/>
+      <c r="AK233" s="11" t="n"/>
+    </row>
+    <row r="234" ht="18" customHeight="1">
+      <c r="B234" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="230" ht="18" customHeight="1">
-      <c r="C230" s="41" t="inlineStr">
+    <row r="235" ht="18" customHeight="1">
+      <c r="C235" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="231" ht="216" customHeight="1">
-      <c r="C231" s="42" t="inlineStr">
+    <row r="236" ht="216" customHeight="1">
+      <c r="C236" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -25027,92 +27624,92 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D231" s="10" t="n"/>
-      <c r="E231" s="10" t="n"/>
-      <c r="F231" s="10" t="n"/>
-      <c r="G231" s="10" t="n"/>
-      <c r="H231" s="10" t="n"/>
-      <c r="I231" s="10" t="n"/>
-      <c r="J231" s="10" t="n"/>
-      <c r="K231" s="10" t="n"/>
-      <c r="L231" s="10" t="n"/>
-      <c r="M231" s="10" t="n"/>
-      <c r="N231" s="10" t="n"/>
-      <c r="O231" s="10" t="n"/>
-      <c r="P231" s="10" t="n"/>
-      <c r="Q231" s="10" t="n"/>
-      <c r="R231" s="10" t="n"/>
-      <c r="S231" s="10" t="n"/>
-      <c r="T231" s="10" t="n"/>
-      <c r="U231" s="10" t="n"/>
-      <c r="V231" s="10" t="n"/>
-      <c r="W231" s="10" t="n"/>
-      <c r="X231" s="10" t="n"/>
-      <c r="Y231" s="10" t="n"/>
-      <c r="Z231" s="10" t="n"/>
-      <c r="AA231" s="10" t="n"/>
-      <c r="AB231" s="10" t="n"/>
-      <c r="AC231" s="10" t="n"/>
-      <c r="AD231" s="10" t="n"/>
-      <c r="AE231" s="10" t="n"/>
-      <c r="AF231" s="10" t="n"/>
-      <c r="AG231" s="10" t="n"/>
-      <c r="AH231" s="10" t="n"/>
-      <c r="AI231" s="10" t="n"/>
-      <c r="AJ231" s="10" t="n"/>
-      <c r="AK231" s="11" t="n"/>
-    </row>
-    <row r="232" ht="18" customHeight="1">
-      <c r="C232" s="41" t="inlineStr">
-        <is>
-          <t>`before_value`：INSERT のため空文字列を設定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="36" customHeight="1">
-      <c r="C233" s="41" t="inlineStr">
-        <is>
-          <t>`after_value`：登録されたデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="18" customHeight="1">
-      <c r="B234" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="18" customHeight="1">
-      <c r="C235" s="41" t="inlineStr">
-        <is>
-          <t>登録されたデータを data オブジェクトとして返却する。HTTP 201。</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="18" customHeight="1">
-      <c r="B236" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
-        </is>
-      </c>
+      <c r="D236" s="10" t="n"/>
+      <c r="E236" s="10" t="n"/>
+      <c r="F236" s="10" t="n"/>
+      <c r="G236" s="10" t="n"/>
+      <c r="H236" s="10" t="n"/>
+      <c r="I236" s="10" t="n"/>
+      <c r="J236" s="10" t="n"/>
+      <c r="K236" s="10" t="n"/>
+      <c r="L236" s="10" t="n"/>
+      <c r="M236" s="10" t="n"/>
+      <c r="N236" s="10" t="n"/>
+      <c r="O236" s="10" t="n"/>
+      <c r="P236" s="10" t="n"/>
+      <c r="Q236" s="10" t="n"/>
+      <c r="R236" s="10" t="n"/>
+      <c r="S236" s="10" t="n"/>
+      <c r="T236" s="10" t="n"/>
+      <c r="U236" s="10" t="n"/>
+      <c r="V236" s="10" t="n"/>
+      <c r="W236" s="10" t="n"/>
+      <c r="X236" s="10" t="n"/>
+      <c r="Y236" s="10" t="n"/>
+      <c r="Z236" s="10" t="n"/>
+      <c r="AA236" s="10" t="n"/>
+      <c r="AB236" s="10" t="n"/>
+      <c r="AC236" s="10" t="n"/>
+      <c r="AD236" s="10" t="n"/>
+      <c r="AE236" s="10" t="n"/>
+      <c r="AF236" s="10" t="n"/>
+      <c r="AG236" s="10" t="n"/>
+      <c r="AH236" s="10" t="n"/>
+      <c r="AI236" s="10" t="n"/>
+      <c r="AJ236" s="10" t="n"/>
+      <c r="AK236" s="11" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="C237" s="41" t="inlineStr">
         <is>
+          <t>`before_value`：INSERT のため空文字列を設定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="36" customHeight="1">
+      <c r="C238" s="41" t="inlineStr">
+        <is>
+          <t>`after_value`：登録されたデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="18" customHeight="1">
+      <c r="B239" s="27" t="inlineStr">
+        <is>
+          <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="18" customHeight="1">
+      <c r="C240" s="41" t="inlineStr">
+        <is>
+          <t>登録されたデータを data オブジェクトとして返却する。HTTP 201。</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="B241" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="18" customHeight="1">
+      <c r="C242" s="41" t="inlineStr">
+        <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="238" ht="18" customHeight="1">
-      <c r="C238" s="41" t="inlineStr">
+    <row r="243" ht="18" customHeight="1">
+      <c r="C243" s="41" t="inlineStr">
         <is>
           <t>エラー発生時はエラーログを記録する（`log_type = 3`、トランザクション外で記録）。</t>
         </is>
       </c>
     </row>
-    <row r="239" ht="216" customHeight="1">
-      <c r="C239" s="42" t="inlineStr">
+    <row r="244" ht="216" customHeight="1">
+      <c r="C244" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -25128,45 +27725,44 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D239" s="10" t="n"/>
-      <c r="E239" s="10" t="n"/>
-      <c r="F239" s="10" t="n"/>
-      <c r="G239" s="10" t="n"/>
-      <c r="H239" s="10" t="n"/>
-      <c r="I239" s="10" t="n"/>
-      <c r="J239" s="10" t="n"/>
-      <c r="K239" s="10" t="n"/>
-      <c r="L239" s="10" t="n"/>
-      <c r="M239" s="10" t="n"/>
-      <c r="N239" s="10" t="n"/>
-      <c r="O239" s="10" t="n"/>
-      <c r="P239" s="10" t="n"/>
-      <c r="Q239" s="10" t="n"/>
-      <c r="R239" s="10" t="n"/>
-      <c r="S239" s="10" t="n"/>
-      <c r="T239" s="10" t="n"/>
-      <c r="U239" s="10" t="n"/>
-      <c r="V239" s="10" t="n"/>
-      <c r="W239" s="10" t="n"/>
-      <c r="X239" s="10" t="n"/>
-      <c r="Y239" s="10" t="n"/>
-      <c r="Z239" s="10" t="n"/>
-      <c r="AA239" s="10" t="n"/>
-      <c r="AB239" s="10" t="n"/>
-      <c r="AC239" s="10" t="n"/>
-      <c r="AD239" s="10" t="n"/>
-      <c r="AE239" s="10" t="n"/>
-      <c r="AF239" s="10" t="n"/>
-      <c r="AG239" s="10" t="n"/>
-      <c r="AH239" s="10" t="n"/>
-      <c r="AI239" s="10" t="n"/>
-      <c r="AJ239" s="10" t="n"/>
-      <c r="AK239" s="11" t="n"/>
+      <c r="D244" s="10" t="n"/>
+      <c r="E244" s="10" t="n"/>
+      <c r="F244" s="10" t="n"/>
+      <c r="G244" s="10" t="n"/>
+      <c r="H244" s="10" t="n"/>
+      <c r="I244" s="10" t="n"/>
+      <c r="J244" s="10" t="n"/>
+      <c r="K244" s="10" t="n"/>
+      <c r="L244" s="10" t="n"/>
+      <c r="M244" s="10" t="n"/>
+      <c r="N244" s="10" t="n"/>
+      <c r="O244" s="10" t="n"/>
+      <c r="P244" s="10" t="n"/>
+      <c r="Q244" s="10" t="n"/>
+      <c r="R244" s="10" t="n"/>
+      <c r="S244" s="10" t="n"/>
+      <c r="T244" s="10" t="n"/>
+      <c r="U244" s="10" t="n"/>
+      <c r="V244" s="10" t="n"/>
+      <c r="W244" s="10" t="n"/>
+      <c r="X244" s="10" t="n"/>
+      <c r="Y244" s="10" t="n"/>
+      <c r="Z244" s="10" t="n"/>
+      <c r="AA244" s="10" t="n"/>
+      <c r="AB244" s="10" t="n"/>
+      <c r="AC244" s="10" t="n"/>
+      <c r="AD244" s="10" t="n"/>
+      <c r="AE244" s="10" t="n"/>
+      <c r="AF244" s="10" t="n"/>
+      <c r="AG244" s="10" t="n"/>
+      <c r="AH244" s="10" t="n"/>
+      <c r="AI244" s="10" t="n"/>
+      <c r="AJ244" s="10" t="n"/>
+      <c r="AK244" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="915">
+  <mergeCells count="940">
     <mergeCell ref="Y46:AB46"/>
-    <mergeCell ref="C174:AK174"/>
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="M135:P135"/>
@@ -25176,7 +27772,6 @@
     <mergeCell ref="M72:P72"/>
     <mergeCell ref="Q114:S114"/>
     <mergeCell ref="T137:X137"/>
-    <mergeCell ref="B229:AK229"/>
     <mergeCell ref="D125:L125"/>
     <mergeCell ref="T53:X53"/>
     <mergeCell ref="T124:X124"/>
@@ -25203,10 +27798,12 @@
     <mergeCell ref="C205:AK205"/>
     <mergeCell ref="Y118:AE118"/>
     <mergeCell ref="M88:P88"/>
+    <mergeCell ref="M148:P148"/>
     <mergeCell ref="M82:P82"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="AF84:AK84"/>
     <mergeCell ref="Q104:S104"/>
+    <mergeCell ref="AF149:AK149"/>
     <mergeCell ref="Q91:S91"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
@@ -25221,8 +27818,8 @@
     <mergeCell ref="AC57:AE57"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Y59:AB59"/>
+    <mergeCell ref="AF151:AK151"/>
     <mergeCell ref="C231:AK231"/>
-    <mergeCell ref="D213:AK213"/>
     <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="AF101:AK101"/>
     <mergeCell ref="T37:X37"/>
@@ -25246,11 +27843,9 @@
     <mergeCell ref="Q59:S59"/>
     <mergeCell ref="T114:X114"/>
     <mergeCell ref="AF104:AK104"/>
-    <mergeCell ref="B152:I152"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="M143:P143"/>
     <mergeCell ref="M118:P118"/>
-    <mergeCell ref="C197:AK197"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
     <mergeCell ref="Q86:S86"/>
@@ -25277,18 +27872,18 @@
     <mergeCell ref="AF145:AK145"/>
     <mergeCell ref="Y51:AB51"/>
     <mergeCell ref="T69:X69"/>
+    <mergeCell ref="C213:AK213"/>
     <mergeCell ref="T140:X140"/>
     <mergeCell ref="D128:L128"/>
     <mergeCell ref="AC71:AE71"/>
     <mergeCell ref="Y144:AE144"/>
-    <mergeCell ref="C150:AK150"/>
     <mergeCell ref="Y119:AE119"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="C208:AK208"/>
     <mergeCell ref="Q141:S141"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="M91:P91"/>
+    <mergeCell ref="B165:I165"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF92:AK92"/>
@@ -25303,7 +27898,6 @@
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="M93:P93"/>
     <mergeCell ref="T87:X87"/>
-    <mergeCell ref="D223:AK223"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q49:S49"/>
     <mergeCell ref="Y75:AB75"/>
@@ -25322,16 +27916,18 @@
     <mergeCell ref="T88:X88"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
+    <mergeCell ref="D218:AK218"/>
     <mergeCell ref="Y39:AB39"/>
     <mergeCell ref="D85:L85"/>
     <mergeCell ref="T128:X128"/>
     <mergeCell ref="M109:P109"/>
     <mergeCell ref="AF56:AK56"/>
+    <mergeCell ref="C236:AK236"/>
     <mergeCell ref="C54:L54"/>
     <mergeCell ref="AF105:AK105"/>
     <mergeCell ref="Q125:S125"/>
     <mergeCell ref="AF43:AK43"/>
-    <mergeCell ref="B158:I158"/>
+    <mergeCell ref="C163:AK163"/>
     <mergeCell ref="Y138:AE138"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="C41:L41"/>
@@ -25351,6 +27947,7 @@
     <mergeCell ref="Q102:S102"/>
     <mergeCell ref="M104:P104"/>
     <mergeCell ref="Q64:S64"/>
+    <mergeCell ref="B153:I153"/>
     <mergeCell ref="T77:X77"/>
     <mergeCell ref="Y65:AB65"/>
     <mergeCell ref="M41:P41"/>
@@ -25365,18 +27962,17 @@
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="M66:P66"/>
-    <mergeCell ref="C83:C147"/>
-    <mergeCell ref="C216:AK216"/>
     <mergeCell ref="T143:X143"/>
     <mergeCell ref="Y87:AE87"/>
     <mergeCell ref="M130:P130"/>
     <mergeCell ref="AF75:AK75"/>
-    <mergeCell ref="C218:AK218"/>
     <mergeCell ref="Y89:AE89"/>
     <mergeCell ref="Q57:S57"/>
+    <mergeCell ref="C211:AK211"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="Q100:S100"/>
+    <mergeCell ref="Q149:S149"/>
     <mergeCell ref="T61:X61"/>
     <mergeCell ref="C65:L65"/>
     <mergeCell ref="Y82:AE82"/>
@@ -25384,7 +27980,9 @@
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="AF70:AK70"/>
     <mergeCell ref="Q115:S115"/>
+    <mergeCell ref="B216:AK216"/>
     <mergeCell ref="C31:L31"/>
+    <mergeCell ref="Q151:S151"/>
     <mergeCell ref="Y60:AB60"/>
     <mergeCell ref="T96:X96"/>
     <mergeCell ref="AC28:AE28"/>
@@ -25392,6 +27990,7 @@
     <mergeCell ref="D84:L84"/>
     <mergeCell ref="T90:X90"/>
     <mergeCell ref="Q52:S52"/>
+    <mergeCell ref="D149:L149"/>
     <mergeCell ref="AF97:AK97"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="M46:P46"/>
@@ -25399,13 +27998,15 @@
     <mergeCell ref="M37:P37"/>
     <mergeCell ref="T98:X98"/>
     <mergeCell ref="AC30:AE30"/>
-    <mergeCell ref="C165:AK165"/>
     <mergeCell ref="D86:L86"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC67:AE67"/>
     <mergeCell ref="Y140:AE140"/>
+    <mergeCell ref="D151:L151"/>
     <mergeCell ref="AF128:AK128"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="B159:I159"/>
+    <mergeCell ref="D150:L150"/>
     <mergeCell ref="D184:AK184"/>
     <mergeCell ref="M125:P125"/>
     <mergeCell ref="AC69:AE69"/>
@@ -25413,8 +28014,8 @@
     <mergeCell ref="M112:P112"/>
     <mergeCell ref="AF121:AK121"/>
     <mergeCell ref="C57:L57"/>
-    <mergeCell ref="B167:I167"/>
-    <mergeCell ref="B161:I161"/>
+    <mergeCell ref="C166:AK166"/>
+    <mergeCell ref="C160:AK160"/>
     <mergeCell ref="Y141:AE141"/>
     <mergeCell ref="D192:AK192"/>
     <mergeCell ref="J17:M17"/>
@@ -25436,9 +28037,12 @@
     <mergeCell ref="Y71:AB71"/>
     <mergeCell ref="M107:P107"/>
     <mergeCell ref="Y58:AB58"/>
+    <mergeCell ref="B162:I162"/>
     <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="B177:AK177"/>
     <mergeCell ref="Y73:AB73"/>
     <mergeCell ref="T109:X109"/>
+    <mergeCell ref="C242:AK242"/>
     <mergeCell ref="M138:P138"/>
     <mergeCell ref="T84:X84"/>
     <mergeCell ref="AF34:AK34"/>
@@ -25451,18 +28055,20 @@
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="T86:X86"/>
-    <mergeCell ref="C219:AK219"/>
     <mergeCell ref="Q83:S83"/>
     <mergeCell ref="Y90:AE90"/>
     <mergeCell ref="D101:L101"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="Q58:S58"/>
     <mergeCell ref="AF103:AK103"/>
+    <mergeCell ref="Q150:S150"/>
     <mergeCell ref="C39:L39"/>
     <mergeCell ref="C70:L70"/>
     <mergeCell ref="Q85:S85"/>
+    <mergeCell ref="D230:AK230"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="C154:AK154"/>
     <mergeCell ref="M62:P62"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="AC42:AE42"/>
@@ -25470,14 +28076,11 @@
     <mergeCell ref="D180:AK180"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="C156:AK156"/>
     <mergeCell ref="Y131:AE131"/>
     <mergeCell ref="AC44:AE44"/>
     <mergeCell ref="T106:X106"/>
     <mergeCell ref="M87:P87"/>
     <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="C230:AK230"/>
-    <mergeCell ref="C168:AK168"/>
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="AF71:AK71"/>
     <mergeCell ref="M51:P51"/>
@@ -25492,8 +28095,9 @@
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="AF73:AK73"/>
     <mergeCell ref="Q71:S71"/>
-    <mergeCell ref="B164:I164"/>
+    <mergeCell ref="C169:AK169"/>
     <mergeCell ref="M65:P65"/>
+    <mergeCell ref="D195:AK195"/>
     <mergeCell ref="T130:X130"/>
     <mergeCell ref="D189:AK189"/>
     <mergeCell ref="T46:X46"/>
@@ -25503,12 +28107,14 @@
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
     <mergeCell ref="C233:AK233"/>
+    <mergeCell ref="D197:AK197"/>
     <mergeCell ref="Y49:AB49"/>
     <mergeCell ref="D120:L120"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF68:AK68"/>
     <mergeCell ref="Y96:AE96"/>
     <mergeCell ref="D107:L107"/>
+    <mergeCell ref="T150:X150"/>
     <mergeCell ref="T125:X125"/>
     <mergeCell ref="Y76:AB76"/>
     <mergeCell ref="M146:P146"/>
@@ -25519,7 +28125,7 @@
     <mergeCell ref="D102:L102"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="M83:P83"/>
-    <mergeCell ref="C162:AK162"/>
+    <mergeCell ref="AF150:AK150"/>
     <mergeCell ref="AF144:AK144"/>
     <mergeCell ref="Y106:AE106"/>
     <mergeCell ref="D182:AK182"/>
@@ -25538,10 +28144,12 @@
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="C222:AK222"/>
     <mergeCell ref="AC45:AE45"/>
     <mergeCell ref="D183:AK183"/>
     <mergeCell ref="T56:X56"/>
     <mergeCell ref="AC32:AE32"/>
+    <mergeCell ref="D219:AK219"/>
     <mergeCell ref="T105:X105"/>
     <mergeCell ref="AC37:AE37"/>
     <mergeCell ref="T43:X43"/>
@@ -25552,12 +28160,12 @@
     <mergeCell ref="Y109:AE109"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="T107:X107"/>
+    <mergeCell ref="C240:AK240"/>
     <mergeCell ref="T101:X101"/>
     <mergeCell ref="M136:P136"/>
     <mergeCell ref="AC76:AE76"/>
     <mergeCell ref="AF63:AK63"/>
     <mergeCell ref="Y111:AE111"/>
-    <mergeCell ref="D214:AK214"/>
     <mergeCell ref="D97:L97"/>
     <mergeCell ref="B14:I19"/>
     <mergeCell ref="AF74:AK74"/>
@@ -25566,6 +28174,7 @@
     <mergeCell ref="Q81:S81"/>
     <mergeCell ref="Q137:S137"/>
     <mergeCell ref="C235:AK235"/>
+    <mergeCell ref="Y150:AE150"/>
     <mergeCell ref="C53:L53"/>
     <mergeCell ref="AC63:AE63"/>
     <mergeCell ref="M131:P131"/>
@@ -25584,6 +28193,7 @@
     <mergeCell ref="D121:L121"/>
     <mergeCell ref="T127:X127"/>
     <mergeCell ref="Q76:S76"/>
+    <mergeCell ref="B171:I171"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="T64:X64"/>
     <mergeCell ref="T135:X135"/>
@@ -25593,12 +28203,15 @@
     <mergeCell ref="C201:AK201"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M84:P84"/>
+    <mergeCell ref="M149:P149"/>
+    <mergeCell ref="C203:AK203"/>
     <mergeCell ref="Q136:S136"/>
     <mergeCell ref="Q92:S92"/>
     <mergeCell ref="Y105:AE105"/>
     <mergeCell ref="M86:P86"/>
     <mergeCell ref="Y99:AE99"/>
     <mergeCell ref="M42:P42"/>
+    <mergeCell ref="M151:P151"/>
     <mergeCell ref="T67:X67"/>
     <mergeCell ref="AF87:AK87"/>
     <mergeCell ref="J11:AK11"/>
@@ -25617,7 +28230,6 @@
     <mergeCell ref="AC55:AE55"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="D193:AK193"/>
-    <mergeCell ref="D224:AK224"/>
     <mergeCell ref="AC38:AE38"/>
     <mergeCell ref="Y100:AE100"/>
     <mergeCell ref="Y32:AB32"/>
@@ -25653,7 +28265,9 @@
     <mergeCell ref="AF77:AK77"/>
     <mergeCell ref="M99:P99"/>
     <mergeCell ref="Q124:S124"/>
+    <mergeCell ref="D229:AK229"/>
     <mergeCell ref="Y50:AB50"/>
+    <mergeCell ref="C178:AK178"/>
     <mergeCell ref="M74:P74"/>
     <mergeCell ref="AC66:AE66"/>
     <mergeCell ref="T34:X34"/>
@@ -25663,6 +28277,7 @@
     <mergeCell ref="Y128:AE128"/>
     <mergeCell ref="D131:L131"/>
     <mergeCell ref="AF141:AK141"/>
+    <mergeCell ref="D198:AK198"/>
     <mergeCell ref="Q126:S126"/>
     <mergeCell ref="Y52:AB52"/>
     <mergeCell ref="AC77:AE77"/>
@@ -25680,6 +28295,7 @@
     <mergeCell ref="D126:L126"/>
     <mergeCell ref="AC72:AE72"/>
     <mergeCell ref="AF59:AK59"/>
+    <mergeCell ref="M150:P150"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="C204:AK204"/>
     <mergeCell ref="Q44:S44"/>
@@ -25705,7 +28321,6 @@
     <mergeCell ref="Y102:AE102"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="D142:L142"/>
-    <mergeCell ref="B211:AK211"/>
     <mergeCell ref="AF90:AK90"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="T129:X129"/>
@@ -25722,12 +28337,13 @@
     <mergeCell ref="T131:X131"/>
     <mergeCell ref="Q139:S139"/>
     <mergeCell ref="C55:L55"/>
+    <mergeCell ref="T149:X149"/>
     <mergeCell ref="AC62:AE62"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M105:P105"/>
-    <mergeCell ref="C159:AK159"/>
     <mergeCell ref="Q121:S121"/>
-    <mergeCell ref="C153:AK153"/>
+    <mergeCell ref="C224:AK224"/>
+    <mergeCell ref="T151:X151"/>
     <mergeCell ref="D139:L139"/>
     <mergeCell ref="M120:P120"/>
     <mergeCell ref="D179:AK179"/>
@@ -25742,13 +28358,13 @@
     <mergeCell ref="AF108:AK108"/>
     <mergeCell ref="Y136:AE136"/>
     <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="B156:I156"/>
+    <mergeCell ref="A175:AK175"/>
     <mergeCell ref="M100:P100"/>
     <mergeCell ref="AF143:AK143"/>
     <mergeCell ref="AF118:AK118"/>
-    <mergeCell ref="B155:I155"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="B149:I149"/>
     <mergeCell ref="C37:L37"/>
     <mergeCell ref="M115:P115"/>
     <mergeCell ref="Y66:AB66"/>
@@ -25761,7 +28377,6 @@
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="T142:X142"/>
     <mergeCell ref="B234:AK234"/>
-    <mergeCell ref="B172:AK172"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="Y68:AB68"/>
     <mergeCell ref="D117:L117"/>
@@ -25769,7 +28384,7 @@
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="Y55:AB55"/>
     <mergeCell ref="Y146:AE146"/>
-    <mergeCell ref="D222:AK222"/>
+    <mergeCell ref="C83:C151"/>
     <mergeCell ref="C212:AK212"/>
     <mergeCell ref="T73:X73"/>
     <mergeCell ref="T144:X144"/>
@@ -25779,6 +28394,7 @@
     <mergeCell ref="D94:L94"/>
     <mergeCell ref="AF96:AK96"/>
     <mergeCell ref="Q116:S116"/>
+    <mergeCell ref="C214:AK214"/>
     <mergeCell ref="Q134:S134"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="Y85:AE85"/>
@@ -25788,7 +28404,7 @@
     <mergeCell ref="Q145:S145"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="M95:P95"/>
-    <mergeCell ref="D225:AK225"/>
+    <mergeCell ref="Y149:AE149"/>
     <mergeCell ref="M89:P89"/>
     <mergeCell ref="Q117:S117"/>
     <mergeCell ref="Q55:S55"/>
@@ -25802,7 +28418,9 @@
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M97:P97"/>
+    <mergeCell ref="D227:AK227"/>
     <mergeCell ref="D145:L145"/>
+    <mergeCell ref="B176:AK176"/>
     <mergeCell ref="AF93:AK93"/>
     <mergeCell ref="AC64:AE64"/>
     <mergeCell ref="Q40:S40"/>
@@ -25810,13 +28428,12 @@
     <mergeCell ref="D87:L87"/>
     <mergeCell ref="D147:L147"/>
     <mergeCell ref="AF124:AK124"/>
+    <mergeCell ref="C225:AK225"/>
     <mergeCell ref="AC65:AE65"/>
-    <mergeCell ref="C200:AK200"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="Y63:AB63"/>
     <mergeCell ref="AF126:AK126"/>
     <mergeCell ref="AF109:AK109"/>
-    <mergeCell ref="C227:AK227"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="C45:L45"/>
@@ -25844,7 +28461,6 @@
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="T81:X81"/>
     <mergeCell ref="Y137:AE137"/>
-    <mergeCell ref="B173:AK173"/>
     <mergeCell ref="Y69:AB69"/>
     <mergeCell ref="C51:L51"/>
     <mergeCell ref="M28:P28"/>
@@ -25867,27 +28483,28 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="M134:P134"/>
     <mergeCell ref="M23:P23"/>
+    <mergeCell ref="Y151:AE151"/>
+    <mergeCell ref="C157:AK157"/>
     <mergeCell ref="M121:P121"/>
     <mergeCell ref="AF139:AK139"/>
     <mergeCell ref="Y126:AE126"/>
-    <mergeCell ref="A171:AK171"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="T63:X63"/>
     <mergeCell ref="M96:P96"/>
     <mergeCell ref="M71:P71"/>
-    <mergeCell ref="D177:AK177"/>
     <mergeCell ref="AF114:AK114"/>
     <mergeCell ref="Y38:AB38"/>
     <mergeCell ref="C77:L77"/>
     <mergeCell ref="C215:AK215"/>
+    <mergeCell ref="Q148:S148"/>
     <mergeCell ref="M111:P111"/>
     <mergeCell ref="T71:X71"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="M98:P98"/>
     <mergeCell ref="T92:X92"/>
+    <mergeCell ref="D228:AK228"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="D178:AK178"/>
     <mergeCell ref="D113:L113"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="T100:X100"/>
@@ -25895,6 +28512,7 @@
     <mergeCell ref="T94:X94"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="D148:L148"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="T66:X66"/>
     <mergeCell ref="D115:L115"/>
@@ -25908,7 +28526,6 @@
     <mergeCell ref="C59:L59"/>
     <mergeCell ref="T95:X95"/>
     <mergeCell ref="Q130:S130"/>
-    <mergeCell ref="C228:AK228"/>
     <mergeCell ref="C46:L46"/>
     <mergeCell ref="Y81:AE81"/>
     <mergeCell ref="M124:P124"/>
@@ -25922,7 +28539,7 @@
     <mergeCell ref="AF112:AK112"/>
     <mergeCell ref="Q132:S132"/>
     <mergeCell ref="Q103:S103"/>
-    <mergeCell ref="D175:AK175"/>
+    <mergeCell ref="C243:AK243"/>
     <mergeCell ref="Y145:AE145"/>
     <mergeCell ref="C48:L48"/>
     <mergeCell ref="M126:P126"/>
@@ -25934,7 +28551,6 @@
     <mergeCell ref="AF127:AK127"/>
     <mergeCell ref="Q69:S69"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D176:AK176"/>
     <mergeCell ref="AF64:AK64"/>
     <mergeCell ref="D103:L103"/>
     <mergeCell ref="AF51:AK51"/>
@@ -25944,16 +28560,16 @@
     <mergeCell ref="M44:P44"/>
     <mergeCell ref="M142:P142"/>
     <mergeCell ref="C221:AK221"/>
-    <mergeCell ref="C196:AK196"/>
+    <mergeCell ref="T148:X148"/>
     <mergeCell ref="AC51:AE51"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="M129:P129"/>
     <mergeCell ref="Y92:AE92"/>
     <mergeCell ref="M73:P73"/>
     <mergeCell ref="M144:P144"/>
+    <mergeCell ref="C223:AK223"/>
     <mergeCell ref="M60:P60"/>
     <mergeCell ref="AF140:AK140"/>
-    <mergeCell ref="C198:AK198"/>
     <mergeCell ref="Q87:S87"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="Y94:AE94"/>
@@ -25963,6 +28579,7 @@
     <mergeCell ref="AF82:AK82"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="T115:X115"/>
+    <mergeCell ref="B200:AK200"/>
     <mergeCell ref="D96:L96"/>
     <mergeCell ref="T102:X102"/>
     <mergeCell ref="M139:P139"/>
@@ -25971,7 +28588,6 @@
     <mergeCell ref="Q82:S82"/>
     <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="T39:X39"/>
-    <mergeCell ref="B236:AK236"/>
     <mergeCell ref="Q118:S118"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
@@ -25985,8 +28601,8 @@
     <mergeCell ref="Q113:S113"/>
     <mergeCell ref="D91:L91"/>
     <mergeCell ref="T97:X97"/>
-    <mergeCell ref="B195:AK195"/>
     <mergeCell ref="Y120:AE120"/>
+    <mergeCell ref="D196:AK196"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
@@ -25996,6 +28612,7 @@
     <mergeCell ref="D106:L106"/>
     <mergeCell ref="AF133:AK133"/>
     <mergeCell ref="C69:L69"/>
+    <mergeCell ref="C172:AK172"/>
     <mergeCell ref="D93:L93"/>
     <mergeCell ref="M68:P68"/>
     <mergeCell ref="Y147:AE147"/>
@@ -26016,8 +28633,11 @@
     <mergeCell ref="C64:L64"/>
     <mergeCell ref="Q75:S75"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="B241:AK241"/>
+    <mergeCell ref="B168:I168"/>
     <mergeCell ref="M69:P69"/>
     <mergeCell ref="AC61:AE61"/>
+    <mergeCell ref="Y148:AE148"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="AF136:AK136"/>
     <mergeCell ref="D186:AK186"/>
@@ -26029,7 +28649,10 @@
     <mergeCell ref="M81:P81"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
+    <mergeCell ref="D194:AK194"/>
+    <mergeCell ref="AF148:AK148"/>
     <mergeCell ref="T116:X116"/>
+    <mergeCell ref="B208:AK208"/>
     <mergeCell ref="D104:L104"/>
     <mergeCell ref="C237:AK237"/>
     <mergeCell ref="M145:P145"/>
@@ -26043,7 +28666,6 @@
     <mergeCell ref="C82:L82"/>
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="Y95:AE95"/>
-    <mergeCell ref="C239:AK239"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="M76:P76"/>
     <mergeCell ref="M147:P147"/>
@@ -26066,17 +28688,17 @@
     <mergeCell ref="AC49:AE49"/>
     <mergeCell ref="D187:AK187"/>
     <mergeCell ref="AC36:AE36"/>
+    <mergeCell ref="B239:AK239"/>
     <mergeCell ref="Y35:AB35"/>
     <mergeCell ref="D132:L132"/>
     <mergeCell ref="T119:X119"/>
     <mergeCell ref="Y113:AE113"/>
     <mergeCell ref="A79:AK79"/>
     <mergeCell ref="M94:P94"/>
-    <mergeCell ref="B203:AK203"/>
+    <mergeCell ref="C244:AK244"/>
     <mergeCell ref="Y129:AE129"/>
     <mergeCell ref="Y123:AE123"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="C194:AK194"/>
     <mergeCell ref="M77:P77"/>
     <mergeCell ref="M133:P133"/>
     <mergeCell ref="AF29:AK29"/>
@@ -26091,7 +28713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK110"/>
+  <dimension ref="A1:AK120"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -26252,7 +28874,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -27312,8 +29934,12 @@
     "biko": "",
     "rireki_no": 2,
     "denshi_shonin_status": null,
+    "denshi_kaiin_id": null,
+    "honshi_kodoku_flg": false,
     "created_at": "2026-04-01T10:00:00+09:00",
-    "updated_at": "2026-05-07T14:30:00+09:00"
+    "updated_at": "2026-05-07T14:30:00+09:00",
+    "has_active_kaiyaku": false,
+    "max_joho_date": null
   }
 }</t>
         </is>
@@ -27889,98 +30515,96 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
+    <row r="78" ht="36" customHeight="1">
       <c r="C78" s="41" t="inlineStr">
         <is>
-          <t>メールアドレスが変更されている場合、重複を確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="108" customHeight="1">
-      <c r="C79" s="42" t="inlineStr">
+          <t>メールアドレスが入力されており、かつ購読種別（保存値・pin 済み）が電子版(2)・併読(3) の場合、以下の条件で重複を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1">
+      <c r="C79" s="41" t="inlineStr">
+        <is>
+          <t>**JA を跨いで全件**を対象とする（顧客要件 2026-08 / #56568）。他 JA に同じメールの電子版・併読レコードがあれば更新できない。紙版(1)は対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>論理削除済み（`deleted_at IS NOT NULL`）は対象外。自身の行は除外する（`dokusya_id &lt;&gt; :dokusya_id`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="108" customHeight="1">
+      <c r="C81" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) FROM t_dokusya
 WHERE email = :email
   AND email &lt;&gt; ''
-  AND ja_id = :ja_id
-  AND dokusya_id &lt;&gt; :dokusya_id
-  AND deleted_at IS NULL</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="n"/>
-      <c r="E79" s="10" t="n"/>
-      <c r="F79" s="10" t="n"/>
-      <c r="G79" s="10" t="n"/>
-      <c r="H79" s="10" t="n"/>
-      <c r="I79" s="10" t="n"/>
-      <c r="J79" s="10" t="n"/>
-      <c r="K79" s="10" t="n"/>
-      <c r="L79" s="10" t="n"/>
-      <c r="M79" s="10" t="n"/>
-      <c r="N79" s="10" t="n"/>
-      <c r="O79" s="10" t="n"/>
-      <c r="P79" s="10" t="n"/>
-      <c r="Q79" s="10" t="n"/>
-      <c r="R79" s="10" t="n"/>
-      <c r="S79" s="10" t="n"/>
-      <c r="T79" s="10" t="n"/>
-      <c r="U79" s="10" t="n"/>
-      <c r="V79" s="10" t="n"/>
-      <c r="W79" s="10" t="n"/>
-      <c r="X79" s="10" t="n"/>
-      <c r="Y79" s="10" t="n"/>
-      <c r="Z79" s="10" t="n"/>
-      <c r="AA79" s="10" t="n"/>
-      <c r="AB79" s="10" t="n"/>
-      <c r="AC79" s="10" t="n"/>
-      <c r="AD79" s="10" t="n"/>
-      <c r="AE79" s="10" t="n"/>
-      <c r="AF79" s="10" t="n"/>
-      <c r="AG79" s="10" t="n"/>
-      <c r="AH79" s="10" t="n"/>
-      <c r="AI79" s="10" t="n"/>
-      <c r="AJ79" s="10" t="n"/>
-      <c r="AK79" s="11" t="n"/>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
+  AND dokusya_shubetsu IN (2, 3)
+  AND deleted_at IS NULL
+  AND dokusya_id &lt;&gt; :dokusya_id</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
+      <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="11" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>重複がある場合：HTTP 400 (`DUPLICATE_EMAIL`)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
-        <is>
-          <t>4.4 データ更新（履歴追記方式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="90" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
-        <is>
-          <t>`bank_shiten_id` が指定された場合、支払方法を問わず `m_shiten` を逆引きし、`jastem_toriatsukai_tenpo_code` および `jastem_tenpo_name` を取得して `t_dokusya.bank_branch_code` / `bank_branch_name` に非正規化保存する（画面設計書 機能定義 §10.1 / §10.2、顧客要件 2026-06）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="72" customHeight="1">
+    <row r="83" ht="90" customHeight="1">
       <c r="C83" s="41" t="inlineStr">
         <is>
-          <t>支払方法=1（口座引落）では `bank_shiten_id` 必須（未指定→VALIDATION_ERROR）。他の支払方法では任意で、未指定なら bank_branch_code/name は空で保存する。指定値が不正（非存在 / 他JA / 金融機関支店でない）の場合は支払方法を問わず VALIDATION_ERROR。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="144" customHeight="1">
+          <t>対象：**紙版のみ・`change_mode='reserved'` のみ**。`change_mode='today'`（当日変更）は対象外 — 当日行は取消不可（ACSMS-SCR-013 の `can_torikeshi` が適用日を過去/当日とする行を取消対象から除外する）ため、ここで制限すると後戻りできなくなる。電子版は予約変更自体が不可（§4.1〜4.3 参照）のため実質対象外。再購読（解約済み→新規）は新しいライフサイクルの開始のため対象外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="108" customHeight="1">
       <c r="C84" s="42" t="inlineStr">
         <is>
-          <t>SELECT shiten_id,
-       jastem_toriatsukai_tenpo_code,
-       jastem_tenpo_name
-FROM m_shiten
-WHERE shiten_id = :bank_shiten_id
-  AND ja_id = :ja_id
-  AND kinyu_shiten_flg = TRUE
-  AND deleted_at IS NULL</t>
+          <t>SELECT 1 FROM t_dokusya_rireki
+WHERE dokusya_id = :dokusya_id
+  AND joho_henko_tekiyo_date = :joho_henko_tekiyo_date
+  AND torikeshi_flg = false
+  AND shinki_flg = false
+LIMIT 1</t>
         </is>
       </c>
       <c r="D84" s="10" t="n"/>
@@ -28018,22 +30642,133 @@
       <c r="AJ84" s="10" t="n"/>
       <c r="AK84" s="11" t="n"/>
     </row>
-    <row r="85" ht="36" customHeight="1">
+    <row r="85" ht="54" customHeight="1">
       <c r="C85" s="41" t="inlineStr">
         <is>
+          <t>上記に該当する行が1件でもあれば：HTTP 400 (`VALIDATION_ERROR`、field=`joho_henko_tekiyo_date`、message=「この適用日には既に変更履歴が登録されています。購読者履歴情報画面から該当の変更を取消してから、まとめて更新してください。」)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="72" customHeight="1">
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>同日に複数項目（住所＋販売店 等）をまとめて変更したいときは、まず ACSMS-SCR-013（購読者履歴情報画面）から該当の変更履歴行を取消（赤伝）してから、1回の更新でまとめて反映する — 取消は当該行の `joho_henko_tekiyo_date` が未来日であることが前提（`can_torikeshi`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="54" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>この検証は ACSMS-API-011-007（`GET .../effective-at`）の予約変更ポップアップ確定時点でも同一ロジックで先に走る（早期検知・UX）。update() 本体でも独立に再検証する（多層防御）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="C88" s="41" t="inlineStr">
+        <is>
+          <t>`dto.hanbaiten_id === before.hanbaiten_id` かつ `dto.tanka_id === before.tanka_id` → 廃店/失効でも通す（据え置き）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
+        <is>
+          <t>どちらかが**変更**されており、かつ変更後の参照先が廃店/失効 → `VALIDATION_ERROR`（field=`hanbaiten_id`／`tanka_id`、§4.1と同一メッセージ）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="72" customHeight="1">
+      <c r="C90" s="41" t="inlineStr">
+        <is>
+          <t>修正前は変更の有無を問わず常に通っており、購読者詳細画面（本画面）にも廃店・失効の旨を示す表示が無いため運用が事後に気付けなかった。Excel取込(SCR-016)は列単位選択のため「未選択＝変更なし」で自然にこの据え置きが成立するが、本画面はフォーム全項目を毎回送信するため明示的な `before` 比較が必要（`DokusyaService.assertFkScope`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>4.4 データ更新（履歴追記方式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="90" customHeight="1">
+      <c r="C92" s="41" t="inlineStr">
+        <is>
+          <t>`bank_shiten_id` が指定された場合、支払方法を問わず `m_shiten` を逆引きし、`jastem_toriatsukai_tenpo_code` および `jastem_tenpo_name` を取得して `t_dokusya.bank_branch_code` / `bank_branch_name` に非正規化保存する（画面設計書 機能定義 §10.1 / §10.2、顧客要件 2026-06）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="72" customHeight="1">
+      <c r="C93" s="41" t="inlineStr">
+        <is>
+          <t>支払方法=1（口座引落）では `bank_shiten_id` 必須（未指定→VALIDATION_ERROR）。他の支払方法では任意で、未指定なら bank_branch_code/name は空で保存する。指定値が不正（非存在 / 他JA / 金融機関支店でない）の場合は支払方法を問わず VALIDATION_ERROR。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="144" customHeight="1">
+      <c r="C94" s="42" t="inlineStr">
+        <is>
+          <t>SELECT shiten_id,
+       jastem_toriatsukai_tenpo_code,
+       jastem_tenpo_name
+FROM m_shiten
+WHERE shiten_id = :bank_shiten_id
+  AND ja_id = :ja_id
+  AND kinyu_shiten_flg = TRUE
+  AND deleted_at IS NULL</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="10" t="n"/>
+      <c r="J94" s="10" t="n"/>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="10" t="n"/>
+      <c r="M94" s="10" t="n"/>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="10" t="n"/>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="10" t="n"/>
+      <c r="X94" s="10" t="n"/>
+      <c r="Y94" s="10" t="n"/>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="10" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="10" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="10" t="n"/>
+      <c r="AK94" s="11" t="n"/>
+    </row>
+    <row r="95" ht="36" customHeight="1">
+      <c r="C95" s="41" t="inlineStr">
+        <is>
           <t>該当レコードがない場合：HTTP 400 (`VALIDATION_ERROR`)（`field: 'bank_shiten_id'`）。</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="36" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
+    <row r="96" ht="36" customHeight="1">
+      <c r="C96" s="41" t="inlineStr">
         <is>
           <t>支払方法 ≠ 1 の場合、`bank_branch_code = ''` / `bank_branch_name = ''` を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="72" customHeight="1">
-      <c r="C87" s="42" t="inlineStr">
+    <row r="97" ht="72" customHeight="1">
+      <c r="C97" s="42" t="inlineStr">
         <is>
           <t>UPDATE t_dokusya_rireki
 SET saishin_data_flg = FALSE
@@ -28041,149 +30776,149 @@
   AND saishin_data_flg = TRUE</t>
         </is>
       </c>
-      <c r="D87" s="10" t="n"/>
-      <c r="E87" s="10" t="n"/>
-      <c r="F87" s="10" t="n"/>
-      <c r="G87" s="10" t="n"/>
-      <c r="H87" s="10" t="n"/>
-      <c r="I87" s="10" t="n"/>
-      <c r="J87" s="10" t="n"/>
-      <c r="K87" s="10" t="n"/>
-      <c r="L87" s="10" t="n"/>
-      <c r="M87" s="10" t="n"/>
-      <c r="N87" s="10" t="n"/>
-      <c r="O87" s="10" t="n"/>
-      <c r="P87" s="10" t="n"/>
-      <c r="Q87" s="10" t="n"/>
-      <c r="R87" s="10" t="n"/>
-      <c r="S87" s="10" t="n"/>
-      <c r="T87" s="10" t="n"/>
-      <c r="U87" s="10" t="n"/>
-      <c r="V87" s="10" t="n"/>
-      <c r="W87" s="10" t="n"/>
-      <c r="X87" s="10" t="n"/>
-      <c r="Y87" s="10" t="n"/>
-      <c r="Z87" s="10" t="n"/>
-      <c r="AA87" s="10" t="n"/>
-      <c r="AB87" s="10" t="n"/>
-      <c r="AC87" s="10" t="n"/>
-      <c r="AD87" s="10" t="n"/>
-      <c r="AE87" s="10" t="n"/>
-      <c r="AF87" s="10" t="n"/>
-      <c r="AG87" s="10" t="n"/>
-      <c r="AH87" s="10" t="n"/>
-      <c r="AI87" s="10" t="n"/>
-      <c r="AJ87" s="10" t="n"/>
-      <c r="AK87" s="11" t="n"/>
-    </row>
-    <row r="88" ht="54" customHeight="1">
-      <c r="C88" s="42" t="inlineStr">
+      <c r="D97" s="10" t="n"/>
+      <c r="E97" s="10" t="n"/>
+      <c r="F97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="10" t="n"/>
+      <c r="J97" s="10" t="n"/>
+      <c r="K97" s="10" t="n"/>
+      <c r="L97" s="10" t="n"/>
+      <c r="M97" s="10" t="n"/>
+      <c r="N97" s="10" t="n"/>
+      <c r="O97" s="10" t="n"/>
+      <c r="P97" s="10" t="n"/>
+      <c r="Q97" s="10" t="n"/>
+      <c r="R97" s="10" t="n"/>
+      <c r="S97" s="10" t="n"/>
+      <c r="T97" s="10" t="n"/>
+      <c r="U97" s="10" t="n"/>
+      <c r="V97" s="10" t="n"/>
+      <c r="W97" s="10" t="n"/>
+      <c r="X97" s="10" t="n"/>
+      <c r="Y97" s="10" t="n"/>
+      <c r="Z97" s="10" t="n"/>
+      <c r="AA97" s="10" t="n"/>
+      <c r="AB97" s="10" t="n"/>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="10" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="10" t="n"/>
+      <c r="AK97" s="11" t="n"/>
+    </row>
+    <row r="98" ht="54" customHeight="1">
+      <c r="C98" s="42" t="inlineStr">
         <is>
           <t>SELECT COALESCE(MAX(rireki_no), 0) + 1 AS new_rireki_no
 FROM t_dokusya_rireki
 WHERE dokusya_id = :dokusya_id</t>
         </is>
       </c>
-      <c r="D88" s="10" t="n"/>
-      <c r="E88" s="10" t="n"/>
-      <c r="F88" s="10" t="n"/>
-      <c r="G88" s="10" t="n"/>
-      <c r="H88" s="10" t="n"/>
-      <c r="I88" s="10" t="n"/>
-      <c r="J88" s="10" t="n"/>
-      <c r="K88" s="10" t="n"/>
-      <c r="L88" s="10" t="n"/>
-      <c r="M88" s="10" t="n"/>
-      <c r="N88" s="10" t="n"/>
-      <c r="O88" s="10" t="n"/>
-      <c r="P88" s="10" t="n"/>
-      <c r="Q88" s="10" t="n"/>
-      <c r="R88" s="10" t="n"/>
-      <c r="S88" s="10" t="n"/>
-      <c r="T88" s="10" t="n"/>
-      <c r="U88" s="10" t="n"/>
-      <c r="V88" s="10" t="n"/>
-      <c r="W88" s="10" t="n"/>
-      <c r="X88" s="10" t="n"/>
-      <c r="Y88" s="10" t="n"/>
-      <c r="Z88" s="10" t="n"/>
-      <c r="AA88" s="10" t="n"/>
-      <c r="AB88" s="10" t="n"/>
-      <c r="AC88" s="10" t="n"/>
-      <c r="AD88" s="10" t="n"/>
-      <c r="AE88" s="10" t="n"/>
-      <c r="AF88" s="10" t="n"/>
-      <c r="AG88" s="10" t="n"/>
-      <c r="AH88" s="10" t="n"/>
-      <c r="AI88" s="10" t="n"/>
-      <c r="AJ88" s="10" t="n"/>
-      <c r="AK88" s="11" t="n"/>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="C89" s="41" t="inlineStr">
+      <c r="D98" s="10" t="n"/>
+      <c r="E98" s="10" t="n"/>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="10" t="n"/>
+      <c r="H98" s="10" t="n"/>
+      <c r="I98" s="10" t="n"/>
+      <c r="J98" s="10" t="n"/>
+      <c r="K98" s="10" t="n"/>
+      <c r="L98" s="10" t="n"/>
+      <c r="M98" s="10" t="n"/>
+      <c r="N98" s="10" t="n"/>
+      <c r="O98" s="10" t="n"/>
+      <c r="P98" s="10" t="n"/>
+      <c r="Q98" s="10" t="n"/>
+      <c r="R98" s="10" t="n"/>
+      <c r="S98" s="10" t="n"/>
+      <c r="T98" s="10" t="n"/>
+      <c r="U98" s="10" t="n"/>
+      <c r="V98" s="10" t="n"/>
+      <c r="W98" s="10" t="n"/>
+      <c r="X98" s="10" t="n"/>
+      <c r="Y98" s="10" t="n"/>
+      <c r="Z98" s="10" t="n"/>
+      <c r="AA98" s="10" t="n"/>
+      <c r="AB98" s="10" t="n"/>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="10" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="10" t="n"/>
+      <c r="AK98" s="11" t="n"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="C99" s="41" t="inlineStr">
         <is>
           <t>フラグ設定ルール（機能定義 14.2 / 増減報告フラグの正準仕様は</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="D90" s="41" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="D100" s="41" t="inlineStr">
         <is>
           <t>saishin_data_flg = TRUE</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="36" customHeight="1">
-      <c r="D91" s="41" t="inlineStr">
+    <row r="101" ht="36" customHeight="1">
+      <c r="D101" s="41" t="inlineStr">
         <is>
           <t>shinki_flg = (tetsuzuki_shurui=1) ? TRUE : FALSE（再読時もTRUE）</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="D92" s="41" t="inlineStr">
+    <row r="102" ht="18" customHeight="1">
+      <c r="D102" s="41" t="inlineStr">
         <is>
           <t>kaiyaku_flg = (tetsuzuki_shurui=0) ? TRUE : FALSE</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="D93" s="41" t="inlineStr">
+    <row r="103" ht="18" customHeight="1">
+      <c r="D103" s="41" t="inlineStr">
         <is>
           <t>zougen_hokoku_flg = 次のいずれかが更新前後で変わったとき TRUE、それ以外の</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
+    <row r="104" ht="18" customHeight="1">
+      <c r="C104" s="41" t="inlineStr">
         <is>
           <t>zenkai_* 列：更新前の対応する値を格納する（増減比較用）。</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="36" customHeight="1">
-      <c r="D95" s="41" t="inlineStr">
+    <row r="105" ht="36" customHeight="1">
+      <c r="D105" s="41" t="inlineStr">
         <is>
           <t>住所5項目の zenkai_*（zenkai_yubin_no / zenkai_todofuken_code /</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="36" customHeight="1">
-      <c r="D96" s="41" t="inlineStr">
+    <row r="106" ht="36" customHeight="1">
+      <c r="D106" s="41" t="inlineStr">
         <is>
           <t>購読部数（zenkai_dokusya_busu）・販売店（zenkai_hanbaiten_id）は変更時のみ退避。</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="36" customHeight="1">
-      <c r="D97" s="41" t="inlineStr">
+    <row r="107" ht="36" customHeight="1">
+      <c r="D107" s="41" t="inlineStr">
         <is>
           <t>zenkai_* の退避有無と zougen_hokoku_flg は独立（same_flg=TRUE で住所無変更でも</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="409" customHeight="1">
-      <c r="C98" s="42" t="inlineStr">
+    <row r="108" ht="409" customHeight="1">
+      <c r="C108" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_dokusya_rireki (
   dokusya_id, rireki_no, ja_id, kanri_shiten_id, shiten_id, kumiaiin_code,
@@ -28234,43 +30969,43 @@
 )</t>
         </is>
       </c>
-      <c r="D98" s="10" t="n"/>
-      <c r="E98" s="10" t="n"/>
-      <c r="F98" s="10" t="n"/>
-      <c r="G98" s="10" t="n"/>
-      <c r="H98" s="10" t="n"/>
-      <c r="I98" s="10" t="n"/>
-      <c r="J98" s="10" t="n"/>
-      <c r="K98" s="10" t="n"/>
-      <c r="L98" s="10" t="n"/>
-      <c r="M98" s="10" t="n"/>
-      <c r="N98" s="10" t="n"/>
-      <c r="O98" s="10" t="n"/>
-      <c r="P98" s="10" t="n"/>
-      <c r="Q98" s="10" t="n"/>
-      <c r="R98" s="10" t="n"/>
-      <c r="S98" s="10" t="n"/>
-      <c r="T98" s="10" t="n"/>
-      <c r="U98" s="10" t="n"/>
-      <c r="V98" s="10" t="n"/>
-      <c r="W98" s="10" t="n"/>
-      <c r="X98" s="10" t="n"/>
-      <c r="Y98" s="10" t="n"/>
-      <c r="Z98" s="10" t="n"/>
-      <c r="AA98" s="10" t="n"/>
-      <c r="AB98" s="10" t="n"/>
-      <c r="AC98" s="10" t="n"/>
-      <c r="AD98" s="10" t="n"/>
-      <c r="AE98" s="10" t="n"/>
-      <c r="AF98" s="10" t="n"/>
-      <c r="AG98" s="10" t="n"/>
-      <c r="AH98" s="10" t="n"/>
-      <c r="AI98" s="10" t="n"/>
-      <c r="AJ98" s="10" t="n"/>
-      <c r="AK98" s="11" t="n"/>
-    </row>
-    <row r="99" ht="409" customHeight="1">
-      <c r="C99" s="42" t="inlineStr">
+      <c r="D108" s="10" t="n"/>
+      <c r="E108" s="10" t="n"/>
+      <c r="F108" s="10" t="n"/>
+      <c r="G108" s="10" t="n"/>
+      <c r="H108" s="10" t="n"/>
+      <c r="I108" s="10" t="n"/>
+      <c r="J108" s="10" t="n"/>
+      <c r="K108" s="10" t="n"/>
+      <c r="L108" s="10" t="n"/>
+      <c r="M108" s="10" t="n"/>
+      <c r="N108" s="10" t="n"/>
+      <c r="O108" s="10" t="n"/>
+      <c r="P108" s="10" t="n"/>
+      <c r="Q108" s="10" t="n"/>
+      <c r="R108" s="10" t="n"/>
+      <c r="S108" s="10" t="n"/>
+      <c r="T108" s="10" t="n"/>
+      <c r="U108" s="10" t="n"/>
+      <c r="V108" s="10" t="n"/>
+      <c r="W108" s="10" t="n"/>
+      <c r="X108" s="10" t="n"/>
+      <c r="Y108" s="10" t="n"/>
+      <c r="Z108" s="10" t="n"/>
+      <c r="AA108" s="10" t="n"/>
+      <c r="AB108" s="10" t="n"/>
+      <c r="AC108" s="10" t="n"/>
+      <c r="AD108" s="10" t="n"/>
+      <c r="AE108" s="10" t="n"/>
+      <c r="AF108" s="10" t="n"/>
+      <c r="AG108" s="10" t="n"/>
+      <c r="AH108" s="10" t="n"/>
+      <c r="AI108" s="10" t="n"/>
+      <c r="AJ108" s="10" t="n"/>
+      <c r="AK108" s="11" t="n"/>
+    </row>
+    <row r="109" ht="409" customHeight="1">
+      <c r="C109" s="42" t="inlineStr">
         <is>
           <t>UPDATE t_dokusya
 SET kanri_shiten_id = :kanri_shiten_id,
@@ -28333,57 +31068,57 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D99" s="10" t="n"/>
-      <c r="E99" s="10" t="n"/>
-      <c r="F99" s="10" t="n"/>
-      <c r="G99" s="10" t="n"/>
-      <c r="H99" s="10" t="n"/>
-      <c r="I99" s="10" t="n"/>
-      <c r="J99" s="10" t="n"/>
-      <c r="K99" s="10" t="n"/>
-      <c r="L99" s="10" t="n"/>
-      <c r="M99" s="10" t="n"/>
-      <c r="N99" s="10" t="n"/>
-      <c r="O99" s="10" t="n"/>
-      <c r="P99" s="10" t="n"/>
-      <c r="Q99" s="10" t="n"/>
-      <c r="R99" s="10" t="n"/>
-      <c r="S99" s="10" t="n"/>
-      <c r="T99" s="10" t="n"/>
-      <c r="U99" s="10" t="n"/>
-      <c r="V99" s="10" t="n"/>
-      <c r="W99" s="10" t="n"/>
-      <c r="X99" s="10" t="n"/>
-      <c r="Y99" s="10" t="n"/>
-      <c r="Z99" s="10" t="n"/>
-      <c r="AA99" s="10" t="n"/>
-      <c r="AB99" s="10" t="n"/>
-      <c r="AC99" s="10" t="n"/>
-      <c r="AD99" s="10" t="n"/>
-      <c r="AE99" s="10" t="n"/>
-      <c r="AF99" s="10" t="n"/>
-      <c r="AG99" s="10" t="n"/>
-      <c r="AH99" s="10" t="n"/>
-      <c r="AI99" s="10" t="n"/>
-      <c r="AJ99" s="10" t="n"/>
-      <c r="AK99" s="11" t="n"/>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="B100" s="27" t="inlineStr">
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="10" t="n"/>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="10" t="n"/>
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="10" t="n"/>
+      <c r="J109" s="10" t="n"/>
+      <c r="K109" s="10" t="n"/>
+      <c r="L109" s="10" t="n"/>
+      <c r="M109" s="10" t="n"/>
+      <c r="N109" s="10" t="n"/>
+      <c r="O109" s="10" t="n"/>
+      <c r="P109" s="10" t="n"/>
+      <c r="Q109" s="10" t="n"/>
+      <c r="R109" s="10" t="n"/>
+      <c r="S109" s="10" t="n"/>
+      <c r="T109" s="10" t="n"/>
+      <c r="U109" s="10" t="n"/>
+      <c r="V109" s="10" t="n"/>
+      <c r="W109" s="10" t="n"/>
+      <c r="X109" s="10" t="n"/>
+      <c r="Y109" s="10" t="n"/>
+      <c r="Z109" s="10" t="n"/>
+      <c r="AA109" s="10" t="n"/>
+      <c r="AB109" s="10" t="n"/>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="10" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="10" t="n"/>
+      <c r="AK109" s="11" t="n"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="B110" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="C101" s="41" t="inlineStr">
+    <row r="111" ht="18" customHeight="1">
+      <c r="C111" s="41" t="inlineStr">
         <is>
           <t>更新前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="216" customHeight="1">
-      <c r="C102" s="42" t="inlineStr">
+    <row r="112" ht="216" customHeight="1">
+      <c r="C112" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -28399,92 +31134,92 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n"/>
-      <c r="E102" s="10" t="n"/>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="10" t="n"/>
-      <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="n"/>
-      <c r="J102" s="10" t="n"/>
-      <c r="K102" s="10" t="n"/>
-      <c r="L102" s="10" t="n"/>
-      <c r="M102" s="10" t="n"/>
-      <c r="N102" s="10" t="n"/>
-      <c r="O102" s="10" t="n"/>
-      <c r="P102" s="10" t="n"/>
-      <c r="Q102" s="10" t="n"/>
-      <c r="R102" s="10" t="n"/>
-      <c r="S102" s="10" t="n"/>
-      <c r="T102" s="10" t="n"/>
-      <c r="U102" s="10" t="n"/>
-      <c r="V102" s="10" t="n"/>
-      <c r="W102" s="10" t="n"/>
-      <c r="X102" s="10" t="n"/>
-      <c r="Y102" s="10" t="n"/>
-      <c r="Z102" s="10" t="n"/>
-      <c r="AA102" s="10" t="n"/>
-      <c r="AB102" s="10" t="n"/>
-      <c r="AC102" s="10" t="n"/>
-      <c r="AD102" s="10" t="n"/>
-      <c r="AE102" s="10" t="n"/>
-      <c r="AF102" s="10" t="n"/>
-      <c r="AG102" s="10" t="n"/>
-      <c r="AH102" s="10" t="n"/>
-      <c r="AI102" s="10" t="n"/>
-      <c r="AJ102" s="10" t="n"/>
-      <c r="AK102" s="11" t="n"/>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="C103" s="41" t="inlineStr">
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="10" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="10" t="n"/>
+      <c r="J112" s="10" t="n"/>
+      <c r="K112" s="10" t="n"/>
+      <c r="L112" s="10" t="n"/>
+      <c r="M112" s="10" t="n"/>
+      <c r="N112" s="10" t="n"/>
+      <c r="O112" s="10" t="n"/>
+      <c r="P112" s="10" t="n"/>
+      <c r="Q112" s="10" t="n"/>
+      <c r="R112" s="10" t="n"/>
+      <c r="S112" s="10" t="n"/>
+      <c r="T112" s="10" t="n"/>
+      <c r="U112" s="10" t="n"/>
+      <c r="V112" s="10" t="n"/>
+      <c r="W112" s="10" t="n"/>
+      <c r="X112" s="10" t="n"/>
+      <c r="Y112" s="10" t="n"/>
+      <c r="Z112" s="10" t="n"/>
+      <c r="AA112" s="10" t="n"/>
+      <c r="AB112" s="10" t="n"/>
+      <c r="AC112" s="10" t="n"/>
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="10" t="n"/>
+      <c r="AF112" s="10" t="n"/>
+      <c r="AG112" s="10" t="n"/>
+      <c r="AH112" s="10" t="n"/>
+      <c r="AI112" s="10" t="n"/>
+      <c r="AJ112" s="10" t="n"/>
+      <c r="AK112" s="11" t="n"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="C113" s="41" t="inlineStr">
         <is>
           <t>`before_value`：更新前のデータをJSON形式で格納する。</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="C104" s="41" t="inlineStr">
+    <row r="114" ht="18" customHeight="1">
+      <c r="C114" s="41" t="inlineStr">
         <is>
           <t>`after_value`：更新後のデータをJSON形式で格納する。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="B105" s="27" t="inlineStr">
+    <row r="115" ht="18" customHeight="1">
+      <c r="B115" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="C106" s="41" t="inlineStr">
+    <row r="116" ht="18" customHeight="1">
+      <c r="C116" s="41" t="inlineStr">
         <is>
           <t>更新されたデータを data オブジェクトとして返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="B107" s="27" t="inlineStr">
+    <row r="117" ht="18" customHeight="1">
+      <c r="B117" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="C108" s="41" t="inlineStr">
+    <row r="118" ht="18" customHeight="1">
+      <c r="C118" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="C109" s="41" t="inlineStr">
+    <row r="119" ht="18" customHeight="1">
+      <c r="C119" s="41" t="inlineStr">
         <is>
           <t>エラー発生時はエラーログを記録する（`log_type = 3`、トランザクション外で記録）。</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="216" customHeight="1">
-      <c r="C110" s="42" t="inlineStr">
+    <row r="120" ht="216" customHeight="1">
+      <c r="C120" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -28500,49 +31235,48 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D110" s="10" t="n"/>
-      <c r="E110" s="10" t="n"/>
-      <c r="F110" s="10" t="n"/>
-      <c r="G110" s="10" t="n"/>
-      <c r="H110" s="10" t="n"/>
-      <c r="I110" s="10" t="n"/>
-      <c r="J110" s="10" t="n"/>
-      <c r="K110" s="10" t="n"/>
-      <c r="L110" s="10" t="n"/>
-      <c r="M110" s="10" t="n"/>
-      <c r="N110" s="10" t="n"/>
-      <c r="O110" s="10" t="n"/>
-      <c r="P110" s="10" t="n"/>
-      <c r="Q110" s="10" t="n"/>
-      <c r="R110" s="10" t="n"/>
-      <c r="S110" s="10" t="n"/>
-      <c r="T110" s="10" t="n"/>
-      <c r="U110" s="10" t="n"/>
-      <c r="V110" s="10" t="n"/>
-      <c r="W110" s="10" t="n"/>
-      <c r="X110" s="10" t="n"/>
-      <c r="Y110" s="10" t="n"/>
-      <c r="Z110" s="10" t="n"/>
-      <c r="AA110" s="10" t="n"/>
-      <c r="AB110" s="10" t="n"/>
-      <c r="AC110" s="10" t="n"/>
-      <c r="AD110" s="10" t="n"/>
-      <c r="AE110" s="10" t="n"/>
-      <c r="AF110" s="10" t="n"/>
-      <c r="AG110" s="10" t="n"/>
-      <c r="AH110" s="10" t="n"/>
-      <c r="AI110" s="10" t="n"/>
-      <c r="AJ110" s="10" t="n"/>
-      <c r="AK110" s="11" t="n"/>
+      <c r="D120" s="10" t="n"/>
+      <c r="E120" s="10" t="n"/>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
+      <c r="H120" s="10" t="n"/>
+      <c r="I120" s="10" t="n"/>
+      <c r="J120" s="10" t="n"/>
+      <c r="K120" s="10" t="n"/>
+      <c r="L120" s="10" t="n"/>
+      <c r="M120" s="10" t="n"/>
+      <c r="N120" s="10" t="n"/>
+      <c r="O120" s="10" t="n"/>
+      <c r="P120" s="10" t="n"/>
+      <c r="Q120" s="10" t="n"/>
+      <c r="R120" s="10" t="n"/>
+      <c r="S120" s="10" t="n"/>
+      <c r="T120" s="10" t="n"/>
+      <c r="U120" s="10" t="n"/>
+      <c r="V120" s="10" t="n"/>
+      <c r="W120" s="10" t="n"/>
+      <c r="X120" s="10" t="n"/>
+      <c r="Y120" s="10" t="n"/>
+      <c r="Z120" s="10" t="n"/>
+      <c r="AA120" s="10" t="n"/>
+      <c r="AB120" s="10" t="n"/>
+      <c r="AC120" s="10" t="n"/>
+      <c r="AD120" s="10" t="n"/>
+      <c r="AE120" s="10" t="n"/>
+      <c r="AF120" s="10" t="n"/>
+      <c r="AG120" s="10" t="n"/>
+      <c r="AH120" s="10" t="n"/>
+      <c r="AI120" s="10" t="n"/>
+      <c r="AJ120" s="10" t="n"/>
+      <c r="AK120" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="137">
+  <mergeCells count="147">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="C66:AK66"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="C53:AK53"/>
-    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D71:AK71"/>
     <mergeCell ref="C77:AK77"/>
     <mergeCell ref="N18:AK18"/>
@@ -28554,10 +31288,12 @@
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
+    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="C85:AK85"/>
+    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
@@ -28570,19 +31306,24 @@
     <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C80:AK80"/>
+    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B9:I9"/>
+    <mergeCell ref="C95:AK95"/>
+    <mergeCell ref="D101:AK101"/>
     <mergeCell ref="N20:AK20"/>
     <mergeCell ref="M25:P25"/>
-    <mergeCell ref="C106:AK106"/>
+    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="C38:AK38"/>
+    <mergeCell ref="B115:AK115"/>
+    <mergeCell ref="D103:AK103"/>
     <mergeCell ref="T29:X29"/>
+    <mergeCell ref="B117:AK117"/>
     <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="C104:AK104"/>
@@ -28592,9 +31333,8 @@
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="C99:AK99"/>
-    <mergeCell ref="D90:AK90"/>
+    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="B14:I20"/>
     <mergeCell ref="B49:I49"/>
@@ -28607,22 +31347,25 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="B81:AK81"/>
+    <mergeCell ref="D107:AK107"/>
     <mergeCell ref="C72:AK72"/>
     <mergeCell ref="C32:AK32"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="B58:AK58"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
+    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="C78:AK78"/>
     <mergeCell ref="C87:AK87"/>
+    <mergeCell ref="D102:AK102"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="C82:AK82"/>
     <mergeCell ref="B57:AK57"/>
-    <mergeCell ref="D92:AK92"/>
+    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="AC25:AE25"/>
-    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="C89:AK89"/>
+    <mergeCell ref="C116:AK116"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C64:AK64"/>
     <mergeCell ref="C79:AK79"/>
@@ -28630,6 +31373,7 @@
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C63:AK63"/>
     <mergeCell ref="C41:AK41"/>
+    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="C50:AK50"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
@@ -28637,40 +31381,41 @@
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="D96:AK96"/>
+    <mergeCell ref="D105:AK105"/>
+    <mergeCell ref="C120:AK120"/>
+    <mergeCell ref="C119:AK119"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="A56:AK56"/>
     <mergeCell ref="A27:AK27"/>
     <mergeCell ref="C67:AK67"/>
-    <mergeCell ref="D97:AK97"/>
-    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B105:AK105"/>
+    <mergeCell ref="C111:AK111"/>
+    <mergeCell ref="D106:AK106"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="C83:AK83"/>
-    <mergeCell ref="D93:AK93"/>
+    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="A22:AK22"/>
     <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B107:AK107"/>
     <mergeCell ref="B52:I52"/>
     <mergeCell ref="T25:X25"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="C47:AK47"/>
     <mergeCell ref="D69:AK69"/>
+    <mergeCell ref="D100:AK100"/>
     <mergeCell ref="B74:AK74"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="C60:AK60"/>
-    <mergeCell ref="D95:AK95"/>
+    <mergeCell ref="B110:AK110"/>
     <mergeCell ref="C76:AK76"/>
-    <mergeCell ref="B100:AK100"/>
-    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="B62:AK62"/>
     <mergeCell ref="D70:AK70"/>
     <mergeCell ref="AF29:AK29"/>
@@ -28846,7 +31591,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
